--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6780" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4BD2349-2699-484A-8BEC-7839A4D2120A}"/>
+  <xr:revisionPtr revIDLastSave="6787" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD847DFB-FE8E-4915-82CF-6CBAF0AD4327}"/>
   <bookViews>
-    <workbookView xWindow="1344" yWindow="0" windowWidth="19464" windowHeight="12336" tabRatio="445" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3144" yWindow="900" windowWidth="19692" windowHeight="10776" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="DEC25" sheetId="92" r:id="rId1"/>
-    <sheet name="NOV25" sheetId="91" r:id="rId2"/>
-    <sheet name="OCT25" sheetId="90" r:id="rId3"/>
-    <sheet name="SEP25" sheetId="89" r:id="rId4"/>
-    <sheet name="AUG25" sheetId="88" r:id="rId5"/>
-    <sheet name="JUL25" sheetId="87" r:id="rId6"/>
-    <sheet name="JUN25" sheetId="86" r:id="rId7"/>
-    <sheet name="MAY25" sheetId="85" r:id="rId8"/>
-    <sheet name="APR25" sheetId="84" r:id="rId9"/>
-    <sheet name="MAR25" sheetId="83" r:id="rId10"/>
-    <sheet name="FEB25" sheetId="82" r:id="rId11"/>
-    <sheet name="JAN25" sheetId="81" r:id="rId12"/>
+    <sheet name="JAN26" sheetId="93" r:id="rId1"/>
+    <sheet name="DEC25" sheetId="92" r:id="rId2"/>
+    <sheet name="NOV25" sheetId="91" r:id="rId3"/>
+    <sheet name="OCT25" sheetId="90" r:id="rId4"/>
+    <sheet name="SEP25" sheetId="89" r:id="rId5"/>
+    <sheet name="AUG25" sheetId="88" r:id="rId6"/>
+    <sheet name="JUL25" sheetId="87" r:id="rId7"/>
+    <sheet name="JUN25" sheetId="86" r:id="rId8"/>
+    <sheet name="MAY25" sheetId="85" r:id="rId9"/>
+    <sheet name="APR25" sheetId="84" r:id="rId10"/>
+    <sheet name="MAR25" sheetId="83" r:id="rId11"/>
+    <sheet name="FEB25" sheetId="82" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -961,28 +961,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDBED0F-338F-4C61-AC0B-5077E6985A08}">
-  <dimension ref="A1:N25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DA818F-D2F1-4405-A36C-2376E8E1DAA2}">
+  <dimension ref="A1:N14"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="8.25" style="5" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
+    <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="8" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.875" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1007,37 +1004,34 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B2" s="28">
-        <v>45995</v>
+        <v>45288</v>
       </c>
       <c r="C2" s="29">
-        <v>45000</v>
+        <v>22500</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="37">
-        <v>0.22220000000000001</v>
+        <v>0</v>
       </c>
       <c r="G2" s="31">
-        <f t="shared" ref="G2:G13" si="0">C2*F2</f>
-        <v>9999</v>
-      </c>
-      <c r="H2" s="40">
-        <f t="shared" ref="H2:H11" si="1">G2*0.9</f>
-        <v>8999.1</v>
+        <f t="shared" ref="G2" si="0">C2*F2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2</f>
+        <v>0</v>
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="7"/>
@@ -1046,29 +1040,17 @@
       <c r="M2" s="15"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="28">
-        <v>45995</v>
-      </c>
-      <c r="C3" s="29">
-        <v>27000</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>9</v>
-      </c>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
       <c r="E3" s="31"/>
-      <c r="F3" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="31">
-        <f t="shared" si="0"/>
-        <v>13500</v>
-      </c>
-      <c r="H3" s="40">
-        <v>12825</v>
+      <c r="F3" s="37"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="32">
+        <f>SUM(H2,H2)</f>
+        <v>0</v>
       </c>
       <c r="I3" s="11"/>
       <c r="J3" s="7"/>
@@ -1077,94 +1059,68 @@
       <c r="M3" s="15"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="B4" s="28">
-        <v>46002</v>
+        <v>45295</v>
       </c>
       <c r="C4" s="29">
-        <v>7200</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="37">
-        <v>0.17499999999999999</v>
+        <v>2000</v>
+      </c>
+      <c r="D4" s="30">
+        <v>21.7</v>
+      </c>
+      <c r="E4" s="31">
+        <v>43496.13</v>
+      </c>
+      <c r="F4" s="30">
+        <v>22.9</v>
       </c>
       <c r="G4" s="31">
-        <f t="shared" si="0"/>
-        <v>1260</v>
-      </c>
-      <c r="H4" s="40">
-        <f t="shared" si="1"/>
-        <v>1134</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="28">
-        <v>46002</v>
-      </c>
-      <c r="C5" s="29">
-        <v>55000</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="54">
-        <v>6.9099999999999995E-2</v>
-      </c>
-      <c r="G5" s="31">
-        <f t="shared" si="0"/>
-        <v>3800.4999999999995</v>
-      </c>
-      <c r="H5" s="40">
-        <f t="shared" si="1"/>
-        <v>3420.45</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="94" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="28">
-        <v>46002</v>
-      </c>
-      <c r="C6" s="29">
-        <v>6800</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="37">
-        <v>0.13</v>
-      </c>
-      <c r="G6" s="31">
-        <f t="shared" ref="G6" si="2">C6*F6</f>
-        <v>884</v>
-      </c>
-      <c r="H6" s="40">
-        <f t="shared" ref="H6" si="3">G6*0.9</f>
-        <v>795.6</v>
+        <v>45698.55</v>
+      </c>
+      <c r="H4" s="32">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="32">
+        <f>SUM(E4:E4)</f>
+        <v>43496.13</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="32">
+        <f>SUM(G4:G4)</f>
+        <v>45698.55</v>
+      </c>
+      <c r="H5" s="32">
+        <f>SUM(H4:H4)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="34">
+        <f>H3+H5</f>
+        <v>0</v>
       </c>
       <c r="I6" s="11"/>
       <c r="J6" s="7"/>
@@ -1173,158 +1129,96 @@
       <c r="M6" s="15"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="28">
-        <v>45995</v>
-      </c>
-      <c r="C7" s="93">
-        <v>17500</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="54">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G7" s="31">
-        <f t="shared" si="0"/>
-        <v>3587.5</v>
-      </c>
-      <c r="H7" s="40">
-        <f t="shared" si="1"/>
-        <v>3228.75</v>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="32">
+        <v>0</v>
       </c>
       <c r="I7" s="11"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="28">
-        <v>46006</v>
-      </c>
-      <c r="C8" s="29">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="37">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="G8" s="31">
-        <f t="shared" si="0"/>
-        <v>1050</v>
-      </c>
-      <c r="H8" s="40">
-        <f t="shared" si="1"/>
-        <v>945</v>
+    </row>
+    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H8" s="41">
+        <f>H6+H7</f>
+        <v>0</v>
       </c>
       <c r="I8" s="11"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="28">
-        <v>46002</v>
-      </c>
-      <c r="C9" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="37">
-        <v>0.193</v>
-      </c>
-      <c r="G9" s="31">
-        <f t="shared" si="0"/>
-        <v>3860</v>
-      </c>
-      <c r="H9" s="40">
-        <f t="shared" si="1"/>
-        <v>3474</v>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="35">
+        <v>0</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="28">
-        <v>46013</v>
-      </c>
-      <c r="C10" s="29">
-        <v>50000</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="54">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="G10" s="31">
-        <f t="shared" si="0"/>
-        <v>6625</v>
-      </c>
-      <c r="H10" s="40">
-        <f t="shared" si="1"/>
-        <v>5962.5</v>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="35">
+        <v>38040</v>
       </c>
       <c r="I10" s="11"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="28">
-        <v>46015</v>
-      </c>
-      <c r="C11" s="93">
-        <v>69000</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="54">
-        <v>0.1825</v>
-      </c>
-      <c r="G11" s="31">
-        <f t="shared" si="0"/>
-        <v>12592.5</v>
-      </c>
-      <c r="H11" s="40">
-        <f t="shared" si="1"/>
-        <v>11333.25</v>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="41">
+        <f>H9+H10</f>
+        <v>38040</v>
       </c>
       <c r="I11" s="11"/>
       <c r="J11" s="7"/>
@@ -1333,30 +1227,19 @@
       <c r="M11" s="15"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="28">
-        <v>46016</v>
-      </c>
-      <c r="C12" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="54">
-        <v>0.114</v>
-      </c>
-      <c r="G12" s="31">
-        <f t="shared" ref="G12" si="4">C12*F12</f>
-        <v>2280</v>
-      </c>
-      <c r="H12" s="40">
-        <f>G12</f>
-        <v>2280</v>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="36">
+        <f>H8-H11</f>
+        <v>-38040</v>
       </c>
       <c r="I12" s="11"/>
       <c r="J12" s="7"/>
@@ -1365,30 +1248,18 @@
       <c r="M12" s="15"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="94" t="s">
-        <v>54</v>
-      </c>
-      <c r="B13" s="28">
-        <v>46013</v>
-      </c>
-      <c r="C13" s="29">
-        <v>120000</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="37">
-        <v>0.13722400000000001</v>
-      </c>
-      <c r="G13" s="31">
-        <f t="shared" si="0"/>
-        <v>16466.88</v>
-      </c>
-      <c r="H13" s="40">
-        <f>G13*0.9</f>
-        <v>14820.192000000001</v>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H13" s="38">
+        <v>60000</v>
       </c>
       <c r="I13" s="11"/>
       <c r="J13" s="7"/>
@@ -1398,16 +1269,18 @@
       <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="34">
-        <f>SUM(H2:H13)</f>
-        <v>69217.84199999999</v>
+      <c r="A14" s="6"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H14" s="48">
+        <f>H12+H13</f>
+        <v>21960</v>
       </c>
       <c r="I14" s="11"/>
       <c r="J14" s="7"/>
@@ -1415,233 +1288,6 @@
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="28">
-        <v>37617</v>
-      </c>
-      <c r="C15" s="29">
-        <v>0</v>
-      </c>
-      <c r="D15" s="30">
-        <v>21.3</v>
-      </c>
-      <c r="E15" s="31">
-        <v>0</v>
-      </c>
-      <c r="F15" s="30">
-        <v>21.3</v>
-      </c>
-      <c r="G15" s="31">
-        <v>0</v>
-      </c>
-      <c r="H15" s="32">
-        <f t="shared" ref="H15" si="5">G15-E15</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32">
-        <f>SUM(E15:E15)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32">
-        <f>SUM(G15:G15)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="40">
-        <f>SUM(H15:H15)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="43">
-        <f>H14+H16</f>
-        <v>69217.84199999999</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="7">
-        <v>30614.600000000002</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="5"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="32">
-        <v>-522636.73</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="6"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H19" s="41">
-        <f>H17+H18</f>
-        <v>-453418.88799999998</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J19" s="7">
-        <v>-522636.73</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G20" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="35">
-        <v>396550</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="M20" s="7"/>
-    </row>
-    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G21" s="32" t="s">
-        <v>58</v>
-      </c>
-      <c r="H21" s="35">
-        <v>12050</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="J21" s="7">
-        <v>10130</v>
-      </c>
-      <c r="M21" s="7"/>
-    </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G22" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="41">
-        <f>H20+H21</f>
-        <v>408600</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="7">
-        <v>396550</v>
-      </c>
-      <c r="M22" s="7"/>
-    </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C23" s="12"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="45">
-        <f>H19-H22</f>
-        <v>-862018.88800000004</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="7">
-        <v>-919186.73</v>
-      </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="7"/>
-    </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G24" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H24" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J24" s="7">
-        <v>57000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G25" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H25" s="42">
-        <f>H23+H24</f>
-        <v>-805018.88800000004</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J25" s="7">
-        <v>-862186.73</v>
-      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -1652,6 +1298,516 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F07CE69-5C67-4DF2-B5BE-CD5590D6A395}">
+  <dimension ref="A1:N22"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45769</v>
+      </c>
+      <c r="C2" s="29">
+        <v>600</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="37">
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>1500</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2*0.9</f>
+        <v>1350</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="28">
+        <v>45771</v>
+      </c>
+      <c r="C3" s="29">
+        <v>6000</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="31">
+        <f>C3*F3</f>
+        <v>3000</v>
+      </c>
+      <c r="H3" s="32">
+        <f>G3*0.9</f>
+        <v>2700</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45777</v>
+      </c>
+      <c r="C4" s="29">
+        <v>4200</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="37">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G4" s="31">
+        <f>C4*F4</f>
+        <v>1176</v>
+      </c>
+      <c r="H4" s="32">
+        <f>G4*0.9</f>
+        <v>1058.4000000000001</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="27"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="31"/>
+      <c r="H5" s="34">
+        <f>SUM(H2:H4)</f>
+        <v>5108.3999999999996</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="28">
+        <v>45757</v>
+      </c>
+      <c r="C6" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="30">
+        <v>61.5</v>
+      </c>
+      <c r="E6" s="31">
+        <v>61636.22</v>
+      </c>
+      <c r="F6" s="30">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="G6" s="31">
+        <v>16563.23</v>
+      </c>
+      <c r="H6" s="50">
+        <f t="shared" ref="H6" si="0">G6-E6</f>
+        <v>-45072.990000000005</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32">
+        <f>SUM(E6:E6)</f>
+        <v>61636.22</v>
+      </c>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32">
+        <f>SUM(G6:G6)</f>
+        <v>16563.23</v>
+      </c>
+      <c r="H7" s="34">
+        <f>SUM(H6:H6)</f>
+        <v>-45072.990000000005</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="34">
+        <f>H5+H7</f>
+        <v>-39964.590000000004</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" s="7">
+        <v>34655.910000000003</v>
+      </c>
+      <c r="L8" s="15">
+        <f t="shared" ref="L8:L12" si="1">H8-K8</f>
+        <v>-74620.5</v>
+      </c>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="7">
+        <v>-122583.36474799996</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="7">
+        <v>-157239.27474799997</v>
+      </c>
+      <c r="L9" s="15">
+        <f t="shared" si="1"/>
+        <v>34655.910000000003</v>
+      </c>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H10" s="34">
+        <f>H8+H9</f>
+        <v>-162547.95474799996</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="7">
+        <v>-122583.36474799996</v>
+      </c>
+      <c r="L10" s="15">
+        <f t="shared" si="1"/>
+        <v>-39964.589999999997</v>
+      </c>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="7">
+        <v>281390</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="K11" s="7">
+        <v>102430</v>
+      </c>
+      <c r="L11" s="15">
+        <f t="shared" si="1"/>
+        <v>178960</v>
+      </c>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="H12" s="35">
+        <v>45870</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="7">
+        <v>178960</v>
+      </c>
+      <c r="L12" s="15">
+        <f t="shared" si="1"/>
+        <v>-133090</v>
+      </c>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="26"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="34">
+        <f>H11+H12</f>
+        <v>327260</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="7">
+        <v>281390</v>
+      </c>
+      <c r="L13" s="15">
+        <f>H13-K13</f>
+        <v>45870</v>
+      </c>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="5"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="45">
+        <f>H10-H13</f>
+        <v>-489807.95474799996</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K14" s="7">
+        <v>-403973.36474799993</v>
+      </c>
+      <c r="L14" s="15">
+        <f t="shared" ref="L14:L16" si="2">H14-K14</f>
+        <v>-85834.590000000026</v>
+      </c>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="5"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H15" s="38">
+        <v>57000</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K15" s="7">
+        <v>57000</v>
+      </c>
+      <c r="L15" s="15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A16" s="6"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="39">
+        <f>H14+H15</f>
+        <v>-432807.95474799996</v>
+      </c>
+      <c r="I16" s="11"/>
+      <c r="J16" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="K16" s="7">
+        <v>-346973.36474799993</v>
+      </c>
+      <c r="L16" s="15">
+        <f t="shared" si="2"/>
+        <v>-85834.590000000026</v>
+      </c>
+      <c r="M16" s="15"/>
+      <c r="N16" s="7"/>
+    </row>
+    <row r="17" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="I17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="N17" s="13"/>
+    </row>
+    <row r="18" spans="9:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="K19" s="7"/>
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" spans="9:14" x14ac:dyDescent="0.3">
+      <c r="K22" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779217B5-9CE8-46BD-8B22-71F5AA3AD105}">
   <dimension ref="A1:L20"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -2140,7 +2296,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F818BAB4-5237-4BD8-9A61-131DACEE1BB2}">
   <dimension ref="A1:N19"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -2568,26 +2724,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32283096-5907-4E30-9E76-682BE04B55EC}">
-  <dimension ref="A1:N14"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDBED0F-338F-4C61-AC0B-5077E6985A08}">
+  <dimension ref="A1:N25"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.25" style="5" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="8" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.875" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.625" style="6"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -2612,34 +2771,37 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="5"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B2" s="28">
-        <v>45288</v>
+        <v>45995</v>
       </c>
       <c r="C2" s="29">
-        <v>22500</v>
+        <v>45000</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="37">
-        <v>0</v>
+        <v>0.22220000000000001</v>
       </c>
       <c r="G2" s="31">
-        <f t="shared" ref="G2" si="0">C2*F2</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2</f>
-        <v>0</v>
+        <f t="shared" ref="G2:G13" si="0">C2*F2</f>
+        <v>9999</v>
+      </c>
+      <c r="H2" s="40">
+        <f t="shared" ref="H2:H11" si="1">G2*0.9</f>
+        <v>8999.1</v>
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="7"/>
@@ -2648,17 +2810,29 @@
       <c r="M2" s="15"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="28">
+        <v>45995</v>
+      </c>
+      <c r="C3" s="29">
+        <v>27000</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>9</v>
+      </c>
       <c r="E3" s="31"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32">
-        <f>SUM(H2,H2)</f>
-        <v>0</v>
+      <c r="F3" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="31">
+        <f t="shared" si="0"/>
+        <v>13500</v>
+      </c>
+      <c r="H3" s="40">
+        <v>12825</v>
       </c>
       <c r="I3" s="11"/>
       <c r="J3" s="7"/>
@@ -2667,68 +2841,94 @@
       <c r="M3" s="15"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="B4" s="28">
-        <v>45295</v>
+        <v>46002</v>
       </c>
       <c r="C4" s="29">
-        <v>2000</v>
-      </c>
-      <c r="D4" s="30">
-        <v>21.7</v>
-      </c>
-      <c r="E4" s="31">
-        <v>43496.13</v>
-      </c>
-      <c r="F4" s="30">
-        <v>22.9</v>
+        <v>7200</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="31"/>
+      <c r="F4" s="37">
+        <v>0.17499999999999999</v>
       </c>
       <c r="G4" s="31">
-        <v>45698.55</v>
-      </c>
-      <c r="H4" s="32">
-        <v>0</v>
-      </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="32">
-        <f>SUM(E4:E4)</f>
-        <v>43496.13</v>
-      </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="32">
-        <f>SUM(G4:G4)</f>
-        <v>45698.55</v>
-      </c>
-      <c r="H5" s="32">
-        <f>SUM(H4:H4)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="26"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="34">
-        <f>H3+H5</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="H4" s="40">
+        <f t="shared" si="1"/>
+        <v>1134</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="28">
+        <v>46002</v>
+      </c>
+      <c r="C5" s="29">
+        <v>55000</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="31"/>
+      <c r="F5" s="54">
+        <v>6.9099999999999995E-2</v>
+      </c>
+      <c r="G5" s="31">
+        <f t="shared" si="0"/>
+        <v>3800.4999999999995</v>
+      </c>
+      <c r="H5" s="40">
+        <f t="shared" si="1"/>
+        <v>3420.45</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="94" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="28">
+        <v>46002</v>
+      </c>
+      <c r="C6" s="29">
+        <v>6800</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="31"/>
+      <c r="F6" s="37">
+        <v>0.13</v>
+      </c>
+      <c r="G6" s="31">
+        <f t="shared" ref="G6" si="2">C6*F6</f>
+        <v>884</v>
+      </c>
+      <c r="H6" s="40">
+        <f t="shared" ref="H6" si="3">G6*0.9</f>
+        <v>795.6</v>
       </c>
       <c r="I6" s="11"/>
       <c r="J6" s="7"/>
@@ -2737,96 +2937,158 @@
       <c r="M6" s="15"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="32">
-        <v>308374.99525200005</v>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="28">
+        <v>45995</v>
+      </c>
+      <c r="C7" s="93">
+        <v>17500</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="31"/>
+      <c r="F7" s="54">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G7" s="31">
+        <f t="shared" si="0"/>
+        <v>3587.5</v>
+      </c>
+      <c r="H7" s="40">
+        <f t="shared" si="1"/>
+        <v>3228.75</v>
       </c>
       <c r="I7" s="11"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
       <c r="L7" s="15"/>
       <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="41">
-        <f>H6+H7</f>
-        <v>308374.99525200005</v>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B8" s="28">
+        <v>46006</v>
+      </c>
+      <c r="C8" s="29">
+        <v>50000</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="37">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="G8" s="31">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="H8" s="40">
+        <f t="shared" si="1"/>
+        <v>945</v>
       </c>
       <c r="I8" s="11"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="15"/>
       <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="35">
-        <v>0</v>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="28">
+        <v>46002</v>
+      </c>
+      <c r="C9" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="31"/>
+      <c r="F9" s="37">
+        <v>0.193</v>
+      </c>
+      <c r="G9" s="31">
+        <f t="shared" si="0"/>
+        <v>3860</v>
+      </c>
+      <c r="H9" s="40">
+        <f t="shared" si="1"/>
+        <v>3474</v>
       </c>
       <c r="I9" s="11"/>
       <c r="J9" s="7"/>
       <c r="K9" s="7"/>
       <c r="L9" s="15"/>
       <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="35">
-        <v>43930</v>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="28">
+        <v>46013</v>
+      </c>
+      <c r="C10" s="29">
+        <v>50000</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="31"/>
+      <c r="F10" s="54">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="G10" s="31">
+        <f t="shared" si="0"/>
+        <v>6625</v>
+      </c>
+      <c r="H10" s="40">
+        <f t="shared" si="1"/>
+        <v>5962.5</v>
       </c>
       <c r="I10" s="11"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="15"/>
       <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="41">
-        <f>H9+H10</f>
-        <v>43930</v>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="28">
+        <v>46015</v>
+      </c>
+      <c r="C11" s="93">
+        <v>69000</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="31"/>
+      <c r="F11" s="54">
+        <v>0.1825</v>
+      </c>
+      <c r="G11" s="31">
+        <f t="shared" si="0"/>
+        <v>12592.5</v>
+      </c>
+      <c r="H11" s="40">
+        <f t="shared" si="1"/>
+        <v>11333.25</v>
       </c>
       <c r="I11" s="11"/>
       <c r="J11" s="7"/>
@@ -2835,19 +3097,30 @@
       <c r="M11" s="15"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="36">
-        <f>H8-H11</f>
-        <v>264444.99525200005</v>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="28">
+        <v>46016</v>
+      </c>
+      <c r="C12" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="31"/>
+      <c r="F12" s="54">
+        <v>0.114</v>
+      </c>
+      <c r="G12" s="31">
+        <f t="shared" ref="G12" si="4">C12*F12</f>
+        <v>2280</v>
+      </c>
+      <c r="H12" s="40">
+        <f>G12</f>
+        <v>2280</v>
       </c>
       <c r="I12" s="11"/>
       <c r="J12" s="7"/>
@@ -2856,18 +3129,30 @@
       <c r="M12" s="15"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="38">
-        <v>57000</v>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="94" t="s">
+        <v>54</v>
+      </c>
+      <c r="B13" s="28">
+        <v>46013</v>
+      </c>
+      <c r="C13" s="29">
+        <v>120000</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="31"/>
+      <c r="F13" s="37">
+        <v>0.13722400000000001</v>
+      </c>
+      <c r="G13" s="31">
+        <f t="shared" si="0"/>
+        <v>16466.88</v>
+      </c>
+      <c r="H13" s="40">
+        <f>G13*0.9</f>
+        <v>14820.192000000001</v>
       </c>
       <c r="I13" s="11"/>
       <c r="J13" s="7"/>
@@ -2877,18 +3162,16 @@
       <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="6"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="48">
-        <f>H12+H13</f>
-        <v>321444.99525200005</v>
+      <c r="A14" s="27"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="34">
+        <f>SUM(H2:H13)</f>
+        <v>69217.84199999999</v>
       </c>
       <c r="I14" s="11"/>
       <c r="J14" s="7"/>
@@ -2896,6 +3179,233 @@
       <c r="L14" s="15"/>
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="28">
+        <v>37617</v>
+      </c>
+      <c r="C15" s="29">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30">
+        <v>21.3</v>
+      </c>
+      <c r="E15" s="31">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30">
+        <v>21.3</v>
+      </c>
+      <c r="G15" s="31">
+        <v>0</v>
+      </c>
+      <c r="H15" s="32">
+        <f t="shared" ref="H15" si="5">G15-E15</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32">
+        <f>SUM(E15:E15)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32">
+        <f>SUM(G15:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="40">
+        <f>SUM(H15:H15)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="43">
+        <f>H14+H16</f>
+        <v>69217.84199999999</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="7">
+        <v>30614.600000000002</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A18" s="5"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="32">
+        <v>-522636.73</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A19" s="6"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="H19" s="41">
+        <f>H17+H18</f>
+        <v>-453418.88799999998</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="7">
+        <v>-522636.73</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G20" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="35">
+        <v>396550</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G21" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="H21" s="35">
+        <v>12050</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="J21" s="7">
+        <v>10130</v>
+      </c>
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G22" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="41">
+        <f>H20+H21</f>
+        <v>408600</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="7">
+        <v>396550</v>
+      </c>
+      <c r="M22" s="7"/>
+    </row>
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C23" s="12"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="45">
+        <f>H19-H22</f>
+        <v>-862018.88800000004</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="7">
+        <v>-919186.73</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="7"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G24" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H24" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" s="7">
+        <v>57000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G25" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="H25" s="42">
+        <f>H23+H24</f>
+        <v>-805018.88800000004</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="J25" s="7">
+        <v>-862186.73</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -2905,7 +3415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F537F07A-D0A7-416B-8994-ABDD1C22435D}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -3312,7 +3822,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801544F9-630F-4E32-B67B-5CF42760770C}">
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -3785,7 +4295,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805BC19F-42DC-4CD3-B954-E9F19E56BFF7}">
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -4874,7 +5384,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961B3AB4-C9A4-46F9-AED6-DC61A66CC09A}">
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -5627,7 +6137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7193655-9E82-4E5C-9879-086AA4339AB9}">
   <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -6301,7 +6811,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAFE1F0-60EA-46C8-9C11-E7180F21BFAA}">
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -7008,7 +7518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E1A231-79A5-4BE4-8C0C-F5E13A4831EB}">
   <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -7917,514 +8427,4 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F07CE69-5C67-4DF2-B5BE-CD5590D6A395}">
-  <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45769</v>
-      </c>
-      <c r="C2" s="29">
-        <v>600</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="37">
-        <v>2.5</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>1500</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2*0.9</f>
-        <v>1350</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B3" s="28">
-        <v>45771</v>
-      </c>
-      <c r="C3" s="29">
-        <v>6000</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="31">
-        <f>C3*F3</f>
-        <v>3000</v>
-      </c>
-      <c r="H3" s="32">
-        <f>G3*0.9</f>
-        <v>2700</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45777</v>
-      </c>
-      <c r="C4" s="29">
-        <v>4200</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="37">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="G4" s="31">
-        <f>C4*F4</f>
-        <v>1176</v>
-      </c>
-      <c r="H4" s="32">
-        <f>G4*0.9</f>
-        <v>1058.4000000000001</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="34">
-        <f>SUM(H2:H4)</f>
-        <v>5108.3999999999996</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45757</v>
-      </c>
-      <c r="C6" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="30">
-        <v>61.5</v>
-      </c>
-      <c r="E6" s="31">
-        <v>61636.22</v>
-      </c>
-      <c r="F6" s="30">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="G6" s="31">
-        <v>16563.23</v>
-      </c>
-      <c r="H6" s="50">
-        <f t="shared" ref="H6" si="0">G6-E6</f>
-        <v>-45072.990000000005</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32">
-        <f>SUM(E6:E6)</f>
-        <v>61636.22</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32">
-        <f>SUM(G6:G6)</f>
-        <v>16563.23</v>
-      </c>
-      <c r="H7" s="34">
-        <f>SUM(H6:H6)</f>
-        <v>-45072.990000000005</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="34">
-        <f>H5+H7</f>
-        <v>-39964.590000000004</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8" s="7">
-        <v>34655.910000000003</v>
-      </c>
-      <c r="L8" s="15">
-        <f t="shared" ref="L8:L12" si="1">H8-K8</f>
-        <v>-74620.5</v>
-      </c>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="7">
-        <v>-122583.36474799996</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="7">
-        <v>-157239.27474799997</v>
-      </c>
-      <c r="L9" s="15">
-        <f t="shared" si="1"/>
-        <v>34655.910000000003</v>
-      </c>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="34">
-        <f>H8+H9</f>
-        <v>-162547.95474799996</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="7">
-        <v>-122583.36474799996</v>
-      </c>
-      <c r="L10" s="15">
-        <f t="shared" si="1"/>
-        <v>-39964.589999999997</v>
-      </c>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="7">
-        <v>281390</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="7">
-        <v>102430</v>
-      </c>
-      <c r="L11" s="15">
-        <f t="shared" si="1"/>
-        <v>178960</v>
-      </c>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="26"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="32" t="s">
-        <v>31</v>
-      </c>
-      <c r="H12" s="35">
-        <v>45870</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" s="7">
-        <v>178960</v>
-      </c>
-      <c r="L12" s="15">
-        <f t="shared" si="1"/>
-        <v>-133090</v>
-      </c>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="26"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="34">
-        <f>H11+H12</f>
-        <v>327260</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="7">
-        <v>281390</v>
-      </c>
-      <c r="L13" s="15">
-        <f>H13-K13</f>
-        <v>45870</v>
-      </c>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="5"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="45">
-        <f>H10-H13</f>
-        <v>-489807.95474799996</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K14" s="7">
-        <v>-403973.36474799993</v>
-      </c>
-      <c r="L14" s="15">
-        <f t="shared" ref="L14:L16" si="2">H14-K14</f>
-        <v>-85834.590000000026</v>
-      </c>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H15" s="38">
-        <v>57000</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K15" s="7">
-        <v>57000</v>
-      </c>
-      <c r="L15" s="15">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="6"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="39">
-        <f>H14+H15</f>
-        <v>-432807.95474799996</v>
-      </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="K16" s="7">
-        <v>-346973.36474799993</v>
-      </c>
-      <c r="L16" s="15">
-        <f t="shared" si="2"/>
-        <v>-85834.590000000026</v>
-      </c>
-      <c r="M16" s="15"/>
-      <c r="N16" s="7"/>
-    </row>
-    <row r="17" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="N17" s="13"/>
-    </row>
-    <row r="18" spans="9:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="K19" s="7"/>
-      <c r="M19" s="7"/>
-    </row>
-    <row r="20" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="M20" s="7"/>
-    </row>
-    <row r="21" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="M21" s="7"/>
-    </row>
-    <row r="22" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="K22" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6787" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD847DFB-FE8E-4915-82CF-6CBAF0AD4327}"/>
+  <xr:revisionPtr revIDLastSave="6899" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{457695F4-4130-44A4-80DD-C52E19936C02}"/>
   <bookViews>
-    <workbookView xWindow="3144" yWindow="900" windowWidth="19692" windowHeight="10776" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5976" yWindow="0" windowWidth="17064" windowHeight="12336" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="JAN26" sheetId="93" r:id="rId1"/>
-    <sheet name="DEC25" sheetId="92" r:id="rId2"/>
-    <sheet name="NOV25" sheetId="91" r:id="rId3"/>
-    <sheet name="OCT25" sheetId="90" r:id="rId4"/>
-    <sheet name="SEP25" sheetId="89" r:id="rId5"/>
-    <sheet name="AUG25" sheetId="88" r:id="rId6"/>
-    <sheet name="JUL25" sheetId="87" r:id="rId7"/>
-    <sheet name="JUN25" sheetId="86" r:id="rId8"/>
-    <sheet name="MAY25" sheetId="85" r:id="rId9"/>
-    <sheet name="APR25" sheetId="84" r:id="rId10"/>
-    <sheet name="MAR25" sheetId="83" r:id="rId11"/>
-    <sheet name="FEB25" sheetId="82" r:id="rId12"/>
+    <sheet name="MAR26" sheetId="95" r:id="rId1"/>
+    <sheet name="FEB26" sheetId="94" r:id="rId2"/>
+    <sheet name="JAN26" sheetId="93" r:id="rId3"/>
+    <sheet name="DEC25" sheetId="92" r:id="rId4"/>
+    <sheet name="NOV25" sheetId="91" r:id="rId5"/>
+    <sheet name="OCT25" sheetId="90" r:id="rId6"/>
+    <sheet name="SEP25" sheetId="89" r:id="rId7"/>
+    <sheet name="AUG25" sheetId="88" r:id="rId8"/>
+    <sheet name="JUL25" sheetId="87" r:id="rId9"/>
+    <sheet name="JUN25" sheetId="86" r:id="rId10"/>
+    <sheet name="MAY25" sheetId="85" r:id="rId11"/>
+    <sheet name="APR25" sheetId="84" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="68">
   <si>
     <t>Name</t>
   </si>
@@ -131,9 +131,6 @@
   </si>
   <si>
     <t>ASK</t>
-  </si>
-  <si>
-    <t>TMT</t>
   </si>
   <si>
     <t>PTT</t>
@@ -246,21 +243,31 @@
   <si>
     <t>CPF</t>
   </si>
+  <si>
+    <t>B/F Dividend</t>
+  </si>
+  <si>
+    <t>C/F Dividend</t>
+  </si>
+  <si>
+    <t>C/F Div - C/F Exp</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="7">
-    <numFmt numFmtId="164" formatCode="0.000"/>
-    <numFmt numFmtId="165" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="166" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="167" formatCode="0.0000"/>
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="169" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
+  <numFmts count="8">
+    <numFmt numFmtId="187" formatCode="0.000"/>
+    <numFmt numFmtId="188" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="189" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="190" formatCode="0.0000"/>
+    <numFmt numFmtId="191" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="192" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="193" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="195" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <name val="Cordia New"/>
@@ -336,14 +343,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -362,26 +369,20 @@
     <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
-      <name val="Verdana"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF333333"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -392,21 +393,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF00B050"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="Tahoma"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -455,19 +456,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -475,24 +476,24 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="191" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -500,103 +501,106 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="187" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="190" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="19" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="20" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="188" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="188" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="188" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="190" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="192" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="191" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="190" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="193" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="19" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="193" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="24" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="195" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="195" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="193" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -961,22 +965,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DA818F-D2F1-4405-A36C-2376E8E1DAA2}">
-  <dimension ref="A1:N14"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6E9199-1687-4EE7-A0F3-54DE6332B9D4}">
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.25" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.625" style="12" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="8" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="7" customWidth="1"/>
-    <col min="8" max="8" width="13.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.875" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="8.625" style="6"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="93" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="14.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.6">
@@ -995,6 +1003,691 @@
       <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="89" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="28">
+        <v>46085</v>
+      </c>
+      <c r="C2" s="29">
+        <v>120000</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="92">
+        <v>0.22412299999999999</v>
+      </c>
+      <c r="G2" s="31">
+        <f t="shared" ref="G2:G8" si="0">C2*F2</f>
+        <v>26894.76</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2*0.9</f>
+        <v>24205.284</v>
+      </c>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="28">
+        <v>46090</v>
+      </c>
+      <c r="C3" s="29">
+        <v>45000</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="90">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="G3" s="31">
+        <f t="shared" ref="G3" si="1">C3*F3</f>
+        <v>9999</v>
+      </c>
+      <c r="H3" s="32">
+        <f>G3*0.9</f>
+        <v>8999.1</v>
+      </c>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" s="28">
+        <v>46093</v>
+      </c>
+      <c r="C4" s="29">
+        <v>69000</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="91">
+        <v>0.17829999999999999</v>
+      </c>
+      <c r="G4" s="31">
+        <f t="shared" si="0"/>
+        <v>12302.699999999999</v>
+      </c>
+      <c r="H4" s="32">
+        <f>G4*0.9</f>
+        <v>11072.429999999998</v>
+      </c>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="28">
+        <v>46099</v>
+      </c>
+      <c r="C5" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="92">
+        <v>0.12189999999999999</v>
+      </c>
+      <c r="G5" s="31">
+        <f t="shared" si="0"/>
+        <v>2438</v>
+      </c>
+      <c r="H5" s="32">
+        <f>G5*0.9</f>
+        <v>2194.2000000000003</v>
+      </c>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="28">
+        <v>46101</v>
+      </c>
+      <c r="C6" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="90">
+        <v>0.1212</v>
+      </c>
+      <c r="G6" s="31">
+        <f t="shared" si="0"/>
+        <v>2424</v>
+      </c>
+      <c r="H6" s="32">
+        <v>2181.6</v>
+      </c>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="28">
+        <v>46101</v>
+      </c>
+      <c r="C7" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="90">
+        <v>7.4800000000000005E-2</v>
+      </c>
+      <c r="G7" s="31">
+        <f t="shared" ref="G7" si="2">C7*F7</f>
+        <v>1496</v>
+      </c>
+      <c r="H7" s="32">
+        <v>1496</v>
+      </c>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="28">
+        <v>46108</v>
+      </c>
+      <c r="C8" s="29">
+        <v>50000</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="91">
+        <v>0.17549999999999999</v>
+      </c>
+      <c r="G8" s="31">
+        <f t="shared" si="0"/>
+        <v>8775</v>
+      </c>
+      <c r="H8" s="32">
+        <f>G8*0.9</f>
+        <v>7897.5</v>
+      </c>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="28">
+        <v>46108</v>
+      </c>
+      <c r="C9" s="29">
+        <v>55000</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="92">
+        <v>0.27939999999999998</v>
+      </c>
+      <c r="G9" s="31">
+        <f>C9*F9</f>
+        <v>15366.999999999998</v>
+      </c>
+      <c r="H9" s="32">
+        <f>G9*0.9</f>
+        <v>13830.3</v>
+      </c>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="32">
+        <f>SUM(H2:H9)</f>
+        <v>71876.41399999999</v>
+      </c>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="28">
+        <v>46085</v>
+      </c>
+      <c r="C11" s="29">
+        <v>17500</v>
+      </c>
+      <c r="D11" s="30">
+        <v>10.6</v>
+      </c>
+      <c r="E11" s="31">
+        <v>185910.87</v>
+      </c>
+      <c r="F11" s="90">
+        <v>11.1</v>
+      </c>
+      <c r="G11" s="31">
+        <v>193819.75</v>
+      </c>
+      <c r="H11" s="40">
+        <f>G11-E11</f>
+        <v>7908.8800000000047</v>
+      </c>
+      <c r="I11" s="96"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="28">
+        <v>46085</v>
+      </c>
+      <c r="C12" s="29">
+        <v>6800</v>
+      </c>
+      <c r="D12" s="30">
+        <v>33</v>
+      </c>
+      <c r="E12" s="31">
+        <v>224897.03</v>
+      </c>
+      <c r="F12" s="90">
+        <v>6.25</v>
+      </c>
+      <c r="G12" s="31">
+        <v>42405.86</v>
+      </c>
+      <c r="H12" s="40">
+        <f>G12-E12</f>
+        <v>-182491.16999999998</v>
+      </c>
+      <c r="I12" s="96"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="27" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="28">
+        <v>46090</v>
+      </c>
+      <c r="C13" s="29">
+        <v>600</v>
+      </c>
+      <c r="D13" s="30">
+        <v>405</v>
+      </c>
+      <c r="E13" s="31">
+        <v>243538.22</v>
+      </c>
+      <c r="F13" s="90">
+        <v>172</v>
+      </c>
+      <c r="G13" s="31">
+        <v>102971.43</v>
+      </c>
+      <c r="H13" s="40">
+        <f>G13-E13</f>
+        <v>-140566.79</v>
+      </c>
+      <c r="I13" s="96"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="26"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="32">
+        <f>SUM(E11:E13)</f>
+        <v>654346.12</v>
+      </c>
+      <c r="F14" s="90"/>
+      <c r="G14" s="32">
+        <f>SUM(G11:G13)</f>
+        <v>339197.04</v>
+      </c>
+      <c r="H14" s="32">
+        <f>SUM(H11:H13)</f>
+        <v>-315149.07999999996</v>
+      </c>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="26"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="34">
+        <f>H10+H14</f>
+        <v>-243272.66599999997</v>
+      </c>
+      <c r="I15" s="96" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="32">
+        <v>-11260</v>
+      </c>
+      <c r="I16" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="62">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="90"/>
+      <c r="G17" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="41">
+        <f>SUM(H15,H16)</f>
+        <v>-254532.66599999997</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="62">
+        <v>0</v>
+      </c>
+      <c r="L17" s="68"/>
+    </row>
+    <row r="18" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="35">
+        <v>71260</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="62">
+        <v>38040</v>
+      </c>
+      <c r="L18" s="68"/>
+    </row>
+    <row r="19" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="26"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="35">
+        <v>19500</v>
+      </c>
+      <c r="I19" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="62">
+        <v>33220</v>
+      </c>
+      <c r="L19" s="68"/>
+    </row>
+    <row r="20" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="26"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="41">
+        <f>H18+H19</f>
+        <v>90760</v>
+      </c>
+      <c r="I20" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="62">
+        <v>71260</v>
+      </c>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="26"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="94">
+        <f>H17-H20</f>
+        <v>-345292.66599999997</v>
+      </c>
+      <c r="I21" s="35" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="62">
+        <v>-71260</v>
+      </c>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="26"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="62" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="97">
+        <v>60000</v>
+      </c>
+      <c r="I22" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" s="62">
+        <v>60000</v>
+      </c>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="26"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="62" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="41">
+        <f>H21+H22</f>
+        <v>-285292.66599999997</v>
+      </c>
+      <c r="I23" s="96" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="62">
+        <v>-11260</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="26"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="H24" s="32">
+        <v>0</v>
+      </c>
+      <c r="I24" s="96"/>
+      <c r="J24" s="32"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="26"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H25" s="32">
+        <f>H24+H10</f>
+        <v>71876.41399999999</v>
+      </c>
+      <c r="I25" s="96"/>
+      <c r="J25" s="32"/>
+    </row>
+    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="26"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H26" s="32">
+        <f>H25-H20</f>
+        <v>-18883.58600000001</v>
+      </c>
+      <c r="I26" s="96"/>
+      <c r="J26" s="32"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAFE1F0-60EA-46C8-9C11-E7180F21BFAA}">
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.375" style="7" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
       <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
@@ -1004,221 +1697,313 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="3"/>
       <c r="K1" s="5"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B2" s="28">
-        <v>45288</v>
+        <v>45812</v>
       </c>
       <c r="C2" s="29">
-        <v>22500</v>
+        <v>55000</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="37">
-        <v>0</v>
+        <v>0.2505</v>
       </c>
       <c r="G2" s="31">
-        <f t="shared" ref="G2" si="0">C2*F2</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2</f>
-        <v>0</v>
+        <f t="shared" ref="G2:G9" si="0">C2*F2</f>
+        <v>13777.5</v>
+      </c>
+      <c r="H2" s="40">
+        <f t="shared" ref="H2:H7" si="1">G2*0.9</f>
+        <v>12399.75</v>
       </c>
       <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
+      <c r="J2" s="17"/>
       <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="28">
+        <v>45814</v>
+      </c>
+      <c r="C3" s="29">
+        <v>12500</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>9</v>
+      </c>
       <c r="E3" s="31"/>
-      <c r="F3" s="37"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="32">
-        <f>SUM(H2,H2)</f>
-        <v>0</v>
+      <c r="F3" s="53">
+        <v>0.215</v>
+      </c>
+      <c r="G3" s="31">
+        <f t="shared" si="0"/>
+        <v>2687.5</v>
+      </c>
+      <c r="H3" s="40">
+        <f t="shared" si="1"/>
+        <v>2418.75</v>
       </c>
       <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
+      <c r="J3" s="17"/>
       <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B4" s="28">
-        <v>45295</v>
+        <v>45814</v>
       </c>
       <c r="C4" s="29">
-        <v>2000</v>
-      </c>
-      <c r="D4" s="30">
-        <v>21.7</v>
-      </c>
-      <c r="E4" s="31">
-        <v>43496.13</v>
-      </c>
-      <c r="F4" s="30">
-        <v>22.9</v>
+        <v>20000</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="31"/>
+      <c r="F4" s="37">
+        <v>0.1915</v>
       </c>
       <c r="G4" s="31">
-        <v>45698.55</v>
-      </c>
-      <c r="H4" s="32">
-        <v>0</v>
-      </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="32">
-        <f>SUM(E4:E4)</f>
-        <v>43496.13</v>
-      </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="32">
-        <f>SUM(G4:G4)</f>
-        <v>45698.55</v>
-      </c>
-      <c r="H5" s="32">
-        <f>SUM(H4:H4)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="26"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="34">
-        <f>H3+H5</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>3830</v>
+      </c>
+      <c r="H4" s="40">
+        <f t="shared" si="1"/>
+        <v>3447</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="28">
+        <v>45817</v>
+      </c>
+      <c r="C5" s="29">
+        <v>40000</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="31"/>
+      <c r="F5" s="37">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="G5" s="31">
+        <f t="shared" si="0"/>
+        <v>8888</v>
+      </c>
+      <c r="H5" s="40">
+        <f t="shared" si="1"/>
+        <v>7999.2</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="28">
+        <v>45820</v>
+      </c>
+      <c r="C6" s="29">
+        <v>75000</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="31"/>
+      <c r="F6" s="54">
+        <v>0.19839999999999999</v>
+      </c>
+      <c r="G6" s="31">
+        <f t="shared" si="0"/>
+        <v>14880</v>
+      </c>
+      <c r="H6" s="40">
+        <f t="shared" si="1"/>
+        <v>13392</v>
       </c>
       <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
+      <c r="J6" s="17"/>
       <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
       <c r="N6" s="6"/>
     </row>
-    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="32">
-        <v>0</v>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="28">
+        <v>45820</v>
+      </c>
+      <c r="C7" s="29">
+        <v>7200</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="31"/>
+      <c r="F7" s="53">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G7" s="31">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="H7" s="40">
+        <f t="shared" si="1"/>
+        <v>1134</v>
       </c>
       <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
+      <c r="J7" s="17"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="41">
-        <f>H6+H7</f>
-        <v>0</v>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="28">
+        <v>45824</v>
+      </c>
+      <c r="C8" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="54">
+        <v>0.1176</v>
+      </c>
+      <c r="G8" s="31">
+        <f t="shared" si="0"/>
+        <v>2352</v>
+      </c>
+      <c r="H8" s="40">
+        <f>G8</f>
+        <v>2352</v>
       </c>
       <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
+      <c r="J8" s="17"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="35">
-        <v>0</v>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="28">
+        <v>45833</v>
+      </c>
+      <c r="C9" s="29">
+        <v>60000</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="31"/>
+      <c r="F9" s="53">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="G9" s="31">
+        <f t="shared" si="0"/>
+        <v>7950</v>
+      </c>
+      <c r="H9" s="40">
+        <f>G9*0.9</f>
+        <v>7155</v>
       </c>
       <c r="I9" s="11"/>
-      <c r="J9" s="7"/>
+      <c r="J9" s="17"/>
       <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="27"/>
       <c r="B10" s="28"/>
       <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="35">
-        <v>38040</v>
+      <c r="G10" s="31"/>
+      <c r="H10" s="43">
+        <f>SUM(H2:H9)</f>
+        <v>50297.7</v>
       </c>
       <c r="I10" s="11"/>
-      <c r="J10" s="7"/>
+      <c r="J10" s="19"/>
       <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="41">
-        <f>H9+H10</f>
-        <v>38040</v>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B11" s="28">
+        <v>45824</v>
+      </c>
+      <c r="C11" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D11" s="30">
+        <v>67</v>
+      </c>
+      <c r="E11" s="52">
+        <v>67148.399999999994</v>
+      </c>
+      <c r="F11" s="30">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="G11" s="31">
+        <v>16563.23</v>
+      </c>
+      <c r="H11" s="32">
+        <f t="shared" ref="H11:H12" si="2">G11-E11</f>
+        <v>-50585.17</v>
       </c>
       <c r="I11" s="11"/>
       <c r="J11" s="7"/>
@@ -1227,19 +2012,31 @@
       <c r="M11" s="15"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="36">
-        <f>H8-H11</f>
-        <v>-38040</v>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="28">
+        <v>45826</v>
+      </c>
+      <c r="C12" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D12" s="30">
+        <v>67</v>
+      </c>
+      <c r="E12" s="52">
+        <v>67148.399999999994</v>
+      </c>
+      <c r="F12" s="30">
+        <v>16.8</v>
+      </c>
+      <c r="G12" s="31">
+        <v>16762.79</v>
+      </c>
+      <c r="H12" s="32">
+        <f t="shared" si="2"/>
+        <v>-50385.609999999993</v>
       </c>
       <c r="I12" s="11"/>
       <c r="J12" s="7"/>
@@ -1248,18 +2045,31 @@
       <c r="M12" s="15"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H13" s="38">
-        <v>60000</v>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="28">
+        <v>45828</v>
+      </c>
+      <c r="C13" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D13" s="30">
+        <v>67</v>
+      </c>
+      <c r="E13" s="52">
+        <v>67148.399999999994</v>
+      </c>
+      <c r="F13" s="30">
+        <v>16.8</v>
+      </c>
+      <c r="G13" s="31">
+        <v>16762.79</v>
+      </c>
+      <c r="H13" s="32">
+        <f t="shared" ref="H13" si="3">G13-E13</f>
+        <v>-50385.609999999993</v>
       </c>
       <c r="I13" s="11"/>
       <c r="J13" s="7"/>
@@ -1268,19 +2078,23 @@
       <c r="M13" s="15"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="6"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H14" s="48">
-        <f>H12+H13</f>
-        <v>21960</v>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="26"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="32">
+        <f>SUM(E13:E13)</f>
+        <v>67148.399999999994</v>
+      </c>
+      <c r="F14" s="30"/>
+      <c r="G14" s="32">
+        <f>SUM(G13:G13)</f>
+        <v>16762.79</v>
+      </c>
+      <c r="H14" s="41">
+        <f>SUM(H11:H13)</f>
+        <v>-151356.38999999998</v>
       </c>
       <c r="I14" s="11"/>
       <c r="J14" s="7"/>
@@ -1289,15 +2103,1172 @@
       <c r="M14" s="15"/>
       <c r="N14" s="6"/>
     </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="26"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="43">
+        <f>H10+H14</f>
+        <v>-101058.68999999999</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="7">
+        <v>76255.710000000021</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="32">
+        <v>-86292.24</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="7">
+        <v>-162547.95474799996</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="34">
+        <f>H15+H16</f>
+        <v>-187350.93</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J17" s="7">
+        <v>-86292.244747999939</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="35">
+        <v>336660</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="7">
+        <v>327260</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A19" s="26"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="H19" s="35">
+        <v>41150</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J19" s="7">
+        <v>9400</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A20" s="26"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="41">
+        <f>H18+H19</f>
+        <v>377810</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="7">
+        <v>336660</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A21" s="5"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="46">
+        <f>H17-H20</f>
+        <v>-565160.92999999993</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J21" s="7">
+        <v>-422952.24474799994</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A22" s="5"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H22" s="38">
+        <v>57000</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J22" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A23" s="6"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H23" s="39">
+        <f>H21+H22</f>
+        <v>-508160.92999999993</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" s="7">
+        <v>-365952.24474799994</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="7"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="I24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="N24" s="13"/>
+    </row>
+    <row r="25" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K25" s="7"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K26" s="7"/>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K29" s="7"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N9">
+    <sortCondition ref="B2:B9"/>
+    <sortCondition ref="A2:A9"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E1A231-79A5-4BE4-8C0C-F5E13A4831EB}">
+  <dimension ref="A1:N35"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="74" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="70"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="72">
+        <v>45784</v>
+      </c>
+      <c r="C2" s="29">
+        <v>81000</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="54">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="31">
+        <f t="shared" ref="G2:G13" si="0">C2*F2</f>
+        <v>40500</v>
+      </c>
+      <c r="H2" s="40">
+        <v>40500</v>
+      </c>
+      <c r="I2" s="13"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="27" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="72">
+        <v>45785</v>
+      </c>
+      <c r="C3" s="29">
+        <v>10000</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="37">
+        <v>1</v>
+      </c>
+      <c r="G3" s="31">
+        <f t="shared" si="0"/>
+        <v>10000</v>
+      </c>
+      <c r="H3" s="40">
+        <v>9000</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="72">
+        <v>45786</v>
+      </c>
+      <c r="C4" s="29">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" s="53">
+        <v>0.6</v>
+      </c>
+      <c r="G4" s="31">
+        <f t="shared" si="0"/>
+        <v>6000</v>
+      </c>
+      <c r="H4" s="40">
+        <v>5540</v>
+      </c>
+      <c r="I4" s="13"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="72">
+        <v>45786</v>
+      </c>
+      <c r="C5" s="29">
+        <v>27000</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="54">
+        <v>0.31</v>
+      </c>
+      <c r="G5" s="31">
+        <f t="shared" si="0"/>
+        <v>8370</v>
+      </c>
+      <c r="H5" s="40">
+        <v>8370</v>
+      </c>
+      <c r="I5" s="13"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="27" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="72">
+        <v>45791</v>
+      </c>
+      <c r="C6" s="29">
+        <v>15000</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="54">
+        <v>0.34</v>
+      </c>
+      <c r="G6" s="31">
+        <f t="shared" si="0"/>
+        <v>5100</v>
+      </c>
+      <c r="H6" s="40">
+        <v>4590</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="72">
+        <v>45793</v>
+      </c>
+      <c r="C7" s="29">
+        <v>3600</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="50">
+        <v>0.25</v>
+      </c>
+      <c r="G7" s="31">
+        <f t="shared" si="0"/>
+        <v>900</v>
+      </c>
+      <c r="H7" s="40">
+        <v>810</v>
+      </c>
+      <c r="I7" s="13"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="72">
+        <v>45793</v>
+      </c>
+      <c r="C8" s="29">
+        <v>27000</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="51">
+        <v>1.5</v>
+      </c>
+      <c r="G8" s="31">
+        <f t="shared" si="0"/>
+        <v>40500</v>
+      </c>
+      <c r="H8" s="40">
+        <v>38340</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="72">
+        <v>45793</v>
+      </c>
+      <c r="C9" s="29">
+        <v>8000</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="69">
+        <v>0.93</v>
+      </c>
+      <c r="G9" s="31">
+        <f t="shared" si="0"/>
+        <v>7440</v>
+      </c>
+      <c r="H9" s="40">
+        <v>6696</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="72">
+        <v>45797</v>
+      </c>
+      <c r="C10" s="29">
+        <v>30000</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" s="50">
+        <v>0.08</v>
+      </c>
+      <c r="G10" s="31">
+        <f t="shared" si="0"/>
+        <v>2400</v>
+      </c>
+      <c r="H10" s="40">
+        <v>2160</v>
+      </c>
+      <c r="I10" s="13"/>
+      <c r="J10" s="17"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="72">
+        <v>45800</v>
+      </c>
+      <c r="C11" s="29">
+        <v>1200</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="53">
+        <v>0.48</v>
+      </c>
+      <c r="G11" s="31">
+        <f t="shared" si="0"/>
+        <v>576</v>
+      </c>
+      <c r="H11" s="40">
+        <v>520.79999999999995</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="72">
+        <v>45800</v>
+      </c>
+      <c r="C12" s="29">
+        <v>4000</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F12" s="54">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G12" s="31">
+        <f t="shared" si="0"/>
+        <v>1120</v>
+      </c>
+      <c r="H12" s="40">
+        <v>1008</v>
+      </c>
+      <c r="I12" s="13"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B13" s="72">
+        <v>45800</v>
+      </c>
+      <c r="C13" s="29">
+        <v>7200</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F13" s="37">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G13" s="31">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="H13" s="40">
+        <v>1134</v>
+      </c>
+      <c r="I13" s="13"/>
+      <c r="J13" s="17"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="72">
+        <v>45800</v>
+      </c>
+      <c r="C14" s="29">
+        <v>105000</v>
+      </c>
+      <c r="D14" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F14" s="53">
+        <v>0.111238</v>
+      </c>
+      <c r="G14" s="31">
+        <v>11676</v>
+      </c>
+      <c r="H14" s="40">
+        <v>10612.21</v>
+      </c>
+      <c r="I14" s="13"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="27" t="s">
+        <v>47</v>
+      </c>
+      <c r="B15" s="72">
+        <v>45800</v>
+      </c>
+      <c r="C15" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D15" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F15" s="53">
+        <v>0.27</v>
+      </c>
+      <c r="G15" s="31">
+        <f>C15*F15</f>
+        <v>270</v>
+      </c>
+      <c r="H15" s="40">
+        <v>243</v>
+      </c>
+      <c r="I15" s="13"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A16" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="72">
+        <v>45805</v>
+      </c>
+      <c r="C16" s="29">
+        <v>9000</v>
+      </c>
+      <c r="D16" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="54">
+        <v>7.4999999999999997E-2</v>
+      </c>
+      <c r="G16" s="31">
+        <f>C16*F16</f>
+        <v>675</v>
+      </c>
+      <c r="H16" s="40">
+        <v>607.5</v>
+      </c>
+      <c r="I16" s="13"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A17" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="72">
+        <v>45806</v>
+      </c>
+      <c r="C17" s="29">
+        <v>6800</v>
+      </c>
+      <c r="D17" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F17" s="37">
+        <v>0.23</v>
+      </c>
+      <c r="G17" s="31">
+        <f>C17*F17</f>
+        <v>1564</v>
+      </c>
+      <c r="H17" s="40">
+        <v>1407.6000000000001</v>
+      </c>
+      <c r="I17" s="13"/>
+      <c r="J17" s="17"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A18" s="27"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="34">
+        <f>SUM(H2:H17)</f>
+        <v>131539.11000000002</v>
+      </c>
+      <c r="I18" s="13"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A19" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="73">
+        <v>45792</v>
+      </c>
+      <c r="C19" s="29">
+        <v>30000</v>
+      </c>
+      <c r="D19" s="30">
+        <v>3.8</v>
+      </c>
+      <c r="E19" s="31">
+        <v>114252.5</v>
+      </c>
+      <c r="F19" s="30">
+        <v>1.97</v>
+      </c>
+      <c r="G19" s="31">
+        <v>58969.1</v>
+      </c>
+      <c r="H19" s="32">
+        <f>G19-E19</f>
+        <v>-55283.4</v>
+      </c>
+      <c r="I19" s="13"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A20" s="26"/>
+      <c r="B20" s="73"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="32">
+        <f>SUM(E19:E19)</f>
+        <v>114252.5</v>
+      </c>
+      <c r="F20" s="30"/>
+      <c r="G20" s="32">
+        <f>SUM(G19:G19)</f>
+        <v>58969.1</v>
+      </c>
+      <c r="H20" s="44">
+        <f>SUM(H19:H19)</f>
+        <v>-55283.4</v>
+      </c>
+      <c r="I20" s="13"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A21" s="26"/>
+      <c r="B21" s="73"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H21" s="34">
+        <f>H18+H20</f>
+        <v>76255.710000000021</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J21" s="7">
+        <v>-39964.590000000004</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A22" s="26"/>
+      <c r="B22" s="73"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="34">
+        <v>-162547.95474799996</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="7">
+        <v>-122583.36474799996</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A23" s="26"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H23" s="34">
+        <f>H21+H22</f>
+        <v>-86292.244747999939</v>
+      </c>
+      <c r="I23" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J23" s="7">
+        <v>-162547.95474799996</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A24" s="26"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="30"/>
+      <c r="G24" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24" s="7">
+        <v>327260</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" s="7">
+        <v>281390</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A25" s="26"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="H25" s="35">
+        <v>9400</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J25" s="7">
+        <v>45870</v>
+      </c>
+      <c r="K25" s="7"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A26" s="26"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="41">
+        <f>H24+H25</f>
+        <v>336660</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J26" s="7">
+        <v>327260</v>
+      </c>
+      <c r="K26" s="7"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A27" s="5"/>
+      <c r="B27" s="74"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H27" s="46">
+        <f>H23-H26</f>
+        <v>-422952.24474799994</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J27" s="7">
+        <v>-489807.95474799996</v>
+      </c>
+      <c r="K27" s="7"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="6"/>
+    </row>
+    <row r="28" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A28" s="5"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="8"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="7"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H28" s="38">
+        <v>57000</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A29" s="6"/>
+      <c r="B29" s="74"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H29" s="39">
+        <f>H27+H28</f>
+        <v>-365952.24474799994</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J29" s="7">
+        <v>-432807.95474799996</v>
+      </c>
+      <c r="K29" s="7"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+      <c r="N29" s="7"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K30" s="7"/>
+      <c r="N30" s="13"/>
+    </row>
+    <row r="31" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="7"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K32" s="7"/>
+      <c r="M32" s="7"/>
+    </row>
+    <row r="33" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="M33" s="7"/>
+    </row>
+    <row r="34" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="M34" s="7"/>
+    </row>
+    <row r="35" spans="11:13" x14ac:dyDescent="0.3">
+      <c r="K35" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N17">
+    <sortCondition ref="B2:B17"/>
+    <sortCondition ref="A2:A17"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F07CE69-5C67-4DF2-B5BE-CD5590D6A395}">
   <dimension ref="A1:N22"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -1421,7 +3392,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" s="28">
         <v>45777</v>
@@ -1474,7 +3445,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A6" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="28">
         <v>45757</v>
@@ -1494,7 +3465,7 @@
       <c r="G6" s="31">
         <v>16563.23</v>
       </c>
-      <c r="H6" s="50">
+      <c r="H6" s="49">
         <f t="shared" ref="H6" si="0">G6-E6</f>
         <v>-45072.990000000005</v>
       </c>
@@ -1593,7 +3564,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H10" s="34">
         <f>H8+H9</f>
@@ -1601,7 +3572,7 @@
       </c>
       <c r="I10" s="11"/>
       <c r="J10" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K10" s="7">
         <v>-122583.36474799996</v>
@@ -1648,7 +3619,7 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H12" s="35">
         <v>45870</v>
@@ -1731,14 +3702,14 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H15" s="38">
         <v>57000</v>
       </c>
       <c r="I15" s="11"/>
       <c r="J15" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="K15" s="7">
         <v>57000</v>
@@ -1758,7 +3729,7 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H16" s="39">
         <f>H14+H15</f>
@@ -1766,7 +3737,7 @@
       </c>
       <c r="I16" s="11"/>
       <c r="J16" s="7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="K16" s="7">
         <v>-346973.36474799993</v>
@@ -1807,498 +3778,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{779217B5-9CE8-46BD-8B22-71F5AA3AD105}">
-  <dimension ref="A1:L20"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="8.375" style="49" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="72" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45722</v>
-      </c>
-      <c r="C2" s="29">
-        <v>35000</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="54">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="G2" s="31">
-        <f t="shared" ref="G2:G8" si="0">C2*F2</f>
-        <v>7777</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2*0.9</f>
-        <v>6999.3</v>
-      </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="28">
-        <v>45728</v>
-      </c>
-      <c r="C3" s="29">
-        <v>75000</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="55">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G3" s="31">
-        <f t="shared" si="0"/>
-        <v>15374.999999999998</v>
-      </c>
-      <c r="H3" s="32">
-        <f>G3*0.9</f>
-        <v>13837.499999999998</v>
-      </c>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="6"/>
-    </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45733</v>
-      </c>
-      <c r="C4" s="29">
-        <v>55000</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="54">
-        <v>9.8699999999999996E-2</v>
-      </c>
-      <c r="G4" s="31">
-        <f t="shared" si="0"/>
-        <v>5428.5</v>
-      </c>
-      <c r="H4" s="32">
-        <f>G4*0.9</f>
-        <v>4885.6500000000005</v>
-      </c>
-      <c r="I4" s="15"/>
-      <c r="J4" s="15"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45733</v>
-      </c>
-      <c r="C5" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="55">
-        <v>0.11890000000000001</v>
-      </c>
-      <c r="G5" s="31">
-        <f t="shared" si="0"/>
-        <v>2378</v>
-      </c>
-      <c r="H5" s="32">
-        <f>G5</f>
-        <v>2378</v>
-      </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45735</v>
-      </c>
-      <c r="C6" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="55">
-        <v>0.1358</v>
-      </c>
-      <c r="G6" s="31">
-        <f t="shared" si="0"/>
-        <v>2716</v>
-      </c>
-      <c r="H6" s="32">
-        <f>G6*0.9</f>
-        <v>2444.4</v>
-      </c>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="28">
-        <v>45737</v>
-      </c>
-      <c r="C7" s="29">
-        <v>12500</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="37">
-        <v>0.215</v>
-      </c>
-      <c r="G7" s="31">
-        <f t="shared" si="0"/>
-        <v>2687.5</v>
-      </c>
-      <c r="H7" s="32">
-        <f>G7*0.9</f>
-        <v>2418.75</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="28">
-        <v>45744</v>
-      </c>
-      <c r="C8" s="29">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="54">
-        <v>5.8200000000000002E-2</v>
-      </c>
-      <c r="G8" s="31">
-        <f t="shared" si="0"/>
-        <v>2910</v>
-      </c>
-      <c r="H8" s="32">
-        <f>G8*0.9</f>
-        <v>2619</v>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="27"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="30"/>
-      <c r="E9" s="31"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="31"/>
-      <c r="H9" s="32">
-        <f>SUM(H2:H8)</f>
-        <v>35582.600000000006</v>
-      </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="B10" s="28">
-        <v>45719</v>
-      </c>
-      <c r="C10" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D10" s="30">
-        <v>2.9</v>
-      </c>
-      <c r="E10" s="31">
-        <v>29064.23</v>
-      </c>
-      <c r="F10" s="37">
-        <v>2.82</v>
-      </c>
-      <c r="G10" s="31">
-        <v>28137.54</v>
-      </c>
-      <c r="H10" s="32">
-        <f t="shared" ref="H10" si="1">G10-E10</f>
-        <v>-926.68999999999869</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32">
-        <f>SUM(E10:E10)</f>
-        <v>29064.23</v>
-      </c>
-      <c r="F11" s="37"/>
-      <c r="G11" s="32">
-        <f>SUM(G10:G10)</f>
-        <v>28137.54</v>
-      </c>
-      <c r="H11" s="32">
-        <f>SUM(H10:H10)</f>
-        <v>-926.68999999999869</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
-      <c r="L11" s="6"/>
-    </row>
-    <row r="12" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H12" s="34">
-        <f>H9+H11</f>
-        <v>34655.910000000003</v>
-      </c>
-      <c r="J12" s="65"/>
-    </row>
-    <row r="13" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="32">
-        <v>-157239.27474799997</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="65"/>
-      <c r="L13" s="6"/>
-    </row>
-    <row r="14" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="26"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="H14" s="41">
-        <f>SUM(H12,H13)</f>
-        <v>-122583.36474799996</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="65"/>
-      <c r="L14" s="74"/>
-    </row>
-    <row r="15" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="37"/>
-      <c r="G15" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H15" s="35">
-        <v>102430</v>
-      </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="65"/>
-      <c r="L15" s="74"/>
-    </row>
-    <row r="16" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="H16" s="35">
-        <v>178960</v>
-      </c>
-      <c r="I16" s="15"/>
-      <c r="J16" s="65"/>
-      <c r="L16" s="74"/>
-    </row>
-    <row r="17" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="37"/>
-      <c r="G17" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="41">
-        <f>H15+H16</f>
-        <v>281390</v>
-      </c>
-      <c r="I17" s="15"/>
-      <c r="J17" s="65"/>
-      <c r="L17" s="6"/>
-    </row>
-    <row r="18" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H18" s="36">
-        <f>H14-H17</f>
-        <v>-403973.36474799993</v>
-      </c>
-      <c r="I18" s="15"/>
-      <c r="J18" s="65"/>
-      <c r="L18" s="6"/>
-    </row>
-    <row r="19" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B19" s="18"/>
-      <c r="G19" s="65" t="s">
-        <v>32</v>
-      </c>
-      <c r="H19" s="6">
-        <v>57000</v>
-      </c>
-      <c r="I19" s="15"/>
-      <c r="J19" s="65"/>
-      <c r="L19" s="6"/>
-    </row>
-    <row r="20" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G20" s="65" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="73">
-        <f>H18+H19</f>
-        <v>-346973.36474799993</v>
-      </c>
-      <c r="J20" s="65"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F818BAB4-5237-4BD8-9A61-131DACEE1BB2}">
-  <dimension ref="A1:N19"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815483-6499-49C9-BB8D-67572F4517B8}">
+  <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8.125" style="5" bestFit="1" customWidth="1"/>
@@ -2307,7 +3789,7 @@
     <col min="4" max="4" width="10.25" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.25" style="7" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.125" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="7" max="7" width="22.875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="19.25" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
     <col min="10" max="10" width="12.375" style="7" customWidth="1"/>
@@ -2348,31 +3830,30 @@
       <c r="J1" s="16"/>
       <c r="K1" s="5"/>
     </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B2" s="28">
-        <v>45705</v>
+        <v>45288</v>
       </c>
       <c r="C2" s="29">
-        <v>4500</v>
-      </c>
-      <c r="D2" s="61">
-        <v>31</v>
-      </c>
-      <c r="E2" s="61">
-        <v>139808.98000000001</v>
-      </c>
-      <c r="F2" s="30">
-        <v>7.35</v>
-      </c>
-      <c r="G2" s="64">
-        <v>33001.74</v>
-      </c>
-      <c r="H2" s="65">
-        <f>G2-E2</f>
-        <v>-106807.24000000002</v>
+        <v>22500</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="37">
+        <v>0</v>
+      </c>
+      <c r="G2" s="31">
+        <f t="shared" ref="G2" si="0">C2*F2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2</f>
+        <v>0</v>
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="7"/>
@@ -2381,31 +3862,17 @@
       <c r="M2" s="15"/>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B3" s="28">
-        <v>45705</v>
-      </c>
-      <c r="C3" s="29">
-        <v>1500</v>
-      </c>
-      <c r="D3" s="61">
-        <v>12</v>
-      </c>
-      <c r="E3" s="61">
-        <v>18039.87</v>
-      </c>
-      <c r="F3" s="30">
-        <v>7.35</v>
-      </c>
-      <c r="G3" s="64">
-        <v>11000.58</v>
-      </c>
-      <c r="H3" s="65">
-        <f>G3-E3</f>
-        <v>-7039.2899999999991</v>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="32">
+        <f>SUM(H2,H2)</f>
+        <v>0</v>
       </c>
       <c r="I3" s="11"/>
       <c r="J3" s="7"/>
@@ -2414,120 +3881,95 @@
       <c r="M3" s="15"/>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B4" s="28">
-        <v>45712</v>
+        <v>45295</v>
       </c>
       <c r="C4" s="29">
-        <v>15000</v>
-      </c>
-      <c r="D4" s="62">
-        <v>10.9</v>
-      </c>
-      <c r="E4" s="61">
-        <v>163862.14000000001</v>
+        <v>2000</v>
+      </c>
+      <c r="D4" s="30">
+        <v>21.7</v>
+      </c>
+      <c r="E4" s="31">
+        <v>43496.13</v>
       </c>
       <c r="F4" s="30">
-        <v>2.94</v>
-      </c>
-      <c r="G4" s="66">
-        <v>44002.32</v>
-      </c>
-      <c r="H4" s="65">
-        <f>G4-E4</f>
-        <v>-119859.82</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45712</v>
-      </c>
-      <c r="C5" s="29">
-        <v>12000</v>
-      </c>
-      <c r="D5" s="62">
-        <v>10</v>
-      </c>
-      <c r="E5" s="61">
-        <v>120265.79</v>
-      </c>
-      <c r="F5" s="30">
-        <v>2.94</v>
-      </c>
-      <c r="G5" s="66">
-        <v>35201.86</v>
-      </c>
-      <c r="H5" s="65">
-        <f>G5-E5</f>
-        <v>-85063.93</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45712</v>
-      </c>
-      <c r="C6" s="29">
-        <v>9000</v>
-      </c>
-      <c r="D6" s="62">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="E6" s="61">
-        <v>83885.39</v>
-      </c>
-      <c r="F6" s="30">
-        <v>2.94</v>
-      </c>
-      <c r="G6" s="66">
-        <v>26401.4</v>
-      </c>
-      <c r="H6" s="65">
-        <f>G6-E6</f>
-        <v>-57483.99</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="27"/>
+        <v>22.9</v>
+      </c>
+      <c r="G4" s="31">
+        <v>45698.55</v>
+      </c>
+      <c r="H4" s="32">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="32">
+        <f>SUM(E4:E4)</f>
+        <v>43496.13</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="32">
+        <f>SUM(G4:G4)</f>
+        <v>45698.55</v>
+      </c>
+      <c r="H5" s="32">
+        <f>SUM(H4:H4)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="22.8" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="27"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="62">
+        <f>SUM(H2:H5)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
       <c r="B7" s="28"/>
       <c r="C7" s="29"/>
-      <c r="D7" s="30"/>
-      <c r="E7" s="31"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
       <c r="F7" s="30"/>
-      <c r="G7" s="64"/>
-      <c r="H7" s="65">
-        <f>SUM(H2:H6)</f>
-        <v>-376254.27</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="6"/>
+      <c r="G7" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="62">
+        <f>H6</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="15">
+        <v>0</v>
+      </c>
+      <c r="L7" s="6"/>
     </row>
     <row r="8" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="26"/>
@@ -2536,15 +3978,18 @@
       <c r="D8" s="33"/>
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
-      <c r="G8" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="65">
-        <f>H7</f>
-        <v>-376254.27</v>
-      </c>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
+      <c r="G8" s="62" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="62">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="15">
+        <v>0</v>
+      </c>
       <c r="L8" s="6"/>
     </row>
     <row r="9" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2554,14 +3999,19 @@
       <c r="D9" s="33"/>
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
-      <c r="G9" s="65" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="65">
-        <v>321444.99525200005</v>
-      </c>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
+      <c r="G9" s="62" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="63">
+        <f>SUM(H7,H8)</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="15">
+        <v>0</v>
+      </c>
       <c r="L9" s="6"/>
     </row>
     <row r="10" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2571,15 +4021,18 @@
       <c r="D10" s="33"/>
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
-      <c r="G10" s="65" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="67">
-        <f>SUM(H8,H9)</f>
-        <v>-54809.274747999967</v>
-      </c>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
+      <c r="G10" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="64">
+        <v>38040</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="15">
+        <v>0</v>
+      </c>
       <c r="L10" s="6"/>
     </row>
     <row r="11" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2589,14 +4042,18 @@
       <c r="D11" s="33"/>
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
-      <c r="G11" s="65" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="68">
-        <v>43930</v>
-      </c>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
+      <c r="G11" s="62" t="s">
+        <v>17</v>
+      </c>
+      <c r="H11" s="64">
+        <v>33220</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="J11" s="15">
+        <v>38040</v>
+      </c>
       <c r="L11" s="6"/>
     </row>
     <row r="12" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2605,15 +4062,22 @@
       <c r="C12" s="29"/>
       <c r="D12" s="33"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="H12" s="68">
-        <v>58500</v>
-      </c>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
+      <c r="F12" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="63">
+        <f>H10+H11</f>
+        <v>71260</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="15">
+        <v>38040</v>
+      </c>
       <c r="L12" s="6"/>
     </row>
     <row r="13" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -2622,100 +4086,118 @@
       <c r="C13" s="29"/>
       <c r="D13" s="33"/>
       <c r="E13" s="32"/>
-      <c r="F13" s="60" t="s">
-        <v>61</v>
-      </c>
-      <c r="G13" s="65" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="67">
-        <f>H11+H12</f>
-        <v>102430</v>
-      </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="62" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="65">
+        <f>H9-H12</f>
+        <v>-71260</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="15">
+        <v>-38040</v>
+      </c>
       <c r="L13" s="6"/>
     </row>
-    <row r="14" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="26"/>
       <c r="B14" s="28"/>
       <c r="C14" s="29"/>
       <c r="D14" s="33"/>
       <c r="E14" s="32"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="65" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="69">
-        <f>H10-H13</f>
-        <v>-157239.27474799997</v>
-      </c>
-      <c r="I14" s="15"/>
-      <c r="J14" s="15"/>
+      <c r="F14" s="59" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="62" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="62">
+        <v>60000</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="15">
+        <v>60000</v>
+      </c>
       <c r="L14" s="6"/>
     </row>
     <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="26"/>
-      <c r="B15" s="28"/>
+      <c r="B15" s="60"/>
       <c r="C15" s="29"/>
       <c r="D15" s="33"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="60" t="s">
-        <v>60</v>
-      </c>
-      <c r="G15" s="65" t="s">
+      <c r="F15" s="30"/>
+      <c r="G15" s="62" t="s">
         <v>32</v>
       </c>
-      <c r="H15" s="65">
-        <v>57000</v>
-      </c>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="L15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="H15" s="66">
+        <f>H13+H14</f>
+        <v>-11260</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" s="7">
+        <v>21960</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
-      <c r="B16" s="63"/>
+      <c r="B16" s="60"/>
       <c r="C16" s="29"/>
       <c r="D16" s="33"/>
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
-      <c r="G16" s="65" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="70">
-        <f>H14+H15</f>
-        <v>-100239.27474799997</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G16" s="62"/>
+      <c r="H16" s="62"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="26"/>
-      <c r="B17" s="63"/>
+      <c r="B17" s="60"/>
       <c r="C17" s="29"/>
       <c r="D17" s="33"/>
       <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="65"/>
-      <c r="H17" s="65"/>
-    </row>
-    <row r="18" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="60" t="s">
+      <c r="F17" s="59" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="67" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="71" t="s">
-        <v>63</v>
-      </c>
-      <c r="H18" s="65">
-        <f>H15-H13</f>
-        <v>-45430</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" ht="8.4" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="H17" s="62">
+        <f>H14-H12</f>
+        <v>-11260</v>
+      </c>
+      <c r="J17" s="7"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" s="11" customFormat="1" ht="8.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
@@ -2724,7 +4206,344 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DA818F-D2F1-4405-A36C-2376E8E1DAA2}">
+  <dimension ref="A1:N14"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.25" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.875" style="7" customWidth="1"/>
+    <col min="6" max="6" width="8" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="7" customWidth="1"/>
+    <col min="8" max="8" width="13.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="15" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.375" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.875" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="5"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45288</v>
+      </c>
+      <c r="C2" s="29">
+        <v>22500</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="37">
+        <v>0</v>
+      </c>
+      <c r="G2" s="31">
+        <f t="shared" ref="G2" si="0">C2*F2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="37"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="32">
+        <f>SUM(H2,H2)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="33.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45295</v>
+      </c>
+      <c r="C4" s="29">
+        <v>2000</v>
+      </c>
+      <c r="D4" s="30">
+        <v>21.7</v>
+      </c>
+      <c r="E4" s="31">
+        <v>43496.13</v>
+      </c>
+      <c r="F4" s="30">
+        <v>22.9</v>
+      </c>
+      <c r="G4" s="31">
+        <v>45698.55</v>
+      </c>
+      <c r="H4" s="32">
+        <v>0</v>
+      </c>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="32">
+        <f>SUM(E4:E4)</f>
+        <v>43496.13</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="32">
+        <f>SUM(G4:G4)</f>
+        <v>45698.55</v>
+      </c>
+      <c r="H5" s="32">
+        <f>SUM(H4:H4)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="15"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="34">
+        <f>H3+H5</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="32">
+        <v>0</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" s="41">
+        <f>H6+H7</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="35">
+        <v>0</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="35">
+        <v>38040</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="41">
+        <f>H9+H10</f>
+        <v>38040</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="36">
+        <f>H8-H11</f>
+        <v>-38040</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H13" s="38">
+        <v>60000</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="6"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" s="48">
+        <f>H12+H13</f>
+        <v>21960</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDBED0F-338F-4C61-AC0B-5077E6985A08}">
   <dimension ref="A1:N25"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -2812,7 +4631,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A3" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="28">
         <v>45995</v>
@@ -2843,7 +4662,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="28">
         <v>46002</v>
@@ -2887,7 +4706,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="31"/>
-      <c r="F5" s="54">
+      <c r="F5" s="53">
         <v>6.9099999999999995E-2</v>
       </c>
       <c r="G5" s="31">
@@ -2906,8 +4725,8 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="94" t="s">
-        <v>38</v>
+      <c r="A6" s="88" t="s">
+        <v>37</v>
       </c>
       <c r="B6" s="28">
         <v>46002</v>
@@ -2944,14 +4763,14 @@
       <c r="B7" s="28">
         <v>45995</v>
       </c>
-      <c r="C7" s="93">
+      <c r="C7" s="87">
         <v>17500</v>
       </c>
       <c r="D7" s="30" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="31"/>
-      <c r="F7" s="54">
+      <c r="F7" s="53">
         <v>0.20499999999999999</v>
       </c>
       <c r="G7" s="31">
@@ -2971,7 +4790,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A8" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B8" s="28">
         <v>46006</v>
@@ -3047,7 +4866,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="31"/>
-      <c r="F10" s="54">
+      <c r="F10" s="53">
         <v>0.13250000000000001</v>
       </c>
       <c r="G10" s="31">
@@ -3072,14 +4891,14 @@
       <c r="B11" s="28">
         <v>46015</v>
       </c>
-      <c r="C11" s="93">
+      <c r="C11" s="87">
         <v>69000</v>
       </c>
       <c r="D11" s="30" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="31"/>
-      <c r="F11" s="54">
+      <c r="F11" s="53">
         <v>0.1825</v>
       </c>
       <c r="G11" s="31">
@@ -3111,7 +4930,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="31"/>
-      <c r="F12" s="54">
+      <c r="F12" s="53">
         <v>0.114</v>
       </c>
       <c r="G12" s="31">
@@ -3130,8 +4949,8 @@
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="94" t="s">
-        <v>54</v>
+      <c r="A13" s="88" t="s">
+        <v>53</v>
       </c>
       <c r="B13" s="28">
         <v>46013</v>
@@ -3292,14 +5111,14 @@
       <c r="E19" s="14"/>
       <c r="F19" s="10"/>
       <c r="G19" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" s="41">
         <f>H17+H18</f>
         <v>-453418.88799999998</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J19" s="7">
         <v>-522636.73</v>
@@ -3327,13 +5146,13 @@
     </row>
     <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G21" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H21" s="35">
         <v>12050</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J21" s="7">
         <v>10130</v>
@@ -3380,13 +5199,13 @@
     </row>
     <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G24" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H24" s="7">
         <v>57000</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J24" s="7">
         <v>57000</v>
@@ -3394,14 +5213,14 @@
     </row>
     <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G25" s="38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H25" s="42">
         <f>H23+H24</f>
         <v>-805018.88800000004</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J25" s="7">
         <v>-862186.73</v>
@@ -3415,7 +5234,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F537F07A-D0A7-416B-8994-ABDD1C22435D}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -3471,7 +5290,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -3631,14 +5450,14 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H8" s="41">
         <f>H6+H7</f>
         <v>-522636.73</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J8" s="7">
         <v>-522636.73</v>
@@ -3678,13 +5497,13 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10" s="35">
         <v>24420</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J10" s="7">
         <v>10130</v>
@@ -3751,13 +5570,13 @@
       <c r="E13" s="7"/>
       <c r="F13" s="10"/>
       <c r="G13" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H13" s="7">
         <v>57000</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J13" s="7">
         <v>57000</v>
@@ -3775,14 +5594,14 @@
       <c r="E14" s="14"/>
       <c r="F14" s="10"/>
       <c r="G14" s="38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
         <v>-886606.73</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J14" s="7">
         <v>-862186.73</v>
@@ -3822,7 +5641,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801544F9-630F-4E32-B67B-5CF42760770C}">
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -3878,7 +5697,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B2" s="28">
         <v>45576</v>
@@ -3890,14 +5709,14 @@
         <v>9</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="55">
+      <c r="F2" s="54">
         <v>0</v>
       </c>
       <c r="G2" s="31">
         <f>C2*F2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="56">
+      <c r="H2" s="55">
         <f>G2*0.9</f>
         <v>0</v>
       </c>
@@ -3929,7 +5748,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B4" s="28">
         <v>45931</v>
@@ -3962,7 +5781,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A5" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B5" s="28">
         <v>45937</v>
@@ -3995,7 +5814,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B6" s="28">
         <v>45954</v>
@@ -4104,14 +5923,14 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H10" s="41">
         <f>H8+H9</f>
         <v>-520323.55</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J10" s="7">
         <v>-522636.73</v>
@@ -4151,13 +5970,13 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H12" s="35">
         <v>19270</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J12" s="7">
         <v>10130</v>
@@ -4224,13 +6043,13 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H15" s="38">
         <v>57000</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J15" s="7">
         <v>57000</v>
@@ -4248,14 +6067,14 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H16" s="42">
         <f>H14+H15</f>
         <v>-879143.55</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J16" s="7">
         <v>-862186.73</v>
@@ -4295,7 +6114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805BC19F-42DC-4CD3-B954-E9F19E56BFF7}">
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -4342,7 +6161,7 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="58"/>
+      <c r="I1" s="57"/>
       <c r="J1" s="5"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
@@ -4350,24 +6169,24 @@
       <c r="N1" s="6"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="83" t="s">
-        <v>54</v>
-      </c>
-      <c r="B2" s="84">
+      <c r="A2" s="77" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="78">
         <v>45903</v>
       </c>
-      <c r="C2" s="85">
+      <c r="C2" s="79">
         <v>120000</v>
       </c>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83">
+      <c r="D2" s="77"/>
+      <c r="E2" s="77"/>
+      <c r="F2" s="77">
         <v>0.15454999999999999</v>
       </c>
-      <c r="G2" s="88">
+      <c r="G2" s="82">
         <v>18546</v>
       </c>
-      <c r="H2" s="88">
+      <c r="H2" s="82">
         <v>16691.400000000001</v>
       </c>
       <c r="I2" s="10"/>
@@ -4378,24 +6197,24 @@
       <c r="N2" s="6"/>
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="83" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="84">
+      <c r="A3" s="77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3" s="78">
         <v>45910</v>
       </c>
-      <c r="C3" s="85">
+      <c r="C3" s="79">
         <v>1200</v>
       </c>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="89">
+      <c r="D3" s="77"/>
+      <c r="E3" s="77"/>
+      <c r="F3" s="83">
         <v>0.31</v>
       </c>
-      <c r="G3" s="88">
+      <c r="G3" s="82">
         <v>372</v>
       </c>
-      <c r="H3" s="88">
+      <c r="H3" s="82">
         <v>339.6</v>
       </c>
       <c r="I3" s="10"/>
@@ -4406,24 +6225,24 @@
       <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="83" t="s">
+      <c r="A4" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="84">
+      <c r="B4" s="78">
         <v>45905</v>
       </c>
-      <c r="C4" s="90">
+      <c r="C4" s="84">
         <v>17500</v>
       </c>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="89">
+      <c r="D4" s="77"/>
+      <c r="E4" s="77"/>
+      <c r="F4" s="83">
         <v>0.20499999999999999</v>
       </c>
-      <c r="G4" s="88">
+      <c r="G4" s="82">
         <v>3587.5</v>
       </c>
-      <c r="H4" s="88">
+      <c r="H4" s="82">
         <v>3228.75</v>
       </c>
       <c r="I4" s="10"/>
@@ -4434,24 +6253,24 @@
       <c r="N4" s="6"/>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="83" t="s">
+      <c r="A5" s="77" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="84">
+      <c r="B5" s="78">
         <v>45912</v>
       </c>
-      <c r="C5" s="85">
+      <c r="C5" s="79">
         <v>4000</v>
       </c>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="89">
+      <c r="D5" s="77"/>
+      <c r="E5" s="77"/>
+      <c r="F5" s="83">
         <v>0.15</v>
       </c>
-      <c r="G5" s="88">
+      <c r="G5" s="82">
         <v>600</v>
       </c>
-      <c r="H5" s="88">
+      <c r="H5" s="82">
         <v>540</v>
       </c>
       <c r="I5" s="10"/>
@@ -4462,24 +6281,24 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="B6" s="84">
+      <c r="A6" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="78">
         <v>45912</v>
       </c>
-      <c r="C6" s="85">
+      <c r="C6" s="79">
         <v>5000</v>
       </c>
-      <c r="D6" s="83"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="83">
+      <c r="D6" s="77"/>
+      <c r="E6" s="77"/>
+      <c r="F6" s="77">
         <v>1</v>
       </c>
-      <c r="G6" s="88">
+      <c r="G6" s="82">
         <v>5000</v>
       </c>
-      <c r="H6" s="88">
+      <c r="H6" s="82">
         <v>4500</v>
       </c>
       <c r="I6" s="10"/>
@@ -4490,24 +6309,24 @@
       <c r="N6" s="6"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="83" t="s">
+      <c r="A7" s="77" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="84">
+      <c r="B7" s="78">
         <v>45911</v>
       </c>
-      <c r="C7" s="91">
+      <c r="C7" s="85">
         <v>55000</v>
       </c>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="89">
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="83">
         <v>0.2261</v>
       </c>
-      <c r="G7" s="88">
+      <c r="G7" s="82">
         <v>12435.5</v>
       </c>
-      <c r="H7" s="88">
+      <c r="H7" s="82">
         <v>11191.95</v>
       </c>
       <c r="I7" s="10"/>
@@ -4518,24 +6337,24 @@
       <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="84">
+      <c r="B8" s="78">
         <v>45909</v>
       </c>
-      <c r="C8" s="90">
+      <c r="C8" s="84">
         <v>50000</v>
       </c>
-      <c r="D8" s="83"/>
-      <c r="E8" s="83"/>
-      <c r="F8" s="83">
+      <c r="D8" s="77"/>
+      <c r="E8" s="77"/>
+      <c r="F8" s="77">
         <v>0.22220000000000001</v>
       </c>
-      <c r="G8" s="88">
+      <c r="G8" s="82">
         <v>11110</v>
       </c>
-      <c r="H8" s="88">
+      <c r="H8" s="82">
         <v>9999</v>
       </c>
       <c r="I8" s="10"/>
@@ -4546,24 +6365,24 @@
       <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="83" t="s">
+      <c r="A9" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="84">
+      <c r="B9" s="78">
         <v>45911</v>
       </c>
-      <c r="C9" s="90">
+      <c r="C9" s="84">
         <v>69000</v>
       </c>
-      <c r="D9" s="83"/>
-      <c r="E9" s="83"/>
-      <c r="F9" s="89">
+      <c r="D9" s="77"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="83">
         <v>0.19650000000000001</v>
       </c>
-      <c r="G9" s="88">
+      <c r="G9" s="82">
         <v>13558.5</v>
       </c>
-      <c r="H9" s="88">
+      <c r="H9" s="82">
         <v>12202.65</v>
       </c>
       <c r="I9" s="10"/>
@@ -4574,24 +6393,24 @@
       <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="83" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="84">
+      <c r="A10" s="77" t="s">
+        <v>42</v>
+      </c>
+      <c r="B10" s="78">
         <v>45911</v>
       </c>
-      <c r="C10" s="91">
+      <c r="C10" s="85">
         <v>7200</v>
       </c>
-      <c r="D10" s="83"/>
-      <c r="E10" s="83"/>
-      <c r="F10" s="83">
+      <c r="D10" s="77"/>
+      <c r="E10" s="77"/>
+      <c r="F10" s="77">
         <v>0.17499999999999999</v>
       </c>
-      <c r="G10" s="88">
+      <c r="G10" s="82">
         <v>1260</v>
       </c>
-      <c r="H10" s="88">
+      <c r="H10" s="82">
         <v>1134</v>
       </c>
       <c r="I10" s="10"/>
@@ -4602,24 +6421,24 @@
       <c r="N10" s="6"/>
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="83" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="84">
+      <c r="A11" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="78">
         <v>45912</v>
       </c>
-      <c r="C11" s="91">
+      <c r="C11" s="85">
         <v>4200</v>
       </c>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="92">
+      <c r="D11" s="77"/>
+      <c r="E11" s="77"/>
+      <c r="F11" s="86">
         <v>0.24</v>
       </c>
-      <c r="G11" s="88">
+      <c r="G11" s="82">
         <v>1008</v>
       </c>
-      <c r="H11" s="88">
+      <c r="H11" s="82">
         <v>907.2</v>
       </c>
       <c r="I11" s="10"/>
@@ -4630,24 +6449,24 @@
       <c r="N11" s="6"/>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="83" t="s">
-        <v>34</v>
-      </c>
-      <c r="B12" s="84">
+      <c r="A12" s="77" t="s">
+        <v>33</v>
+      </c>
+      <c r="B12" s="78">
         <v>45910</v>
       </c>
-      <c r="C12" s="90">
+      <c r="C12" s="84">
         <v>81000</v>
       </c>
-      <c r="D12" s="83"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="89">
+      <c r="D12" s="77"/>
+      <c r="E12" s="77"/>
+      <c r="F12" s="83">
         <v>0.25</v>
       </c>
-      <c r="G12" s="88">
+      <c r="G12" s="82">
         <v>20250</v>
       </c>
-      <c r="H12" s="88">
+      <c r="H12" s="82">
         <v>19926</v>
       </c>
       <c r="I12" s="10"/>
@@ -4658,24 +6477,24 @@
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="83" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="84">
+      <c r="A13" s="77" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" s="78">
         <v>45905</v>
       </c>
-      <c r="C13" s="85">
+      <c r="C13" s="79">
         <v>27000</v>
       </c>
-      <c r="D13" s="83"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="83">
+      <c r="D13" s="77"/>
+      <c r="E13" s="77"/>
+      <c r="F13" s="77">
         <v>0.05</v>
       </c>
-      <c r="G13" s="88">
+      <c r="G13" s="82">
         <v>1350</v>
       </c>
-      <c r="H13" s="88">
+      <c r="H13" s="82">
         <v>1350</v>
       </c>
       <c r="I13" s="10"/>
@@ -4686,24 +6505,24 @@
       <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="B14" s="84">
+      <c r="A14" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="78">
         <v>45905</v>
       </c>
-      <c r="C14" s="85">
+      <c r="C14" s="79">
         <v>27000</v>
       </c>
-      <c r="D14" s="83"/>
-      <c r="E14" s="83"/>
-      <c r="F14" s="83">
+      <c r="D14" s="77"/>
+      <c r="E14" s="77"/>
+      <c r="F14" s="77">
         <v>0.5</v>
       </c>
-      <c r="G14" s="88">
+      <c r="G14" s="82">
         <v>13500</v>
       </c>
-      <c r="H14" s="88">
+      <c r="H14" s="82">
         <v>12825</v>
       </c>
       <c r="I14" s="10"/>
@@ -4714,24 +6533,24 @@
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="83" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="84">
+      <c r="A15" s="77" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="78">
         <v>45910</v>
       </c>
-      <c r="C15" s="90">
+      <c r="C15" s="84">
         <v>17500</v>
       </c>
-      <c r="D15" s="83"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="83">
+      <c r="D15" s="77"/>
+      <c r="E15" s="77"/>
+      <c r="F15" s="77">
         <v>0.1</v>
       </c>
-      <c r="G15" s="88">
+      <c r="G15" s="82">
         <v>1750</v>
       </c>
-      <c r="H15" s="88">
+      <c r="H15" s="82">
         <v>1575</v>
       </c>
       <c r="I15" s="10"/>
@@ -4742,24 +6561,24 @@
       <c r="N15" s="6"/>
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="83" t="s">
+      <c r="A16" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="84">
+      <c r="B16" s="78">
         <v>45915</v>
       </c>
-      <c r="C16" s="85">
+      <c r="C16" s="79">
         <v>20000</v>
       </c>
-      <c r="D16" s="83"/>
-      <c r="E16" s="83"/>
-      <c r="F16" s="89">
+      <c r="D16" s="77"/>
+      <c r="E16" s="77"/>
+      <c r="F16" s="83">
         <v>0.1128</v>
       </c>
-      <c r="G16" s="88">
+      <c r="G16" s="82">
         <v>2256</v>
       </c>
-      <c r="H16" s="88">
+      <c r="H16" s="82">
         <v>2256</v>
       </c>
       <c r="I16" s="10"/>
@@ -4770,24 +6589,24 @@
       <c r="N16" s="6"/>
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="83" t="s">
-        <v>48</v>
-      </c>
-      <c r="B17" s="84">
+      <c r="A17" s="77" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17" s="78">
         <v>45912</v>
       </c>
-      <c r="C17" s="85">
+      <c r="C17" s="79">
         <v>1000</v>
       </c>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="89">
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+      <c r="F17" s="83">
         <v>0.36</v>
       </c>
-      <c r="G17" s="88">
+      <c r="G17" s="82">
         <v>360</v>
       </c>
-      <c r="H17" s="88">
+      <c r="H17" s="82">
         <v>324</v>
       </c>
       <c r="I17" s="10"/>
@@ -4798,24 +6617,24 @@
       <c r="N17" s="6"/>
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="B18" s="84">
+      <c r="A18" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" s="78">
         <v>45905</v>
       </c>
-      <c r="C18" s="85">
+      <c r="C18" s="79">
         <v>8000</v>
       </c>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83">
+      <c r="D18" s="77"/>
+      <c r="E18" s="77"/>
+      <c r="F18" s="77">
         <v>0.8</v>
       </c>
-      <c r="G18" s="88">
+      <c r="G18" s="82">
         <v>6400</v>
       </c>
-      <c r="H18" s="88">
+      <c r="H18" s="82">
         <v>5760</v>
       </c>
       <c r="I18" s="10"/>
@@ -4826,24 +6645,24 @@
       <c r="N18" s="6"/>
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="83" t="s">
+      <c r="A19" s="77" t="s">
         <v>23</v>
       </c>
-      <c r="B19" s="84">
+      <c r="B19" s="78">
         <v>45915</v>
       </c>
-      <c r="C19" s="85">
+      <c r="C19" s="79">
         <v>50000</v>
       </c>
-      <c r="D19" s="83"/>
-      <c r="E19" s="83"/>
-      <c r="F19" s="92">
+      <c r="D19" s="77"/>
+      <c r="E19" s="77"/>
+      <c r="F19" s="86">
         <v>0.13250000000000001</v>
       </c>
-      <c r="G19" s="88">
+      <c r="G19" s="82">
         <v>6625</v>
       </c>
-      <c r="H19" s="88">
+      <c r="H19" s="82">
         <v>5962.5</v>
       </c>
       <c r="I19" s="10"/>
@@ -4854,24 +6673,24 @@
       <c r="N19" s="6"/>
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="83" t="s">
+      <c r="A20" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="84">
+      <c r="B20" s="78">
         <v>45905</v>
       </c>
-      <c r="C20" s="91">
+      <c r="C20" s="85">
         <v>25000</v>
       </c>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="F20" s="92">
+      <c r="D20" s="77"/>
+      <c r="E20" s="77"/>
+      <c r="F20" s="86">
         <v>0.17169999999999999</v>
       </c>
-      <c r="G20" s="88">
+      <c r="G20" s="82">
         <v>4292.5</v>
       </c>
-      <c r="H20" s="88">
+      <c r="H20" s="82">
         <v>3863.25</v>
       </c>
       <c r="I20" s="10"/>
@@ -4901,31 +6720,31 @@
       <c r="N21" s="6"/>
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="83" t="s">
+      <c r="A22" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B22" s="84">
+      <c r="B22" s="78">
         <v>45903</v>
       </c>
-      <c r="C22" s="83">
+      <c r="C22" s="77">
         <v>5000</v>
       </c>
-      <c r="D22" s="83">
+      <c r="D22" s="77">
         <v>7.5</v>
       </c>
-      <c r="E22" s="88">
+      <c r="E22" s="82">
         <v>37583.06</v>
       </c>
-      <c r="F22" s="83">
+      <c r="F22" s="77">
         <v>8.3000000000000007</v>
       </c>
-      <c r="G22" s="88">
+      <c r="G22" s="82">
         <v>41408.080000000002</v>
       </c>
-      <c r="H22" s="88">
+      <c r="H22" s="82">
         <v>3825.02</v>
       </c>
-      <c r="I22" s="59"/>
+      <c r="I22" s="58"/>
       <c r="J22" s="7"/>
       <c r="K22" s="7"/>
       <c r="L22" s="15"/>
@@ -4933,31 +6752,31 @@
       <c r="N22" s="6"/>
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="84">
+      <c r="A23" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23" s="78">
         <v>45908</v>
       </c>
-      <c r="C23" s="83">
+      <c r="C23" s="77">
         <v>5000</v>
       </c>
-      <c r="D23" s="83">
+      <c r="D23" s="77">
         <v>24.1</v>
       </c>
-      <c r="E23" s="88">
+      <c r="E23" s="82">
         <v>120766.9</v>
       </c>
-      <c r="F23" s="83">
+      <c r="F23" s="77">
         <v>23.4</v>
       </c>
-      <c r="G23" s="88">
+      <c r="G23" s="82">
         <v>116740.86</v>
       </c>
-      <c r="H23" s="88">
+      <c r="H23" s="82">
         <v>-4026.04</v>
       </c>
-      <c r="I23" s="59"/>
+      <c r="I23" s="58"/>
       <c r="J23" s="7"/>
       <c r="K23" s="7"/>
       <c r="L23" s="15"/>
@@ -4965,31 +6784,31 @@
       <c r="N23" s="6"/>
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="B24" s="84">
+      <c r="A24" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" s="78">
         <v>45911</v>
       </c>
-      <c r="C24" s="83">
+      <c r="C24" s="77">
         <v>5000</v>
       </c>
-      <c r="D24" s="83">
+      <c r="D24" s="77">
         <v>23.2</v>
       </c>
-      <c r="E24" s="88">
+      <c r="E24" s="82">
         <v>116256.93</v>
       </c>
-      <c r="F24" s="83">
+      <c r="F24" s="77">
         <v>23.4</v>
       </c>
-      <c r="G24" s="88">
+      <c r="G24" s="82">
         <v>116740.86</v>
       </c>
-      <c r="H24" s="83">
+      <c r="H24" s="77">
         <v>483.93</v>
       </c>
-      <c r="I24" s="59"/>
+      <c r="I24" s="58"/>
       <c r="J24" s="7"/>
       <c r="K24" s="7"/>
       <c r="L24" s="15"/>
@@ -4997,31 +6816,31 @@
       <c r="N24" s="6"/>
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="83" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="84">
+      <c r="A25" s="77" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="78">
         <v>45915</v>
       </c>
-      <c r="C25" s="83">
+      <c r="C25" s="77">
         <v>4000</v>
       </c>
-      <c r="D25" s="83">
+      <c r="D25" s="77">
         <v>23.1</v>
       </c>
-      <c r="E25" s="88">
+      <c r="E25" s="82">
         <v>92604.66</v>
       </c>
-      <c r="F25" s="83">
+      <c r="F25" s="77">
         <v>25.75</v>
       </c>
-      <c r="G25" s="88">
+      <c r="G25" s="82">
         <v>102771.87</v>
       </c>
-      <c r="H25" s="88">
+      <c r="H25" s="82">
         <v>10167.209999999999</v>
       </c>
-      <c r="I25" s="59"/>
+      <c r="I25" s="58"/>
       <c r="J25" s="7"/>
       <c r="K25" s="7"/>
       <c r="L25" s="15"/>
@@ -5029,31 +6848,31 @@
       <c r="N25" s="6"/>
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="83" t="s">
+      <c r="A26" s="77" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="84">
+      <c r="B26" s="78">
         <v>45915</v>
       </c>
-      <c r="C26" s="83">
+      <c r="C26" s="77">
         <v>5000</v>
       </c>
-      <c r="D26" s="83">
+      <c r="D26" s="77">
         <v>8.8000000000000007</v>
       </c>
-      <c r="E26" s="88">
+      <c r="E26" s="82">
         <v>44097.46</v>
       </c>
-      <c r="F26" s="83">
+      <c r="F26" s="77">
         <v>9.6999999999999993</v>
       </c>
-      <c r="G26" s="88">
+      <c r="G26" s="82">
         <v>48392.57</v>
       </c>
-      <c r="H26" s="88">
+      <c r="H26" s="82">
         <v>4295.1099999999997</v>
       </c>
-      <c r="I26" s="59"/>
+      <c r="I26" s="58"/>
       <c r="J26" s="7"/>
       <c r="K26" s="7"/>
       <c r="L26" s="15"/>
@@ -5139,14 +6958,14 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H30" s="41">
         <f>H28+H29</f>
         <v>-393315.2</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J30" s="7">
         <v>-522636.73</v>
@@ -5186,13 +7005,13 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H32" s="35">
         <v>62010</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J32" s="7">
         <v>10130</v>
@@ -5259,13 +7078,13 @@
       <c r="E35" s="7"/>
       <c r="F35" s="10"/>
       <c r="G35" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H35" s="7">
         <v>57000</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J35" s="7">
         <v>57000</v>
@@ -5283,14 +7102,14 @@
       <c r="E36" s="14"/>
       <c r="F36" s="10"/>
       <c r="G36" s="38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H36" s="42">
         <f>H34+H35</f>
         <v>-794875.2</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J36" s="7">
         <v>-862186.73</v>
@@ -5305,7 +7124,7 @@
       <c r="M37" s="7"/>
     </row>
     <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="57" t="s">
+      <c r="A38" s="56" t="s">
         <v>20</v>
       </c>
       <c r="B38" s="28">
@@ -5318,14 +7137,14 @@
         <v>9</v>
       </c>
       <c r="E38" s="31"/>
-      <c r="F38" s="54">
+      <c r="F38" s="53">
         <v>3.9899999999999998E-2</v>
       </c>
       <c r="G38" s="31">
         <f>C38*F38</f>
         <v>957.59999999999991</v>
       </c>
-      <c r="H38" s="56">
+      <c r="H38" s="55">
         <f>G38*0.9</f>
         <v>861.83999999999992</v>
       </c>
@@ -5334,8 +7153,8 @@
       <c r="M38" s="15"/>
     </row>
     <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="57" t="s">
-        <v>54</v>
+      <c r="A39" s="56" t="s">
+        <v>53</v>
       </c>
       <c r="B39" s="28">
         <v>45530</v>
@@ -5384,7 +7203,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961B3AB4-C9A4-46F9-AED6-DC61A66CC09A}">
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -5440,7 +7259,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" s="28">
         <v>45897</v>
@@ -5452,7 +7271,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="81">
+      <c r="F2" s="75">
         <v>2.5</v>
       </c>
       <c r="G2" s="31">
@@ -5490,28 +7309,28 @@
       <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" s="84">
+      <c r="A4" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="B4" s="78">
         <v>45874</v>
       </c>
-      <c r="C4" s="85">
+      <c r="C4" s="79">
         <v>10000</v>
       </c>
-      <c r="D4" s="86">
+      <c r="D4" s="80">
         <v>1.88</v>
       </c>
-      <c r="E4" s="86">
+      <c r="E4" s="80">
         <v>18841.64</v>
       </c>
-      <c r="F4" s="86">
+      <c r="F4" s="80">
         <v>1.9</v>
       </c>
-      <c r="G4" s="86">
+      <c r="G4" s="80">
         <v>18957.919999999998</v>
       </c>
-      <c r="H4" s="86">
+      <c r="H4" s="80">
         <v>116.28</v>
       </c>
       <c r="I4" s="11"/>
@@ -5522,28 +7341,28 @@
       <c r="N4" s="6"/>
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="83" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="84">
+      <c r="A5" s="77" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="78">
         <v>45875</v>
       </c>
-      <c r="C5" s="85">
+      <c r="C5" s="79">
         <v>2800</v>
       </c>
-      <c r="D5" s="86">
+      <c r="D5" s="80">
         <v>10.5</v>
       </c>
-      <c r="E5" s="86">
+      <c r="E5" s="80">
         <v>29465.119999999999</v>
       </c>
-      <c r="F5" s="86">
+      <c r="F5" s="80">
         <v>11.6</v>
       </c>
-      <c r="G5" s="86">
+      <c r="G5" s="80">
         <v>32408.06</v>
       </c>
-      <c r="H5" s="86">
+      <c r="H5" s="80">
         <v>2942.94</v>
       </c>
       <c r="I5" s="11"/>
@@ -5554,28 +7373,28 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="83" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="84">
+      <c r="A6" s="77" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="78">
         <v>45875</v>
       </c>
-      <c r="C6" s="85">
+      <c r="C6" s="79">
         <v>5000</v>
       </c>
-      <c r="D6" s="86">
+      <c r="D6" s="80">
         <v>3.9</v>
       </c>
-      <c r="E6" s="86">
+      <c r="E6" s="80">
         <v>19543.2</v>
       </c>
-      <c r="F6" s="86">
+      <c r="F6" s="80">
         <v>4.5199999999999996</v>
       </c>
-      <c r="G6" s="86">
+      <c r="G6" s="80">
         <v>22549.95</v>
       </c>
-      <c r="H6" s="86">
+      <c r="H6" s="80">
         <v>3006.75</v>
       </c>
       <c r="I6" s="11"/>
@@ -5586,28 +7405,28 @@
       <c r="N6" s="6"/>
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="83" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="84">
+      <c r="A7" s="77" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="78">
         <v>45876</v>
       </c>
-      <c r="C7" s="85">
+      <c r="C7" s="79">
         <v>3200</v>
       </c>
-      <c r="D7" s="86">
+      <c r="D7" s="80">
         <v>9.25</v>
       </c>
-      <c r="E7" s="86">
+      <c r="E7" s="80">
         <v>29665.56</v>
       </c>
-      <c r="F7" s="86">
+      <c r="F7" s="80">
         <v>9.4</v>
       </c>
-      <c r="G7" s="86">
+      <c r="G7" s="80">
         <v>30013.37</v>
       </c>
-      <c r="H7" s="86">
+      <c r="H7" s="80">
         <v>347.81</v>
       </c>
       <c r="I7" s="11"/>
@@ -5618,28 +7437,28 @@
       <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="B8" s="84">
+      <c r="A8" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8" s="78">
         <v>45876</v>
       </c>
-      <c r="C8" s="85">
+      <c r="C8" s="79">
         <v>10000</v>
       </c>
-      <c r="D8" s="86">
+      <c r="D8" s="80">
         <v>1.85</v>
       </c>
-      <c r="E8" s="86">
+      <c r="E8" s="80">
         <v>18540.98</v>
       </c>
-      <c r="F8" s="86">
+      <c r="F8" s="80">
         <v>2.06</v>
       </c>
-      <c r="G8" s="86">
+      <c r="G8" s="80">
         <v>20554.38</v>
       </c>
-      <c r="H8" s="86">
+      <c r="H8" s="80">
         <v>2013.4</v>
       </c>
       <c r="I8" s="11"/>
@@ -5650,28 +7469,28 @@
       <c r="N8" s="6"/>
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="83" t="s">
+      <c r="A9" s="77" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="84">
+      <c r="B9" s="78">
         <v>45877</v>
       </c>
-      <c r="C9" s="85">
+      <c r="C9" s="79">
         <v>6000</v>
       </c>
-      <c r="D9" s="86">
+      <c r="D9" s="80">
         <v>6.1</v>
       </c>
-      <c r="E9" s="86">
+      <c r="E9" s="80">
         <v>36681.06</v>
       </c>
-      <c r="F9" s="86">
+      <c r="F9" s="80">
         <v>6.7</v>
       </c>
-      <c r="G9" s="86">
+      <c r="G9" s="80">
         <v>40110.97</v>
       </c>
-      <c r="H9" s="86">
+      <c r="H9" s="80">
         <v>3429.91</v>
       </c>
       <c r="I9" s="11"/>
@@ -5682,31 +7501,31 @@
       <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="83" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="84">
+      <c r="A10" s="77" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="78">
         <v>45877</v>
       </c>
-      <c r="C10" s="85">
+      <c r="C10" s="79">
         <v>3000</v>
       </c>
-      <c r="D10" s="86">
+      <c r="D10" s="80">
         <v>27.75</v>
       </c>
-      <c r="E10" s="86">
+      <c r="E10" s="80">
         <v>83434.39</v>
       </c>
-      <c r="F10" s="86">
+      <c r="F10" s="80">
         <v>31</v>
       </c>
-      <c r="G10" s="86">
+      <c r="G10" s="80">
         <v>92794.01</v>
       </c>
-      <c r="H10" s="86">
+      <c r="H10" s="80">
         <v>9359.6200000000008</v>
       </c>
-      <c r="I10" s="82"/>
+      <c r="I10" s="76"/>
       <c r="J10" s="7"/>
       <c r="K10" s="7"/>
       <c r="L10" s="15"/>
@@ -5714,28 +7533,28 @@
       <c r="N10" s="6"/>
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="B11" s="84">
+      <c r="A11" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="78">
         <v>45889</v>
       </c>
-      <c r="C11" s="85">
+      <c r="C11" s="79">
         <v>4000</v>
       </c>
-      <c r="D11" s="86">
+      <c r="D11" s="80">
         <v>24.1</v>
       </c>
-      <c r="E11" s="86">
+      <c r="E11" s="80">
         <v>96613.52</v>
       </c>
-      <c r="F11" s="86">
+      <c r="F11" s="80">
         <v>24.3</v>
       </c>
-      <c r="G11" s="86">
+      <c r="G11" s="80">
         <v>96984.72</v>
       </c>
-      <c r="H11" s="86">
+      <c r="H11" s="80">
         <v>371.2</v>
       </c>
       <c r="J11" s="7"/>
@@ -5745,28 +7564,28 @@
       <c r="N11" s="6"/>
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="B12" s="84">
+      <c r="A12" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B12" s="78">
         <v>45890</v>
       </c>
-      <c r="C12" s="85">
+      <c r="C12" s="79">
         <v>4000</v>
       </c>
-      <c r="D12" s="86">
+      <c r="D12" s="80">
         <v>24.1</v>
       </c>
-      <c r="E12" s="86">
+      <c r="E12" s="80">
         <v>96613.52</v>
       </c>
-      <c r="F12" s="86">
+      <c r="F12" s="80">
         <v>24.3</v>
       </c>
-      <c r="G12" s="86">
+      <c r="G12" s="80">
         <v>96984.72</v>
       </c>
-      <c r="H12" s="86">
+      <c r="H12" s="80">
         <v>371.2</v>
       </c>
       <c r="J12" s="7"/>
@@ -5776,28 +7595,28 @@
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="83" t="s">
-        <v>65</v>
-      </c>
-      <c r="B13" s="84">
+      <c r="A13" s="77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="78">
         <v>45891</v>
       </c>
-      <c r="C13" s="85">
+      <c r="C13" s="79">
         <v>5000</v>
       </c>
-      <c r="D13" s="86">
+      <c r="D13" s="80">
         <v>24.1</v>
       </c>
-      <c r="E13" s="86">
+      <c r="E13" s="80">
         <v>120766.9</v>
       </c>
-      <c r="F13" s="86">
+      <c r="F13" s="80">
         <v>24.3</v>
       </c>
-      <c r="G13" s="86">
+      <c r="G13" s="80">
         <v>121230.88</v>
       </c>
-      <c r="H13" s="86">
+      <c r="H13" s="80">
         <v>463.98</v>
       </c>
       <c r="J13" s="7"/>
@@ -5807,28 +7626,28 @@
       <c r="N13" s="6"/>
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="83" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="84">
+      <c r="A14" s="77" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="78">
         <v>45896</v>
       </c>
-      <c r="C14" s="85">
+      <c r="C14" s="79">
         <v>6000</v>
       </c>
-      <c r="D14" s="86">
+      <c r="D14" s="80">
         <v>7.3</v>
       </c>
-      <c r="E14" s="86">
+      <c r="E14" s="80">
         <v>43897.02</v>
       </c>
-      <c r="F14" s="86">
+      <c r="F14" s="80">
         <v>8.4</v>
       </c>
-      <c r="G14" s="86">
+      <c r="G14" s="80">
         <v>50288.37</v>
       </c>
-      <c r="H14" s="86">
+      <c r="H14" s="80">
         <v>6391.35</v>
       </c>
       <c r="J14" s="7"/>
@@ -5838,31 +7657,31 @@
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="B15" s="84">
+      <c r="A15" s="77" t="s">
+        <v>43</v>
+      </c>
+      <c r="B15" s="78">
         <v>45897</v>
       </c>
-      <c r="C15" s="85">
+      <c r="C15" s="79">
         <v>5000</v>
       </c>
-      <c r="D15" s="86">
+      <c r="D15" s="80">
         <v>2.2000000000000002</v>
       </c>
-      <c r="E15" s="86">
+      <c r="E15" s="80">
         <v>11024.36</v>
       </c>
-      <c r="F15" s="86">
+      <c r="F15" s="80">
         <v>2.2999999999999998</v>
       </c>
-      <c r="G15" s="86">
+      <c r="G15" s="80">
         <v>11474.52</v>
       </c>
-      <c r="H15" s="86">
+      <c r="H15" s="80">
         <v>450.16</v>
       </c>
-      <c r="I15" s="87"/>
+      <c r="I15" s="81"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7"/>
       <c r="L15" s="15"/>
@@ -5947,14 +7766,14 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" s="41">
         <f>H17+H18</f>
         <v>-522636.73</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J19" s="7">
         <v>-553251.32999999996</v>
@@ -5994,13 +7813,13 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H21" s="35">
         <v>10130</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J21" s="7">
         <v>8610</v>
@@ -6067,13 +7886,13 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H24" s="7">
         <v>57000</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J24" s="7">
         <v>57000</v>
@@ -6091,14 +7910,14 @@
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
       <c r="G25" s="38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H25" s="42">
         <f>H23+H24</f>
         <v>-862186.73</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J25" s="7">
         <v>-882671.33</v>
@@ -6137,7 +7956,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7193655-9E82-4E5C-9879-086AA4339AB9}">
   <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -6243,7 +8062,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="28">
         <v>45868</v>
@@ -6309,7 +8128,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A6" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B6" s="28">
         <v>45867</v>
@@ -6342,7 +8161,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A7" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" s="28">
         <v>45862</v>
@@ -6375,7 +8194,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A8" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B8" s="28">
         <v>45856</v>
@@ -6408,7 +8227,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A9" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="28">
         <v>45854</v>
@@ -6441,7 +8260,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A10" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="28">
         <v>45841</v>
@@ -6474,7 +8293,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A11" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="28">
         <v>45841</v>
@@ -6507,7 +8326,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A12" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B12" s="28">
         <v>45840</v>
@@ -6616,14 +8435,14 @@
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H16" s="34">
         <f>H14+H15</f>
         <v>-553251.32999999996</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J16" s="7">
         <v>-187350.93</v>
@@ -6663,13 +8482,13 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="H18" s="35">
         <v>8610</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J18" s="7">
         <v>41150</v>
@@ -6736,13 +8555,13 @@
       <c r="E21" s="7"/>
       <c r="F21" s="10"/>
       <c r="G21" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H21" s="38">
         <v>57000</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J21" s="7">
         <v>57000</v>
@@ -6760,14 +8579,14 @@
       <c r="E22" s="14"/>
       <c r="F22" s="10"/>
       <c r="G22" s="38" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H22" s="39">
         <f>H20+H21</f>
         <v>-882671.33</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J22" s="7">
         <v>-508160.92999999993</v>
@@ -6809,1622 +8628,4 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAFE1F0-60EA-46C8-9C11-E7180F21BFAA}">
-  <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45812</v>
-      </c>
-      <c r="C2" s="29">
-        <v>55000</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="37">
-        <v>0.2505</v>
-      </c>
-      <c r="G2" s="31">
-        <f t="shared" ref="G2:G9" si="0">C2*F2</f>
-        <v>13777.5</v>
-      </c>
-      <c r="H2" s="40">
-        <f t="shared" ref="H2:H7" si="1">G2*0.9</f>
-        <v>12399.75</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="28">
-        <v>45814</v>
-      </c>
-      <c r="C3" s="29">
-        <v>12500</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="54">
-        <v>0.215</v>
-      </c>
-      <c r="G3" s="31">
-        <f t="shared" si="0"/>
-        <v>2687.5</v>
-      </c>
-      <c r="H3" s="40">
-        <f t="shared" si="1"/>
-        <v>2418.75</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45814</v>
-      </c>
-      <c r="C4" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="37">
-        <v>0.1915</v>
-      </c>
-      <c r="G4" s="31">
-        <f t="shared" si="0"/>
-        <v>3830</v>
-      </c>
-      <c r="H4" s="40">
-        <f t="shared" si="1"/>
-        <v>3447</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45817</v>
-      </c>
-      <c r="C5" s="29">
-        <v>40000</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="37">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="G5" s="31">
-        <f t="shared" si="0"/>
-        <v>8888</v>
-      </c>
-      <c r="H5" s="40">
-        <f t="shared" si="1"/>
-        <v>7999.2</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45820</v>
-      </c>
-      <c r="C6" s="29">
-        <v>75000</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="55">
-        <v>0.19839999999999999</v>
-      </c>
-      <c r="G6" s="31">
-        <f t="shared" si="0"/>
-        <v>14880</v>
-      </c>
-      <c r="H6" s="40">
-        <f t="shared" si="1"/>
-        <v>13392</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B7" s="28">
-        <v>45820</v>
-      </c>
-      <c r="C7" s="29">
-        <v>7200</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="54">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G7" s="31">
-        <f t="shared" si="0"/>
-        <v>1260</v>
-      </c>
-      <c r="H7" s="40">
-        <f t="shared" si="1"/>
-        <v>1134</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="28">
-        <v>45824</v>
-      </c>
-      <c r="C8" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="55">
-        <v>0.1176</v>
-      </c>
-      <c r="G8" s="31">
-        <f t="shared" si="0"/>
-        <v>2352</v>
-      </c>
-      <c r="H8" s="40">
-        <f>G8</f>
-        <v>2352</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="28">
-        <v>45833</v>
-      </c>
-      <c r="C9" s="29">
-        <v>60000</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="54">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="G9" s="31">
-        <f t="shared" si="0"/>
-        <v>7950</v>
-      </c>
-      <c r="H9" s="40">
-        <f>G9*0.9</f>
-        <v>7155</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="27"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="43">
-        <f>SUM(H2:H9)</f>
-        <v>50297.7</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11" s="28">
-        <v>45824</v>
-      </c>
-      <c r="C11" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D11" s="30">
-        <v>67</v>
-      </c>
-      <c r="E11" s="53">
-        <v>67148.399999999994</v>
-      </c>
-      <c r="F11" s="30">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="G11" s="31">
-        <v>16563.23</v>
-      </c>
-      <c r="H11" s="32">
-        <f t="shared" ref="H11:H12" si="2">G11-E11</f>
-        <v>-50585.17</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B12" s="28">
-        <v>45826</v>
-      </c>
-      <c r="C12" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="30">
-        <v>67</v>
-      </c>
-      <c r="E12" s="53">
-        <v>67148.399999999994</v>
-      </c>
-      <c r="F12" s="30">
-        <v>16.8</v>
-      </c>
-      <c r="G12" s="31">
-        <v>16762.79</v>
-      </c>
-      <c r="H12" s="32">
-        <f t="shared" si="2"/>
-        <v>-50385.609999999993</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="28">
-        <v>45828</v>
-      </c>
-      <c r="C13" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D13" s="30">
-        <v>67</v>
-      </c>
-      <c r="E13" s="53">
-        <v>67148.399999999994</v>
-      </c>
-      <c r="F13" s="30">
-        <v>16.8</v>
-      </c>
-      <c r="G13" s="31">
-        <v>16762.79</v>
-      </c>
-      <c r="H13" s="32">
-        <f t="shared" ref="H13" si="3">G13-E13</f>
-        <v>-50385.609999999993</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="26"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32">
-        <f>SUM(E13:E13)</f>
-        <v>67148.399999999994</v>
-      </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="32">
-        <f>SUM(G13:G13)</f>
-        <v>16762.79</v>
-      </c>
-      <c r="H14" s="41">
-        <f>SUM(H11:H13)</f>
-        <v>-151356.38999999998</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="26"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="43">
-        <f>H10+H14</f>
-        <v>-101058.68999999999</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="7">
-        <v>76255.710000000021</v>
-      </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="32">
-        <v>-86292.24</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="7">
-        <v>-162547.95474799996</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H17" s="34">
-        <f>H15+H16</f>
-        <v>-187350.93</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J17" s="7">
-        <v>-86292.244747999939</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="35">
-        <v>336660</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="7">
-        <v>327260</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="26"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="H19" s="35">
-        <v>41150</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J19" s="7">
-        <v>9400</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="41">
-        <f>H18+H19</f>
-        <v>377810</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20" s="7">
-        <v>336660</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A21" s="5"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="46">
-        <f>H17-H20</f>
-        <v>-565160.92999999993</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="7">
-        <v>-422952.24474799994</v>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A22" s="5"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="38">
-        <v>57000</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A23" s="6"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H23" s="39">
-        <f>H21+H22</f>
-        <v>-508160.92999999993</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J23" s="7">
-        <v>-365952.24474799994</v>
-      </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="7"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="I24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="N24" s="13"/>
-    </row>
-    <row r="25" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K26" s="7"/>
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M28" s="7"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K29" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N9">
-    <sortCondition ref="B2:B9"/>
-    <sortCondition ref="A2:A9"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E1A231-79A5-4BE4-8C0C-F5E13A4831EB}">
-  <dimension ref="A1:N35"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="80" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.75" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.125" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="77" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="76"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B2" s="78">
-        <v>45784</v>
-      </c>
-      <c r="C2" s="29">
-        <v>81000</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="55">
-        <v>0.5</v>
-      </c>
-      <c r="G2" s="31">
-        <f t="shared" ref="G2:G13" si="0">C2*F2</f>
-        <v>40500</v>
-      </c>
-      <c r="H2" s="40">
-        <v>40500</v>
-      </c>
-      <c r="I2" s="13"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="78">
-        <v>45785</v>
-      </c>
-      <c r="C3" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="37">
-        <v>1</v>
-      </c>
-      <c r="G3" s="31">
-        <f t="shared" si="0"/>
-        <v>10000</v>
-      </c>
-      <c r="H3" s="40">
-        <v>9000</v>
-      </c>
-      <c r="I3" s="13"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="78">
-        <v>45786</v>
-      </c>
-      <c r="C4" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="54">
-        <v>0.6</v>
-      </c>
-      <c r="G4" s="31">
-        <f t="shared" si="0"/>
-        <v>6000</v>
-      </c>
-      <c r="H4" s="40">
-        <v>5540</v>
-      </c>
-      <c r="I4" s="13"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B5" s="78">
-        <v>45786</v>
-      </c>
-      <c r="C5" s="29">
-        <v>27000</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="55">
-        <v>0.31</v>
-      </c>
-      <c r="G5" s="31">
-        <f t="shared" si="0"/>
-        <v>8370</v>
-      </c>
-      <c r="H5" s="40">
-        <v>8370</v>
-      </c>
-      <c r="I5" s="13"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="78">
-        <v>45791</v>
-      </c>
-      <c r="C6" s="29">
-        <v>15000</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="55">
-        <v>0.34</v>
-      </c>
-      <c r="G6" s="31">
-        <f t="shared" si="0"/>
-        <v>5100</v>
-      </c>
-      <c r="H6" s="40">
-        <v>4590</v>
-      </c>
-      <c r="I6" s="13"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="78">
-        <v>45793</v>
-      </c>
-      <c r="C7" s="29">
-        <v>3600</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="51">
-        <v>0.25</v>
-      </c>
-      <c r="G7" s="31">
-        <f t="shared" si="0"/>
-        <v>900</v>
-      </c>
-      <c r="H7" s="40">
-        <v>810</v>
-      </c>
-      <c r="I7" s="13"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="78">
-        <v>45793</v>
-      </c>
-      <c r="C8" s="29">
-        <v>27000</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="52">
-        <v>1.5</v>
-      </c>
-      <c r="G8" s="31">
-        <f t="shared" si="0"/>
-        <v>40500</v>
-      </c>
-      <c r="H8" s="40">
-        <v>38340</v>
-      </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B9" s="78">
-        <v>45793</v>
-      </c>
-      <c r="C9" s="29">
-        <v>8000</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="75">
-        <v>0.93</v>
-      </c>
-      <c r="G9" s="31">
-        <f t="shared" si="0"/>
-        <v>7440</v>
-      </c>
-      <c r="H9" s="40">
-        <v>6696</v>
-      </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="78">
-        <v>45797</v>
-      </c>
-      <c r="C10" s="29">
-        <v>30000</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" s="51">
-        <v>0.08</v>
-      </c>
-      <c r="G10" s="31">
-        <f t="shared" si="0"/>
-        <v>2400</v>
-      </c>
-      <c r="H10" s="40">
-        <v>2160</v>
-      </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B11" s="78">
-        <v>45800</v>
-      </c>
-      <c r="C11" s="29">
-        <v>1200</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" s="54">
-        <v>0.48</v>
-      </c>
-      <c r="G11" s="31">
-        <f t="shared" si="0"/>
-        <v>576</v>
-      </c>
-      <c r="H11" s="40">
-        <v>520.79999999999995</v>
-      </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="78">
-        <v>45800</v>
-      </c>
-      <c r="C12" s="29">
-        <v>4000</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F12" s="55">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="G12" s="31">
-        <f t="shared" si="0"/>
-        <v>1120</v>
-      </c>
-      <c r="H12" s="40">
-        <v>1008</v>
-      </c>
-      <c r="I12" s="13"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="78">
-        <v>45800</v>
-      </c>
-      <c r="C13" s="29">
-        <v>7200</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F13" s="37">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G13" s="31">
-        <f t="shared" si="0"/>
-        <v>1260</v>
-      </c>
-      <c r="H13" s="40">
-        <v>1134</v>
-      </c>
-      <c r="I13" s="13"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="6"/>
-      <c r="M13" s="6"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="27" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="78">
-        <v>45800</v>
-      </c>
-      <c r="C14" s="29">
-        <v>105000</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F14" s="54">
-        <v>0.111238</v>
-      </c>
-      <c r="G14" s="31">
-        <v>11676</v>
-      </c>
-      <c r="H14" s="40">
-        <v>10612.21</v>
-      </c>
-      <c r="I14" s="13"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="6"/>
-      <c r="M14" s="6"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="B15" s="78">
-        <v>45800</v>
-      </c>
-      <c r="C15" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F15" s="54">
-        <v>0.27</v>
-      </c>
-      <c r="G15" s="31">
-        <f>C15*F15</f>
-        <v>270</v>
-      </c>
-      <c r="H15" s="40">
-        <v>243</v>
-      </c>
-      <c r="I15" s="13"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="6"/>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="78">
-        <v>45805</v>
-      </c>
-      <c r="C16" s="29">
-        <v>9000</v>
-      </c>
-      <c r="D16" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F16" s="55">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="G16" s="31">
-        <f>C16*F16</f>
-        <v>675</v>
-      </c>
-      <c r="H16" s="40">
-        <v>607.5</v>
-      </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="6"/>
-      <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B17" s="78">
-        <v>45806</v>
-      </c>
-      <c r="C17" s="29">
-        <v>6800</v>
-      </c>
-      <c r="D17" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F17" s="37">
-        <v>0.23</v>
-      </c>
-      <c r="G17" s="31">
-        <f>C17*F17</f>
-        <v>1564</v>
-      </c>
-      <c r="H17" s="40">
-        <v>1407.6000000000001</v>
-      </c>
-      <c r="I17" s="13"/>
-      <c r="J17" s="17"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="6"/>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="27"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="34">
-        <f>SUM(H2:H17)</f>
-        <v>131539.11000000002</v>
-      </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="6"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="79">
-        <v>45792</v>
-      </c>
-      <c r="C19" s="29">
-        <v>30000</v>
-      </c>
-      <c r="D19" s="30">
-        <v>3.8</v>
-      </c>
-      <c r="E19" s="31">
-        <v>114252.5</v>
-      </c>
-      <c r="F19" s="30">
-        <v>1.97</v>
-      </c>
-      <c r="G19" s="31">
-        <v>58969.1</v>
-      </c>
-      <c r="H19" s="32">
-        <f>G19-E19</f>
-        <v>-55283.4</v>
-      </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="26"/>
-      <c r="B20" s="79"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32">
-        <f>SUM(E19:E19)</f>
-        <v>114252.5</v>
-      </c>
-      <c r="F20" s="30"/>
-      <c r="G20" s="32">
-        <f>SUM(G19:G19)</f>
-        <v>58969.1</v>
-      </c>
-      <c r="H20" s="44">
-        <f>SUM(H19:H19)</f>
-        <v>-55283.4</v>
-      </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A21" s="26"/>
-      <c r="B21" s="79"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H21" s="34">
-        <f>H18+H20</f>
-        <v>76255.710000000021</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J21" s="7">
-        <v>-39964.590000000004</v>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A22" s="26"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H22" s="34">
-        <v>-162547.95474799996</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="7">
-        <v>-122583.36474799996</v>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A23" s="26"/>
-      <c r="B23" s="79"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H23" s="34">
-        <f>H21+H22</f>
-        <v>-86292.244747999939</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J23" s="7">
-        <v>-162547.95474799996</v>
-      </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A24" s="26"/>
-      <c r="B24" s="79"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="30"/>
-      <c r="G24" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H24" s="7">
-        <v>327260</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J24" s="7">
-        <v>281390</v>
-      </c>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A25" s="26"/>
-      <c r="B25" s="79"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="32" t="s">
-        <v>49</v>
-      </c>
-      <c r="H25" s="35">
-        <v>9400</v>
-      </c>
-      <c r="I25" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="7">
-        <v>45870</v>
-      </c>
-      <c r="K25" s="7"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A26" s="26"/>
-      <c r="B26" s="79"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" s="41">
-        <f>H24+H25</f>
-        <v>336660</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J26" s="7">
-        <v>327260</v>
-      </c>
-      <c r="K26" s="7"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A27" s="5"/>
-      <c r="B27" s="80"/>
-      <c r="C27" s="8"/>
-      <c r="D27" s="9"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H27" s="46">
-        <f>H23-H26</f>
-        <v>-422952.24474799994</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J27" s="7">
-        <v>-489807.95474799996</v>
-      </c>
-      <c r="K27" s="7"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-      <c r="N27" s="6"/>
-    </row>
-    <row r="28" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A28" s="5"/>
-      <c r="B28" s="80"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="9"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H28" s="38">
-        <v>57000</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="J28" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K28" s="7"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="6"/>
-    </row>
-    <row r="29" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A29" s="6"/>
-      <c r="B29" s="80"/>
-      <c r="C29" s="8"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="38" t="s">
-        <v>33</v>
-      </c>
-      <c r="H29" s="39">
-        <f>H27+H28</f>
-        <v>-365952.24474799994</v>
-      </c>
-      <c r="I29" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="J29" s="7">
-        <v>-432807.95474799996</v>
-      </c>
-      <c r="K29" s="7"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-      <c r="N29" s="7"/>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K30" s="7"/>
-      <c r="N30" s="13"/>
-    </row>
-    <row r="31" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K31" s="7"/>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K32" s="7"/>
-      <c r="M32" s="7"/>
-    </row>
-    <row r="33" spans="11:13" x14ac:dyDescent="0.3">
-      <c r="M33" s="7"/>
-    </row>
-    <row r="34" spans="11:13" x14ac:dyDescent="0.3">
-      <c r="M34" s="7"/>
-    </row>
-    <row r="35" spans="11:13" x14ac:dyDescent="0.3">
-      <c r="K35" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N17">
-    <sortCondition ref="B2:B17"/>
-    <sortCondition ref="A2:A17"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6899" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{457695F4-4130-44A4-80DD-C52E19936C02}"/>
+  <xr:revisionPtr revIDLastSave="6900" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6FF506A-322B-47A4-B1A2-25325FB798D3}"/>
   <bookViews>
-    <workbookView xWindow="5976" yWindow="0" windowWidth="17064" windowHeight="12336" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7296" yWindow="864" windowWidth="15288" windowHeight="11364" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MAR26" sheetId="95" r:id="rId1"/>
@@ -265,7 +265,7 @@
     <numFmt numFmtId="191" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="192" formatCode="yyyy/mm/dd;@"/>
     <numFmt numFmtId="193" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="195" formatCode="0.000000"/>
+    <numFmt numFmtId="194" formatCode="0.000000"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -590,13 +590,13 @@
     </xf>
     <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="195" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="194" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="195" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="195" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="194" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="193" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -616,6 +616,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1496,7 +1500,7 @@
         <v>24</v>
       </c>
       <c r="H19" s="35">
-        <v>19500</v>
+        <v>26910</v>
       </c>
       <c r="I19" s="35" t="s">
         <v>17</v>
@@ -1518,7 +1522,7 @@
       </c>
       <c r="H20" s="41">
         <f>H18+H19</f>
-        <v>90760</v>
+        <v>98170</v>
       </c>
       <c r="I20" s="35" t="s">
         <v>14</v>
@@ -1540,7 +1544,7 @@
       </c>
       <c r="H21" s="94">
         <f>H17-H20</f>
-        <v>-345292.66599999997</v>
+        <v>-352702.66599999997</v>
       </c>
       <c r="I21" s="35" t="s">
         <v>15</v>
@@ -1583,7 +1587,7 @@
       </c>
       <c r="H23" s="41">
         <f>H21+H22</f>
-        <v>-285292.66599999997</v>
+        <v>-292702.66599999997</v>
       </c>
       <c r="I23" s="96" t="s">
         <v>32</v>
@@ -1637,7 +1641,7 @@
       </c>
       <c r="H26" s="32">
         <f>H25-H20</f>
-        <v>-18883.58600000001</v>
+        <v>-26293.58600000001</v>
       </c>
       <c r="I26" s="96"/>
       <c r="J26" s="32"/>

--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6900" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6FF506A-322B-47A4-B1A2-25325FB798D3}"/>
+  <xr:revisionPtr revIDLastSave="6937" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ACB508E-7D19-423E-A7C2-E8E031655DCE}"/>
   <bookViews>
-    <workbookView xWindow="7296" yWindow="864" windowWidth="15288" windowHeight="11364" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5748" yWindow="1104" windowWidth="17292" windowHeight="10764" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="MAR26" sheetId="95" r:id="rId1"/>
-    <sheet name="FEB26" sheetId="94" r:id="rId2"/>
-    <sheet name="JAN26" sheetId="93" r:id="rId3"/>
-    <sheet name="DEC25" sheetId="92" r:id="rId4"/>
-    <sheet name="NOV25" sheetId="91" r:id="rId5"/>
-    <sheet name="OCT25" sheetId="90" r:id="rId6"/>
-    <sheet name="SEP25" sheetId="89" r:id="rId7"/>
-    <sheet name="AUG25" sheetId="88" r:id="rId8"/>
-    <sheet name="JUL25" sheetId="87" r:id="rId9"/>
-    <sheet name="JUN25" sheetId="86" r:id="rId10"/>
-    <sheet name="MAY25" sheetId="85" r:id="rId11"/>
-    <sheet name="APR25" sheetId="84" r:id="rId12"/>
+    <sheet name="APR26" sheetId="96" r:id="rId1"/>
+    <sheet name="MAR26" sheetId="95" r:id="rId2"/>
+    <sheet name="FEB26" sheetId="94" r:id="rId3"/>
+    <sheet name="JAN26" sheetId="93" r:id="rId4"/>
+    <sheet name="DEC25" sheetId="92" r:id="rId5"/>
+    <sheet name="NOV25" sheetId="91" r:id="rId6"/>
+    <sheet name="OCT25" sheetId="90" r:id="rId7"/>
+    <sheet name="SEP25" sheetId="89" r:id="rId8"/>
+    <sheet name="AUG25" sheetId="88" r:id="rId9"/>
+    <sheet name="JUL25" sheetId="87" r:id="rId10"/>
+    <sheet name="JUN25" sheetId="86" r:id="rId11"/>
+    <sheet name="MAY25" sheetId="85" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="69">
   <si>
     <t>Name</t>
   </si>
@@ -122,9 +122,6 @@
   </si>
   <si>
     <t>March Exp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCC </t>
   </si>
   <si>
     <t>PTTGC</t>
@@ -252,20 +249,26 @@
   <si>
     <t>C/F Div - C/F Exp</t>
   </si>
+  <si>
+    <t xml:space="preserve">PTT </t>
+  </si>
+  <si>
+    <t>Dummy</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="8">
-    <numFmt numFmtId="187" formatCode="0.000"/>
-    <numFmt numFmtId="188" formatCode="\฿#,##0.00"/>
-    <numFmt numFmtId="189" formatCode="&quot;฿&quot;#,##0.00"/>
-    <numFmt numFmtId="190" formatCode="0.0000"/>
-    <numFmt numFmtId="191" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="192" formatCode="yyyy/mm/dd;@"/>
-    <numFmt numFmtId="193" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="194" formatCode="0.000000"/>
+    <numFmt numFmtId="164" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="\฿#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="&quot;฿&quot;#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="169" formatCode="yyyy/mm/dd;@"/>
+    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="171" formatCode="0.000000"/>
   </numFmts>
   <fonts count="24" x14ac:knownFonts="1">
     <font>
@@ -343,14 +346,14 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -369,20 +372,20 @@
     <font>
       <sz val="12"/>
       <color rgb="FF333333"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -393,21 +396,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF00B050"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FFFF0000"/>
-      <name val="Tahoma"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -459,16 +462,16 @@
   <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="188" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -476,24 +479,24 @@
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="189" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="191" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -501,36 +504,36 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="191" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="188" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="187" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="190" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="4" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -541,24 +544,24 @@
     <xf numFmtId="4" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="188" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="188" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="188" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="190" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="192" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="191" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="190" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="167" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -569,10 +572,10 @@
     <xf numFmtId="3" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="193" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="193" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -590,17 +593,17 @@
     </xf>
     <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="194" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="194" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="194" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="189" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="193" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,10 +619,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -969,29 +968,464 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6E9199-1687-4EE7-A0F3-54DE6332B9D4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DFDC5F2-0211-490B-8DD7-A2B28B5D4706}">
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+    </row>
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="28">
+        <v>46136</v>
+      </c>
+      <c r="C2" s="29">
+        <v>6000</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>3000</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2*0.9</f>
+        <v>2700</v>
+      </c>
+      <c r="I2" s="17"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="28">
+        <v>46140</v>
+      </c>
+      <c r="C3" s="29">
+        <v>7500</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="37">
+        <v>1.4</v>
+      </c>
+      <c r="G3" s="31">
+        <f>C3*F3</f>
+        <v>10500</v>
+      </c>
+      <c r="H3" s="32">
+        <v>9472.5</v>
+      </c>
+      <c r="I3" s="17"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="34">
+        <f>SUM(H2:H3)</f>
+        <v>12172.5</v>
+      </c>
+      <c r="I4" s="19"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" s="28">
+        <v>45757</v>
+      </c>
+      <c r="C5" s="29">
+        <v>0</v>
+      </c>
+      <c r="D5" s="30">
+        <v>61.5</v>
+      </c>
+      <c r="E5" s="31">
+        <v>61636.22</v>
+      </c>
+      <c r="F5" s="30">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="G5" s="31">
+        <v>16563.23</v>
+      </c>
+      <c r="H5" s="49">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32">
+        <f>SUM(E5:E5)</f>
+        <v>61636.22</v>
+      </c>
+      <c r="F6" s="30"/>
+      <c r="G6" s="32">
+        <f>SUM(G5:G5)</f>
+        <v>16563.23</v>
+      </c>
+      <c r="H6" s="34">
+        <f>SUM(H5:H5)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="34">
+        <f>H4+H6</f>
+        <v>12172.5</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="34">
+        <v>-243272.66599999997</v>
+      </c>
+      <c r="K7" s="15"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="7">
+        <v>-254532.66599999997</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="32">
+        <v>-11260</v>
+      </c>
+      <c r="K8" s="15"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="34">
+        <f>H7+H8</f>
+        <v>-242360.16599999997</v>
+      </c>
+      <c r="I9" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="41">
+        <v>-254532.66599999997</v>
+      </c>
+      <c r="K9" s="15"/>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="7">
+        <v>98300</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="35">
+        <v>71260</v>
+      </c>
+      <c r="K10" s="15"/>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="35">
+        <v>28860</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="35">
+        <v>26910</v>
+      </c>
+      <c r="K11" s="15"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="34">
+        <f>H10+H11</f>
+        <v>127160</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="41">
+        <v>98300</v>
+      </c>
+      <c r="K12" s="15"/>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="45">
+        <f>H9-H12</f>
+        <v>-369520.16599999997</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="45">
+        <f>J9-J12</f>
+        <v>-352832.66599999997</v>
+      </c>
+      <c r="K13" s="15"/>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="5"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="38">
+        <v>60000</v>
+      </c>
+      <c r="I14" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="97">
+        <v>60000</v>
+      </c>
+      <c r="K14" s="15"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="6"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="39">
+        <f>H13+H14</f>
+        <v>-309520.16599999997</v>
+      </c>
+      <c r="I15" s="62" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="41">
+        <f>J13+J14</f>
+        <v>-292832.66599999997</v>
+      </c>
+      <c r="K15" s="15"/>
+      <c r="L15" s="7"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G16" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="32">
+        <v>71876.41399999999</v>
+      </c>
+      <c r="J16" s="7"/>
+      <c r="L16" s="13"/>
+    </row>
+    <row r="17" spans="7:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G17" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="32">
+        <f>H16+H4</f>
+        <v>84048.91399999999</v>
+      </c>
+      <c r="J17" s="7"/>
+    </row>
+    <row r="18" spans="7:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G18" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="32">
+        <f>H17-H12</f>
+        <v>-43111.08600000001</v>
+      </c>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="J21" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7193655-9E82-4E5C-9879-086AA4339AB9}">
   <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.625" style="12" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="93" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="14.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" style="6" customWidth="1"/>
     <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
     <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10" style="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="8.625" style="6"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1007,7 +1441,7 @@
       <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="89" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="24" t="s">
@@ -1016,645 +1450,634 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="B2" s="28">
-        <v>46085</v>
+        <v>44736</v>
       </c>
       <c r="C2" s="29">
-        <v>120000</v>
+        <v>40000</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="31" t="s">
+      <c r="E2" s="31"/>
+      <c r="F2" s="37">
+        <v>0.15559999999999999</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>6223.9999999999991</v>
+      </c>
+      <c r="H2" s="32">
+        <v>0</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="34">
+        <f>SUM(H2:H2)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45868</v>
+      </c>
+      <c r="C4" s="29">
+        <v>1800</v>
+      </c>
+      <c r="D4" s="30">
+        <v>20</v>
+      </c>
+      <c r="E4" s="31">
+        <v>36079.74</v>
+      </c>
+      <c r="F4" s="30">
+        <v>22.9</v>
+      </c>
+      <c r="G4" s="31">
+        <v>41128.699999999997</v>
+      </c>
+      <c r="H4" s="32">
+        <f t="shared" ref="H4:H12" si="0">G4-E4</f>
+        <v>5048.9599999999991</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="28">
+        <v>45868</v>
+      </c>
+      <c r="C5" s="29">
+        <v>10000</v>
+      </c>
+      <c r="D5" s="30">
+        <v>4.7</v>
+      </c>
+      <c r="E5" s="31">
+        <v>47104.1</v>
+      </c>
+      <c r="F5" s="30">
+        <v>5.5</v>
+      </c>
+      <c r="G5" s="31">
+        <v>54878.18</v>
+      </c>
+      <c r="H5" s="32">
+        <f t="shared" si="0"/>
+        <v>7774.0800000000017</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="28">
+        <v>45867</v>
+      </c>
+      <c r="C6" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D6" s="30">
+        <v>87</v>
+      </c>
+      <c r="E6" s="31">
+        <v>87192.7</v>
+      </c>
+      <c r="F6" s="30">
+        <v>22.9</v>
+      </c>
+      <c r="G6" s="31">
+        <v>22849.279999999999</v>
+      </c>
+      <c r="H6" s="32">
+        <f t="shared" si="0"/>
+        <v>-64343.42</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="28">
+        <v>45862</v>
+      </c>
+      <c r="C7" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D7" s="30">
+        <v>87</v>
+      </c>
+      <c r="E7" s="31">
+        <v>87192.7</v>
+      </c>
+      <c r="F7" s="30">
+        <v>22.4</v>
+      </c>
+      <c r="G7" s="31">
+        <v>22350.38</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" si="0"/>
+        <v>-64842.319999999992</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="28">
+        <v>45856</v>
+      </c>
+      <c r="C8" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D8" s="30">
+        <v>87</v>
+      </c>
+      <c r="E8" s="31">
+        <v>87192.7</v>
+      </c>
+      <c r="F8" s="30">
+        <v>22.2</v>
+      </c>
+      <c r="G8" s="31">
+        <v>22150.83</v>
+      </c>
+      <c r="H8" s="32">
+        <f t="shared" si="0"/>
+        <v>-65041.869999999995</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B9" s="28">
+        <v>45854</v>
+      </c>
+      <c r="C9" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D9" s="30">
+        <v>87</v>
+      </c>
+      <c r="E9" s="31">
+        <v>87192.7</v>
+      </c>
+      <c r="F9" s="30">
+        <v>21.7</v>
+      </c>
+      <c r="G9" s="31">
+        <v>21651.94</v>
+      </c>
+      <c r="H9" s="32">
+        <f t="shared" si="0"/>
+        <v>-65540.759999999995</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="28">
+        <v>45841</v>
+      </c>
+      <c r="C10" s="29">
+        <v>1000</v>
+      </c>
+      <c r="D10" s="30">
+        <v>81</v>
+      </c>
+      <c r="E10" s="31">
+        <v>81179.41</v>
+      </c>
+      <c r="F10" s="30">
+        <v>21</v>
+      </c>
+      <c r="G10" s="31">
+        <v>20953.490000000002</v>
+      </c>
+      <c r="H10" s="32">
+        <f t="shared" si="0"/>
+        <v>-60225.919999999998</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="28">
+        <v>45841</v>
+      </c>
+      <c r="C11" s="29">
+        <v>2500</v>
+      </c>
+      <c r="D11" s="30">
         <v>9</v>
       </c>
-      <c r="F2" s="92">
-        <v>0.22412299999999999</v>
-      </c>
-      <c r="G2" s="31">
-        <f t="shared" ref="G2:G8" si="0">C2*F2</f>
-        <v>26894.76</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2*0.9</f>
-        <v>24205.284</v>
-      </c>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="28">
-        <v>46090</v>
-      </c>
-      <c r="C3" s="29">
-        <v>45000</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="90">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="G3" s="31">
-        <f t="shared" ref="G3" si="1">C3*F3</f>
-        <v>9999</v>
-      </c>
-      <c r="H3" s="32">
-        <f>G3*0.9</f>
-        <v>8999.1</v>
-      </c>
-      <c r="I3" s="35"/>
-      <c r="J3" s="35"/>
-      <c r="K3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="28">
-        <v>46093</v>
-      </c>
-      <c r="C4" s="29">
-        <v>69000</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" s="91">
-        <v>0.17829999999999999</v>
-      </c>
-      <c r="G4" s="31">
+      <c r="E11" s="31">
+        <v>22549.84</v>
+      </c>
+      <c r="F11" s="30">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="G11" s="31">
+        <v>25443.51</v>
+      </c>
+      <c r="H11" s="32">
         <f t="shared" si="0"/>
-        <v>12302.699999999999</v>
-      </c>
-      <c r="H4" s="32">
-        <f>G4*0.9</f>
-        <v>11072.429999999998</v>
-      </c>
-      <c r="I4" s="35"/>
-      <c r="J4" s="35"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="28">
-        <v>46099</v>
-      </c>
-      <c r="C5" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F5" s="92">
-        <v>0.12189999999999999</v>
-      </c>
-      <c r="G5" s="31">
-        <f t="shared" si="0"/>
-        <v>2438</v>
-      </c>
-      <c r="H5" s="32">
-        <f>G5*0.9</f>
-        <v>2194.2000000000003</v>
-      </c>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="28">
-        <v>46101</v>
-      </c>
-      <c r="C6" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F6" s="90">
-        <v>0.1212</v>
-      </c>
-      <c r="G6" s="31">
-        <f t="shared" si="0"/>
-        <v>2424</v>
-      </c>
-      <c r="H6" s="32">
-        <v>2181.6</v>
-      </c>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="28">
-        <v>46101</v>
-      </c>
-      <c r="C7" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F7" s="90">
-        <v>7.4800000000000005E-2</v>
-      </c>
-      <c r="G7" s="31">
-        <f t="shared" ref="G7" si="2">C7*F7</f>
-        <v>1496</v>
-      </c>
-      <c r="H7" s="32">
-        <v>1496</v>
-      </c>
-      <c r="I7" s="35"/>
-      <c r="J7" s="35"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="28">
-        <v>46108</v>
-      </c>
-      <c r="C8" s="29">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="91">
-        <v>0.17549999999999999</v>
-      </c>
-      <c r="G8" s="31">
-        <f t="shared" si="0"/>
-        <v>8775</v>
-      </c>
-      <c r="H8" s="32">
-        <f>G8*0.9</f>
-        <v>7897.5</v>
-      </c>
-      <c r="I8" s="35"/>
-      <c r="J8" s="35"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="28">
-        <v>46108</v>
-      </c>
-      <c r="C9" s="29">
-        <v>55000</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="92">
-        <v>0.27939999999999998</v>
-      </c>
-      <c r="G9" s="31">
-        <f>C9*F9</f>
-        <v>15366.999999999998</v>
-      </c>
-      <c r="H9" s="32">
-        <f>G9*0.9</f>
-        <v>13830.3</v>
-      </c>
-      <c r="I9" s="35"/>
-      <c r="J9" s="35"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="27"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="90"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="32">
-        <f>SUM(H2:H9)</f>
-        <v>71876.41399999999</v>
-      </c>
-      <c r="I10" s="35"/>
-      <c r="J10" s="35"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" s="28">
-        <v>46085</v>
-      </c>
-      <c r="C11" s="29">
-        <v>17500</v>
-      </c>
-      <c r="D11" s="30">
-        <v>10.6</v>
-      </c>
-      <c r="E11" s="31">
-        <v>185910.87</v>
-      </c>
-      <c r="F11" s="90">
-        <v>11.1</v>
-      </c>
-      <c r="G11" s="31">
-        <v>193819.75</v>
-      </c>
-      <c r="H11" s="40">
-        <f>G11-E11</f>
-        <v>7908.8800000000047</v>
-      </c>
-      <c r="I11" s="96"/>
-      <c r="J11" s="32"/>
+        <v>2893.6699999999983</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="7"/>
       <c r="K11" s="7"/>
       <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A12" s="27" t="s">
         <v>37</v>
       </c>
       <c r="B12" s="28">
-        <v>46085</v>
+        <v>45840</v>
       </c>
       <c r="C12" s="29">
-        <v>6800</v>
+        <v>1000</v>
       </c>
       <c r="D12" s="30">
-        <v>33</v>
+        <v>81</v>
       </c>
       <c r="E12" s="31">
-        <v>224897.03</v>
-      </c>
-      <c r="F12" s="90">
-        <v>6.25</v>
+        <v>81179.41</v>
+      </c>
+      <c r="F12" s="30">
+        <v>19.600000000000001</v>
       </c>
       <c r="G12" s="31">
-        <v>42405.86</v>
-      </c>
-      <c r="H12" s="40">
-        <f>G12-E12</f>
-        <v>-182491.16999999998</v>
-      </c>
-      <c r="I12" s="96"/>
-      <c r="J12" s="32"/>
+        <v>19556.59</v>
+      </c>
+      <c r="H12" s="32">
+        <f t="shared" si="0"/>
+        <v>-61622.820000000007</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="7"/>
       <c r="K12" s="7"/>
       <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="28">
-        <v>46090</v>
-      </c>
-      <c r="C13" s="29">
-        <v>600</v>
-      </c>
-      <c r="D13" s="30">
-        <v>405</v>
-      </c>
-      <c r="E13" s="31">
-        <v>243538.22</v>
-      </c>
-      <c r="F13" s="90">
-        <v>172</v>
-      </c>
-      <c r="G13" s="31">
-        <v>102971.43</v>
-      </c>
-      <c r="H13" s="40">
-        <f>G13-E13</f>
-        <v>-140566.79</v>
-      </c>
-      <c r="I13" s="96"/>
-      <c r="J13" s="32"/>
+    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="26"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="32">
+        <f>SUM(E4:E12)</f>
+        <v>616863.30000000005</v>
+      </c>
+      <c r="F13" s="30"/>
+      <c r="G13" s="32">
+        <f t="shared" ref="G13:H13" si="1">SUM(G4:G12)</f>
+        <v>250962.9</v>
+      </c>
+      <c r="H13" s="32">
+        <f t="shared" si="1"/>
+        <v>-365900.39999999997</v>
+      </c>
       <c r="K13" s="7"/>
       <c r="L13" s="15"/>
       <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A14" s="26"/>
       <c r="B14" s="28"/>
       <c r="C14" s="29"/>
       <c r="D14" s="33"/>
-      <c r="E14" s="32">
-        <f>SUM(E11:E13)</f>
-        <v>654346.12</v>
-      </c>
-      <c r="F14" s="90"/>
-      <c r="G14" s="32">
-        <f>SUM(G11:G13)</f>
-        <v>339197.04</v>
-      </c>
-      <c r="H14" s="32">
-        <f>SUM(H11:H13)</f>
-        <v>-315149.07999999996</v>
-      </c>
-      <c r="I14" s="35"/>
-      <c r="J14" s="35"/>
-      <c r="K14" s="15"/>
-      <c r="L14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E14" s="32"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H14" s="34">
+        <f>H3+H13</f>
+        <v>-365900.39999999997</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J14" s="7">
+        <v>-101058.68999999999</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="26"/>
       <c r="B15" s="28"/>
       <c r="C15" s="29"/>
       <c r="D15" s="33"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="90"/>
+      <c r="F15" s="30"/>
       <c r="G15" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="34">
-        <f>H10+H14</f>
-        <v>-243272.66599999997</v>
-      </c>
-      <c r="I15" s="96" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>16</v>
+      </c>
+      <c r="H15" s="32">
+        <v>-187350.93</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J15" s="7">
+        <v>-86292.24</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
       <c r="B16" s="28"/>
       <c r="C16" s="29"/>
       <c r="D16" s="33"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="90"/>
+      <c r="F16" s="30"/>
       <c r="G16" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="32">
-        <v>-11260</v>
-      </c>
-      <c r="I16" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="62">
-        <v>0</v>
-      </c>
-      <c r="L16" s="6"/>
-    </row>
-    <row r="17" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>28</v>
+      </c>
+      <c r="H16" s="34">
+        <f>H14+H15</f>
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J16" s="7">
+        <v>-187350.93</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+    </row>
+    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="26"/>
       <c r="B17" s="28"/>
       <c r="C17" s="29"/>
       <c r="D17" s="33"/>
       <c r="E17" s="32"/>
-      <c r="F17" s="90"/>
-      <c r="G17" s="62" t="s">
-        <v>29</v>
-      </c>
-      <c r="H17" s="41">
-        <f>SUM(H15,H16)</f>
-        <v>-254532.66599999997</v>
-      </c>
-      <c r="I17" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="J17" s="62">
-        <v>0</v>
-      </c>
-      <c r="L17" s="68"/>
-    </row>
-    <row r="18" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F17" s="30"/>
+      <c r="G17" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17" s="35">
+        <v>377810</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J17" s="7">
+        <v>336660</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+    </row>
+    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18" s="26"/>
       <c r="B18" s="28"/>
       <c r="C18" s="29"/>
       <c r="D18" s="33"/>
       <c r="E18" s="32"/>
-      <c r="F18" s="90"/>
+      <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="H18" s="35">
-        <v>71260</v>
-      </c>
-      <c r="I18" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="62">
-        <v>38040</v>
-      </c>
-      <c r="L18" s="68"/>
-    </row>
-    <row r="19" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+        <v>8610</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J18" s="7">
+        <v>41150</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A19" s="26"/>
       <c r="B19" s="28"/>
       <c r="C19" s="29"/>
       <c r="D19" s="33"/>
       <c r="E19" s="32"/>
-      <c r="F19" s="90"/>
+      <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="H19" s="35">
-        <v>26910</v>
-      </c>
-      <c r="I19" s="35" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="62">
-        <v>33220</v>
-      </c>
-      <c r="L19" s="68"/>
-    </row>
-    <row r="20" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="90"/>
+        <v>14</v>
+      </c>
+      <c r="H19" s="41">
+        <f>H17+H18</f>
+        <v>386420</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="7">
+        <v>377810</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A20" s="5"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="10"/>
       <c r="G20" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="41">
-        <f>H18+H19</f>
-        <v>98170</v>
-      </c>
-      <c r="I20" s="35" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20" s="62">
-        <v>71260</v>
-      </c>
-      <c r="L20" s="6"/>
-    </row>
-    <row r="21" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="94">
-        <f>H17-H20</f>
-        <v>-352702.66599999997</v>
-      </c>
-      <c r="I21" s="35" t="s">
+      <c r="H20" s="46">
+        <f>H16-H19</f>
+        <v>-939671.33</v>
+      </c>
+      <c r="I20" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="62">
-        <v>-71260</v>
-      </c>
-      <c r="L21" s="6"/>
-    </row>
-    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="26"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="62" t="s">
+      <c r="J20" s="7">
+        <v>-565160.92999999993</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A21" s="5"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H21" s="38">
+        <v>57000</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J21" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A22" s="6"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="8"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="H22" s="97">
-        <v>60000</v>
-      </c>
-      <c r="I22" s="35" t="s">
+      <c r="H22" s="39">
+        <f>H20+H21</f>
+        <v>-882671.33</v>
+      </c>
+      <c r="I22" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="J22" s="62">
-        <v>60000</v>
-      </c>
-      <c r="L22" s="6"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
-      <c r="B23" s="60"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="33"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="H23" s="41">
-        <f>H21+H22</f>
-        <v>-292702.66599999997</v>
-      </c>
-      <c r="I23" s="96" t="s">
-        <v>32</v>
-      </c>
-      <c r="J23" s="62">
-        <v>-11260</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="26"/>
-      <c r="B24" s="60"/>
-      <c r="C24" s="29"/>
-      <c r="D24" s="33"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="90"/>
-      <c r="G24" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="H24" s="32">
-        <v>0</v>
-      </c>
-      <c r="I24" s="96"/>
-      <c r="J24" s="32"/>
-    </row>
-    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="26"/>
-      <c r="B25" s="60"/>
-      <c r="C25" s="29"/>
-      <c r="D25" s="33"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="90"/>
-      <c r="G25" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="H25" s="32">
-        <f>H24+H10</f>
-        <v>71876.41399999999</v>
-      </c>
-      <c r="I25" s="96"/>
-      <c r="J25" s="32"/>
-    </row>
-    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="26"/>
-      <c r="B26" s="60"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="33"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="90"/>
-      <c r="G26" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="H26" s="32">
-        <f>H25-H20</f>
-        <v>-26293.58600000001</v>
-      </c>
-      <c r="I26" s="96"/>
-      <c r="J26" s="32"/>
+      <c r="J22" s="7">
+        <v>-508160.92999999993</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K23" s="7"/>
+      <c r="M23" s="7"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M24" s="7"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M25" s="7"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C26" s="12"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="10"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="11"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="7"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:H12">
+    <sortCondition descending="1" ref="B4:B12"/>
+    <sortCondition ref="A4:A12"/>
+  </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAFE1F0-60EA-46C8-9C11-E7180F21BFAA}">
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -1870,7 +2293,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A7" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="28">
         <v>45820</v>
@@ -1985,7 +2408,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A11" s="27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B11" s="28">
         <v>45824</v>
@@ -2018,7 +2441,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A12" s="27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="28">
         <v>45826</v>
@@ -2051,7 +2474,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A13" s="27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B13" s="28">
         <v>45828</v>
@@ -2164,14 +2587,14 @@
       <c r="E17" s="32"/>
       <c r="F17" s="30"/>
       <c r="G17" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H17" s="34">
         <f>H15+H16</f>
         <v>-187350.93</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J17" s="7">
         <v>-86292.244747999939</v>
@@ -2213,13 +2636,13 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H19" s="35">
         <v>41150</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J19" s="7">
         <v>9400</v>
@@ -2287,13 +2710,13 @@
       <c r="E22" s="7"/>
       <c r="F22" s="10"/>
       <c r="G22" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H22" s="38">
         <v>57000</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J22" s="7">
         <v>57000</v>
@@ -2311,14 +2734,14 @@
       <c r="E23" s="14"/>
       <c r="F23" s="10"/>
       <c r="G23" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H23" s="39">
         <f>H21+H22</f>
         <v>-508160.92999999993</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J23" s="7">
         <v>-365952.24474799994</v>
@@ -2361,7 +2784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E1A231-79A5-4BE4-8C0C-F5E13A4831EB}">
   <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -2417,7 +2840,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="72">
         <v>45784</v>
@@ -2483,7 +2906,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B4" s="72">
         <v>45786</v>
@@ -2516,7 +2939,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A5" s="27" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B5" s="72">
         <v>45786</v>
@@ -2549,7 +2972,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A6" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B6" s="72">
         <v>45791</v>
@@ -2582,7 +3005,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A7" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B7" s="72">
         <v>45793</v>
@@ -2615,7 +3038,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A8" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B8" s="72">
         <v>45793</v>
@@ -2648,7 +3071,7 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A9" s="27" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="72">
         <v>45793</v>
@@ -2681,7 +3104,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A10" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="72">
         <v>45797</v>
@@ -2714,7 +3137,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A11" s="27" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B11" s="72">
         <v>45800</v>
@@ -2780,7 +3203,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A13" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B13" s="72">
         <v>45800</v>
@@ -2813,7 +3236,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A14" s="27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B14" s="72">
         <v>45800</v>
@@ -2845,7 +3268,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A15" s="27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B15" s="72">
         <v>45800</v>
@@ -2878,7 +3301,7 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A16" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B16" s="72">
         <v>45805</v>
@@ -2911,7 +3334,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A17" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B17" s="72">
         <v>45806</v>
@@ -2963,7 +3386,7 @@
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A19" s="27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B19" s="73">
         <v>45792</v>
@@ -3076,14 +3499,14 @@
       <c r="E23" s="32"/>
       <c r="F23" s="30"/>
       <c r="G23" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H23" s="34">
         <f>H21+H22</f>
         <v>-86292.244747999939</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J23" s="7">
         <v>-162547.95474799996</v>
@@ -3125,13 +3548,13 @@
       <c r="E25" s="32"/>
       <c r="F25" s="30"/>
       <c r="G25" s="32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H25" s="35">
         <v>9400</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J25" s="7">
         <v>45870</v>
@@ -3199,13 +3622,13 @@
       <c r="E28" s="7"/>
       <c r="F28" s="10"/>
       <c r="G28" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H28" s="38">
         <v>57000</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J28" s="7">
         <v>57000</v>
@@ -3223,14 +3646,14 @@
       <c r="E29" s="14"/>
       <c r="F29" s="10"/>
       <c r="G29" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H29" s="39">
         <f>H27+H28</f>
         <v>-365952.24474799994</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J29" s="7">
         <v>-432807.95474799996</v>
@@ -3272,29 +3695,30 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F07CE69-5C67-4DF2-B5BE-CD5590D6A395}">
-  <dimension ref="A1:N22"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6E9199-1687-4EE7-A0F3-54DE6332B9D4}">
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.625" style="12" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="93" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.75" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="10.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.875" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
+    <col min="9" max="9" width="17.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10" style="6" bestFit="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -3310,7 +3734,7 @@
       <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="89" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="24" t="s">
@@ -3319,22 +3743,19 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="3"/>
+      <c r="I1" s="95"/>
+      <c r="J1" s="95"/>
       <c r="K1" s="5"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="B2" s="28">
-        <v>45769</v>
+        <v>46085</v>
       </c>
       <c r="C2" s="29">
-        <v>600</v>
+        <v>120000</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>9</v>
@@ -3342,33 +3763,30 @@
       <c r="E2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="37">
-        <v>2.5</v>
+      <c r="F2" s="92">
+        <v>0.22412299999999999</v>
       </c>
       <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>1500</v>
+        <f t="shared" ref="G2:G8" si="0">C2*F2</f>
+        <v>26894.76</v>
       </c>
       <c r="H2" s="32">
         <f>G2*0.9</f>
-        <v>1350</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+        <v>24205.284</v>
+      </c>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A3" s="27" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B3" s="28">
-        <v>45771</v>
+        <v>46090</v>
       </c>
       <c r="C3" s="29">
-        <v>6000</v>
+        <v>45000</v>
       </c>
       <c r="D3" s="30" t="s">
         <v>9</v>
@@ -3376,33 +3794,30 @@
       <c r="E3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="37">
-        <v>0.5</v>
+      <c r="F3" s="90">
+        <v>0.22220000000000001</v>
       </c>
       <c r="G3" s="31">
-        <f>C3*F3</f>
-        <v>3000</v>
+        <f t="shared" ref="G3" si="1">C3*F3</f>
+        <v>9999</v>
       </c>
       <c r="H3" s="32">
         <f>G3*0.9</f>
-        <v>2700</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+        <v>8999.1</v>
+      </c>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35"/>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="B4" s="28">
-        <v>45777</v>
+        <v>46093</v>
       </c>
       <c r="C4" s="29">
-        <v>4200</v>
+        <v>69000</v>
       </c>
       <c r="D4" s="30" t="s">
         <v>9</v>
@@ -3410,379 +3825,563 @@
       <c r="E4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="37">
-        <v>0.28000000000000003</v>
+      <c r="F4" s="91">
+        <v>0.17829999999999999</v>
       </c>
       <c r="G4" s="31">
-        <f>C4*F4</f>
-        <v>1176</v>
+        <f t="shared" si="0"/>
+        <v>12302.699999999999</v>
       </c>
       <c r="H4" s="32">
         <f>G4*0.9</f>
-        <v>1058.4000000000001</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="31"/>
-      <c r="H5" s="34">
-        <f>SUM(H2:H4)</f>
-        <v>5108.3999999999996</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+        <v>11072.429999999998</v>
+      </c>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="28">
+        <v>46099</v>
+      </c>
+      <c r="C5" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="92">
+        <v>0.12189999999999999</v>
+      </c>
+      <c r="G5" s="31">
+        <f t="shared" si="0"/>
+        <v>2438</v>
+      </c>
+      <c r="H5" s="32">
+        <f>G5*0.9</f>
+        <v>2194.2000000000003</v>
+      </c>
+      <c r="I5" s="35"/>
+      <c r="J5" s="35"/>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="27" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B6" s="28">
-        <v>45757</v>
+        <v>46101</v>
       </c>
       <c r="C6" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="30">
-        <v>61.5</v>
-      </c>
-      <c r="E6" s="31">
-        <v>61636.22</v>
-      </c>
-      <c r="F6" s="30">
-        <v>16.600000000000001</v>
+        <v>20000</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6" s="90">
+        <v>0.1212</v>
       </c>
       <c r="G6" s="31">
-        <v>16563.23</v>
-      </c>
-      <c r="H6" s="49">
-        <f t="shared" ref="H6" si="0">G6-E6</f>
-        <v>-45072.990000000005</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32">
-        <f>SUM(E6:E6)</f>
-        <v>61636.22</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32">
-        <f>SUM(G6:G6)</f>
-        <v>16563.23</v>
-      </c>
-      <c r="H7" s="34">
-        <f>SUM(H6:H6)</f>
-        <v>-45072.990000000005</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="34">
-        <f>H5+H7</f>
-        <v>-39964.590000000004</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="K8" s="7">
-        <v>34655.910000000003</v>
-      </c>
-      <c r="L8" s="15">
-        <f t="shared" ref="L8:L12" si="1">H8-K8</f>
-        <v>-74620.5</v>
-      </c>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="7">
-        <v>-122583.36474799996</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="7">
-        <v>-157239.27474799997</v>
-      </c>
-      <c r="L9" s="15">
-        <f t="shared" si="1"/>
-        <v>34655.910000000003</v>
-      </c>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="26"/>
+        <f t="shared" si="0"/>
+        <v>2424</v>
+      </c>
+      <c r="H6" s="32">
+        <v>2181.6</v>
+      </c>
+      <c r="I6" s="35"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="28">
+        <v>46101</v>
+      </c>
+      <c r="C7" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F7" s="90">
+        <v>7.4800000000000005E-2</v>
+      </c>
+      <c r="G7" s="31">
+        <f t="shared" ref="G7" si="2">C7*F7</f>
+        <v>1496</v>
+      </c>
+      <c r="H7" s="32">
+        <v>1496</v>
+      </c>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="28">
+        <v>46108</v>
+      </c>
+      <c r="C8" s="29">
+        <v>50000</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="91">
+        <v>0.17549999999999999</v>
+      </c>
+      <c r="G8" s="31">
+        <f t="shared" si="0"/>
+        <v>8775</v>
+      </c>
+      <c r="H8" s="32">
+        <f>G8*0.9</f>
+        <v>7897.5</v>
+      </c>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="28">
+        <v>46108</v>
+      </c>
+      <c r="C9" s="29">
+        <v>55000</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9" s="92">
+        <v>0.27939999999999998</v>
+      </c>
+      <c r="G9" s="31">
+        <f>C9*F9</f>
+        <v>15366.999999999998</v>
+      </c>
+      <c r="H9" s="32">
+        <f>G9*0.9</f>
+        <v>13830.3</v>
+      </c>
+      <c r="I9" s="35"/>
+      <c r="J9" s="35"/>
+      <c r="K9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="27"/>
       <c r="B10" s="28"/>
       <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="H10" s="34">
-        <f>H8+H9</f>
-        <v>-162547.95474799996</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="K10" s="7">
-        <v>-122583.36474799996</v>
-      </c>
-      <c r="L10" s="15">
-        <f t="shared" si="1"/>
-        <v>-39964.589999999997</v>
-      </c>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="7">
-        <v>281390</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="K11" s="7">
-        <v>102430</v>
-      </c>
-      <c r="L11" s="15">
-        <f t="shared" si="1"/>
-        <v>178960</v>
-      </c>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="90"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="32">
+        <f>SUM(H2:H9)</f>
+        <v>71876.41399999999</v>
+      </c>
+      <c r="I10" s="35"/>
+      <c r="J10" s="35"/>
+      <c r="K10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="28">
+        <v>46085</v>
+      </c>
+      <c r="C11" s="29">
+        <v>17500</v>
+      </c>
+      <c r="D11" s="30">
+        <v>10.6</v>
+      </c>
+      <c r="E11" s="31">
+        <v>185910.87</v>
+      </c>
+      <c r="F11" s="90">
+        <v>11.1</v>
+      </c>
+      <c r="G11" s="31">
+        <v>193819.75</v>
+      </c>
+      <c r="H11" s="40">
+        <f>G11-E11</f>
+        <v>7908.8800000000047</v>
+      </c>
+      <c r="I11" s="96"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
       <c r="M11" s="15"/>
       <c r="N11" s="6"/>
     </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="26"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="H12" s="35">
-        <v>45870</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="K12" s="7">
-        <v>178960</v>
-      </c>
-      <c r="L12" s="15">
-        <f t="shared" si="1"/>
-        <v>-133090</v>
-      </c>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="28">
+        <v>46085</v>
+      </c>
+      <c r="C12" s="29">
+        <v>6800</v>
+      </c>
+      <c r="D12" s="30">
+        <v>33</v>
+      </c>
+      <c r="E12" s="31">
+        <v>224897.03</v>
+      </c>
+      <c r="F12" s="90">
+        <v>6.25</v>
+      </c>
+      <c r="G12" s="31">
+        <v>42405.86</v>
+      </c>
+      <c r="H12" s="40">
+        <f>G12-E12</f>
+        <v>-182491.16999999998</v>
+      </c>
+      <c r="I12" s="96"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
       <c r="M12" s="15"/>
       <c r="N12" s="6"/>
     </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="26"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="34">
-        <f>H11+H12</f>
-        <v>327260</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="7">
-        <v>281390</v>
-      </c>
-      <c r="L13" s="15">
-        <f>H13-K13</f>
-        <v>45870</v>
-      </c>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="28">
+        <v>46090</v>
+      </c>
+      <c r="C13" s="29">
+        <v>600</v>
+      </c>
+      <c r="D13" s="30">
+        <v>405</v>
+      </c>
+      <c r="E13" s="31">
+        <v>243538.22</v>
+      </c>
+      <c r="F13" s="90">
+        <v>172</v>
+      </c>
+      <c r="G13" s="31">
+        <v>102971.43</v>
+      </c>
+      <c r="H13" s="40">
+        <f>G13-E13</f>
+        <v>-140566.79</v>
+      </c>
+      <c r="I13" s="96"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
       <c r="M13" s="15"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="5"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="32" t="s">
+    <row r="14" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="26"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="32">
+        <f>SUM(E11:E13)</f>
+        <v>654346.12</v>
+      </c>
+      <c r="F14" s="90"/>
+      <c r="G14" s="32">
+        <f>SUM(G11:G13)</f>
+        <v>339197.04</v>
+      </c>
+      <c r="H14" s="32">
+        <f>SUM(H11:H13)</f>
+        <v>-315149.07999999996</v>
+      </c>
+      <c r="I14" s="35"/>
+      <c r="J14" s="35"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="26"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="90"/>
+      <c r="G15" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="34">
+        <f>H10+H14</f>
+        <v>-243272.66599999997</v>
+      </c>
+      <c r="I15" s="96" t="s">
+        <v>12</v>
+      </c>
+      <c r="J15" s="62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="90"/>
+      <c r="G16" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="32">
+        <v>-11260</v>
+      </c>
+      <c r="I16" s="35" t="s">
+        <v>16</v>
+      </c>
+      <c r="J16" s="62">
+        <v>0</v>
+      </c>
+      <c r="L16" s="6"/>
+    </row>
+    <row r="17" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="90"/>
+      <c r="G17" s="62" t="s">
+        <v>28</v>
+      </c>
+      <c r="H17" s="41">
+        <f>SUM(H15,H16)</f>
+        <v>-254532.66599999997</v>
+      </c>
+      <c r="I17" s="35" t="s">
+        <v>28</v>
+      </c>
+      <c r="J17" s="62">
+        <v>0</v>
+      </c>
+      <c r="L17" s="68"/>
+    </row>
+    <row r="18" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="90"/>
+      <c r="G18" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="35">
+        <v>71260</v>
+      </c>
+      <c r="I18" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="62">
+        <v>38040</v>
+      </c>
+      <c r="L18" s="68"/>
+    </row>
+    <row r="19" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="26"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="H19" s="35">
+        <v>26910</v>
+      </c>
+      <c r="I19" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="62">
+        <v>33220</v>
+      </c>
+      <c r="L19" s="68"/>
+    </row>
+    <row r="20" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="26"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="90"/>
+      <c r="G20" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H20" s="41">
+        <f>H18+H19</f>
+        <v>98170</v>
+      </c>
+      <c r="I20" s="35" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20" s="62">
+        <v>71260</v>
+      </c>
+      <c r="L20" s="6"/>
+    </row>
+    <row r="21" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="26"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="45">
-        <f>H10-H13</f>
-        <v>-489807.95474799996</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="7" t="s">
+      <c r="H21" s="94">
+        <f>H17-H20</f>
+        <v>-352702.66599999997</v>
+      </c>
+      <c r="I21" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="K14" s="7">
-        <v>-403973.36474799993</v>
-      </c>
-      <c r="L14" s="15">
-        <f t="shared" ref="L14:L16" si="2">H14-K14</f>
-        <v>-85834.590000000026</v>
-      </c>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="38" t="s">
+      <c r="J21" s="62">
+        <v>-71260</v>
+      </c>
+      <c r="L21" s="6"/>
+    </row>
+    <row r="22" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="26"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="90"/>
+      <c r="G22" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="H22" s="97">
+        <v>60000</v>
+      </c>
+      <c r="I22" s="35" t="s">
+        <v>30</v>
+      </c>
+      <c r="J22" s="62">
+        <v>60000</v>
+      </c>
+      <c r="L22" s="6"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="26"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="62" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="38">
-        <v>57000</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="7" t="s">
+      <c r="H23" s="41">
+        <f>H21+H22</f>
+        <v>-292702.66599999997</v>
+      </c>
+      <c r="I23" s="96" t="s">
         <v>31</v>
       </c>
-      <c r="K15" s="7">
-        <v>57000</v>
-      </c>
-      <c r="L15" s="15">
-        <f t="shared" si="2"/>
+      <c r="J23" s="62">
+        <v>-11260</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="26"/>
+      <c r="B24" s="60"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="33"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="90"/>
+      <c r="G24" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="H24" s="32">
         <v>0</v>
       </c>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="6"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H16" s="39">
-        <f>H14+H15</f>
-        <v>-432807.95474799996</v>
-      </c>
-      <c r="I16" s="11"/>
-      <c r="J16" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="K16" s="7">
-        <v>-346973.36474799993</v>
-      </c>
-      <c r="L16" s="15">
-        <f t="shared" si="2"/>
-        <v>-85834.590000000026</v>
-      </c>
-      <c r="M16" s="15"/>
-      <c r="N16" s="7"/>
-    </row>
-    <row r="17" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="I17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="N17" s="13"/>
-    </row>
-    <row r="18" spans="9:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="K19" s="7"/>
-      <c r="M19" s="7"/>
-    </row>
-    <row r="20" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="M20" s="7"/>
-    </row>
-    <row r="21" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="M21" s="7"/>
-    </row>
-    <row r="22" spans="9:14" x14ac:dyDescent="0.3">
-      <c r="K22" s="7"/>
+      <c r="I24" s="96"/>
+      <c r="J24" s="32"/>
+    </row>
+    <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="26"/>
+      <c r="B25" s="60"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="33"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="90"/>
+      <c r="G25" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="H25" s="32">
+        <f>H24+H10</f>
+        <v>71876.41399999999</v>
+      </c>
+      <c r="I25" s="96"/>
+      <c r="J25" s="32"/>
+    </row>
+    <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="26"/>
+      <c r="B26" s="60"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="90"/>
+      <c r="G26" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="H26" s="32">
+        <f>H25-H20</f>
+        <v>-26293.58600000001</v>
+      </c>
+      <c r="I26" s="96"/>
+      <c r="J26" s="32"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815483-6499-49C9-BB8D-67572F4517B8}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -4004,14 +4603,14 @@
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
       <c r="G9" s="62" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H9" s="63">
         <f>SUM(H7,H8)</f>
         <v>0</v>
       </c>
       <c r="I9" s="15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J9" s="15">
         <v>0</v>
@@ -4053,7 +4652,7 @@
         <v>33220</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J11" s="15">
         <v>38040</v>
@@ -4067,7 +4666,7 @@
       <c r="D12" s="33"/>
       <c r="E12" s="32"/>
       <c r="F12" s="59" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12" s="62" t="s">
         <v>14</v>
@@ -4113,16 +4712,16 @@
       <c r="D14" s="33"/>
       <c r="E14" s="32"/>
       <c r="F14" s="59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G14" s="62" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H14" s="62">
         <v>60000</v>
       </c>
       <c r="I14" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J14" s="15">
         <v>60000</v>
@@ -4137,14 +4736,14 @@
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
       <c r="G15" s="62" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H15" s="66">
         <f>H13+H14</f>
         <v>-11260</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J15" s="7">
         <v>21960</v>
@@ -4172,10 +4771,10 @@
       <c r="D17" s="33"/>
       <c r="E17" s="32"/>
       <c r="F17" s="59" t="s">
+        <v>60</v>
+      </c>
+      <c r="G17" s="67" t="s">
         <v>61</v>
-      </c>
-      <c r="G17" s="67" t="s">
-        <v>62</v>
       </c>
       <c r="H17" s="62">
         <f>H14-H12</f>
@@ -4210,7 +4809,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DA818F-D2F1-4405-A36C-2376E8E1DAA2}">
   <dimension ref="A1:N14"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -4406,7 +5005,7 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H8" s="41">
         <f>H6+H7</f>
@@ -4445,7 +5044,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H10" s="35">
         <v>38040</v>
@@ -4506,7 +5105,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="10"/>
       <c r="G13" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" s="38">
         <v>60000</v>
@@ -4526,7 +5125,7 @@
       <c r="E14" s="14"/>
       <c r="F14" s="10"/>
       <c r="G14" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H14" s="48">
         <f>H12+H13</f>
@@ -4547,7 +5146,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDBED0F-338F-4C61-AC0B-5077E6985A08}">
   <dimension ref="A1:N25"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -4635,7 +5234,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A3" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="28">
         <v>45995</v>
@@ -4666,7 +5265,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="28">
         <v>46002</v>
@@ -4730,7 +5329,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A6" s="88" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B6" s="28">
         <v>46002</v>
@@ -4794,7 +5393,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A8" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="28">
         <v>46006</v>
@@ -4954,7 +5553,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A13" s="88" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="28">
         <v>46013</v>
@@ -5115,14 +5714,14 @@
       <c r="E19" s="14"/>
       <c r="F19" s="10"/>
       <c r="G19" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H19" s="41">
         <f>H17+H18</f>
         <v>-453418.88799999998</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J19" s="7">
         <v>-522636.73</v>
@@ -5150,13 +5749,13 @@
     </row>
     <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G21" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H21" s="35">
         <v>12050</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J21" s="7">
         <v>10130</v>
@@ -5203,13 +5802,13 @@
     </row>
     <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G24" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H24" s="7">
         <v>57000</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J24" s="7">
         <v>57000</v>
@@ -5217,14 +5816,14 @@
     </row>
     <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G25" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H25" s="42">
         <f>H23+H24</f>
         <v>-805018.88800000004</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J25" s="7">
         <v>-862186.73</v>
@@ -5238,7 +5837,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F537F07A-D0A7-416B-8994-ABDD1C22435D}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -5294,7 +5893,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B2" s="28">
         <v>44846</v>
@@ -5345,7 +5944,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B4" s="28">
         <v>45590</v>
@@ -5454,14 +6053,14 @@
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
       <c r="G8" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H8" s="41">
         <f>H6+H7</f>
         <v>-522636.73</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J8" s="7">
         <v>-522636.73</v>
@@ -5501,13 +6100,13 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H10" s="35">
         <v>24420</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J10" s="7">
         <v>10130</v>
@@ -5574,13 +6173,13 @@
       <c r="E13" s="7"/>
       <c r="F13" s="10"/>
       <c r="G13" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H13" s="7">
         <v>57000</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J13" s="7">
         <v>57000</v>
@@ -5598,14 +6197,14 @@
       <c r="E14" s="14"/>
       <c r="F14" s="10"/>
       <c r="G14" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H14" s="42">
         <f>H12+H13</f>
         <v>-886606.73</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J14" s="7">
         <v>-862186.73</v>
@@ -5645,7 +6244,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801544F9-630F-4E32-B67B-5CF42760770C}">
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -5701,7 +6300,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B2" s="28">
         <v>45576</v>
@@ -5752,7 +6351,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="28">
         <v>45931</v>
@@ -5785,7 +6384,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A5" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B5" s="28">
         <v>45937</v>
@@ -5818,7 +6417,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="27" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B6" s="28">
         <v>45954</v>
@@ -5927,14 +6526,14 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H10" s="41">
         <f>H8+H9</f>
         <v>-520323.55</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J10" s="7">
         <v>-522636.73</v>
@@ -5974,13 +6573,13 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H12" s="35">
         <v>19270</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J12" s="7">
         <v>10130</v>
@@ -6047,13 +6646,13 @@
       <c r="E15" s="7"/>
       <c r="F15" s="10"/>
       <c r="G15" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H15" s="38">
         <v>57000</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J15" s="7">
         <v>57000</v>
@@ -6071,14 +6670,14 @@
       <c r="E16" s="14"/>
       <c r="F16" s="10"/>
       <c r="G16" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H16" s="42">
         <f>H14+H15</f>
         <v>-879143.55</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J16" s="7">
         <v>-862186.73</v>
@@ -6118,7 +6717,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805BC19F-42DC-4CD3-B954-E9F19E56BFF7}">
   <dimension ref="A1:N40"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -6174,7 +6773,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="77" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="78">
         <v>45903</v>
@@ -6202,7 +6801,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A3" s="77" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B3" s="78">
         <v>45910</v>
@@ -6286,7 +6885,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A6" s="77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B6" s="78">
         <v>45912</v>
@@ -6398,7 +6997,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A10" s="77" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B10" s="78">
         <v>45911</v>
@@ -6426,7 +7025,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A11" s="77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="78">
         <v>45912</v>
@@ -6454,7 +7053,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A12" s="77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="78">
         <v>45910</v>
@@ -6482,7 +7081,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A13" s="77" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13" s="78">
         <v>45905</v>
@@ -6510,7 +7109,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A14" s="77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B14" s="78">
         <v>45905</v>
@@ -6538,7 +7137,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A15" s="77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="78">
         <v>45910</v>
@@ -6594,7 +7193,7 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A17" s="77" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B17" s="78">
         <v>45912</v>
@@ -6622,7 +7221,7 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A18" s="77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" s="78">
         <v>45905</v>
@@ -6757,7 +7356,7 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A23" s="77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B23" s="78">
         <v>45908</v>
@@ -6789,7 +7388,7 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A24" s="77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B24" s="78">
         <v>45911</v>
@@ -6821,7 +7420,7 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A25" s="77" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B25" s="78">
         <v>45915</v>
@@ -6962,14 +7561,14 @@
       <c r="E30" s="32"/>
       <c r="F30" s="30"/>
       <c r="G30" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H30" s="41">
         <f>H28+H29</f>
         <v>-393315.2</v>
       </c>
       <c r="I30" s="10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J30" s="7">
         <v>-522636.73</v>
@@ -7009,13 +7608,13 @@
       <c r="E32" s="32"/>
       <c r="F32" s="30"/>
       <c r="G32" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H32" s="35">
         <v>62010</v>
       </c>
       <c r="I32" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J32" s="7">
         <v>10130</v>
@@ -7082,13 +7681,13 @@
       <c r="E35" s="7"/>
       <c r="F35" s="10"/>
       <c r="G35" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H35" s="7">
         <v>57000</v>
       </c>
       <c r="I35" s="10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J35" s="7">
         <v>57000</v>
@@ -7106,14 +7705,14 @@
       <c r="E36" s="14"/>
       <c r="F36" s="10"/>
       <c r="G36" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H36" s="42">
         <f>H34+H35</f>
         <v>-794875.2</v>
       </c>
       <c r="I36" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J36" s="7">
         <v>-862186.73</v>
@@ -7158,7 +7757,7 @@
     </row>
     <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A39" s="56" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B39" s="28">
         <v>45530</v>
@@ -7207,7 +7806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961B3AB4-C9A4-46F9-AED6-DC61A66CC09A}">
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -7263,7 +7862,7 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" s="28">
         <v>45897</v>
@@ -7314,7 +7913,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="78">
         <v>45874</v>
@@ -7346,7 +7945,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A5" s="77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="78">
         <v>45875</v>
@@ -7378,7 +7977,7 @@
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A6" s="77" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B6" s="78">
         <v>45875</v>
@@ -7410,7 +8009,7 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A7" s="77" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B7" s="78">
         <v>45876</v>
@@ -7442,7 +8041,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A8" s="77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="78">
         <v>45876</v>
@@ -7506,7 +8105,7 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A10" s="77" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B10" s="78">
         <v>45877</v>
@@ -7538,7 +8137,7 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A11" s="77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B11" s="78">
         <v>45889</v>
@@ -7569,7 +8168,7 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A12" s="77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B12" s="78">
         <v>45890</v>
@@ -7600,7 +8199,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B13" s="78">
         <v>45891</v>
@@ -7631,7 +8230,7 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A14" s="77" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B14" s="78">
         <v>45896</v>
@@ -7662,7 +8261,7 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A15" s="77" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="78">
         <v>45897</v>
@@ -7770,14 +8369,14 @@
       <c r="E19" s="32"/>
       <c r="F19" s="30"/>
       <c r="G19" s="32" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H19" s="41">
         <f>H17+H18</f>
         <v>-522636.73</v>
       </c>
       <c r="I19" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J19" s="7">
         <v>-553251.32999999996</v>
@@ -7817,13 +8416,13 @@
       <c r="E21" s="32"/>
       <c r="F21" s="30"/>
       <c r="G21" s="32" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H21" s="35">
         <v>10130</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J21" s="7">
         <v>8610</v>
@@ -7890,13 +8489,13 @@
       <c r="E24" s="7"/>
       <c r="F24" s="10"/>
       <c r="G24" s="38" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H24" s="7">
         <v>57000</v>
       </c>
       <c r="I24" s="11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J24" s="7">
         <v>57000</v>
@@ -7914,14 +8513,14 @@
       <c r="E25" s="14"/>
       <c r="F25" s="10"/>
       <c r="G25" s="38" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="H25" s="42">
         <f>H23+H24</f>
         <v>-862186.73</v>
       </c>
       <c r="I25" s="11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J25" s="7">
         <v>-882671.33</v>
@@ -7958,678 +8557,4 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7193655-9E82-4E5C-9879-086AA4339AB9}">
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="28">
-        <v>44736</v>
-      </c>
-      <c r="C2" s="29">
-        <v>40000</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="37">
-        <v>0.15559999999999999</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>6223.9999999999991</v>
-      </c>
-      <c r="H2" s="32">
-        <v>0</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="34">
-        <f>SUM(H2:H2)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45868</v>
-      </c>
-      <c r="C4" s="29">
-        <v>1800</v>
-      </c>
-      <c r="D4" s="30">
-        <v>20</v>
-      </c>
-      <c r="E4" s="31">
-        <v>36079.74</v>
-      </c>
-      <c r="F4" s="30">
-        <v>22.9</v>
-      </c>
-      <c r="G4" s="31">
-        <v>41128.699999999997</v>
-      </c>
-      <c r="H4" s="32">
-        <f t="shared" ref="H4:H12" si="0">G4-E4</f>
-        <v>5048.9599999999991</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45868</v>
-      </c>
-      <c r="C5" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D5" s="30">
-        <v>4.7</v>
-      </c>
-      <c r="E5" s="31">
-        <v>47104.1</v>
-      </c>
-      <c r="F5" s="30">
-        <v>5.5</v>
-      </c>
-      <c r="G5" s="31">
-        <v>54878.18</v>
-      </c>
-      <c r="H5" s="32">
-        <f t="shared" si="0"/>
-        <v>7774.0800000000017</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45867</v>
-      </c>
-      <c r="C6" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="30">
-        <v>87</v>
-      </c>
-      <c r="E6" s="31">
-        <v>87192.7</v>
-      </c>
-      <c r="F6" s="30">
-        <v>22.9</v>
-      </c>
-      <c r="G6" s="31">
-        <v>22849.279999999999</v>
-      </c>
-      <c r="H6" s="32">
-        <f t="shared" si="0"/>
-        <v>-64343.42</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="28">
-        <v>45862</v>
-      </c>
-      <c r="C7" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D7" s="30">
-        <v>87</v>
-      </c>
-      <c r="E7" s="31">
-        <v>87192.7</v>
-      </c>
-      <c r="F7" s="30">
-        <v>22.4</v>
-      </c>
-      <c r="G7" s="31">
-        <v>22350.38</v>
-      </c>
-      <c r="H7" s="32">
-        <f t="shared" si="0"/>
-        <v>-64842.319999999992</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="28">
-        <v>45856</v>
-      </c>
-      <c r="C8" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D8" s="30">
-        <v>87</v>
-      </c>
-      <c r="E8" s="31">
-        <v>87192.7</v>
-      </c>
-      <c r="F8" s="30">
-        <v>22.2</v>
-      </c>
-      <c r="G8" s="31">
-        <v>22150.83</v>
-      </c>
-      <c r="H8" s="32">
-        <f t="shared" si="0"/>
-        <v>-65041.869999999995</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="28">
-        <v>45854</v>
-      </c>
-      <c r="C9" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D9" s="30">
-        <v>87</v>
-      </c>
-      <c r="E9" s="31">
-        <v>87192.7</v>
-      </c>
-      <c r="F9" s="30">
-        <v>21.7</v>
-      </c>
-      <c r="G9" s="31">
-        <v>21651.94</v>
-      </c>
-      <c r="H9" s="32">
-        <f t="shared" si="0"/>
-        <v>-65540.759999999995</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="28">
-        <v>45841</v>
-      </c>
-      <c r="C10" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D10" s="30">
-        <v>81</v>
-      </c>
-      <c r="E10" s="31">
-        <v>81179.41</v>
-      </c>
-      <c r="F10" s="30">
-        <v>21</v>
-      </c>
-      <c r="G10" s="31">
-        <v>20953.490000000002</v>
-      </c>
-      <c r="H10" s="32">
-        <f t="shared" si="0"/>
-        <v>-60225.919999999998</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="B11" s="28">
-        <v>45841</v>
-      </c>
-      <c r="C11" s="29">
-        <v>2500</v>
-      </c>
-      <c r="D11" s="30">
-        <v>9</v>
-      </c>
-      <c r="E11" s="31">
-        <v>22549.84</v>
-      </c>
-      <c r="F11" s="30">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="G11" s="31">
-        <v>25443.51</v>
-      </c>
-      <c r="H11" s="32">
-        <f t="shared" si="0"/>
-        <v>2893.6699999999983</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="28">
-        <v>45840</v>
-      </c>
-      <c r="C12" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="30">
-        <v>81</v>
-      </c>
-      <c r="E12" s="31">
-        <v>81179.41</v>
-      </c>
-      <c r="F12" s="30">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="G12" s="31">
-        <v>19556.59</v>
-      </c>
-      <c r="H12" s="32">
-        <f t="shared" si="0"/>
-        <v>-61622.820000000007</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32">
-        <f>SUM(E4:E12)</f>
-        <v>616863.30000000005</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="32">
-        <f t="shared" ref="G13:H13" si="1">SUM(G4:G12)</f>
-        <v>250962.9</v>
-      </c>
-      <c r="H13" s="32">
-        <f t="shared" si="1"/>
-        <v>-365900.39999999997</v>
-      </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="26"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="34">
-        <f>H3+H13</f>
-        <v>-365900.39999999997</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="7">
-        <v>-101058.68999999999</v>
-      </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="32">
-        <v>-187350.93</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="7">
-        <v>-86292.24</v>
-      </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-    </row>
-    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="H16" s="34">
-        <f>H14+H15</f>
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="J16" s="7">
-        <v>-187350.93</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="35">
-        <v>377810</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="7">
-        <v>336660</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-    </row>
-    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="H18" s="35">
-        <v>8610</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J18" s="7">
-        <v>41150</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="26"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="41">
-        <f>H17+H18</f>
-        <v>386420</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="7">
-        <v>377810</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="5"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="46">
-        <f>H16-H19</f>
-        <v>-939671.33</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="7">
-        <v>-565160.92999999993</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A21" s="5"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H21" s="38">
-        <v>57000</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J21" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A22" s="6"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="H22" s="39">
-        <f>H20+H21</f>
-        <v>-882671.33</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>32</v>
-      </c>
-      <c r="J22" s="7">
-        <v>-508160.92999999993</v>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K23" s="7"/>
-      <c r="M23" s="7"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M24" s="7"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M25" s="7"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C26" s="12"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="10"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:H12">
-    <sortCondition descending="1" ref="B4:B12"/>
-    <sortCondition ref="A4:A12"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6937" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0ACB508E-7D19-423E-A7C2-E8E031655DCE}"/>
+  <xr:revisionPtr revIDLastSave="7142" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADE64E70-6270-4B39-9CFD-D47E37DA75DD}"/>
   <bookViews>
-    <workbookView xWindow="5748" yWindow="1104" windowWidth="17292" windowHeight="10764" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1152" yWindow="1152" windowWidth="15996" windowHeight="10764" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="APR26" sheetId="96" r:id="rId1"/>
-    <sheet name="MAR26" sheetId="95" r:id="rId2"/>
-    <sheet name="FEB26" sheetId="94" r:id="rId3"/>
-    <sheet name="JAN26" sheetId="93" r:id="rId4"/>
-    <sheet name="DEC25" sheetId="92" r:id="rId5"/>
-    <sheet name="NOV25" sheetId="91" r:id="rId6"/>
-    <sheet name="OCT25" sheetId="90" r:id="rId7"/>
-    <sheet name="SEP25" sheetId="89" r:id="rId8"/>
-    <sheet name="AUG25" sheetId="88" r:id="rId9"/>
-    <sheet name="JUL25" sheetId="87" r:id="rId10"/>
-    <sheet name="JUN25" sheetId="86" r:id="rId11"/>
-    <sheet name="MAY25" sheetId="85" r:id="rId12"/>
+    <sheet name="JUN26" sheetId="98" r:id="rId1"/>
+    <sheet name="MAY26" sheetId="97" r:id="rId2"/>
+    <sheet name="APR26" sheetId="96" r:id="rId3"/>
+    <sheet name="MAR26" sheetId="95" r:id="rId4"/>
+    <sheet name="FEB26" sheetId="94" r:id="rId5"/>
+    <sheet name="JAN26" sheetId="93" r:id="rId6"/>
+    <sheet name="DEC25" sheetId="92" r:id="rId7"/>
+    <sheet name="NOV25" sheetId="91" r:id="rId8"/>
+    <sheet name="OCT25" sheetId="90" r:id="rId9"/>
+    <sheet name="SEP25" sheetId="89" r:id="rId10"/>
+    <sheet name="AUG25" sheetId="88" r:id="rId11"/>
+    <sheet name="JUL25" sheetId="87" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="68">
   <si>
     <t>Name</t>
   </si>
@@ -163,9 +163,6 @@
     <t>KCE</t>
   </si>
   <si>
-    <t>ASP</t>
-  </si>
-  <si>
     <t>PTG</t>
   </si>
   <si>
@@ -270,7 +267,7 @@
     <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00"/>
     <numFmt numFmtId="171" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <name val="Cordia New"/>
@@ -342,13 +339,6 @@
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -528,12 +518,10 @@
     <xf numFmtId="4" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="10" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -541,69 +529,71 @@
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="14" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="17" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="17" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="18" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="18" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="19" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="165" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="14" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="167" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="18" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="17" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="21" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="22" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="171" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="171" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="171" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="171" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="10" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="171" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -619,6 +609,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -968,26 +962,1794 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DFDC5F2-0211-490B-8DD7-A2B28B5D4706}">
-  <dimension ref="A1:L21"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24B6D7D9-1BF8-42AF-8BE9-2337E6298F4C}">
+  <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="12.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.25" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.375" style="7" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.75" style="7" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="21.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.625" style="6"/>
+    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="28">
+        <v>46178</v>
+      </c>
+      <c r="C2" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="37">
+        <v>0.1915</v>
+      </c>
+      <c r="G2" s="31">
+        <f t="shared" ref="G2:G9" si="0">C2*F2</f>
+        <v>3830</v>
+      </c>
+      <c r="H2" s="40">
+        <f t="shared" ref="H2:H9" si="1">G2*0.9</f>
+        <v>3447</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="28">
+        <v>46183</v>
+      </c>
+      <c r="C3" s="29">
+        <v>900</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="51">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G3" s="31">
+        <f t="shared" si="0"/>
+        <v>184.5</v>
+      </c>
+      <c r="H3" s="40">
+        <f t="shared" si="1"/>
+        <v>166.05</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="28">
+        <v>46183</v>
+      </c>
+      <c r="C4" s="84">
+        <v>45000</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="31"/>
+      <c r="F4" s="37">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="G4" s="31">
+        <f t="shared" si="0"/>
+        <v>9999</v>
+      </c>
+      <c r="H4" s="40">
+        <f t="shared" si="1"/>
+        <v>8999.1</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="28">
+        <v>46184</v>
+      </c>
+      <c r="C5" s="29">
+        <v>55000</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="31"/>
+      <c r="F5" s="52">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="G5" s="31">
+        <f t="shared" si="0"/>
+        <v>15400.000000000002</v>
+      </c>
+      <c r="H5" s="40">
+        <f t="shared" si="1"/>
+        <v>13860.000000000002</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="28">
+        <v>46184</v>
+      </c>
+      <c r="C6" s="97">
+        <v>69000</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="31"/>
+      <c r="F6" s="51">
+        <v>0.1946</v>
+      </c>
+      <c r="G6" s="31">
+        <f t="shared" si="0"/>
+        <v>13427.4</v>
+      </c>
+      <c r="H6" s="40">
+        <f t="shared" si="1"/>
+        <v>12084.66</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B7" s="28">
+        <v>46185</v>
+      </c>
+      <c r="C7" s="29">
+        <v>7200</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="31"/>
+      <c r="F7" s="37">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G7" s="31">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="H7" s="40">
+        <f t="shared" si="1"/>
+        <v>1134</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="28">
+        <v>46189</v>
+      </c>
+      <c r="C8" s="84">
+        <v>25000</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="52">
+        <v>0.12039999999999999</v>
+      </c>
+      <c r="G8" s="31">
+        <f t="shared" si="0"/>
+        <v>3010</v>
+      </c>
+      <c r="H8" s="40">
+        <f t="shared" si="1"/>
+        <v>2709</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="17"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="28">
+        <v>46191</v>
+      </c>
+      <c r="C9" s="97">
+        <v>50000</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="31"/>
+      <c r="F9" s="52">
+        <v>0.1434</v>
+      </c>
+      <c r="G9" s="31">
+        <f t="shared" si="0"/>
+        <v>7170</v>
+      </c>
+      <c r="H9" s="40">
+        <f t="shared" si="1"/>
+        <v>6453</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="31"/>
+      <c r="H10" s="43">
+        <f>SUM(H2:H9)</f>
+        <v>48852.81</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B11" s="28">
+        <v>45824</v>
+      </c>
+      <c r="C11" s="29">
+        <v>0</v>
+      </c>
+      <c r="D11" s="30">
+        <v>67</v>
+      </c>
+      <c r="E11" s="50">
+        <v>0</v>
+      </c>
+      <c r="F11" s="30">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="G11" s="31">
+        <v>0</v>
+      </c>
+      <c r="H11" s="32">
+        <f t="shared" ref="H11" si="2">G11-E11</f>
+        <v>0</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+      <c r="H12" s="41">
+        <f>SUM(H11:H11)</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="26"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H13" s="43">
+        <f>H10+H12</f>
+        <v>48852.81</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="J13" s="7">
+        <v>136023.70199999999</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="26"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="32">
+        <v>-106336.46400000001</v>
+      </c>
+      <c r="I14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" s="7">
+        <v>-242360.16599999997</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="26"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H15" s="34">
+        <f>H13+H14</f>
+        <v>-57483.65400000001</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J15" s="7">
+        <v>-106336.46399999998</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H16" s="7">
+        <v>169620</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J16" s="7">
+        <v>127030</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="H17" s="35">
+        <v>14610</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="J17" s="7">
+        <v>42590</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H18" s="41">
+        <f>H16+H17</f>
+        <v>184230</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="J18" s="7">
+        <v>169620</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A19" s="5"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="46">
+        <f>H15-H18</f>
+        <v>-241713.65400000001</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="J19" s="7">
+        <v>-275956.46399999998</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A20" s="5"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H20" s="7">
+        <v>60000</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J20" s="7">
+        <v>60000</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A21" s="6"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="8"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H21" s="39">
+        <f>H19+H20</f>
+        <v>-181713.65400000001</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J21" s="7">
+        <v>-215956.46399999998</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="7"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G22" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" s="7">
+        <v>221247.59599999999</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J22" s="7">
+        <v>84048.91399999999</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="N22" s="13"/>
+    </row>
+    <row r="23" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G23" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="H23" s="32">
+        <f>H22+H10</f>
+        <v>270100.40599999996</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J23" s="7">
+        <v>221247.59599999999</v>
+      </c>
+      <c r="K23" s="7"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G24" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="H24" s="32">
+        <f>H23-H18</f>
+        <v>85870.405999999959</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J24" s="7">
+        <v>51627.59599999999</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="M24" s="7"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M25" s="7"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K27" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N9">
+    <sortCondition ref="B2:B9"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805BC19F-42DC-4CD3-B954-E9F19E56BFF7}">
+  <dimension ref="A1:N40"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="55"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="74" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="75">
+        <v>45903</v>
+      </c>
+      <c r="C2" s="76">
+        <v>120000</v>
+      </c>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74">
+        <v>0.15454999999999999</v>
+      </c>
+      <c r="G2" s="79">
+        <v>18546</v>
+      </c>
+      <c r="H2" s="79">
+        <v>16691.400000000001</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="74" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="75">
+        <v>45910</v>
+      </c>
+      <c r="C3" s="76">
+        <v>1200</v>
+      </c>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="80">
+        <v>0.31</v>
+      </c>
+      <c r="G3" s="79">
+        <v>372</v>
+      </c>
+      <c r="H3" s="79">
+        <v>339.6</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C4" s="81">
+        <v>17500</v>
+      </c>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="80">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G4" s="79">
+        <v>3587.5</v>
+      </c>
+      <c r="H4" s="79">
+        <v>3228.75</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C5" s="76">
+        <v>4000</v>
+      </c>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="80">
+        <v>0.15</v>
+      </c>
+      <c r="G5" s="79">
+        <v>600</v>
+      </c>
+      <c r="H5" s="79">
+        <v>540</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C6" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74">
+        <v>1</v>
+      </c>
+      <c r="G6" s="79">
+        <v>5000</v>
+      </c>
+      <c r="H6" s="79">
+        <v>4500</v>
+      </c>
+      <c r="I6" s="10"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C7" s="82">
+        <v>55000</v>
+      </c>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="80">
+        <v>0.2261</v>
+      </c>
+      <c r="G7" s="79">
+        <v>12435.5</v>
+      </c>
+      <c r="H7" s="79">
+        <v>11191.95</v>
+      </c>
+      <c r="I7" s="10"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="75">
+        <v>45909</v>
+      </c>
+      <c r="C8" s="81">
+        <v>50000</v>
+      </c>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="G8" s="79">
+        <v>11110</v>
+      </c>
+      <c r="H8" s="79">
+        <v>9999</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C9" s="81">
+        <v>69000</v>
+      </c>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="80">
+        <v>0.19650000000000001</v>
+      </c>
+      <c r="G9" s="79">
+        <v>13558.5</v>
+      </c>
+      <c r="H9" s="79">
+        <v>12202.65</v>
+      </c>
+      <c r="I9" s="10"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C10" s="82">
+        <v>7200</v>
+      </c>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G10" s="79">
+        <v>1260</v>
+      </c>
+      <c r="H10" s="79">
+        <v>1134</v>
+      </c>
+      <c r="I10" s="10"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C11" s="82">
+        <v>4200</v>
+      </c>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="83">
+        <v>0.24</v>
+      </c>
+      <c r="G11" s="79">
+        <v>1008</v>
+      </c>
+      <c r="H11" s="79">
+        <v>907.2</v>
+      </c>
+      <c r="I11" s="10"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="75">
+        <v>45910</v>
+      </c>
+      <c r="C12" s="81">
+        <v>81000</v>
+      </c>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="80">
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="79">
+        <v>20250</v>
+      </c>
+      <c r="H12" s="79">
+        <v>19926</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C13" s="76">
+        <v>27000</v>
+      </c>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="79">
+        <v>1350</v>
+      </c>
+      <c r="H13" s="79">
+        <v>1350</v>
+      </c>
+      <c r="I13" s="10"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C14" s="76">
+        <v>27000</v>
+      </c>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="79">
+        <v>13500</v>
+      </c>
+      <c r="H14" s="79">
+        <v>12825</v>
+      </c>
+      <c r="I14" s="10"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="75">
+        <v>45910</v>
+      </c>
+      <c r="C15" s="81">
+        <v>17500</v>
+      </c>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="79">
+        <v>1750</v>
+      </c>
+      <c r="H15" s="79">
+        <v>1575</v>
+      </c>
+      <c r="I15" s="10"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A16" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C16" s="76">
+        <v>20000</v>
+      </c>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="80">
+        <v>0.1128</v>
+      </c>
+      <c r="G16" s="79">
+        <v>2256</v>
+      </c>
+      <c r="H16" s="79">
+        <v>2256</v>
+      </c>
+      <c r="I16" s="10"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A17" s="74" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C17" s="76">
+        <v>1000</v>
+      </c>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="80">
+        <v>0.36</v>
+      </c>
+      <c r="G17" s="79">
+        <v>360</v>
+      </c>
+      <c r="H17" s="79">
+        <v>324</v>
+      </c>
+      <c r="I17" s="10"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A18" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C18" s="76">
+        <v>8000</v>
+      </c>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74">
+        <v>0.8</v>
+      </c>
+      <c r="G18" s="79">
+        <v>6400</v>
+      </c>
+      <c r="H18" s="79">
+        <v>5760</v>
+      </c>
+      <c r="I18" s="10"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A19" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C19" s="76">
+        <v>50000</v>
+      </c>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="83">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="G19" s="79">
+        <v>6625</v>
+      </c>
+      <c r="H19" s="79">
+        <v>5962.5</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A20" s="74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C20" s="82">
+        <v>25000</v>
+      </c>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="83">
+        <v>0.17169999999999999</v>
+      </c>
+      <c r="G20" s="79">
+        <v>4292.5</v>
+      </c>
+      <c r="H20" s="79">
+        <v>3863.25</v>
+      </c>
+      <c r="I20" s="10"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="34">
+        <f>SUM(H2:H20)</f>
+        <v>114576.29999999999</v>
+      </c>
+      <c r="I21" s="10"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="75">
+        <v>45903</v>
+      </c>
+      <c r="C22" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D22" s="74">
+        <v>7.5</v>
+      </c>
+      <c r="E22" s="79">
+        <v>37583.06</v>
+      </c>
+      <c r="F22" s="74">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G22" s="79">
+        <v>41408.080000000002</v>
+      </c>
+      <c r="H22" s="79">
+        <v>3825.02</v>
+      </c>
+      <c r="I22" s="56"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="75">
+        <v>45908</v>
+      </c>
+      <c r="C23" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D23" s="74">
+        <v>24.1</v>
+      </c>
+      <c r="E23" s="79">
+        <v>120766.9</v>
+      </c>
+      <c r="F23" s="74">
+        <v>23.4</v>
+      </c>
+      <c r="G23" s="79">
+        <v>116740.86</v>
+      </c>
+      <c r="H23" s="79">
+        <v>-4026.04</v>
+      </c>
+      <c r="I23" s="56"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C24" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D24" s="74">
+        <v>23.2</v>
+      </c>
+      <c r="E24" s="79">
+        <v>116256.93</v>
+      </c>
+      <c r="F24" s="74">
+        <v>23.4</v>
+      </c>
+      <c r="G24" s="79">
+        <v>116740.86</v>
+      </c>
+      <c r="H24" s="74">
+        <v>483.93</v>
+      </c>
+      <c r="I24" s="56"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C25" s="74">
+        <v>4000</v>
+      </c>
+      <c r="D25" s="74">
+        <v>23.1</v>
+      </c>
+      <c r="E25" s="79">
+        <v>92604.66</v>
+      </c>
+      <c r="F25" s="74">
+        <v>25.75</v>
+      </c>
+      <c r="G25" s="79">
+        <v>102771.87</v>
+      </c>
+      <c r="H25" s="79">
+        <v>10167.209999999999</v>
+      </c>
+      <c r="I25" s="56"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C26" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D26" s="74">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E26" s="79">
+        <v>44097.46</v>
+      </c>
+      <c r="F26" s="74">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G26" s="79">
+        <v>48392.57</v>
+      </c>
+      <c r="H26" s="79">
+        <v>4295.1099999999997</v>
+      </c>
+      <c r="I26" s="56"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="26"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="32">
+        <f>SUM(E22:E26)</f>
+        <v>411309.01000000007</v>
+      </c>
+      <c r="F27" s="30"/>
+      <c r="G27" s="32">
+        <f>SUM(G22:G26)</f>
+        <v>426054.24</v>
+      </c>
+      <c r="H27" s="32">
+        <f>SUM(H22:H26)</f>
+        <v>14745.23</v>
+      </c>
+      <c r="I27" s="32"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+    </row>
+    <row r="28" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A28" s="26"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="34">
+        <f>H21+H27</f>
+        <v>129321.52999999998</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J28" s="7">
+        <v>30614.600000000002</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="26"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="32">
+        <v>-522636.73</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K29" s="7"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+    </row>
+    <row r="30" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="26"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="41">
+        <f>H28+H29</f>
+        <v>-393315.2</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" s="7">
+        <v>-522636.73</v>
+      </c>
+      <c r="K30" s="7"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+    </row>
+    <row r="31" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="26"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="35">
+        <v>396550</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+    </row>
+    <row r="32" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="26"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="35">
+        <v>62010</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="7">
+        <v>10130</v>
+      </c>
+      <c r="K32" s="7"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+    </row>
+    <row r="33" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="26"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="41">
+        <f>H31+H32</f>
+        <v>458560</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" s="7">
+        <v>396550</v>
+      </c>
+      <c r="K33" s="7"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="5"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="45">
+        <f>H30-H33</f>
+        <v>-851875.2</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="7">
+        <v>-919186.73</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="5"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K35" s="7"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="6"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="42">
+        <f>H34+H35</f>
+        <v>-794875.2</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="7">
+        <v>-862186.73</v>
+      </c>
+      <c r="K36" s="7"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K37" s="7"/>
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="28">
+        <v>45546</v>
+      </c>
+      <c r="C38" s="29">
+        <v>24000</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="31"/>
+      <c r="F38" s="51">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="G38" s="31">
+        <f>C38*F38</f>
+        <v>957.59999999999991</v>
+      </c>
+      <c r="H38" s="53">
+        <f>G38*0.9</f>
+        <v>861.83999999999992</v>
+      </c>
+      <c r="K38" s="7"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+    </row>
+    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="28">
+        <v>45530</v>
+      </c>
+      <c r="C39" s="29">
+        <v>30000</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="31"/>
+      <c r="F39" s="37">
+        <v>0.19</v>
+      </c>
+      <c r="G39" s="31">
+        <f>C39*F39</f>
+        <v>5700</v>
+      </c>
+      <c r="H39" s="32">
+        <f>G39</f>
+        <v>5700</v>
+      </c>
+      <c r="K39" s="7"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C40" s="12"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="10"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N20">
+    <sortCondition ref="A2:A20"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961B3AB4-C9A4-46F9-AED6-DC61A66CC09A}">
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1016,384 +2778,699 @@
       <c r="J1" s="5"/>
       <c r="K1" s="6"/>
       <c r="L1" s="6"/>
-    </row>
-    <row r="2" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="B2" s="28">
-        <v>46136</v>
+        <v>45897</v>
       </c>
       <c r="C2" s="29">
-        <v>6000</v>
+        <v>600</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" s="37">
-        <v>0.5</v>
+      <c r="E2" s="31"/>
+      <c r="F2" s="72">
+        <v>2.5</v>
       </c>
       <c r="G2" s="31">
         <f>C2*F2</f>
-        <v>3000</v>
+        <v>1500</v>
       </c>
       <c r="H2" s="32">
         <f>G2*0.9</f>
-        <v>2700</v>
-      </c>
-      <c r="I2" s="17"/>
+        <v>1350</v>
+      </c>
+      <c r="I2" s="11"/>
       <c r="J2" s="7"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-    </row>
-    <row r="3" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="B3" s="28">
-        <v>46140</v>
-      </c>
-      <c r="C3" s="29">
-        <v>7500</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="37">
-        <v>1.4</v>
-      </c>
-      <c r="G3" s="31">
-        <f>C3*F3</f>
-        <v>10500</v>
-      </c>
-      <c r="H3" s="32">
-        <v>9472.5</v>
-      </c>
-      <c r="I3" s="17"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="41">
+        <f>SUM(H2:H2)</f>
+        <v>1350</v>
+      </c>
+      <c r="I3" s="11"/>
       <c r="J3" s="7"/>
-      <c r="K3" s="6"/>
-      <c r="L3" s="6"/>
-    </row>
-    <row r="4" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="27"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="31"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="31"/>
-      <c r="H4" s="34">
-        <f>SUM(H2:H3)</f>
-        <v>12172.5</v>
-      </c>
-      <c r="I4" s="19"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="75">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="76">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="77">
+        <v>1.88</v>
+      </c>
+      <c r="E4" s="77">
+        <v>18841.64</v>
+      </c>
+      <c r="F4" s="77">
+        <v>1.9</v>
+      </c>
+      <c r="G4" s="77">
+        <v>18957.919999999998</v>
+      </c>
+      <c r="H4" s="77">
+        <v>116.28</v>
+      </c>
+      <c r="I4" s="11"/>
       <c r="J4" s="7"/>
-      <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-    </row>
-    <row r="5" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45757</v>
-      </c>
-      <c r="C5" s="29">
-        <v>0</v>
-      </c>
-      <c r="D5" s="30">
-        <v>61.5</v>
-      </c>
-      <c r="E5" s="31">
-        <v>61636.22</v>
-      </c>
-      <c r="F5" s="30">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="G5" s="31">
-        <v>16563.23</v>
-      </c>
-      <c r="H5" s="49">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="75">
+        <v>45875</v>
+      </c>
+      <c r="C5" s="76">
+        <v>2800</v>
+      </c>
+      <c r="D5" s="77">
+        <v>10.5</v>
+      </c>
+      <c r="E5" s="77">
+        <v>29465.119999999999</v>
+      </c>
+      <c r="F5" s="77">
+        <v>11.6</v>
+      </c>
+      <c r="G5" s="77">
+        <v>32408.06</v>
+      </c>
+      <c r="H5" s="77">
+        <v>2942.94</v>
+      </c>
+      <c r="I5" s="11"/>
       <c r="J5" s="7"/>
-      <c r="K5" s="15"/>
-      <c r="L5" s="6"/>
-    </row>
-    <row r="6" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="26"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32">
-        <f>SUM(E5:E5)</f>
-        <v>61636.22</v>
-      </c>
-      <c r="F6" s="30"/>
-      <c r="G6" s="32">
-        <f>SUM(G5:G5)</f>
-        <v>16563.23</v>
-      </c>
-      <c r="H6" s="34">
-        <f>SUM(H5:H5)</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="75">
+        <v>45875</v>
+      </c>
+      <c r="C6" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D6" s="77">
+        <v>3.9</v>
+      </c>
+      <c r="E6" s="77">
+        <v>19543.2</v>
+      </c>
+      <c r="F6" s="77">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="G6" s="77">
+        <v>22549.95</v>
+      </c>
+      <c r="H6" s="77">
+        <v>3006.75</v>
+      </c>
+      <c r="I6" s="11"/>
       <c r="J6" s="7"/>
-      <c r="K6" s="15"/>
-      <c r="L6" s="6"/>
-    </row>
-    <row r="7" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32" t="s">
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="75">
+        <v>45876</v>
+      </c>
+      <c r="C7" s="76">
+        <v>3200</v>
+      </c>
+      <c r="D7" s="77">
+        <v>9.25</v>
+      </c>
+      <c r="E7" s="77">
+        <v>29665.56</v>
+      </c>
+      <c r="F7" s="77">
+        <v>9.4</v>
+      </c>
+      <c r="G7" s="77">
+        <v>30013.37</v>
+      </c>
+      <c r="H7" s="77">
+        <v>347.81</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="75">
+        <v>45876</v>
+      </c>
+      <c r="C8" s="76">
+        <v>10000</v>
+      </c>
+      <c r="D8" s="77">
+        <v>1.85</v>
+      </c>
+      <c r="E8" s="77">
+        <v>18540.98</v>
+      </c>
+      <c r="F8" s="77">
+        <v>2.06</v>
+      </c>
+      <c r="G8" s="77">
+        <v>20554.38</v>
+      </c>
+      <c r="H8" s="77">
+        <v>2013.4</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="75">
+        <v>45877</v>
+      </c>
+      <c r="C9" s="76">
+        <v>6000</v>
+      </c>
+      <c r="D9" s="77">
+        <v>6.1</v>
+      </c>
+      <c r="E9" s="77">
+        <v>36681.06</v>
+      </c>
+      <c r="F9" s="77">
+        <v>6.7</v>
+      </c>
+      <c r="G9" s="77">
+        <v>40110.97</v>
+      </c>
+      <c r="H9" s="77">
+        <v>3429.91</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="75">
+        <v>45877</v>
+      </c>
+      <c r="C10" s="76">
+        <v>3000</v>
+      </c>
+      <c r="D10" s="77">
+        <v>27.75</v>
+      </c>
+      <c r="E10" s="77">
+        <v>83434.39</v>
+      </c>
+      <c r="F10" s="77">
+        <v>31</v>
+      </c>
+      <c r="G10" s="77">
+        <v>92794.01</v>
+      </c>
+      <c r="H10" s="77">
+        <v>9359.6200000000008</v>
+      </c>
+      <c r="I10" s="73"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="75">
+        <v>45889</v>
+      </c>
+      <c r="C11" s="76">
+        <v>4000</v>
+      </c>
+      <c r="D11" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E11" s="77">
+        <v>96613.52</v>
+      </c>
+      <c r="F11" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G11" s="77">
+        <v>96984.72</v>
+      </c>
+      <c r="H11" s="77">
+        <v>371.2</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="75">
+        <v>45890</v>
+      </c>
+      <c r="C12" s="76">
+        <v>4000</v>
+      </c>
+      <c r="D12" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E12" s="77">
+        <v>96613.52</v>
+      </c>
+      <c r="F12" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G12" s="77">
+        <v>96984.72</v>
+      </c>
+      <c r="H12" s="77">
+        <v>371.2</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="75">
+        <v>45891</v>
+      </c>
+      <c r="C13" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D13" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E13" s="77">
+        <v>120766.9</v>
+      </c>
+      <c r="F13" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G13" s="77">
+        <v>121230.88</v>
+      </c>
+      <c r="H13" s="77">
+        <v>463.98</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="75">
+        <v>45896</v>
+      </c>
+      <c r="C14" s="76">
+        <v>6000</v>
+      </c>
+      <c r="D14" s="77">
+        <v>7.3</v>
+      </c>
+      <c r="E14" s="77">
+        <v>43897.02</v>
+      </c>
+      <c r="F14" s="77">
+        <v>8.4</v>
+      </c>
+      <c r="G14" s="77">
+        <v>50288.37</v>
+      </c>
+      <c r="H14" s="77">
+        <v>6391.35</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="75">
+        <v>45897</v>
+      </c>
+      <c r="C15" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D15" s="77">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E15" s="77">
+        <v>11024.36</v>
+      </c>
+      <c r="F15" s="77">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G15" s="77">
+        <v>11474.52</v>
+      </c>
+      <c r="H15" s="77">
+        <v>450.16</v>
+      </c>
+      <c r="I15" s="78"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32">
+        <f>SUM(E4:E15)</f>
+        <v>605087.27</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32">
+        <f>SUM(G4:G15)</f>
+        <v>634351.87</v>
+      </c>
+      <c r="H16" s="32">
+        <f>SUM(H4:H15)</f>
+        <v>29264.600000000002</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="34">
-        <f>H4+H6</f>
-        <v>12172.5</v>
-      </c>
-      <c r="I7" s="32" t="s">
+      <c r="H17" s="41">
+        <f>H3+H16</f>
+        <v>30614.600000000002</v>
+      </c>
+      <c r="I17" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="J7" s="34">
-        <v>-243272.66599999997</v>
-      </c>
-      <c r="K7" s="15"/>
-      <c r="L7" s="6"/>
-    </row>
-    <row r="8" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
+      <c r="J17" s="7">
+        <v>-365900.39999999997</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="7">
-        <v>-254532.66599999997</v>
-      </c>
-      <c r="I8" s="32" t="s">
+      <c r="H18" s="32">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="I18" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="32">
-        <v>-11260</v>
-      </c>
-      <c r="K8" s="15"/>
-      <c r="L8" s="6"/>
-    </row>
-    <row r="9" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
+      <c r="J18" s="7">
+        <v>-187350.93</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+    </row>
+    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="26"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="34">
-        <f>H7+H8</f>
-        <v>-242360.16599999997</v>
-      </c>
-      <c r="I9" s="62" t="s">
+      <c r="H19" s="41">
+        <f>H17+H18</f>
+        <v>-522636.73</v>
+      </c>
+      <c r="I19" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="41">
-        <v>-254532.66599999997</v>
-      </c>
-      <c r="K9" s="15"/>
-      <c r="L9" s="6"/>
-    </row>
-    <row r="10" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
+      <c r="J19" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+    </row>
+    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="26"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="32" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="7">
-        <v>98300</v>
-      </c>
-      <c r="I10" s="32" t="s">
+      <c r="H20" s="7">
+        <v>386420</v>
+      </c>
+      <c r="I20" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="J10" s="35">
-        <v>71260</v>
-      </c>
-      <c r="K10" s="15"/>
-      <c r="L10" s="6"/>
-    </row>
-    <row r="11" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="35">
-        <v>28860</v>
-      </c>
-      <c r="I11" s="32" t="s">
-        <v>24</v>
-      </c>
-      <c r="J11" s="35">
-        <v>26910</v>
-      </c>
-      <c r="K11" s="15"/>
-      <c r="L11" s="6"/>
-    </row>
-    <row r="12" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="26"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="32" t="s">
+      <c r="J20" s="7">
+        <v>377810</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+    </row>
+    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="26"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="35">
+        <v>10130</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" s="7">
+        <v>8610</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="26"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="34">
-        <f>H10+H11</f>
-        <v>127160</v>
-      </c>
-      <c r="I12" s="32" t="s">
+      <c r="H22" s="41">
+        <f>H20+H21</f>
+        <v>396550</v>
+      </c>
+      <c r="I22" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="J12" s="41">
-        <v>98300</v>
-      </c>
-      <c r="K12" s="15"/>
-      <c r="L12" s="6"/>
-    </row>
-    <row r="13" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="32" t="s">
+      <c r="J22" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="5"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="45">
-        <f>H9-H12</f>
-        <v>-369520.16599999997</v>
-      </c>
-      <c r="I13" s="32" t="s">
+      <c r="H23" s="47">
+        <f>H19-H22</f>
+        <v>-919186.73</v>
+      </c>
+      <c r="I23" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J13" s="45">
-        <f>J9-J12</f>
-        <v>-352832.66599999997</v>
-      </c>
-      <c r="K13" s="15"/>
-      <c r="L13" s="6"/>
-    </row>
-    <row r="14" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="5"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="38" t="s">
+      <c r="J23" s="7">
+        <v>-939671.33</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="5"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="38">
-        <v>60000</v>
-      </c>
-      <c r="I14" s="62" t="s">
+      <c r="H24" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I24" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="J14" s="97">
-        <v>60000</v>
-      </c>
-      <c r="K14" s="15"/>
-      <c r="L14" s="6"/>
-    </row>
-    <row r="15" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="6"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="38" t="s">
+      <c r="J24" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="6"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="38" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="39">
-        <f>H13+H14</f>
-        <v>-309520.16599999997</v>
-      </c>
-      <c r="I15" s="62" t="s">
+      <c r="H25" s="42">
+        <f>H23+H24</f>
+        <v>-862186.73</v>
+      </c>
+      <c r="I25" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="J15" s="41">
-        <f>J13+J14</f>
-        <v>-292832.66599999997</v>
-      </c>
-      <c r="K15" s="15"/>
-      <c r="L15" s="7"/>
-    </row>
-    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G16" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="H16" s="32">
-        <v>71876.41399999999</v>
-      </c>
-      <c r="J16" s="7"/>
-      <c r="L16" s="13"/>
-    </row>
-    <row r="17" spans="7:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="G17" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="H17" s="32">
-        <f>H16+H4</f>
-        <v>84048.91399999999</v>
-      </c>
-      <c r="J17" s="7"/>
-    </row>
-    <row r="18" spans="7:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G18" s="32" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="32">
-        <f>H17-H12</f>
-        <v>-43111.08600000001</v>
-      </c>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-    </row>
-    <row r="19" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="K19" s="7"/>
-    </row>
-    <row r="20" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="K20" s="7"/>
-    </row>
-    <row r="21" spans="7:11" x14ac:dyDescent="0.3">
-      <c r="J21" s="7"/>
+      <c r="J25" s="7">
+        <v>-882671.33</v>
+      </c>
+      <c r="K25" s="7"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K26" s="7"/>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D29" s="8"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="10"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="7"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -1403,7 +3480,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7193655-9E82-4E5C-9879-086AA4339AB9}">
   <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -1509,7 +3586,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="28">
         <v>45868</v>
@@ -1929,13 +4006,13 @@
       <c r="E18" s="32"/>
       <c r="F18" s="30"/>
       <c r="G18" s="32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H18" s="35">
         <v>8610</v>
       </c>
       <c r="I18" s="11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J18" s="7">
         <v>41150</v>
@@ -2077,724 +4154,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5EAFE1F0-60EA-46C8-9C11-E7180F21BFAA}">
-  <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
-    <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="29.375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.625" style="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.625" style="6" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.25" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="4"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45812</v>
-      </c>
-      <c r="C2" s="29">
-        <v>55000</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="37">
-        <v>0.2505</v>
-      </c>
-      <c r="G2" s="31">
-        <f t="shared" ref="G2:G9" si="0">C2*F2</f>
-        <v>13777.5</v>
-      </c>
-      <c r="H2" s="40">
-        <f t="shared" ref="H2:H7" si="1">G2*0.9</f>
-        <v>12399.75</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B3" s="28">
-        <v>45814</v>
-      </c>
-      <c r="C3" s="29">
-        <v>12500</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="53">
-        <v>0.215</v>
-      </c>
-      <c r="G3" s="31">
-        <f t="shared" si="0"/>
-        <v>2687.5</v>
-      </c>
-      <c r="H3" s="40">
-        <f t="shared" si="1"/>
-        <v>2418.75</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="6"/>
-      <c r="M3" s="6"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45814</v>
-      </c>
-      <c r="C4" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="37">
-        <v>0.1915</v>
-      </c>
-      <c r="G4" s="31">
-        <f t="shared" si="0"/>
-        <v>3830</v>
-      </c>
-      <c r="H4" s="40">
-        <f t="shared" si="1"/>
-        <v>3447</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="6"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45817</v>
-      </c>
-      <c r="C5" s="29">
-        <v>40000</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="37">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="G5" s="31">
-        <f t="shared" si="0"/>
-        <v>8888</v>
-      </c>
-      <c r="H5" s="40">
-        <f t="shared" si="1"/>
-        <v>7999.2</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="6"/>
-      <c r="M5" s="6"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45820</v>
-      </c>
-      <c r="C6" s="29">
-        <v>75000</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="54">
-        <v>0.19839999999999999</v>
-      </c>
-      <c r="G6" s="31">
-        <f t="shared" si="0"/>
-        <v>14880</v>
-      </c>
-      <c r="H6" s="40">
-        <f t="shared" si="1"/>
-        <v>13392</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="6"/>
-      <c r="M6" s="6"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B7" s="28">
-        <v>45820</v>
-      </c>
-      <c r="C7" s="29">
-        <v>7200</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="53">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G7" s="31">
-        <f t="shared" si="0"/>
-        <v>1260</v>
-      </c>
-      <c r="H7" s="40">
-        <f t="shared" si="1"/>
-        <v>1134</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="6"/>
-      <c r="M7" s="6"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="28">
-        <v>45824</v>
-      </c>
-      <c r="C8" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="54">
-        <v>0.1176</v>
-      </c>
-      <c r="G8" s="31">
-        <f t="shared" si="0"/>
-        <v>2352</v>
-      </c>
-      <c r="H8" s="40">
-        <f>G8</f>
-        <v>2352</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="17"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="6"/>
-      <c r="M8" s="6"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="28">
-        <v>45833</v>
-      </c>
-      <c r="C9" s="29">
-        <v>60000</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="53">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="G9" s="31">
-        <f t="shared" si="0"/>
-        <v>7950</v>
-      </c>
-      <c r="H9" s="40">
-        <f>G9*0.9</f>
-        <v>7155</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="6"/>
-      <c r="M9" s="6"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="27"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="30"/>
-      <c r="E10" s="31"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="43">
-        <f>SUM(H2:H9)</f>
-        <v>50297.7</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="19"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="6"/>
-      <c r="M10" s="6"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" s="28">
-        <v>45824</v>
-      </c>
-      <c r="C11" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D11" s="30">
-        <v>67</v>
-      </c>
-      <c r="E11" s="52">
-        <v>67148.399999999994</v>
-      </c>
-      <c r="F11" s="30">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="G11" s="31">
-        <v>16563.23</v>
-      </c>
-      <c r="H11" s="32">
-        <f t="shared" ref="H11:H12" si="2">G11-E11</f>
-        <v>-50585.17</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="28">
-        <v>45826</v>
-      </c>
-      <c r="C12" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="30">
-        <v>67</v>
-      </c>
-      <c r="E12" s="52">
-        <v>67148.399999999994</v>
-      </c>
-      <c r="F12" s="30">
-        <v>16.8</v>
-      </c>
-      <c r="G12" s="31">
-        <v>16762.79</v>
-      </c>
-      <c r="H12" s="32">
-        <f t="shared" si="2"/>
-        <v>-50385.609999999993</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B13" s="28">
-        <v>45828</v>
-      </c>
-      <c r="C13" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D13" s="30">
-        <v>67</v>
-      </c>
-      <c r="E13" s="52">
-        <v>67148.399999999994</v>
-      </c>
-      <c r="F13" s="30">
-        <v>16.8</v>
-      </c>
-      <c r="G13" s="31">
-        <v>16762.79</v>
-      </c>
-      <c r="H13" s="32">
-        <f t="shared" ref="H13" si="3">G13-E13</f>
-        <v>-50385.609999999993</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="26"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32">
-        <f>SUM(E13:E13)</f>
-        <v>67148.399999999994</v>
-      </c>
-      <c r="F14" s="30"/>
-      <c r="G14" s="32">
-        <f>SUM(G13:G13)</f>
-        <v>16762.79</v>
-      </c>
-      <c r="H14" s="41">
-        <f>SUM(H11:H13)</f>
-        <v>-151356.38999999998</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="26"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H15" s="43">
-        <f>H10+H14</f>
-        <v>-101058.68999999999</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="J15" s="7">
-        <v>76255.710000000021</v>
-      </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H16" s="32">
-        <v>-86292.24</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="J16" s="7">
-        <v>-162547.95474799996</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H17" s="34">
-        <f>H15+H16</f>
-        <v>-187350.93</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="J17" s="7">
-        <v>-86292.244747999939</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H18" s="35">
-        <v>336660</v>
-      </c>
-      <c r="I18" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="J18" s="7">
-        <v>327260</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="26"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="H19" s="35">
-        <v>41150</v>
-      </c>
-      <c r="I19" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="J19" s="7">
-        <v>9400</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H20" s="41">
-        <f>H18+H19</f>
-        <v>377810</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="J20" s="7">
-        <v>336660</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A21" s="5"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H21" s="46">
-        <f>H17-H20</f>
-        <v>-565160.92999999993</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="J21" s="7">
-        <v>-422952.24474799994</v>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A22" s="5"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22" s="38">
-        <v>57000</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="J22" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A23" s="6"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H23" s="39">
-        <f>H21+H22</f>
-        <v>-508160.92999999993</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="7">
-        <v>-365952.24474799994</v>
-      </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="7"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="I24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="N24" s="13"/>
-    </row>
-    <row r="25" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="K25" s="7"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K26" s="7"/>
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M28" s="7"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K29" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N9">
-    <sortCondition ref="B2:B9"/>
-    <sortCondition ref="A2:A9"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1E1A231-79A5-4BE4-8C0C-F5E13A4831EB}">
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68993354-A7E2-4931-8BC9-D8891EC066BA}">
   <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="74" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="71" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
     <col min="5" max="5" width="14.375" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.75" style="10" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.5" style="90" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.875" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.125" style="13" bestFit="1" customWidth="1"/>
@@ -2810,7 +4180,7 @@
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="68" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="22" t="s">
@@ -2822,7 +4192,7 @@
       <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="25" t="s">
+      <c r="F1" s="86" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="24" t="s">
@@ -2831,7 +4201,7 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="70"/>
+      <c r="I1" s="67"/>
       <c r="J1" s="3"/>
       <c r="K1" s="5"/>
       <c r="L1" s="7"/>
@@ -2840,13 +4210,13 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="72">
-        <v>45784</v>
+        <v>33</v>
+      </c>
+      <c r="B2" s="69">
+        <v>46148</v>
       </c>
       <c r="C2" s="29">
-        <v>81000</v>
+        <v>7000</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>9</v>
@@ -2854,15 +4224,16 @@
       <c r="E2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="54">
-        <v>0.5</v>
+      <c r="F2" s="87">
+        <v>0.43</v>
       </c>
       <c r="G2" s="31">
         <f t="shared" ref="G2:G13" si="0">C2*F2</f>
-        <v>40500</v>
+        <v>3010</v>
       </c>
       <c r="H2" s="40">
-        <v>40500</v>
+        <f>G2*0.9</f>
+        <v>2709</v>
       </c>
       <c r="I2" s="13"/>
       <c r="J2" s="17"/>
@@ -2873,13 +4244,13 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A3" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="72">
-        <v>45785</v>
-      </c>
-      <c r="C3" s="29">
-        <v>10000</v>
+        <v>32</v>
+      </c>
+      <c r="B3" s="69">
+        <v>46149</v>
+      </c>
+      <c r="C3" s="97">
+        <v>75000</v>
       </c>
       <c r="D3" s="30" t="s">
         <v>9</v>
@@ -2887,15 +4258,15 @@
       <c r="E3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="37">
-        <v>1</v>
+      <c r="F3" s="89">
+        <v>0.7</v>
       </c>
       <c r="G3" s="31">
         <f t="shared" si="0"/>
-        <v>10000</v>
+        <v>52500</v>
       </c>
       <c r="H3" s="40">
-        <v>9000</v>
+        <v>51975</v>
       </c>
       <c r="I3" s="13"/>
       <c r="J3" s="17"/>
@@ -2906,13 +4277,13 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="72">
-        <v>45786</v>
+        <v>35</v>
+      </c>
+      <c r="B4" s="69">
+        <v>46149</v>
       </c>
       <c r="C4" s="29">
-        <v>10000</v>
+        <v>27000</v>
       </c>
       <c r="D4" s="30" t="s">
         <v>9</v>
@@ -2920,15 +4291,16 @@
       <c r="E4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="53">
-        <v>0.6</v>
+      <c r="F4" s="88">
+        <v>0.26</v>
       </c>
       <c r="G4" s="31">
         <f t="shared" si="0"/>
-        <v>6000</v>
+        <v>7020</v>
       </c>
       <c r="H4" s="40">
-        <v>5540</v>
+        <f>G4</f>
+        <v>7020</v>
       </c>
       <c r="I4" s="13"/>
       <c r="J4" s="17"/>
@@ -2939,13 +4311,13 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A5" s="27" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="72">
-        <v>45786</v>
+        <v>10</v>
+      </c>
+      <c r="B5" s="69">
+        <v>46150</v>
       </c>
       <c r="C5" s="29">
-        <v>27000</v>
+        <v>10000</v>
       </c>
       <c r="D5" s="30" t="s">
         <v>9</v>
@@ -2953,15 +4325,16 @@
       <c r="E5" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="54">
-        <v>0.31</v>
+      <c r="F5" s="89">
+        <v>0.5</v>
       </c>
       <c r="G5" s="31">
         <f t="shared" si="0"/>
-        <v>8370</v>
+        <v>5000</v>
       </c>
       <c r="H5" s="40">
-        <v>8370</v>
+        <f>G5*0.9</f>
+        <v>4500</v>
       </c>
       <c r="I5" s="13"/>
       <c r="J5" s="17"/>
@@ -2974,11 +4347,11 @@
       <c r="A6" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="72">
-        <v>45791</v>
-      </c>
-      <c r="C6" s="29">
-        <v>15000</v>
+      <c r="B6" s="69">
+        <v>46154</v>
+      </c>
+      <c r="C6" s="84">
+        <v>17500</v>
       </c>
       <c r="D6" s="30" t="s">
         <v>9</v>
@@ -2986,15 +4359,16 @@
       <c r="E6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="54">
-        <v>0.34</v>
+      <c r="F6" s="89">
+        <v>0.38</v>
       </c>
       <c r="G6" s="31">
         <f t="shared" si="0"/>
-        <v>5100</v>
+        <v>6650</v>
       </c>
       <c r="H6" s="40">
-        <v>4590</v>
+        <f>G6*0.9</f>
+        <v>5985</v>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="17"/>
@@ -3005,10 +4379,10 @@
     </row>
     <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A7" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B7" s="72">
-        <v>45793</v>
+        <v>38</v>
+      </c>
+      <c r="B7" s="69">
+        <v>46157</v>
       </c>
       <c r="C7" s="29">
         <v>3600</v>
@@ -3019,15 +4393,16 @@
       <c r="E7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="50">
-        <v>0.25</v>
+      <c r="F7" s="95">
+        <v>0.35</v>
       </c>
       <c r="G7" s="31">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>1260</v>
       </c>
       <c r="H7" s="40">
-        <v>810</v>
+        <f>G7*0.9</f>
+        <v>1134</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="17"/>
@@ -3038,10 +4413,10 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A8" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="72">
-        <v>45793</v>
+        <v>39</v>
+      </c>
+      <c r="B8" s="69">
+        <v>46157</v>
       </c>
       <c r="C8" s="29">
         <v>27000</v>
@@ -3052,7 +4427,7 @@
       <c r="E8" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="51">
+      <c r="F8" s="96">
         <v>1.5</v>
       </c>
       <c r="G8" s="31">
@@ -3071,13 +4446,13 @@
     </row>
     <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A9" s="27" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="72">
-        <v>45793</v>
+        <v>61</v>
+      </c>
+      <c r="B9" s="69">
+        <v>46157</v>
       </c>
       <c r="C9" s="29">
-        <v>8000</v>
+        <v>4000</v>
       </c>
       <c r="D9" s="30" t="s">
         <v>9</v>
@@ -3085,15 +4460,15 @@
       <c r="E9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="69">
-        <v>0.93</v>
+      <c r="F9" s="95">
+        <v>1.17</v>
       </c>
       <c r="G9" s="31">
         <f t="shared" si="0"/>
-        <v>7440</v>
+        <v>4680</v>
       </c>
       <c r="H9" s="40">
-        <v>6696</v>
+        <v>4272</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="17"/>
@@ -3104,13 +4479,13 @@
     </row>
     <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A10" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="72">
-        <v>45797</v>
+        <v>42</v>
+      </c>
+      <c r="B10" s="69">
+        <v>46164</v>
       </c>
       <c r="C10" s="29">
-        <v>30000</v>
+        <v>1200</v>
       </c>
       <c r="D10" s="30" t="s">
         <v>9</v>
@@ -3118,18 +4493,19 @@
       <c r="E10" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F10" s="50">
-        <v>0.08</v>
+      <c r="F10" s="87">
+        <v>0.48</v>
       </c>
       <c r="G10" s="31">
         <f t="shared" si="0"/>
-        <v>2400</v>
+        <v>576</v>
       </c>
       <c r="H10" s="40">
-        <v>2160</v>
+        <f>526.8</f>
+        <v>526.79999999999995</v>
       </c>
       <c r="I10" s="13"/>
-      <c r="J10" s="17"/>
+      <c r="J10" s="2"/>
       <c r="K10" s="7"/>
       <c r="L10" s="6"/>
       <c r="M10" s="6"/>
@@ -3137,13 +4513,13 @@
     </row>
     <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A11" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B11" s="72">
-        <v>45800</v>
+        <v>11</v>
+      </c>
+      <c r="B11" s="69">
+        <v>46164</v>
       </c>
       <c r="C11" s="29">
-        <v>1200</v>
+        <v>4000</v>
       </c>
       <c r="D11" s="30" t="s">
         <v>9</v>
@@ -3151,15 +4527,16 @@
       <c r="E11" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="53">
-        <v>0.48</v>
+      <c r="F11" s="89">
+        <v>0.3</v>
       </c>
       <c r="G11" s="31">
         <f t="shared" si="0"/>
-        <v>576</v>
+        <v>1200</v>
       </c>
       <c r="H11" s="40">
-        <v>520.79999999999995</v>
+        <f t="shared" ref="H11:H17" si="1">G11*0.9</f>
+        <v>1080</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="2"/>
@@ -3170,13 +4547,13 @@
     </row>
     <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A12" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="72">
-        <v>45800</v>
+        <v>62</v>
+      </c>
+      <c r="B12" s="69">
+        <v>46164</v>
       </c>
       <c r="C12" s="29">
-        <v>4000</v>
+        <v>10000</v>
       </c>
       <c r="D12" s="30" t="s">
         <v>9</v>
@@ -3184,18 +4561,19 @@
       <c r="E12" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="54">
-        <v>0.28000000000000003</v>
+      <c r="F12" s="87">
+        <v>0.25</v>
       </c>
       <c r="G12" s="31">
         <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>2500</v>
       </c>
       <c r="H12" s="40">
-        <v>1008</v>
+        <f t="shared" si="1"/>
+        <v>2250</v>
       </c>
       <c r="I12" s="13"/>
-      <c r="J12" s="2"/>
+      <c r="J12" s="17"/>
       <c r="K12" s="7"/>
       <c r="L12" s="6"/>
       <c r="M12" s="6"/>
@@ -3203,10 +4581,10 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A13" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="72">
-        <v>45800</v>
+        <v>40</v>
+      </c>
+      <c r="B13" s="69">
+        <v>46164</v>
       </c>
       <c r="C13" s="29">
         <v>7200</v>
@@ -3217,7 +4595,7 @@
       <c r="E13" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="87">
         <v>0.17499999999999999</v>
       </c>
       <c r="G13" s="31">
@@ -3225,10 +4603,11 @@
         <v>1260</v>
       </c>
       <c r="H13" s="40">
+        <f t="shared" si="1"/>
         <v>1134</v>
       </c>
       <c r="I13" s="13"/>
-      <c r="J13" s="17"/>
+      <c r="J13" s="2"/>
       <c r="K13" s="7"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -3236,10 +4615,10 @@
     </row>
     <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A14" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B14" s="72">
-        <v>45800</v>
+        <v>44</v>
+      </c>
+      <c r="B14" s="69">
+        <v>46167</v>
       </c>
       <c r="C14" s="29">
         <v>105000</v>
@@ -3250,14 +4629,15 @@
       <c r="E14" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="53">
-        <v>0.111238</v>
+      <c r="F14" s="89">
+        <v>0.138295</v>
       </c>
       <c r="G14" s="31">
-        <v>11676</v>
+        <v>14520.98</v>
       </c>
       <c r="H14" s="40">
-        <v>10612.21</v>
+        <f t="shared" si="1"/>
+        <v>13068.882</v>
       </c>
       <c r="I14" s="13"/>
       <c r="J14" s="2"/>
@@ -3268,10 +4648,10 @@
     </row>
     <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A15" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="B15" s="72">
-        <v>45800</v>
+        <v>45</v>
+      </c>
+      <c r="B15" s="69">
+        <v>46168</v>
       </c>
       <c r="C15" s="29">
         <v>1000</v>
@@ -3282,15 +4662,16 @@
       <c r="E15" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="53">
-        <v>0.27</v>
+      <c r="F15" s="89">
+        <v>0.39</v>
       </c>
       <c r="G15" s="31">
         <f>C15*F15</f>
-        <v>270</v>
+        <v>390</v>
       </c>
       <c r="H15" s="40">
-        <v>243</v>
+        <f t="shared" si="1"/>
+        <v>351</v>
       </c>
       <c r="I15" s="13"/>
       <c r="J15" s="2"/>
@@ -3301,10 +4682,10 @@
     </row>
     <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A16" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="72">
-        <v>45805</v>
+        <v>43</v>
+      </c>
+      <c r="B16" s="69">
+        <v>46170</v>
       </c>
       <c r="C16" s="29">
         <v>9000</v>
@@ -3315,18 +4696,19 @@
       <c r="E16" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="54">
-        <v>7.4999999999999997E-2</v>
+      <c r="F16" s="89">
+        <v>0.08</v>
       </c>
       <c r="G16" s="31">
         <f>C16*F16</f>
-        <v>675</v>
+        <v>720</v>
       </c>
       <c r="H16" s="40">
-        <v>607.5</v>
+        <f t="shared" si="1"/>
+        <v>648</v>
       </c>
       <c r="I16" s="13"/>
-      <c r="J16" s="2"/>
+      <c r="J16" s="17"/>
       <c r="K16" s="7"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
@@ -3334,13 +4716,13 @@
     </row>
     <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A17" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="72">
-        <v>45806</v>
+        <v>41</v>
+      </c>
+      <c r="B17" s="69">
+        <v>46170</v>
       </c>
       <c r="C17" s="29">
-        <v>6800</v>
+        <v>50000</v>
       </c>
       <c r="D17" s="30" t="s">
         <v>9</v>
@@ -3348,15 +4730,16 @@
       <c r="E17" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="37">
-        <v>0.23</v>
+      <c r="F17" s="87">
+        <v>4.9000000000000002E-2</v>
       </c>
       <c r="G17" s="31">
         <f>C17*F17</f>
-        <v>1564</v>
+        <v>2450</v>
       </c>
       <c r="H17" s="40">
-        <v>1407.6000000000001</v>
+        <f t="shared" si="1"/>
+        <v>2205</v>
       </c>
       <c r="I17" s="13"/>
       <c r="J17" s="17"/>
@@ -3367,15 +4750,15 @@
     </row>
     <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A18" s="27"/>
-      <c r="B18" s="73"/>
+      <c r="B18" s="70"/>
       <c r="C18" s="29"/>
       <c r="D18" s="30"/>
       <c r="E18" s="31"/>
-      <c r="F18" s="30"/>
+      <c r="F18" s="87"/>
       <c r="G18" s="31"/>
       <c r="H18" s="34">
         <f>SUM(H2:H17)</f>
-        <v>131539.11000000002</v>
+        <v>137198.682</v>
       </c>
       <c r="I18" s="13"/>
       <c r="J18" s="19"/>
@@ -3386,29 +4769,29 @@
     </row>
     <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A19" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="B19" s="73">
-        <v>45792</v>
+        <v>32</v>
+      </c>
+      <c r="B19" s="70">
+        <v>46153</v>
       </c>
       <c r="C19" s="29">
-        <v>30000</v>
+        <v>5000</v>
       </c>
       <c r="D19" s="30">
-        <v>3.8</v>
+        <v>8</v>
       </c>
       <c r="E19" s="31">
-        <v>114252.5</v>
-      </c>
-      <c r="F19" s="30">
-        <v>1.97</v>
+        <v>40088.6</v>
+      </c>
+      <c r="F19" s="87">
+        <v>7.8</v>
       </c>
       <c r="G19" s="31">
-        <v>58969.1</v>
+        <v>38913.620000000003</v>
       </c>
       <c r="H19" s="32">
         <f>G19-E19</f>
-        <v>-55283.4</v>
+        <v>-1174.9799999999959</v>
       </c>
       <c r="I19" s="13"/>
       <c r="J19" s="7"/>
@@ -3419,21 +4802,21 @@
     </row>
     <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A20" s="26"/>
-      <c r="B20" s="73"/>
+      <c r="B20" s="70"/>
       <c r="C20" s="29"/>
       <c r="D20" s="33"/>
       <c r="E20" s="32">
         <f>SUM(E19:E19)</f>
-        <v>114252.5</v>
-      </c>
-      <c r="F20" s="30"/>
+        <v>40088.6</v>
+      </c>
+      <c r="F20" s="87"/>
       <c r="G20" s="32">
         <f>SUM(G19:G19)</f>
-        <v>58969.1</v>
+        <v>38913.620000000003</v>
       </c>
       <c r="H20" s="44">
         <f>SUM(H19:H19)</f>
-        <v>-55283.4</v>
+        <v>-1174.9799999999959</v>
       </c>
       <c r="I20" s="13"/>
       <c r="J20" s="7"/>
@@ -3444,23 +4827,23 @@
     </row>
     <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A21" s="26"/>
-      <c r="B21" s="73"/>
+      <c r="B21" s="70"/>
       <c r="C21" s="29"/>
       <c r="D21" s="33"/>
       <c r="E21" s="32"/>
-      <c r="F21" s="30"/>
+      <c r="F21" s="87"/>
       <c r="G21" s="32" t="s">
         <v>12</v>
       </c>
       <c r="H21" s="34">
         <f>H18+H20</f>
-        <v>76255.710000000021</v>
+        <v>136023.70199999999</v>
       </c>
       <c r="I21" s="13" t="s">
         <v>12</v>
       </c>
       <c r="J21" s="7">
-        <v>-39964.590000000004</v>
+        <v>12172.5</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="15"/>
@@ -3469,22 +4852,22 @@
     </row>
     <row r="22" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A22" s="26"/>
-      <c r="B22" s="73"/>
+      <c r="B22" s="70"/>
       <c r="C22" s="29"/>
       <c r="D22" s="33"/>
       <c r="E22" s="32"/>
-      <c r="F22" s="30"/>
+      <c r="F22" s="87"/>
       <c r="G22" s="32" t="s">
         <v>16</v>
       </c>
-      <c r="H22" s="34">
-        <v>-162547.95474799996</v>
+      <c r="H22" s="7">
+        <v>-242360.16599999997</v>
       </c>
       <c r="I22" s="13" t="s">
         <v>16</v>
       </c>
       <c r="J22" s="7">
-        <v>-122583.36474799996</v>
+        <v>-254532.66599999997</v>
       </c>
       <c r="K22" s="7"/>
       <c r="L22" s="15"/>
@@ -3493,23 +4876,23 @@
     </row>
     <row r="23" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A23" s="26"/>
-      <c r="B23" s="73"/>
+      <c r="B23" s="70"/>
       <c r="C23" s="29"/>
       <c r="D23" s="33"/>
       <c r="E23" s="32"/>
-      <c r="F23" s="30"/>
+      <c r="F23" s="87"/>
       <c r="G23" s="32" t="s">
         <v>28</v>
       </c>
       <c r="H23" s="34">
         <f>H21+H22</f>
-        <v>-86292.244747999939</v>
+        <v>-106336.46399999998</v>
       </c>
       <c r="I23" s="13" t="s">
         <v>28</v>
       </c>
       <c r="J23" s="7">
-        <v>-162547.95474799996</v>
+        <v>-242360.16599999997</v>
       </c>
       <c r="K23" s="7"/>
       <c r="L23" s="15"/>
@@ -3518,22 +4901,22 @@
     </row>
     <row r="24" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A24" s="26"/>
-      <c r="B24" s="73"/>
+      <c r="B24" s="70"/>
       <c r="C24" s="29"/>
       <c r="D24" s="33"/>
       <c r="E24" s="32"/>
-      <c r="F24" s="30"/>
+      <c r="F24" s="87"/>
       <c r="G24" s="32" t="s">
         <v>13</v>
       </c>
       <c r="H24" s="7">
-        <v>327260</v>
+        <v>127030</v>
       </c>
       <c r="I24" s="13" t="s">
         <v>13</v>
       </c>
       <c r="J24" s="7">
-        <v>281390</v>
+        <v>98170</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="15"/>
@@ -3542,22 +4925,22 @@
     </row>
     <row r="25" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A25" s="26"/>
-      <c r="B25" s="73"/>
+      <c r="B25" s="70"/>
       <c r="C25" s="29"/>
       <c r="D25" s="33"/>
       <c r="E25" s="32"/>
-      <c r="F25" s="30"/>
+      <c r="F25" s="87"/>
       <c r="G25" s="32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H25" s="35">
-        <v>9400</v>
+        <v>42590</v>
       </c>
       <c r="I25" s="13" t="s">
         <v>29</v>
       </c>
       <c r="J25" s="7">
-        <v>45870</v>
+        <v>28860</v>
       </c>
       <c r="K25" s="7"/>
       <c r="L25" s="15"/>
@@ -3566,23 +4949,23 @@
     </row>
     <row r="26" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A26" s="26"/>
-      <c r="B26" s="73"/>
+      <c r="B26" s="70"/>
       <c r="C26" s="29"/>
       <c r="D26" s="33"/>
       <c r="E26" s="32"/>
-      <c r="F26" s="30"/>
+      <c r="F26" s="87"/>
       <c r="G26" s="32" t="s">
         <v>14</v>
       </c>
       <c r="H26" s="41">
         <f>H24+H25</f>
-        <v>336660</v>
+        <v>169620</v>
       </c>
       <c r="I26" s="13" t="s">
         <v>14</v>
       </c>
       <c r="J26" s="7">
-        <v>327260</v>
+        <v>127030</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="15"/>
@@ -3591,23 +4974,23 @@
     </row>
     <row r="27" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A27" s="5"/>
-      <c r="B27" s="74"/>
+      <c r="B27" s="71"/>
       <c r="C27" s="8"/>
       <c r="D27" s="9"/>
       <c r="E27" s="7"/>
-      <c r="F27" s="10"/>
+      <c r="F27" s="90"/>
       <c r="G27" s="32" t="s">
         <v>15</v>
       </c>
       <c r="H27" s="46">
         <f>H23-H26</f>
-        <v>-422952.24474799994</v>
+        <v>-275956.46399999998</v>
       </c>
       <c r="I27" s="13" t="s">
         <v>15</v>
       </c>
       <c r="J27" s="7">
-        <v>-489807.95474799996</v>
+        <v>-369390.16599999997</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="15"/>
@@ -3616,22 +4999,22 @@
     </row>
     <row r="28" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A28" s="5"/>
-      <c r="B28" s="74"/>
+      <c r="B28" s="71"/>
       <c r="C28" s="8"/>
       <c r="D28" s="9"/>
       <c r="E28" s="7"/>
-      <c r="F28" s="10"/>
+      <c r="F28" s="90"/>
       <c r="G28" s="38" t="s">
         <v>30</v>
       </c>
       <c r="H28" s="38">
-        <v>57000</v>
+        <v>60000</v>
       </c>
       <c r="I28" s="13" t="s">
         <v>30</v>
       </c>
       <c r="J28" s="7">
-        <v>57000</v>
+        <v>60000</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="15"/>
@@ -3640,23 +5023,23 @@
     </row>
     <row r="29" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A29" s="6"/>
-      <c r="B29" s="74"/>
+      <c r="B29" s="71"/>
       <c r="C29" s="8"/>
       <c r="D29" s="10"/>
       <c r="E29" s="14"/>
-      <c r="F29" s="10"/>
+      <c r="F29" s="90"/>
       <c r="G29" s="38" t="s">
         <v>31</v>
       </c>
       <c r="H29" s="39">
         <f>H27+H28</f>
-        <v>-365952.24474799994</v>
+        <v>-215956.46399999998</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>31</v>
       </c>
       <c r="J29" s="7">
-        <v>-432807.95474799996</v>
+        <v>-309390.16599999997</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="15"/>
@@ -3664,13 +5047,51 @@
       <c r="N29" s="7"/>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="G30" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H30" s="7">
+        <v>84048.91399999999</v>
+      </c>
+      <c r="I30" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="J30" s="7">
+        <v>71876.41399999999</v>
+      </c>
       <c r="K30" s="7"/>
       <c r="N30" s="13"/>
     </row>
     <row r="31" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G31" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="H31" s="32">
+        <f>H30+H18</f>
+        <v>221247.59599999999</v>
+      </c>
+      <c r="I31" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J31" s="7">
+        <v>84048.91399999999</v>
+      </c>
       <c r="K31" s="7"/>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="G32" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="H32" s="32">
+        <f>H31-H26</f>
+        <v>51627.59599999999</v>
+      </c>
+      <c r="I32" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="J32" s="7">
+        <v>-42981.08600000001</v>
+      </c>
       <c r="K32" s="7"/>
       <c r="M32" s="7"/>
     </row>
@@ -3685,7 +5106,7 @@
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N17">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H17">
     <sortCondition ref="B2:B17"/>
     <sortCondition ref="A2:A17"/>
   </sortState>
@@ -3695,7 +5116,456 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DFDC5F2-0211-490B-8DD7-A2B28B5D4706}">
+  <dimension ref="A1:L21"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.25" style="9" customWidth="1"/>
+    <col min="5" max="5" width="12.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.625" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.25" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+    </row>
+    <row r="2" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="B2" s="28">
+        <v>46136</v>
+      </c>
+      <c r="C2" s="29">
+        <v>6000</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>3000</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2*0.9</f>
+        <v>2700</v>
+      </c>
+      <c r="I2" s="17"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="B3" s="28">
+        <v>46140</v>
+      </c>
+      <c r="C3" s="29">
+        <v>7500</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="31" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" s="37">
+        <v>1.4</v>
+      </c>
+      <c r="G3" s="31">
+        <f>C3*F3</f>
+        <v>10500</v>
+      </c>
+      <c r="H3" s="32">
+        <v>9472.5</v>
+      </c>
+      <c r="I3" s="17"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+    </row>
+    <row r="4" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="27"/>
+      <c r="B4" s="28"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="30"/>
+      <c r="G4" s="31"/>
+      <c r="H4" s="34">
+        <f>SUM(H2:H3)</f>
+        <v>12172.5</v>
+      </c>
+      <c r="I4" s="19"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+    </row>
+    <row r="5" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="28">
+        <v>45757</v>
+      </c>
+      <c r="C5" s="29">
+        <v>0</v>
+      </c>
+      <c r="D5" s="30">
+        <v>61.5</v>
+      </c>
+      <c r="E5" s="31">
+        <v>61636.22</v>
+      </c>
+      <c r="F5" s="30">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="G5" s="31">
+        <v>16563.23</v>
+      </c>
+      <c r="H5" s="49">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="6"/>
+    </row>
+    <row r="6" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32">
+        <f>SUM(E5:E5)</f>
+        <v>61636.22</v>
+      </c>
+      <c r="F6" s="30"/>
+      <c r="G6" s="32">
+        <f>SUM(G5:G5)</f>
+        <v>16563.23</v>
+      </c>
+      <c r="H6" s="34">
+        <f>SUM(H5:H5)</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="15"/>
+      <c r="L6" s="6"/>
+    </row>
+    <row r="7" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="34">
+        <f>H4+H6</f>
+        <v>12172.5</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="34">
+        <v>-243272.66599999997</v>
+      </c>
+      <c r="K7" s="15"/>
+      <c r="L7" s="6"/>
+    </row>
+    <row r="8" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H8" s="7">
+        <v>-254532.66599999997</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="32">
+        <v>-11260</v>
+      </c>
+      <c r="K8" s="15"/>
+      <c r="L8" s="6"/>
+    </row>
+    <row r="9" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="34">
+        <f>H7+H8</f>
+        <v>-242360.16599999997</v>
+      </c>
+      <c r="I9" s="60" t="s">
+        <v>28</v>
+      </c>
+      <c r="J9" s="41">
+        <v>-254532.66599999997</v>
+      </c>
+      <c r="K9" s="15"/>
+      <c r="L9" s="6"/>
+    </row>
+    <row r="10" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H10" s="7">
+        <v>98170</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J10" s="35">
+        <v>71260</v>
+      </c>
+      <c r="K10" s="15"/>
+      <c r="L10" s="6"/>
+    </row>
+    <row r="11" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="H11" s="35">
+        <v>28860</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="J11" s="35">
+        <v>26910</v>
+      </c>
+      <c r="K11" s="15"/>
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="34">
+        <f>H10+H11</f>
+        <v>127030</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="41">
+        <v>98170</v>
+      </c>
+      <c r="K12" s="15"/>
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="45">
+        <f>H9-H12</f>
+        <v>-369390.16599999997</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="J13" s="45">
+        <v>-352702.66599999997</v>
+      </c>
+      <c r="K13" s="15"/>
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="5"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H14" s="38">
+        <v>60000</v>
+      </c>
+      <c r="I14" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="J14" s="94">
+        <v>60000</v>
+      </c>
+      <c r="K14" s="15"/>
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:12" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="6"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H15" s="39">
+        <f>H13+H14</f>
+        <v>-309390.16599999997</v>
+      </c>
+      <c r="I15" s="60" t="s">
+        <v>31</v>
+      </c>
+      <c r="J15" s="41">
+        <v>-292702.66599999997</v>
+      </c>
+      <c r="K15" s="15"/>
+      <c r="L15" s="7"/>
+    </row>
+    <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G16" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H16" s="32">
+        <v>71876.41399999999</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="7">
+        <v>0</v>
+      </c>
+      <c r="L16" s="13"/>
+    </row>
+    <row r="17" spans="7:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G17" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="32">
+        <f>H16+H4</f>
+        <v>84048.91399999999</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="J17" s="7">
+        <v>71876.41399999999</v>
+      </c>
+    </row>
+    <row r="18" spans="7:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G18" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="32">
+        <f>H17-H12</f>
+        <v>-42981.08600000001</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="J18" s="7">
+        <v>-26293.58600000001</v>
+      </c>
+      <c r="K18" s="7"/>
+    </row>
+    <row r="19" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="K19" s="7"/>
+    </row>
+    <row r="20" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="K20" s="7"/>
+    </row>
+    <row r="21" spans="7:11" x14ac:dyDescent="0.3">
+      <c r="J21" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6E9199-1687-4EE7-A0F3-54DE6332B9D4}">
   <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -3705,7 +5575,7 @@
     <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8" style="9" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="93" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="90" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.75" style="7" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.75" style="11" bestFit="1" customWidth="1"/>
@@ -3734,7 +5604,7 @@
       <c r="E1" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="89" t="s">
+      <c r="F1" s="86" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="24" t="s">
@@ -3743,13 +5613,13 @@
       <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="95"/>
-      <c r="J1" s="95"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
       <c r="K1" s="5"/>
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2" s="28">
         <v>46085</v>
@@ -3763,7 +5633,7 @@
       <c r="E2" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="92">
+      <c r="F2" s="89">
         <v>0.22412299999999999</v>
       </c>
       <c r="G2" s="31">
@@ -3794,7 +5664,7 @@
       <c r="E3" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="90">
+      <c r="F3" s="87">
         <v>0.22220000000000001</v>
       </c>
       <c r="G3" s="31">
@@ -3825,7 +5695,7 @@
       <c r="E4" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="91">
+      <c r="F4" s="88">
         <v>0.17829999999999999</v>
       </c>
       <c r="G4" s="31">
@@ -3856,7 +5726,7 @@
       <c r="E5" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="92">
+      <c r="F5" s="89">
         <v>0.12189999999999999</v>
       </c>
       <c r="G5" s="31">
@@ -3887,7 +5757,7 @@
       <c r="E6" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="90">
+      <c r="F6" s="87">
         <v>0.1212</v>
       </c>
       <c r="G6" s="31">
@@ -3917,7 +5787,7 @@
       <c r="E7" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="90">
+      <c r="F7" s="87">
         <v>7.4800000000000005E-2</v>
       </c>
       <c r="G7" s="31">
@@ -3947,7 +5817,7 @@
       <c r="E8" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="91">
+      <c r="F8" s="88">
         <v>0.17549999999999999</v>
       </c>
       <c r="G8" s="31">
@@ -3978,7 +5848,7 @@
       <c r="E9" s="31" t="s">
         <v>9</v>
       </c>
-      <c r="F9" s="92">
+      <c r="F9" s="89">
         <v>0.27939999999999998</v>
       </c>
       <c r="G9" s="31">
@@ -3999,7 +5869,7 @@
       <c r="C10" s="29"/>
       <c r="D10" s="30"/>
       <c r="E10" s="31"/>
-      <c r="F10" s="90"/>
+      <c r="F10" s="87"/>
       <c r="G10" s="31"/>
       <c r="H10" s="32">
         <f>SUM(H2:H9)</f>
@@ -4025,7 +5895,7 @@
       <c r="E11" s="31">
         <v>185910.87</v>
       </c>
-      <c r="F11" s="90">
+      <c r="F11" s="87">
         <v>11.1</v>
       </c>
       <c r="G11" s="31">
@@ -4035,7 +5905,7 @@
         <f>G11-E11</f>
         <v>7908.8800000000047</v>
       </c>
-      <c r="I11" s="96"/>
+      <c r="I11" s="93"/>
       <c r="J11" s="32"/>
       <c r="K11" s="7"/>
       <c r="L11" s="15"/>
@@ -4058,7 +5928,7 @@
       <c r="E12" s="31">
         <v>224897.03</v>
       </c>
-      <c r="F12" s="90">
+      <c r="F12" s="87">
         <v>6.25</v>
       </c>
       <c r="G12" s="31">
@@ -4068,7 +5938,7 @@
         <f>G12-E12</f>
         <v>-182491.16999999998</v>
       </c>
-      <c r="I12" s="96"/>
+      <c r="I12" s="93"/>
       <c r="J12" s="32"/>
       <c r="K12" s="7"/>
       <c r="L12" s="15"/>
@@ -4077,7 +5947,7 @@
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A13" s="27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B13" s="28">
         <v>46090</v>
@@ -4091,7 +5961,7 @@
       <c r="E13" s="31">
         <v>243538.22</v>
       </c>
-      <c r="F13" s="90">
+      <c r="F13" s="87">
         <v>172</v>
       </c>
       <c r="G13" s="31">
@@ -4101,7 +5971,7 @@
         <f>G13-E13</f>
         <v>-140566.79</v>
       </c>
-      <c r="I13" s="96"/>
+      <c r="I13" s="93"/>
       <c r="J13" s="32"/>
       <c r="K13" s="7"/>
       <c r="L13" s="15"/>
@@ -4117,7 +5987,7 @@
         <f>SUM(E11:E13)</f>
         <v>654346.12</v>
       </c>
-      <c r="F14" s="90"/>
+      <c r="F14" s="87"/>
       <c r="G14" s="32">
         <f>SUM(G11:G13)</f>
         <v>339197.04</v>
@@ -4137,7 +6007,7 @@
       <c r="C15" s="29"/>
       <c r="D15" s="33"/>
       <c r="E15" s="32"/>
-      <c r="F15" s="90"/>
+      <c r="F15" s="87"/>
       <c r="G15" s="32" t="s">
         <v>12</v>
       </c>
@@ -4145,10 +6015,10 @@
         <f>H10+H14</f>
         <v>-243272.66599999997</v>
       </c>
-      <c r="I15" s="96" t="s">
+      <c r="I15" s="93" t="s">
         <v>12</v>
       </c>
-      <c r="J15" s="62">
+      <c r="J15" s="60">
         <v>0</v>
       </c>
     </row>
@@ -4158,7 +6028,7 @@
       <c r="C16" s="29"/>
       <c r="D16" s="33"/>
       <c r="E16" s="32"/>
-      <c r="F16" s="90"/>
+      <c r="F16" s="87"/>
       <c r="G16" s="32" t="s">
         <v>16</v>
       </c>
@@ -4168,7 +6038,7 @@
       <c r="I16" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="J16" s="62">
+      <c r="J16" s="60">
         <v>0</v>
       </c>
       <c r="L16" s="6"/>
@@ -4179,8 +6049,8 @@
       <c r="C17" s="29"/>
       <c r="D17" s="33"/>
       <c r="E17" s="32"/>
-      <c r="F17" s="90"/>
-      <c r="G17" s="62" t="s">
+      <c r="F17" s="87"/>
+      <c r="G17" s="60" t="s">
         <v>28</v>
       </c>
       <c r="H17" s="41">
@@ -4190,10 +6060,10 @@
       <c r="I17" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="J17" s="62">
+      <c r="J17" s="60">
         <v>0</v>
       </c>
-      <c r="L17" s="68"/>
+      <c r="L17" s="66"/>
     </row>
     <row r="18" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="26"/>
@@ -4201,7 +6071,7 @@
       <c r="C18" s="29"/>
       <c r="D18" s="33"/>
       <c r="E18" s="32"/>
-      <c r="F18" s="90"/>
+      <c r="F18" s="87"/>
       <c r="G18" s="32" t="s">
         <v>13</v>
       </c>
@@ -4211,10 +6081,10 @@
       <c r="I18" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="J18" s="62">
+      <c r="J18" s="60">
         <v>38040</v>
       </c>
-      <c r="L18" s="68"/>
+      <c r="L18" s="66"/>
     </row>
     <row r="19" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="26"/>
@@ -4222,7 +6092,7 @@
       <c r="C19" s="29"/>
       <c r="D19" s="33"/>
       <c r="E19" s="32"/>
-      <c r="F19" s="90"/>
+      <c r="F19" s="87"/>
       <c r="G19" s="32" t="s">
         <v>24</v>
       </c>
@@ -4232,10 +6102,10 @@
       <c r="I19" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="J19" s="62">
+      <c r="J19" s="60">
         <v>33220</v>
       </c>
-      <c r="L19" s="68"/>
+      <c r="L19" s="66"/>
     </row>
     <row r="20" spans="1:12" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="26"/>
@@ -4243,7 +6113,7 @@
       <c r="C20" s="29"/>
       <c r="D20" s="33"/>
       <c r="E20" s="32"/>
-      <c r="F20" s="90"/>
+      <c r="F20" s="87"/>
       <c r="G20" s="32" t="s">
         <v>14</v>
       </c>
@@ -4254,7 +6124,7 @@
       <c r="I20" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="J20" s="62">
+      <c r="J20" s="60">
         <v>71260</v>
       </c>
       <c r="L20" s="6"/>
@@ -4265,18 +6135,18 @@
       <c r="C21" s="29"/>
       <c r="D21" s="33"/>
       <c r="E21" s="32"/>
-      <c r="F21" s="90"/>
+      <c r="F21" s="87"/>
       <c r="G21" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="94">
+      <c r="H21" s="91">
         <f>H17-H20</f>
         <v>-352702.66599999997</v>
       </c>
       <c r="I21" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="J21" s="62">
+      <c r="J21" s="60">
         <v>-71260</v>
       </c>
       <c r="L21" s="6"/>
@@ -4287,90 +6157,90 @@
       <c r="C22" s="29"/>
       <c r="D22" s="33"/>
       <c r="E22" s="32"/>
-      <c r="F22" s="90"/>
-      <c r="G22" s="62" t="s">
+      <c r="F22" s="87"/>
+      <c r="G22" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="97">
+      <c r="H22" s="94">
         <v>60000</v>
       </c>
       <c r="I22" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="J22" s="62">
+      <c r="J22" s="60">
         <v>60000</v>
       </c>
       <c r="L22" s="6"/>
     </row>
     <row r="23" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A23" s="26"/>
-      <c r="B23" s="60"/>
+      <c r="B23" s="58"/>
       <c r="C23" s="29"/>
       <c r="D23" s="33"/>
       <c r="E23" s="32"/>
-      <c r="F23" s="90"/>
-      <c r="G23" s="62" t="s">
+      <c r="F23" s="87"/>
+      <c r="G23" s="60" t="s">
         <v>31</v>
       </c>
       <c r="H23" s="41">
         <f>H21+H22</f>
         <v>-292702.66599999997</v>
       </c>
-      <c r="I23" s="96" t="s">
+      <c r="I23" s="93" t="s">
         <v>31</v>
       </c>
-      <c r="J23" s="62">
+      <c r="J23" s="60">
         <v>-11260</v>
       </c>
     </row>
     <row r="24" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="26"/>
-      <c r="B24" s="60"/>
+      <c r="B24" s="58"/>
       <c r="C24" s="29"/>
       <c r="D24" s="33"/>
       <c r="E24" s="32"/>
-      <c r="F24" s="90"/>
+      <c r="F24" s="87"/>
       <c r="G24" s="32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="H24" s="32">
         <v>0</v>
       </c>
-      <c r="I24" s="96"/>
+      <c r="I24" s="93"/>
       <c r="J24" s="32"/>
     </row>
     <row r="25" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A25" s="26"/>
-      <c r="B25" s="60"/>
+      <c r="B25" s="58"/>
       <c r="C25" s="29"/>
       <c r="D25" s="33"/>
       <c r="E25" s="32"/>
-      <c r="F25" s="90"/>
+      <c r="F25" s="87"/>
       <c r="G25" s="32" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H25" s="32">
         <f>H24+H10</f>
         <v>71876.41399999999</v>
       </c>
-      <c r="I25" s="96"/>
+      <c r="I25" s="93"/>
       <c r="J25" s="32"/>
     </row>
     <row r="26" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A26" s="26"/>
-      <c r="B26" s="60"/>
+      <c r="B26" s="58"/>
       <c r="C26" s="29"/>
       <c r="D26" s="33"/>
       <c r="E26" s="32"/>
-      <c r="F26" s="90"/>
+      <c r="F26" s="87"/>
       <c r="G26" s="32" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H26" s="32">
         <f>H25-H20</f>
         <v>-26293.58600000001</v>
       </c>
-      <c r="I26" s="96"/>
+      <c r="I26" s="93"/>
       <c r="J26" s="32"/>
     </row>
   </sheetData>
@@ -4381,7 +6251,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815483-6499-49C9-BB8D-67572F4517B8}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -4543,8 +6413,8 @@
       <c r="D6" s="30"/>
       <c r="E6" s="31"/>
       <c r="F6" s="30"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="62">
+      <c r="G6" s="59"/>
+      <c r="H6" s="60">
         <f>SUM(H2:H5)</f>
         <v>0</v>
       </c>
@@ -4559,10 +6429,10 @@
       <c r="D7" s="33"/>
       <c r="E7" s="32"/>
       <c r="F7" s="30"/>
-      <c r="G7" s="62" t="s">
+      <c r="G7" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="H7" s="62">
+      <c r="H7" s="60">
         <f>H6</f>
         <v>0</v>
       </c>
@@ -4581,10 +6451,10 @@
       <c r="D8" s="33"/>
       <c r="E8" s="32"/>
       <c r="F8" s="30"/>
-      <c r="G8" s="62" t="s">
+      <c r="G8" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="62">
+      <c r="H8" s="60">
         <v>0</v>
       </c>
       <c r="I8" s="15" t="s">
@@ -4602,10 +6472,10 @@
       <c r="D9" s="33"/>
       <c r="E9" s="32"/>
       <c r="F9" s="30"/>
-      <c r="G9" s="62" t="s">
+      <c r="G9" s="60" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="63">
+      <c r="H9" s="61">
         <f>SUM(H7,H8)</f>
         <v>0</v>
       </c>
@@ -4624,10 +6494,10 @@
       <c r="D10" s="33"/>
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
-      <c r="G10" s="62" t="s">
+      <c r="G10" s="60" t="s">
         <v>13</v>
       </c>
-      <c r="H10" s="64">
+      <c r="H10" s="62">
         <v>38040</v>
       </c>
       <c r="I10" s="15" t="s">
@@ -4645,14 +6515,14 @@
       <c r="D11" s="33"/>
       <c r="E11" s="32"/>
       <c r="F11" s="30"/>
-      <c r="G11" s="62" t="s">
+      <c r="G11" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="H11" s="64">
+      <c r="H11" s="62">
         <v>33220</v>
       </c>
       <c r="I11" s="15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="J11" s="15">
         <v>38040</v>
@@ -4665,13 +6535,13 @@
       <c r="C12" s="29"/>
       <c r="D12" s="33"/>
       <c r="E12" s="32"/>
-      <c r="F12" s="59" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="62" t="s">
+      <c r="F12" s="57" t="s">
+        <v>58</v>
+      </c>
+      <c r="G12" s="60" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="63">
+      <c r="H12" s="61">
         <f>H10+H11</f>
         <v>71260</v>
       </c>
@@ -4690,10 +6560,10 @@
       <c r="D13" s="33"/>
       <c r="E13" s="32"/>
       <c r="F13" s="30"/>
-      <c r="G13" s="62" t="s">
+      <c r="G13" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="65">
+      <c r="H13" s="63">
         <f>H9-H12</f>
         <v>-71260</v>
       </c>
@@ -4711,13 +6581,13 @@
       <c r="C14" s="29"/>
       <c r="D14" s="33"/>
       <c r="E14" s="32"/>
-      <c r="F14" s="59" t="s">
-        <v>58</v>
-      </c>
-      <c r="G14" s="62" t="s">
+      <c r="F14" s="57" t="s">
+        <v>57</v>
+      </c>
+      <c r="G14" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="H14" s="62">
+      <c r="H14" s="60">
         <v>60000</v>
       </c>
       <c r="I14" s="15" t="s">
@@ -4730,15 +6600,15 @@
     </row>
     <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="26"/>
-      <c r="B15" s="60"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="29"/>
       <c r="D15" s="33"/>
       <c r="E15" s="32"/>
       <c r="F15" s="30"/>
-      <c r="G15" s="62" t="s">
+      <c r="G15" s="60" t="s">
         <v>31</v>
       </c>
-      <c r="H15" s="66">
+      <c r="H15" s="64">
         <f>H13+H14</f>
         <v>-11260</v>
       </c>
@@ -4751,13 +6621,13 @@
     </row>
     <row r="16" spans="1:14" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="26"/>
-      <c r="B16" s="60"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="29"/>
       <c r="D16" s="33"/>
       <c r="E16" s="32"/>
       <c r="F16" s="30"/>
-      <c r="G16" s="62"/>
-      <c r="H16" s="62"/>
+      <c r="G16" s="60"/>
+      <c r="H16" s="60"/>
       <c r="J16" s="7"/>
       <c r="K16" s="6"/>
       <c r="L16" s="7"/>
@@ -4766,17 +6636,17 @@
     </row>
     <row r="17" spans="1:14" s="11" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="26"/>
-      <c r="B17" s="60"/>
+      <c r="B17" s="58"/>
       <c r="C17" s="29"/>
       <c r="D17" s="33"/>
       <c r="E17" s="32"/>
-      <c r="F17" s="59" t="s">
+      <c r="F17" s="57" t="s">
+        <v>59</v>
+      </c>
+      <c r="G17" s="65" t="s">
         <v>60</v>
       </c>
-      <c r="G17" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="H17" s="62">
+      <c r="H17" s="60">
         <f>H14-H12</f>
         <v>-11260</v>
       </c>
@@ -4809,7 +6679,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DA818F-D2F1-4405-A36C-2376E8E1DAA2}">
   <dimension ref="A1:N14"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -5044,7 +6914,7 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="H10" s="35">
         <v>38040</v>
@@ -5146,7 +7016,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDBED0F-338F-4C61-AC0B-5077E6985A08}">
   <dimension ref="A1:N25"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -5234,7 +7104,7 @@
     </row>
     <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A3" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="28">
         <v>45995</v>
@@ -5265,7 +7135,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B4" s="28">
         <v>46002</v>
@@ -5309,7 +7179,7 @@
         <v>9</v>
       </c>
       <c r="E5" s="31"/>
-      <c r="F5" s="53">
+      <c r="F5" s="51">
         <v>6.9099999999999995E-2</v>
       </c>
       <c r="G5" s="31">
@@ -5328,7 +7198,7 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="88" t="s">
+      <c r="A6" s="85" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="28">
@@ -5366,14 +7236,14 @@
       <c r="B7" s="28">
         <v>45995</v>
       </c>
-      <c r="C7" s="87">
+      <c r="C7" s="84">
         <v>17500</v>
       </c>
       <c r="D7" s="30" t="s">
         <v>9</v>
       </c>
       <c r="E7" s="31"/>
-      <c r="F7" s="53">
+      <c r="F7" s="51">
         <v>0.20499999999999999</v>
       </c>
       <c r="G7" s="31">
@@ -5393,7 +7263,7 @@
     </row>
     <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A8" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="28">
         <v>46006</v>
@@ -5469,7 +7339,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="31"/>
-      <c r="F10" s="53">
+      <c r="F10" s="51">
         <v>0.13250000000000001</v>
       </c>
       <c r="G10" s="31">
@@ -5494,14 +7364,14 @@
       <c r="B11" s="28">
         <v>46015</v>
       </c>
-      <c r="C11" s="87">
+      <c r="C11" s="84">
         <v>69000</v>
       </c>
       <c r="D11" s="30" t="s">
         <v>9</v>
       </c>
       <c r="E11" s="31"/>
-      <c r="F11" s="53">
+      <c r="F11" s="51">
         <v>0.1825</v>
       </c>
       <c r="G11" s="31">
@@ -5533,7 +7403,7 @@
         <v>9</v>
       </c>
       <c r="E12" s="31"/>
-      <c r="F12" s="53">
+      <c r="F12" s="51">
         <v>0.114</v>
       </c>
       <c r="G12" s="31">
@@ -5552,8 +7422,8 @@
       <c r="N12" s="6"/>
     </row>
     <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="88" t="s">
-        <v>52</v>
+      <c r="A13" s="85" t="s">
+        <v>51</v>
       </c>
       <c r="B13" s="28">
         <v>46013</v>
@@ -5749,13 +7619,13 @@
     </row>
     <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
       <c r="G21" s="32" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="H21" s="35">
         <v>12050</v>
       </c>
       <c r="I21" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J21" s="7">
         <v>10130</v>
@@ -5837,7 +7707,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F537F07A-D0A7-416B-8994-ABDD1C22435D}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -6100,13 +7970,13 @@
       <c r="E10" s="32"/>
       <c r="F10" s="30"/>
       <c r="G10" s="32" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H10" s="35">
         <v>24420</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J10" s="7">
         <v>10130</v>
@@ -6244,7 +8114,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801544F9-630F-4E32-B67B-5CF42760770C}">
   <dimension ref="A1:N20"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -6312,14 +8182,14 @@
         <v>9</v>
       </c>
       <c r="E2" s="31"/>
-      <c r="F2" s="54">
+      <c r="F2" s="52">
         <v>0</v>
       </c>
       <c r="G2" s="31">
         <f>C2*F2</f>
         <v>0</v>
       </c>
-      <c r="H2" s="55">
+      <c r="H2" s="53">
         <f>G2*0.9</f>
         <v>0</v>
       </c>
@@ -6351,7 +8221,7 @@
     </row>
     <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A4" s="27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B4" s="28">
         <v>45931</v>
@@ -6384,7 +8254,7 @@
     </row>
     <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
       <c r="A5" s="27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="28">
         <v>45937</v>
@@ -6573,13 +8443,13 @@
       <c r="E12" s="32"/>
       <c r="F12" s="30"/>
       <c r="G12" s="32" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H12" s="35">
         <v>19270</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J12" s="7">
         <v>10130</v>
@@ -6715,1846 +8585,4 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805BC19F-42DC-4CD3-B954-E9F19E56BFF7}">
-  <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="57"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="77" t="s">
-        <v>52</v>
-      </c>
-      <c r="B2" s="78">
-        <v>45903</v>
-      </c>
-      <c r="C2" s="79">
-        <v>120000</v>
-      </c>
-      <c r="D2" s="77"/>
-      <c r="E2" s="77"/>
-      <c r="F2" s="77">
-        <v>0.15454999999999999</v>
-      </c>
-      <c r="G2" s="82">
-        <v>18546</v>
-      </c>
-      <c r="H2" s="82">
-        <v>16691.400000000001</v>
-      </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="77" t="s">
-        <v>43</v>
-      </c>
-      <c r="B3" s="78">
-        <v>45910</v>
-      </c>
-      <c r="C3" s="79">
-        <v>1200</v>
-      </c>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="83">
-        <v>0.31</v>
-      </c>
-      <c r="G3" s="82">
-        <v>372</v>
-      </c>
-      <c r="H3" s="82">
-        <v>339.6</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="77" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="78">
-        <v>45905</v>
-      </c>
-      <c r="C4" s="84">
-        <v>17500</v>
-      </c>
-      <c r="D4" s="77"/>
-      <c r="E4" s="77"/>
-      <c r="F4" s="83">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G4" s="82">
-        <v>3587.5</v>
-      </c>
-      <c r="H4" s="82">
-        <v>3228.75</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="77" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="78">
-        <v>45912</v>
-      </c>
-      <c r="C5" s="79">
-        <v>4000</v>
-      </c>
-      <c r="D5" s="77"/>
-      <c r="E5" s="77"/>
-      <c r="F5" s="83">
-        <v>0.15</v>
-      </c>
-      <c r="G5" s="82">
-        <v>600</v>
-      </c>
-      <c r="H5" s="82">
-        <v>540</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="B6" s="78">
-        <v>45912</v>
-      </c>
-      <c r="C6" s="79">
-        <v>5000</v>
-      </c>
-      <c r="D6" s="77"/>
-      <c r="E6" s="77"/>
-      <c r="F6" s="77">
-        <v>1</v>
-      </c>
-      <c r="G6" s="82">
-        <v>5000</v>
-      </c>
-      <c r="H6" s="82">
-        <v>4500</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="77" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="78">
-        <v>45911</v>
-      </c>
-      <c r="C7" s="85">
-        <v>55000</v>
-      </c>
-      <c r="D7" s="77"/>
-      <c r="E7" s="77"/>
-      <c r="F7" s="83">
-        <v>0.2261</v>
-      </c>
-      <c r="G7" s="82">
-        <v>12435.5</v>
-      </c>
-      <c r="H7" s="82">
-        <v>11191.95</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="78">
-        <v>45909</v>
-      </c>
-      <c r="C8" s="84">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="77"/>
-      <c r="E8" s="77"/>
-      <c r="F8" s="77">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="G8" s="82">
-        <v>11110</v>
-      </c>
-      <c r="H8" s="82">
-        <v>9999</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="78">
-        <v>45911</v>
-      </c>
-      <c r="C9" s="84">
-        <v>69000</v>
-      </c>
-      <c r="D9" s="77"/>
-      <c r="E9" s="77"/>
-      <c r="F9" s="83">
-        <v>0.19650000000000001</v>
-      </c>
-      <c r="G9" s="82">
-        <v>13558.5</v>
-      </c>
-      <c r="H9" s="82">
-        <v>12202.65</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="77" t="s">
-        <v>41</v>
-      </c>
-      <c r="B10" s="78">
-        <v>45911</v>
-      </c>
-      <c r="C10" s="85">
-        <v>7200</v>
-      </c>
-      <c r="D10" s="77"/>
-      <c r="E10" s="77"/>
-      <c r="F10" s="77">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G10" s="82">
-        <v>1260</v>
-      </c>
-      <c r="H10" s="82">
-        <v>1134</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="77" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="78">
-        <v>45912</v>
-      </c>
-      <c r="C11" s="85">
-        <v>4200</v>
-      </c>
-      <c r="D11" s="77"/>
-      <c r="E11" s="77"/>
-      <c r="F11" s="86">
-        <v>0.24</v>
-      </c>
-      <c r="G11" s="82">
-        <v>1008</v>
-      </c>
-      <c r="H11" s="82">
-        <v>907.2</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="77" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="78">
-        <v>45910</v>
-      </c>
-      <c r="C12" s="84">
-        <v>81000</v>
-      </c>
-      <c r="D12" s="77"/>
-      <c r="E12" s="77"/>
-      <c r="F12" s="83">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="82">
-        <v>20250</v>
-      </c>
-      <c r="H12" s="82">
-        <v>19926</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="78">
-        <v>45905</v>
-      </c>
-      <c r="C13" s="79">
-        <v>27000</v>
-      </c>
-      <c r="D13" s="77"/>
-      <c r="E13" s="77"/>
-      <c r="F13" s="77">
-        <v>0.05</v>
-      </c>
-      <c r="G13" s="82">
-        <v>1350</v>
-      </c>
-      <c r="H13" s="82">
-        <v>1350</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="77" t="s">
-        <v>40</v>
-      </c>
-      <c r="B14" s="78">
-        <v>45905</v>
-      </c>
-      <c r="C14" s="79">
-        <v>27000</v>
-      </c>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="77">
-        <v>0.5</v>
-      </c>
-      <c r="G14" s="82">
-        <v>13500</v>
-      </c>
-      <c r="H14" s="82">
-        <v>12825</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="77" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="78">
-        <v>45910</v>
-      </c>
-      <c r="C15" s="84">
-        <v>17500</v>
-      </c>
-      <c r="D15" s="77"/>
-      <c r="E15" s="77"/>
-      <c r="F15" s="77">
-        <v>0.1</v>
-      </c>
-      <c r="G15" s="82">
-        <v>1750</v>
-      </c>
-      <c r="H15" s="82">
-        <v>1575</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="77" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="78">
-        <v>45915</v>
-      </c>
-      <c r="C16" s="79">
-        <v>20000</v>
-      </c>
-      <c r="D16" s="77"/>
-      <c r="E16" s="77"/>
-      <c r="F16" s="83">
-        <v>0.1128</v>
-      </c>
-      <c r="G16" s="82">
-        <v>2256</v>
-      </c>
-      <c r="H16" s="82">
-        <v>2256</v>
-      </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="77" t="s">
-        <v>46</v>
-      </c>
-      <c r="B17" s="78">
-        <v>45912</v>
-      </c>
-      <c r="C17" s="79">
-        <v>1000</v>
-      </c>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
-      <c r="F17" s="83">
-        <v>0.36</v>
-      </c>
-      <c r="G17" s="82">
-        <v>360</v>
-      </c>
-      <c r="H17" s="82">
-        <v>324</v>
-      </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="77" t="s">
-        <v>62</v>
-      </c>
-      <c r="B18" s="78">
-        <v>45905</v>
-      </c>
-      <c r="C18" s="79">
-        <v>8000</v>
-      </c>
-      <c r="D18" s="77"/>
-      <c r="E18" s="77"/>
-      <c r="F18" s="77">
-        <v>0.8</v>
-      </c>
-      <c r="G18" s="82">
-        <v>6400</v>
-      </c>
-      <c r="H18" s="82">
-        <v>5760</v>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="77" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="78">
-        <v>45915</v>
-      </c>
-      <c r="C19" s="79">
-        <v>50000</v>
-      </c>
-      <c r="D19" s="77"/>
-      <c r="E19" s="77"/>
-      <c r="F19" s="86">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="G19" s="82">
-        <v>6625</v>
-      </c>
-      <c r="H19" s="82">
-        <v>5962.5</v>
-      </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="77" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="78">
-        <v>45905</v>
-      </c>
-      <c r="C20" s="85">
-        <v>25000</v>
-      </c>
-      <c r="D20" s="77"/>
-      <c r="E20" s="77"/>
-      <c r="F20" s="86">
-        <v>0.17169999999999999</v>
-      </c>
-      <c r="G20" s="82">
-        <v>4292.5</v>
-      </c>
-      <c r="H20" s="82">
-        <v>3863.25</v>
-      </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="34">
-        <f>SUM(H2:H20)</f>
-        <v>114576.29999999999</v>
-      </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="78">
-        <v>45903</v>
-      </c>
-      <c r="C22" s="77">
-        <v>5000</v>
-      </c>
-      <c r="D22" s="77">
-        <v>7.5</v>
-      </c>
-      <c r="E22" s="82">
-        <v>37583.06</v>
-      </c>
-      <c r="F22" s="77">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="G22" s="82">
-        <v>41408.080000000002</v>
-      </c>
-      <c r="H22" s="82">
-        <v>3825.02</v>
-      </c>
-      <c r="I22" s="58"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="78">
-        <v>45908</v>
-      </c>
-      <c r="C23" s="77">
-        <v>5000</v>
-      </c>
-      <c r="D23" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E23" s="82">
-        <v>120766.9</v>
-      </c>
-      <c r="F23" s="77">
-        <v>23.4</v>
-      </c>
-      <c r="G23" s="82">
-        <v>116740.86</v>
-      </c>
-      <c r="H23" s="82">
-        <v>-4026.04</v>
-      </c>
-      <c r="I23" s="58"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="B24" s="78">
-        <v>45911</v>
-      </c>
-      <c r="C24" s="77">
-        <v>5000</v>
-      </c>
-      <c r="D24" s="77">
-        <v>23.2</v>
-      </c>
-      <c r="E24" s="82">
-        <v>116256.93</v>
-      </c>
-      <c r="F24" s="77">
-        <v>23.4</v>
-      </c>
-      <c r="G24" s="82">
-        <v>116740.86</v>
-      </c>
-      <c r="H24" s="77">
-        <v>483.93</v>
-      </c>
-      <c r="I24" s="58"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="77" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="78">
-        <v>45915</v>
-      </c>
-      <c r="C25" s="77">
-        <v>4000</v>
-      </c>
-      <c r="D25" s="77">
-        <v>23.1</v>
-      </c>
-      <c r="E25" s="82">
-        <v>92604.66</v>
-      </c>
-      <c r="F25" s="77">
-        <v>25.75</v>
-      </c>
-      <c r="G25" s="82">
-        <v>102771.87</v>
-      </c>
-      <c r="H25" s="82">
-        <v>10167.209999999999</v>
-      </c>
-      <c r="I25" s="58"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="77" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="78">
-        <v>45915</v>
-      </c>
-      <c r="C26" s="77">
-        <v>5000</v>
-      </c>
-      <c r="D26" s="77">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="E26" s="82">
-        <v>44097.46</v>
-      </c>
-      <c r="F26" s="77">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="G26" s="82">
-        <v>48392.57</v>
-      </c>
-      <c r="H26" s="82">
-        <v>4295.1099999999997</v>
-      </c>
-      <c r="I26" s="58"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="32">
-        <f>SUM(E22:E26)</f>
-        <v>411309.01000000007</v>
-      </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="32">
-        <f>SUM(G22:G26)</f>
-        <v>426054.24</v>
-      </c>
-      <c r="H27" s="32">
-        <f>SUM(H22:H26)</f>
-        <v>14745.23</v>
-      </c>
-      <c r="I27" s="32"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-    </row>
-    <row r="28" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="26"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="34">
-        <f>H21+H27</f>
-        <v>129321.52999999998</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J28" s="7">
-        <v>30614.600000000002</v>
-      </c>
-      <c r="K28" s="7"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="6"/>
-    </row>
-    <row r="29" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="32">
-        <v>-522636.73</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K29" s="7"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-    </row>
-    <row r="30" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="41">
-        <f>H28+H29</f>
-        <v>-393315.2</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="7">
-        <v>-522636.73</v>
-      </c>
-      <c r="K30" s="7"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-    </row>
-    <row r="31" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="35">
-        <v>396550</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K31" s="7"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-    </row>
-    <row r="32" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="H32" s="35">
-        <v>62010</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>51</v>
-      </c>
-      <c r="J32" s="7">
-        <v>10130</v>
-      </c>
-      <c r="K32" s="7"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-    </row>
-    <row r="33" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="26"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="41">
-        <f>H31+H32</f>
-        <v>458560</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33" s="7">
-        <v>396550</v>
-      </c>
-      <c r="K33" s="7"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="6"/>
-    </row>
-    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="5"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" s="45">
-        <f>H30-H33</f>
-        <v>-851875.2</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="7">
-        <v>-919186.73</v>
-      </c>
-      <c r="K34" s="7"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="6"/>
-    </row>
-    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="5"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H35" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J35" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K35" s="7"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="6"/>
-    </row>
-    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="6"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="42">
-        <f>H34+H35</f>
-        <v>-794875.2</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J36" s="7">
-        <v>-862186.73</v>
-      </c>
-      <c r="K36" s="7"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="6"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K37" s="7"/>
-      <c r="M37" s="7"/>
-    </row>
-    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="56" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="28">
-        <v>45546</v>
-      </c>
-      <c r="C38" s="29">
-        <v>24000</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="31"/>
-      <c r="F38" s="53">
-        <v>3.9899999999999998E-2</v>
-      </c>
-      <c r="G38" s="31">
-        <f>C38*F38</f>
-        <v>957.59999999999991</v>
-      </c>
-      <c r="H38" s="55">
-        <f>G38*0.9</f>
-        <v>861.83999999999992</v>
-      </c>
-      <c r="K38" s="7"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-    </row>
-    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="56" t="s">
-        <v>52</v>
-      </c>
-      <c r="B39" s="28">
-        <v>45530</v>
-      </c>
-      <c r="C39" s="29">
-        <v>30000</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="31"/>
-      <c r="F39" s="37">
-        <v>0.19</v>
-      </c>
-      <c r="G39" s="31">
-        <f>C39*F39</f>
-        <v>5700</v>
-      </c>
-      <c r="H39" s="32">
-        <f>G39</f>
-        <v>5700</v>
-      </c>
-      <c r="K39" s="7"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C40" s="12"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="10"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N20">
-    <sortCondition ref="A2:A20"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961B3AB4-C9A4-46F9-AED6-DC61A66CC09A}">
-  <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45897</v>
-      </c>
-      <c r="C2" s="29">
-        <v>600</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="75">
-        <v>2.5</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>1500</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2*0.9</f>
-        <v>1350</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="41">
-        <f>SUM(H2:H2)</f>
-        <v>1350</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4" s="78">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="79">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="80">
-        <v>1.88</v>
-      </c>
-      <c r="E4" s="80">
-        <v>18841.64</v>
-      </c>
-      <c r="F4" s="80">
-        <v>1.9</v>
-      </c>
-      <c r="G4" s="80">
-        <v>18957.919999999998</v>
-      </c>
-      <c r="H4" s="80">
-        <v>116.28</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="77" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="78">
-        <v>45875</v>
-      </c>
-      <c r="C5" s="79">
-        <v>2800</v>
-      </c>
-      <c r="D5" s="80">
-        <v>10.5</v>
-      </c>
-      <c r="E5" s="80">
-        <v>29465.119999999999</v>
-      </c>
-      <c r="F5" s="80">
-        <v>11.6</v>
-      </c>
-      <c r="G5" s="80">
-        <v>32408.06</v>
-      </c>
-      <c r="H5" s="80">
-        <v>2942.94</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="77" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="78">
-        <v>45875</v>
-      </c>
-      <c r="C6" s="79">
-        <v>5000</v>
-      </c>
-      <c r="D6" s="80">
-        <v>3.9</v>
-      </c>
-      <c r="E6" s="80">
-        <v>19543.2</v>
-      </c>
-      <c r="F6" s="80">
-        <v>4.5199999999999996</v>
-      </c>
-      <c r="G6" s="80">
-        <v>22549.95</v>
-      </c>
-      <c r="H6" s="80">
-        <v>3006.75</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="77" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="78">
-        <v>45876</v>
-      </c>
-      <c r="C7" s="79">
-        <v>3200</v>
-      </c>
-      <c r="D7" s="80">
-        <v>9.25</v>
-      </c>
-      <c r="E7" s="80">
-        <v>29665.56</v>
-      </c>
-      <c r="F7" s="80">
-        <v>9.4</v>
-      </c>
-      <c r="G7" s="80">
-        <v>30013.37</v>
-      </c>
-      <c r="H7" s="80">
-        <v>347.81</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="B8" s="78">
-        <v>45876</v>
-      </c>
-      <c r="C8" s="79">
-        <v>10000</v>
-      </c>
-      <c r="D8" s="80">
-        <v>1.85</v>
-      </c>
-      <c r="E8" s="80">
-        <v>18540.98</v>
-      </c>
-      <c r="F8" s="80">
-        <v>2.06</v>
-      </c>
-      <c r="G8" s="80">
-        <v>20554.38</v>
-      </c>
-      <c r="H8" s="80">
-        <v>2013.4</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="77" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="78">
-        <v>45877</v>
-      </c>
-      <c r="C9" s="79">
-        <v>6000</v>
-      </c>
-      <c r="D9" s="80">
-        <v>6.1</v>
-      </c>
-      <c r="E9" s="80">
-        <v>36681.06</v>
-      </c>
-      <c r="F9" s="80">
-        <v>6.7</v>
-      </c>
-      <c r="G9" s="80">
-        <v>40110.97</v>
-      </c>
-      <c r="H9" s="80">
-        <v>3429.91</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="77" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="78">
-        <v>45877</v>
-      </c>
-      <c r="C10" s="79">
-        <v>3000</v>
-      </c>
-      <c r="D10" s="80">
-        <v>27.75</v>
-      </c>
-      <c r="E10" s="80">
-        <v>83434.39</v>
-      </c>
-      <c r="F10" s="80">
-        <v>31</v>
-      </c>
-      <c r="G10" s="80">
-        <v>92794.01</v>
-      </c>
-      <c r="H10" s="80">
-        <v>9359.6200000000008</v>
-      </c>
-      <c r="I10" s="76"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="B11" s="78">
-        <v>45889</v>
-      </c>
-      <c r="C11" s="79">
-        <v>4000</v>
-      </c>
-      <c r="D11" s="80">
-        <v>24.1</v>
-      </c>
-      <c r="E11" s="80">
-        <v>96613.52</v>
-      </c>
-      <c r="F11" s="80">
-        <v>24.3</v>
-      </c>
-      <c r="G11" s="80">
-        <v>96984.72</v>
-      </c>
-      <c r="H11" s="80">
-        <v>371.2</v>
-      </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12" s="78">
-        <v>45890</v>
-      </c>
-      <c r="C12" s="79">
-        <v>4000</v>
-      </c>
-      <c r="D12" s="80">
-        <v>24.1</v>
-      </c>
-      <c r="E12" s="80">
-        <v>96613.52</v>
-      </c>
-      <c r="F12" s="80">
-        <v>24.3</v>
-      </c>
-      <c r="G12" s="80">
-        <v>96984.72</v>
-      </c>
-      <c r="H12" s="80">
-        <v>371.2</v>
-      </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="77" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="78">
-        <v>45891</v>
-      </c>
-      <c r="C13" s="79">
-        <v>5000</v>
-      </c>
-      <c r="D13" s="80">
-        <v>24.1</v>
-      </c>
-      <c r="E13" s="80">
-        <v>120766.9</v>
-      </c>
-      <c r="F13" s="80">
-        <v>24.3</v>
-      </c>
-      <c r="G13" s="80">
-        <v>121230.88</v>
-      </c>
-      <c r="H13" s="80">
-        <v>463.98</v>
-      </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="77" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="78">
-        <v>45896</v>
-      </c>
-      <c r="C14" s="79">
-        <v>6000</v>
-      </c>
-      <c r="D14" s="80">
-        <v>7.3</v>
-      </c>
-      <c r="E14" s="80">
-        <v>43897.02</v>
-      </c>
-      <c r="F14" s="80">
-        <v>8.4</v>
-      </c>
-      <c r="G14" s="80">
-        <v>50288.37</v>
-      </c>
-      <c r="H14" s="80">
-        <v>6391.35</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="77" t="s">
-        <v>42</v>
-      </c>
-      <c r="B15" s="78">
-        <v>45897</v>
-      </c>
-      <c r="C15" s="79">
-        <v>5000</v>
-      </c>
-      <c r="D15" s="80">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E15" s="80">
-        <v>11024.36</v>
-      </c>
-      <c r="F15" s="80">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G15" s="80">
-        <v>11474.52</v>
-      </c>
-      <c r="H15" s="80">
-        <v>450.16</v>
-      </c>
-      <c r="I15" s="81"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32">
-        <f>SUM(E4:E15)</f>
-        <v>605087.27</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32">
-        <f>SUM(G4:G15)</f>
-        <v>634351.87</v>
-      </c>
-      <c r="H16" s="32">
-        <f>SUM(H4:H15)</f>
-        <v>29264.600000000002</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="41">
-        <f>H3+H16</f>
-        <v>30614.600000000002</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="7">
-        <v>-365900.39999999997</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="32">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="7">
-        <v>-187350.93</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="41">
-        <f>H17+H18</f>
-        <v>-522636.73</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-    </row>
-    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="7">
-        <v>386420</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="7">
-        <v>377810</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-    </row>
-    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="H21" s="35">
-        <v>10130</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="J21" s="7">
-        <v>8610</v>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="26"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="41">
-        <f>H20+H21</f>
-        <v>396550</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="5"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="47">
-        <f>H19-H22</f>
-        <v>-919186.73</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="7">
-        <v>-939671.33</v>
-      </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="5"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J24" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="6"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="42">
-        <f>H23+H24</f>
-        <v>-862186.73</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="7">
-        <v>-882671.33</v>
-      </c>
-      <c r="K25" s="7"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K26" s="7"/>
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M28" s="7"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D29" s="8"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="10"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -1,30 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7142" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADE64E70-6270-4B39-9CFD-D47E37DA75DD}"/>
+  <xr:revisionPtr revIDLastSave="7157" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81AB62B3-7E47-4B15-88AC-EB2493449B96}"/>
   <bookViews>
-    <workbookView xWindow="1152" yWindow="1152" windowWidth="15996" windowHeight="10764" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="JUN26" sheetId="98" r:id="rId1"/>
-    <sheet name="MAY26" sheetId="97" r:id="rId2"/>
-    <sheet name="APR26" sheetId="96" r:id="rId3"/>
-    <sheet name="MAR26" sheetId="95" r:id="rId4"/>
-    <sheet name="FEB26" sheetId="94" r:id="rId5"/>
-    <sheet name="JAN26" sheetId="93" r:id="rId6"/>
-    <sheet name="DEC25" sheetId="92" r:id="rId7"/>
-    <sheet name="NOV25" sheetId="91" r:id="rId8"/>
-    <sheet name="OCT25" sheetId="90" r:id="rId9"/>
-    <sheet name="SEP25" sheetId="89" r:id="rId10"/>
-    <sheet name="AUG25" sheetId="88" r:id="rId11"/>
-    <sheet name="JUL25" sheetId="87" r:id="rId12"/>
+    <sheet name="JUL26" sheetId="99" r:id="rId1"/>
+    <sheet name="JUN26" sheetId="98" r:id="rId2"/>
+    <sheet name="MAY26" sheetId="97" r:id="rId3"/>
+    <sheet name="APR26" sheetId="96" r:id="rId4"/>
+    <sheet name="MAR26" sheetId="95" r:id="rId5"/>
+    <sheet name="FEB26" sheetId="94" r:id="rId6"/>
+    <sheet name="JAN26" sheetId="93" r:id="rId7"/>
+    <sheet name="DEC25" sheetId="92" r:id="rId8"/>
+    <sheet name="NOV25" sheetId="91" r:id="rId9"/>
+    <sheet name="OCT25" sheetId="90" r:id="rId10"/>
+    <sheet name="SEP25" sheetId="89" r:id="rId11"/>
+    <sheet name="AUG25" sheetId="88" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="68">
   <si>
     <t>Name</t>
   </si>
@@ -611,10 +611,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -962,6 +958,2765 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B9F8AE-F947-4FC1-BF85-790919A908D8}">
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.75" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="28">
+        <v>44736</v>
+      </c>
+      <c r="C2" s="29">
+        <v>40000</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="37">
+        <v>0.15559999999999999</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>6223.9999999999991</v>
+      </c>
+      <c r="H2" s="32">
+        <v>0</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="34">
+        <f>SUM(H2:H2)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45868</v>
+      </c>
+      <c r="C4" s="29">
+        <v>1800</v>
+      </c>
+      <c r="D4" s="30">
+        <v>20</v>
+      </c>
+      <c r="E4" s="31">
+        <v>36079.74</v>
+      </c>
+      <c r="F4" s="30">
+        <v>22.9</v>
+      </c>
+      <c r="G4" s="31">
+        <v>41128.699999999997</v>
+      </c>
+      <c r="H4" s="32">
+        <v>0</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="32">
+        <f>SUM(E4:E4)</f>
+        <v>36079.74</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="32">
+        <f>SUM(G4:G4)</f>
+        <v>41128.699999999997</v>
+      </c>
+      <c r="H5" s="32">
+        <f>SUM(H4:H4)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="34">
+        <f>H3+H5</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="7">
+        <v>48852.81</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="32">
+        <v>-57483.65400000001</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="7">
+        <v>-106336.46400000001</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="34">
+        <f>H6+H7</f>
+        <v>-57483.65400000001</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="7">
+        <v>-57483.65400000001</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="35">
+        <v>184230</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="7">
+        <v>169620</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10" s="35">
+        <v>34310</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="J10" s="7">
+        <v>14610</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="41">
+        <f>H9+H10</f>
+        <v>218540</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7">
+        <v>184230</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="46">
+        <f>H8-H11</f>
+        <v>-276023.65399999998</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="7">
+        <v>-241713.65400000001</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="38">
+        <f>J13</f>
+        <v>60000</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="7">
+        <v>60000</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="6"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="39">
+        <f>H12+H13</f>
+        <v>-216023.65399999998</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="7">
+        <v>-181713.65400000001</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G15" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="H15" s="7">
+        <v>270100.40599999996</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="7">
+        <v>221247.59599999999</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G16" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="H16" s="32">
+        <f>H15+H3</f>
+        <v>270100.40599999996</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="7">
+        <v>270100.40599999996</v>
+      </c>
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="3:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G17" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="32">
+        <f>H16-H11</f>
+        <v>51560.405999999959</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="7">
+        <v>85870.405999999959</v>
+      </c>
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C18" s="12"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="10"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801544F9-630F-4E32-B67B-5CF42760770C}">
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45576</v>
+      </c>
+      <c r="C2" s="29">
+        <v>6800</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="52">
+        <v>0</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="53">
+        <f>G2*0.9</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="34">
+        <f>SUM(H2:H2)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45931</v>
+      </c>
+      <c r="C4" s="29">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="30">
+        <v>2.62</v>
+      </c>
+      <c r="E4" s="31">
+        <v>26258.03</v>
+      </c>
+      <c r="F4" s="30">
+        <v>2.72</v>
+      </c>
+      <c r="G4" s="31">
+        <v>27139.759999999998</v>
+      </c>
+      <c r="H4" s="40">
+        <f>G4-E4</f>
+        <v>881.72999999999956</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="28">
+        <v>45937</v>
+      </c>
+      <c r="C5" s="29">
+        <v>3000</v>
+      </c>
+      <c r="D5" s="30">
+        <v>26</v>
+      </c>
+      <c r="E5" s="31">
+        <v>78172.759999999995</v>
+      </c>
+      <c r="F5" s="30">
+        <v>26.5</v>
+      </c>
+      <c r="G5" s="31">
+        <v>79323.91</v>
+      </c>
+      <c r="H5" s="40">
+        <f>G5-E5</f>
+        <v>1151.1500000000087</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="28">
+        <v>45954</v>
+      </c>
+      <c r="C6" s="29">
+        <v>2500</v>
+      </c>
+      <c r="D6" s="30">
+        <v>31</v>
+      </c>
+      <c r="E6" s="31">
+        <v>77671.66</v>
+      </c>
+      <c r="F6" s="30">
+        <v>31.25</v>
+      </c>
+      <c r="G6" s="31">
+        <v>77951.960000000006</v>
+      </c>
+      <c r="H6" s="40">
+        <f>G6-E6</f>
+        <v>280.30000000000291</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32">
+        <f>SUM(E4:E6)</f>
+        <v>182102.45</v>
+      </c>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32">
+        <f t="shared" ref="G7:H7" si="0">SUM(G4:G6)</f>
+        <v>184415.63</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" si="0"/>
+        <v>2313.1800000000112</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="34">
+        <f>H3+H7</f>
+        <v>2313.1800000000112</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="7">
+        <v>30614.600000000002</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="32">
+        <v>-522636.73</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="41">
+        <f>H8+H9</f>
+        <v>-520323.55</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="7">
+        <v>-522636.73</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="35">
+        <v>396550</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+    </row>
+    <row r="12" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="35">
+        <v>19270</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="7">
+        <v>10130</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="26"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="41">
+        <f>H11+H12</f>
+        <v>415820</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="7">
+        <v>396550</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="5"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="45">
+        <f>H10-H13</f>
+        <v>-936143.55</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="7">
+        <v>-919186.73</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="5"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="38">
+        <v>57000</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="6"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="42">
+        <f>H14+H15</f>
+        <v>-879143.55</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="7">
+        <v>-862186.73</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="K17" s="7"/>
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C20" s="12"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="10"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805BC19F-42DC-4CD3-B954-E9F19E56BFF7}">
+  <dimension ref="A1:N40"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="55"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="74" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="75">
+        <v>45903</v>
+      </c>
+      <c r="C2" s="76">
+        <v>120000</v>
+      </c>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74">
+        <v>0.15454999999999999</v>
+      </c>
+      <c r="G2" s="79">
+        <v>18546</v>
+      </c>
+      <c r="H2" s="79">
+        <v>16691.400000000001</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="74" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="75">
+        <v>45910</v>
+      </c>
+      <c r="C3" s="76">
+        <v>1200</v>
+      </c>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="80">
+        <v>0.31</v>
+      </c>
+      <c r="G3" s="79">
+        <v>372</v>
+      </c>
+      <c r="H3" s="79">
+        <v>339.6</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C4" s="81">
+        <v>17500</v>
+      </c>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="80">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G4" s="79">
+        <v>3587.5</v>
+      </c>
+      <c r="H4" s="79">
+        <v>3228.75</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C5" s="76">
+        <v>4000</v>
+      </c>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="80">
+        <v>0.15</v>
+      </c>
+      <c r="G5" s="79">
+        <v>600</v>
+      </c>
+      <c r="H5" s="79">
+        <v>540</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C6" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74">
+        <v>1</v>
+      </c>
+      <c r="G6" s="79">
+        <v>5000</v>
+      </c>
+      <c r="H6" s="79">
+        <v>4500</v>
+      </c>
+      <c r="I6" s="10"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C7" s="82">
+        <v>55000</v>
+      </c>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="80">
+        <v>0.2261</v>
+      </c>
+      <c r="G7" s="79">
+        <v>12435.5</v>
+      </c>
+      <c r="H7" s="79">
+        <v>11191.95</v>
+      </c>
+      <c r="I7" s="10"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="75">
+        <v>45909</v>
+      </c>
+      <c r="C8" s="81">
+        <v>50000</v>
+      </c>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="G8" s="79">
+        <v>11110</v>
+      </c>
+      <c r="H8" s="79">
+        <v>9999</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C9" s="81">
+        <v>69000</v>
+      </c>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="80">
+        <v>0.19650000000000001</v>
+      </c>
+      <c r="G9" s="79">
+        <v>13558.5</v>
+      </c>
+      <c r="H9" s="79">
+        <v>12202.65</v>
+      </c>
+      <c r="I9" s="10"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C10" s="82">
+        <v>7200</v>
+      </c>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G10" s="79">
+        <v>1260</v>
+      </c>
+      <c r="H10" s="79">
+        <v>1134</v>
+      </c>
+      <c r="I10" s="10"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C11" s="82">
+        <v>4200</v>
+      </c>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="83">
+        <v>0.24</v>
+      </c>
+      <c r="G11" s="79">
+        <v>1008</v>
+      </c>
+      <c r="H11" s="79">
+        <v>907.2</v>
+      </c>
+      <c r="I11" s="10"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="75">
+        <v>45910</v>
+      </c>
+      <c r="C12" s="81">
+        <v>81000</v>
+      </c>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="80">
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="79">
+        <v>20250</v>
+      </c>
+      <c r="H12" s="79">
+        <v>19926</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C13" s="76">
+        <v>27000</v>
+      </c>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="79">
+        <v>1350</v>
+      </c>
+      <c r="H13" s="79">
+        <v>1350</v>
+      </c>
+      <c r="I13" s="10"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C14" s="76">
+        <v>27000</v>
+      </c>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="79">
+        <v>13500</v>
+      </c>
+      <c r="H14" s="79">
+        <v>12825</v>
+      </c>
+      <c r="I14" s="10"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="75">
+        <v>45910</v>
+      </c>
+      <c r="C15" s="81">
+        <v>17500</v>
+      </c>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="79">
+        <v>1750</v>
+      </c>
+      <c r="H15" s="79">
+        <v>1575</v>
+      </c>
+      <c r="I15" s="10"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A16" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C16" s="76">
+        <v>20000</v>
+      </c>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="80">
+        <v>0.1128</v>
+      </c>
+      <c r="G16" s="79">
+        <v>2256</v>
+      </c>
+      <c r="H16" s="79">
+        <v>2256</v>
+      </c>
+      <c r="I16" s="10"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A17" s="74" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C17" s="76">
+        <v>1000</v>
+      </c>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="80">
+        <v>0.36</v>
+      </c>
+      <c r="G17" s="79">
+        <v>360</v>
+      </c>
+      <c r="H17" s="79">
+        <v>324</v>
+      </c>
+      <c r="I17" s="10"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A18" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C18" s="76">
+        <v>8000</v>
+      </c>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74">
+        <v>0.8</v>
+      </c>
+      <c r="G18" s="79">
+        <v>6400</v>
+      </c>
+      <c r="H18" s="79">
+        <v>5760</v>
+      </c>
+      <c r="I18" s="10"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A19" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C19" s="76">
+        <v>50000</v>
+      </c>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="83">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="G19" s="79">
+        <v>6625</v>
+      </c>
+      <c r="H19" s="79">
+        <v>5962.5</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A20" s="74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C20" s="82">
+        <v>25000</v>
+      </c>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="83">
+        <v>0.17169999999999999</v>
+      </c>
+      <c r="G20" s="79">
+        <v>4292.5</v>
+      </c>
+      <c r="H20" s="79">
+        <v>3863.25</v>
+      </c>
+      <c r="I20" s="10"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="34">
+        <f>SUM(H2:H20)</f>
+        <v>114576.29999999999</v>
+      </c>
+      <c r="I21" s="10"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="75">
+        <v>45903</v>
+      </c>
+      <c r="C22" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D22" s="74">
+        <v>7.5</v>
+      </c>
+      <c r="E22" s="79">
+        <v>37583.06</v>
+      </c>
+      <c r="F22" s="74">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G22" s="79">
+        <v>41408.080000000002</v>
+      </c>
+      <c r="H22" s="79">
+        <v>3825.02</v>
+      </c>
+      <c r="I22" s="56"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="75">
+        <v>45908</v>
+      </c>
+      <c r="C23" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D23" s="74">
+        <v>24.1</v>
+      </c>
+      <c r="E23" s="79">
+        <v>120766.9</v>
+      </c>
+      <c r="F23" s="74">
+        <v>23.4</v>
+      </c>
+      <c r="G23" s="79">
+        <v>116740.86</v>
+      </c>
+      <c r="H23" s="79">
+        <v>-4026.04</v>
+      </c>
+      <c r="I23" s="56"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C24" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D24" s="74">
+        <v>23.2</v>
+      </c>
+      <c r="E24" s="79">
+        <v>116256.93</v>
+      </c>
+      <c r="F24" s="74">
+        <v>23.4</v>
+      </c>
+      <c r="G24" s="79">
+        <v>116740.86</v>
+      </c>
+      <c r="H24" s="74">
+        <v>483.93</v>
+      </c>
+      <c r="I24" s="56"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C25" s="74">
+        <v>4000</v>
+      </c>
+      <c r="D25" s="74">
+        <v>23.1</v>
+      </c>
+      <c r="E25" s="79">
+        <v>92604.66</v>
+      </c>
+      <c r="F25" s="74">
+        <v>25.75</v>
+      </c>
+      <c r="G25" s="79">
+        <v>102771.87</v>
+      </c>
+      <c r="H25" s="79">
+        <v>10167.209999999999</v>
+      </c>
+      <c r="I25" s="56"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C26" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D26" s="74">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E26" s="79">
+        <v>44097.46</v>
+      </c>
+      <c r="F26" s="74">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G26" s="79">
+        <v>48392.57</v>
+      </c>
+      <c r="H26" s="79">
+        <v>4295.1099999999997</v>
+      </c>
+      <c r="I26" s="56"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="26"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="32">
+        <f>SUM(E22:E26)</f>
+        <v>411309.01000000007</v>
+      </c>
+      <c r="F27" s="30"/>
+      <c r="G27" s="32">
+        <f>SUM(G22:G26)</f>
+        <v>426054.24</v>
+      </c>
+      <c r="H27" s="32">
+        <f>SUM(H22:H26)</f>
+        <v>14745.23</v>
+      </c>
+      <c r="I27" s="32"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+    </row>
+    <row r="28" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A28" s="26"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="34">
+        <f>H21+H27</f>
+        <v>129321.52999999998</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J28" s="7">
+        <v>30614.600000000002</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="26"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="32">
+        <v>-522636.73</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K29" s="7"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+    </row>
+    <row r="30" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="26"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="41">
+        <f>H28+H29</f>
+        <v>-393315.2</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" s="7">
+        <v>-522636.73</v>
+      </c>
+      <c r="K30" s="7"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+    </row>
+    <row r="31" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="26"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="35">
+        <v>396550</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+    </row>
+    <row r="32" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="26"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="35">
+        <v>62010</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="7">
+        <v>10130</v>
+      </c>
+      <c r="K32" s="7"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+    </row>
+    <row r="33" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="26"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="41">
+        <f>H31+H32</f>
+        <v>458560</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" s="7">
+        <v>396550</v>
+      </c>
+      <c r="K33" s="7"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="5"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="45">
+        <f>H30-H33</f>
+        <v>-851875.2</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="7">
+        <v>-919186.73</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="5"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K35" s="7"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="6"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="42">
+        <f>H34+H35</f>
+        <v>-794875.2</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="7">
+        <v>-862186.73</v>
+      </c>
+      <c r="K36" s="7"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K37" s="7"/>
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="28">
+        <v>45546</v>
+      </c>
+      <c r="C38" s="29">
+        <v>24000</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="31"/>
+      <c r="F38" s="51">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="G38" s="31">
+        <f>C38*F38</f>
+        <v>957.59999999999991</v>
+      </c>
+      <c r="H38" s="53">
+        <f>G38*0.9</f>
+        <v>861.83999999999992</v>
+      </c>
+      <c r="K38" s="7"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+    </row>
+    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="28">
+        <v>45530</v>
+      </c>
+      <c r="C39" s="29">
+        <v>30000</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="31"/>
+      <c r="F39" s="37">
+        <v>0.19</v>
+      </c>
+      <c r="G39" s="31">
+        <f>C39*F39</f>
+        <v>5700</v>
+      </c>
+      <c r="H39" s="32">
+        <f>G39</f>
+        <v>5700</v>
+      </c>
+      <c r="K39" s="7"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C40" s="12"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="10"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N20">
+    <sortCondition ref="A2:A20"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961B3AB4-C9A4-46F9-AED6-DC61A66CC09A}">
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45897</v>
+      </c>
+      <c r="C2" s="29">
+        <v>600</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="72">
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>1500</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2*0.9</f>
+        <v>1350</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="41">
+        <f>SUM(H2:H2)</f>
+        <v>1350</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="75">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="76">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="77">
+        <v>1.88</v>
+      </c>
+      <c r="E4" s="77">
+        <v>18841.64</v>
+      </c>
+      <c r="F4" s="77">
+        <v>1.9</v>
+      </c>
+      <c r="G4" s="77">
+        <v>18957.919999999998</v>
+      </c>
+      <c r="H4" s="77">
+        <v>116.28</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="75">
+        <v>45875</v>
+      </c>
+      <c r="C5" s="76">
+        <v>2800</v>
+      </c>
+      <c r="D5" s="77">
+        <v>10.5</v>
+      </c>
+      <c r="E5" s="77">
+        <v>29465.119999999999</v>
+      </c>
+      <c r="F5" s="77">
+        <v>11.6</v>
+      </c>
+      <c r="G5" s="77">
+        <v>32408.06</v>
+      </c>
+      <c r="H5" s="77">
+        <v>2942.94</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="75">
+        <v>45875</v>
+      </c>
+      <c r="C6" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D6" s="77">
+        <v>3.9</v>
+      </c>
+      <c r="E6" s="77">
+        <v>19543.2</v>
+      </c>
+      <c r="F6" s="77">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="G6" s="77">
+        <v>22549.95</v>
+      </c>
+      <c r="H6" s="77">
+        <v>3006.75</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="75">
+        <v>45876</v>
+      </c>
+      <c r="C7" s="76">
+        <v>3200</v>
+      </c>
+      <c r="D7" s="77">
+        <v>9.25</v>
+      </c>
+      <c r="E7" s="77">
+        <v>29665.56</v>
+      </c>
+      <c r="F7" s="77">
+        <v>9.4</v>
+      </c>
+      <c r="G7" s="77">
+        <v>30013.37</v>
+      </c>
+      <c r="H7" s="77">
+        <v>347.81</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="75">
+        <v>45876</v>
+      </c>
+      <c r="C8" s="76">
+        <v>10000</v>
+      </c>
+      <c r="D8" s="77">
+        <v>1.85</v>
+      </c>
+      <c r="E8" s="77">
+        <v>18540.98</v>
+      </c>
+      <c r="F8" s="77">
+        <v>2.06</v>
+      </c>
+      <c r="G8" s="77">
+        <v>20554.38</v>
+      </c>
+      <c r="H8" s="77">
+        <v>2013.4</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="75">
+        <v>45877</v>
+      </c>
+      <c r="C9" s="76">
+        <v>6000</v>
+      </c>
+      <c r="D9" s="77">
+        <v>6.1</v>
+      </c>
+      <c r="E9" s="77">
+        <v>36681.06</v>
+      </c>
+      <c r="F9" s="77">
+        <v>6.7</v>
+      </c>
+      <c r="G9" s="77">
+        <v>40110.97</v>
+      </c>
+      <c r="H9" s="77">
+        <v>3429.91</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="75">
+        <v>45877</v>
+      </c>
+      <c r="C10" s="76">
+        <v>3000</v>
+      </c>
+      <c r="D10" s="77">
+        <v>27.75</v>
+      </c>
+      <c r="E10" s="77">
+        <v>83434.39</v>
+      </c>
+      <c r="F10" s="77">
+        <v>31</v>
+      </c>
+      <c r="G10" s="77">
+        <v>92794.01</v>
+      </c>
+      <c r="H10" s="77">
+        <v>9359.6200000000008</v>
+      </c>
+      <c r="I10" s="73"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="75">
+        <v>45889</v>
+      </c>
+      <c r="C11" s="76">
+        <v>4000</v>
+      </c>
+      <c r="D11" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E11" s="77">
+        <v>96613.52</v>
+      </c>
+      <c r="F11" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G11" s="77">
+        <v>96984.72</v>
+      </c>
+      <c r="H11" s="77">
+        <v>371.2</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="75">
+        <v>45890</v>
+      </c>
+      <c r="C12" s="76">
+        <v>4000</v>
+      </c>
+      <c r="D12" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E12" s="77">
+        <v>96613.52</v>
+      </c>
+      <c r="F12" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G12" s="77">
+        <v>96984.72</v>
+      </c>
+      <c r="H12" s="77">
+        <v>371.2</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="75">
+        <v>45891</v>
+      </c>
+      <c r="C13" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D13" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E13" s="77">
+        <v>120766.9</v>
+      </c>
+      <c r="F13" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G13" s="77">
+        <v>121230.88</v>
+      </c>
+      <c r="H13" s="77">
+        <v>463.98</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="75">
+        <v>45896</v>
+      </c>
+      <c r="C14" s="76">
+        <v>6000</v>
+      </c>
+      <c r="D14" s="77">
+        <v>7.3</v>
+      </c>
+      <c r="E14" s="77">
+        <v>43897.02</v>
+      </c>
+      <c r="F14" s="77">
+        <v>8.4</v>
+      </c>
+      <c r="G14" s="77">
+        <v>50288.37</v>
+      </c>
+      <c r="H14" s="77">
+        <v>6391.35</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="75">
+        <v>45897</v>
+      </c>
+      <c r="C15" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D15" s="77">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E15" s="77">
+        <v>11024.36</v>
+      </c>
+      <c r="F15" s="77">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G15" s="77">
+        <v>11474.52</v>
+      </c>
+      <c r="H15" s="77">
+        <v>450.16</v>
+      </c>
+      <c r="I15" s="78"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32">
+        <f>SUM(E4:E15)</f>
+        <v>605087.27</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32">
+        <f>SUM(G4:G15)</f>
+        <v>634351.87</v>
+      </c>
+      <c r="H16" s="32">
+        <f>SUM(H4:H15)</f>
+        <v>29264.600000000002</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="41">
+        <f>H3+H16</f>
+        <v>30614.600000000002</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="7">
+        <v>-365900.39999999997</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="32">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="7">
+        <v>-187350.93</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+    </row>
+    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="26"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="41">
+        <f>H17+H18</f>
+        <v>-522636.73</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+    </row>
+    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="26"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="7">
+        <v>386420</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="7">
+        <v>377810</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+    </row>
+    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="26"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="35">
+        <v>10130</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" s="7">
+        <v>8610</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="26"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="41">
+        <f>H20+H21</f>
+        <v>396550</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="5"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="47">
+        <f>H19-H22</f>
+        <v>-919186.73</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="7">
+        <v>-939671.33</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="5"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="6"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="42">
+        <f>H23+H24</f>
+        <v>-862186.73</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="7">
+        <v>-882671.33</v>
+      </c>
+      <c r="K25" s="7"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K26" s="7"/>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D29" s="8"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="10"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24B6D7D9-1BF8-42AF-8BE9-2337E6298F4C}">
   <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -1638,2523 +4393,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805BC19F-42DC-4CD3-B954-E9F19E56BFF7}">
-  <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="55"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="74" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="75">
-        <v>45903</v>
-      </c>
-      <c r="C2" s="76">
-        <v>120000</v>
-      </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74">
-        <v>0.15454999999999999</v>
-      </c>
-      <c r="G2" s="79">
-        <v>18546</v>
-      </c>
-      <c r="H2" s="79">
-        <v>16691.400000000001</v>
-      </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="74" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="75">
-        <v>45910</v>
-      </c>
-      <c r="C3" s="76">
-        <v>1200</v>
-      </c>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="80">
-        <v>0.31</v>
-      </c>
-      <c r="G3" s="79">
-        <v>372</v>
-      </c>
-      <c r="H3" s="79">
-        <v>339.6</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C4" s="81">
-        <v>17500</v>
-      </c>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="80">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G4" s="79">
-        <v>3587.5</v>
-      </c>
-      <c r="H4" s="79">
-        <v>3228.75</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C5" s="76">
-        <v>4000</v>
-      </c>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="80">
-        <v>0.15</v>
-      </c>
-      <c r="G5" s="79">
-        <v>600</v>
-      </c>
-      <c r="H5" s="79">
-        <v>540</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C6" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74">
-        <v>1</v>
-      </c>
-      <c r="G6" s="79">
-        <v>5000</v>
-      </c>
-      <c r="H6" s="79">
-        <v>4500</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C7" s="82">
-        <v>55000</v>
-      </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="80">
-        <v>0.2261</v>
-      </c>
-      <c r="G7" s="79">
-        <v>12435.5</v>
-      </c>
-      <c r="H7" s="79">
-        <v>11191.95</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="75">
-        <v>45909</v>
-      </c>
-      <c r="C8" s="81">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="G8" s="79">
-        <v>11110</v>
-      </c>
-      <c r="H8" s="79">
-        <v>9999</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="74" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C9" s="81">
-        <v>69000</v>
-      </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="80">
-        <v>0.19650000000000001</v>
-      </c>
-      <c r="G9" s="79">
-        <v>13558.5</v>
-      </c>
-      <c r="H9" s="79">
-        <v>12202.65</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="74" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C10" s="82">
-        <v>7200</v>
-      </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G10" s="79">
-        <v>1260</v>
-      </c>
-      <c r="H10" s="79">
-        <v>1134</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="74" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C11" s="82">
-        <v>4200</v>
-      </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="83">
-        <v>0.24</v>
-      </c>
-      <c r="G11" s="79">
-        <v>1008</v>
-      </c>
-      <c r="H11" s="79">
-        <v>907.2</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="75">
-        <v>45910</v>
-      </c>
-      <c r="C12" s="81">
-        <v>81000</v>
-      </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="80">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="79">
-        <v>20250</v>
-      </c>
-      <c r="H12" s="79">
-        <v>19926</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C13" s="76">
-        <v>27000</v>
-      </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74">
-        <v>0.05</v>
-      </c>
-      <c r="G13" s="79">
-        <v>1350</v>
-      </c>
-      <c r="H13" s="79">
-        <v>1350</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C14" s="76">
-        <v>27000</v>
-      </c>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74">
-        <v>0.5</v>
-      </c>
-      <c r="G14" s="79">
-        <v>13500</v>
-      </c>
-      <c r="H14" s="79">
-        <v>12825</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="74" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="75">
-        <v>45910</v>
-      </c>
-      <c r="C15" s="81">
-        <v>17500</v>
-      </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74">
-        <v>0.1</v>
-      </c>
-      <c r="G15" s="79">
-        <v>1750</v>
-      </c>
-      <c r="H15" s="79">
-        <v>1575</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C16" s="76">
-        <v>20000</v>
-      </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="80">
-        <v>0.1128</v>
-      </c>
-      <c r="G16" s="79">
-        <v>2256</v>
-      </c>
-      <c r="H16" s="79">
-        <v>2256</v>
-      </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C17" s="76">
-        <v>1000</v>
-      </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="80">
-        <v>0.36</v>
-      </c>
-      <c r="G17" s="79">
-        <v>360</v>
-      </c>
-      <c r="H17" s="79">
-        <v>324</v>
-      </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C18" s="76">
-        <v>8000</v>
-      </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74">
-        <v>0.8</v>
-      </c>
-      <c r="G18" s="79">
-        <v>6400</v>
-      </c>
-      <c r="H18" s="79">
-        <v>5760</v>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="74" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C19" s="76">
-        <v>50000</v>
-      </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="83">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="G19" s="79">
-        <v>6625</v>
-      </c>
-      <c r="H19" s="79">
-        <v>5962.5</v>
-      </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C20" s="82">
-        <v>25000</v>
-      </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="83">
-        <v>0.17169999999999999</v>
-      </c>
-      <c r="G20" s="79">
-        <v>4292.5</v>
-      </c>
-      <c r="H20" s="79">
-        <v>3863.25</v>
-      </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="34">
-        <f>SUM(H2:H20)</f>
-        <v>114576.29999999999</v>
-      </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="75">
-        <v>45903</v>
-      </c>
-      <c r="C22" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D22" s="74">
-        <v>7.5</v>
-      </c>
-      <c r="E22" s="79">
-        <v>37583.06</v>
-      </c>
-      <c r="F22" s="74">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="G22" s="79">
-        <v>41408.080000000002</v>
-      </c>
-      <c r="H22" s="79">
-        <v>3825.02</v>
-      </c>
-      <c r="I22" s="56"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="75">
-        <v>45908</v>
-      </c>
-      <c r="C23" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D23" s="74">
-        <v>24.1</v>
-      </c>
-      <c r="E23" s="79">
-        <v>120766.9</v>
-      </c>
-      <c r="F23" s="74">
-        <v>23.4</v>
-      </c>
-      <c r="G23" s="79">
-        <v>116740.86</v>
-      </c>
-      <c r="H23" s="79">
-        <v>-4026.04</v>
-      </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C24" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D24" s="74">
-        <v>23.2</v>
-      </c>
-      <c r="E24" s="79">
-        <v>116256.93</v>
-      </c>
-      <c r="F24" s="74">
-        <v>23.4</v>
-      </c>
-      <c r="G24" s="79">
-        <v>116740.86</v>
-      </c>
-      <c r="H24" s="74">
-        <v>483.93</v>
-      </c>
-      <c r="I24" s="56"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C25" s="74">
-        <v>4000</v>
-      </c>
-      <c r="D25" s="74">
-        <v>23.1</v>
-      </c>
-      <c r="E25" s="79">
-        <v>92604.66</v>
-      </c>
-      <c r="F25" s="74">
-        <v>25.75</v>
-      </c>
-      <c r="G25" s="79">
-        <v>102771.87</v>
-      </c>
-      <c r="H25" s="79">
-        <v>10167.209999999999</v>
-      </c>
-      <c r="I25" s="56"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C26" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D26" s="74">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="E26" s="79">
-        <v>44097.46</v>
-      </c>
-      <c r="F26" s="74">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="G26" s="79">
-        <v>48392.57</v>
-      </c>
-      <c r="H26" s="79">
-        <v>4295.1099999999997</v>
-      </c>
-      <c r="I26" s="56"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="32">
-        <f>SUM(E22:E26)</f>
-        <v>411309.01000000007</v>
-      </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="32">
-        <f>SUM(G22:G26)</f>
-        <v>426054.24</v>
-      </c>
-      <c r="H27" s="32">
-        <f>SUM(H22:H26)</f>
-        <v>14745.23</v>
-      </c>
-      <c r="I27" s="32"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-    </row>
-    <row r="28" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="26"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="34">
-        <f>H21+H27</f>
-        <v>129321.52999999998</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J28" s="7">
-        <v>30614.600000000002</v>
-      </c>
-      <c r="K28" s="7"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="6"/>
-    </row>
-    <row r="29" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="32">
-        <v>-522636.73</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K29" s="7"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-    </row>
-    <row r="30" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="41">
-        <f>H28+H29</f>
-        <v>-393315.2</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="7">
-        <v>-522636.73</v>
-      </c>
-      <c r="K30" s="7"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-    </row>
-    <row r="31" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="35">
-        <v>396550</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K31" s="7"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-    </row>
-    <row r="32" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="H32" s="35">
-        <v>62010</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="J32" s="7">
-        <v>10130</v>
-      </c>
-      <c r="K32" s="7"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-    </row>
-    <row r="33" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="26"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="41">
-        <f>H31+H32</f>
-        <v>458560</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33" s="7">
-        <v>396550</v>
-      </c>
-      <c r="K33" s="7"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="6"/>
-    </row>
-    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="5"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" s="45">
-        <f>H30-H33</f>
-        <v>-851875.2</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="7">
-        <v>-919186.73</v>
-      </c>
-      <c r="K34" s="7"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="6"/>
-    </row>
-    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="5"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H35" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J35" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K35" s="7"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="6"/>
-    </row>
-    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="6"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="42">
-        <f>H34+H35</f>
-        <v>-794875.2</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J36" s="7">
-        <v>-862186.73</v>
-      </c>
-      <c r="K36" s="7"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="6"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K37" s="7"/>
-      <c r="M37" s="7"/>
-    </row>
-    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="28">
-        <v>45546</v>
-      </c>
-      <c r="C38" s="29">
-        <v>24000</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="31"/>
-      <c r="F38" s="51">
-        <v>3.9899999999999998E-2</v>
-      </c>
-      <c r="G38" s="31">
-        <f>C38*F38</f>
-        <v>957.59999999999991</v>
-      </c>
-      <c r="H38" s="53">
-        <f>G38*0.9</f>
-        <v>861.83999999999992</v>
-      </c>
-      <c r="K38" s="7"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-    </row>
-    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" s="28">
-        <v>45530</v>
-      </c>
-      <c r="C39" s="29">
-        <v>30000</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="31"/>
-      <c r="F39" s="37">
-        <v>0.19</v>
-      </c>
-      <c r="G39" s="31">
-        <f>C39*F39</f>
-        <v>5700</v>
-      </c>
-      <c r="H39" s="32">
-        <f>G39</f>
-        <v>5700</v>
-      </c>
-      <c r="K39" s="7"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C40" s="12"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="10"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N20">
-    <sortCondition ref="A2:A20"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961B3AB4-C9A4-46F9-AED6-DC61A66CC09A}">
-  <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45897</v>
-      </c>
-      <c r="C2" s="29">
-        <v>600</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="72">
-        <v>2.5</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>1500</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2*0.9</f>
-        <v>1350</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="41">
-        <f>SUM(H2:H2)</f>
-        <v>1350</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="75">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="76">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="77">
-        <v>1.88</v>
-      </c>
-      <c r="E4" s="77">
-        <v>18841.64</v>
-      </c>
-      <c r="F4" s="77">
-        <v>1.9</v>
-      </c>
-      <c r="G4" s="77">
-        <v>18957.919999999998</v>
-      </c>
-      <c r="H4" s="77">
-        <v>116.28</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="74" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="75">
-        <v>45875</v>
-      </c>
-      <c r="C5" s="76">
-        <v>2800</v>
-      </c>
-      <c r="D5" s="77">
-        <v>10.5</v>
-      </c>
-      <c r="E5" s="77">
-        <v>29465.119999999999</v>
-      </c>
-      <c r="F5" s="77">
-        <v>11.6</v>
-      </c>
-      <c r="G5" s="77">
-        <v>32408.06</v>
-      </c>
-      <c r="H5" s="77">
-        <v>2942.94</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="75">
-        <v>45875</v>
-      </c>
-      <c r="C6" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D6" s="77">
-        <v>3.9</v>
-      </c>
-      <c r="E6" s="77">
-        <v>19543.2</v>
-      </c>
-      <c r="F6" s="77">
-        <v>4.5199999999999996</v>
-      </c>
-      <c r="G6" s="77">
-        <v>22549.95</v>
-      </c>
-      <c r="H6" s="77">
-        <v>3006.75</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="74" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="75">
-        <v>45876</v>
-      </c>
-      <c r="C7" s="76">
-        <v>3200</v>
-      </c>
-      <c r="D7" s="77">
-        <v>9.25</v>
-      </c>
-      <c r="E7" s="77">
-        <v>29665.56</v>
-      </c>
-      <c r="F7" s="77">
-        <v>9.4</v>
-      </c>
-      <c r="G7" s="77">
-        <v>30013.37</v>
-      </c>
-      <c r="H7" s="77">
-        <v>347.81</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="75">
-        <v>45876</v>
-      </c>
-      <c r="C8" s="76">
-        <v>10000</v>
-      </c>
-      <c r="D8" s="77">
-        <v>1.85</v>
-      </c>
-      <c r="E8" s="77">
-        <v>18540.98</v>
-      </c>
-      <c r="F8" s="77">
-        <v>2.06</v>
-      </c>
-      <c r="G8" s="77">
-        <v>20554.38</v>
-      </c>
-      <c r="H8" s="77">
-        <v>2013.4</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="74" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="75">
-        <v>45877</v>
-      </c>
-      <c r="C9" s="76">
-        <v>6000</v>
-      </c>
-      <c r="D9" s="77">
-        <v>6.1</v>
-      </c>
-      <c r="E9" s="77">
-        <v>36681.06</v>
-      </c>
-      <c r="F9" s="77">
-        <v>6.7</v>
-      </c>
-      <c r="G9" s="77">
-        <v>40110.97</v>
-      </c>
-      <c r="H9" s="77">
-        <v>3429.91</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="75">
-        <v>45877</v>
-      </c>
-      <c r="C10" s="76">
-        <v>3000</v>
-      </c>
-      <c r="D10" s="77">
-        <v>27.75</v>
-      </c>
-      <c r="E10" s="77">
-        <v>83434.39</v>
-      </c>
-      <c r="F10" s="77">
-        <v>31</v>
-      </c>
-      <c r="G10" s="77">
-        <v>92794.01</v>
-      </c>
-      <c r="H10" s="77">
-        <v>9359.6200000000008</v>
-      </c>
-      <c r="I10" s="73"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="75">
-        <v>45889</v>
-      </c>
-      <c r="C11" s="76">
-        <v>4000</v>
-      </c>
-      <c r="D11" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E11" s="77">
-        <v>96613.52</v>
-      </c>
-      <c r="F11" s="77">
-        <v>24.3</v>
-      </c>
-      <c r="G11" s="77">
-        <v>96984.72</v>
-      </c>
-      <c r="H11" s="77">
-        <v>371.2</v>
-      </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="75">
-        <v>45890</v>
-      </c>
-      <c r="C12" s="76">
-        <v>4000</v>
-      </c>
-      <c r="D12" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E12" s="77">
-        <v>96613.52</v>
-      </c>
-      <c r="F12" s="77">
-        <v>24.3</v>
-      </c>
-      <c r="G12" s="77">
-        <v>96984.72</v>
-      </c>
-      <c r="H12" s="77">
-        <v>371.2</v>
-      </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="75">
-        <v>45891</v>
-      </c>
-      <c r="C13" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D13" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E13" s="77">
-        <v>120766.9</v>
-      </c>
-      <c r="F13" s="77">
-        <v>24.3</v>
-      </c>
-      <c r="G13" s="77">
-        <v>121230.88</v>
-      </c>
-      <c r="H13" s="77">
-        <v>463.98</v>
-      </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="75">
-        <v>45896</v>
-      </c>
-      <c r="C14" s="76">
-        <v>6000</v>
-      </c>
-      <c r="D14" s="77">
-        <v>7.3</v>
-      </c>
-      <c r="E14" s="77">
-        <v>43897.02</v>
-      </c>
-      <c r="F14" s="77">
-        <v>8.4</v>
-      </c>
-      <c r="G14" s="77">
-        <v>50288.37</v>
-      </c>
-      <c r="H14" s="77">
-        <v>6391.35</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="75">
-        <v>45897</v>
-      </c>
-      <c r="C15" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D15" s="77">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E15" s="77">
-        <v>11024.36</v>
-      </c>
-      <c r="F15" s="77">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G15" s="77">
-        <v>11474.52</v>
-      </c>
-      <c r="H15" s="77">
-        <v>450.16</v>
-      </c>
-      <c r="I15" s="78"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32">
-        <f>SUM(E4:E15)</f>
-        <v>605087.27</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32">
-        <f>SUM(G4:G15)</f>
-        <v>634351.87</v>
-      </c>
-      <c r="H16" s="32">
-        <f>SUM(H4:H15)</f>
-        <v>29264.600000000002</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="41">
-        <f>H3+H16</f>
-        <v>30614.600000000002</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="7">
-        <v>-365900.39999999997</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="32">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="7">
-        <v>-187350.93</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="41">
-        <f>H17+H18</f>
-        <v>-522636.73</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-    </row>
-    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="7">
-        <v>386420</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="7">
-        <v>377810</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-    </row>
-    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" s="35">
-        <v>10130</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J21" s="7">
-        <v>8610</v>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="26"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="41">
-        <f>H20+H21</f>
-        <v>396550</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="5"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="47">
-        <f>H19-H22</f>
-        <v>-919186.73</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="7">
-        <v>-939671.33</v>
-      </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="5"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J24" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="6"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="42">
-        <f>H23+H24</f>
-        <v>-862186.73</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="7">
-        <v>-882671.33</v>
-      </c>
-      <c r="K25" s="7"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K26" s="7"/>
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M28" s="7"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D29" s="8"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="10"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7193655-9E82-4E5C-9879-086AA4339AB9}">
-  <dimension ref="A1:N26"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.75" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B2" s="28">
-        <v>44736</v>
-      </c>
-      <c r="C2" s="29">
-        <v>40000</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="37">
-        <v>0.15559999999999999</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>6223.9999999999991</v>
-      </c>
-      <c r="H2" s="32">
-        <v>0</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="34">
-        <f>SUM(H2:H2)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45868</v>
-      </c>
-      <c r="C4" s="29">
-        <v>1800</v>
-      </c>
-      <c r="D4" s="30">
-        <v>20</v>
-      </c>
-      <c r="E4" s="31">
-        <v>36079.74</v>
-      </c>
-      <c r="F4" s="30">
-        <v>22.9</v>
-      </c>
-      <c r="G4" s="31">
-        <v>41128.699999999997</v>
-      </c>
-      <c r="H4" s="32">
-        <f t="shared" ref="H4:H12" si="0">G4-E4</f>
-        <v>5048.9599999999991</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45868</v>
-      </c>
-      <c r="C5" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D5" s="30">
-        <v>4.7</v>
-      </c>
-      <c r="E5" s="31">
-        <v>47104.1</v>
-      </c>
-      <c r="F5" s="30">
-        <v>5.5</v>
-      </c>
-      <c r="G5" s="31">
-        <v>54878.18</v>
-      </c>
-      <c r="H5" s="32">
-        <f t="shared" si="0"/>
-        <v>7774.0800000000017</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45867</v>
-      </c>
-      <c r="C6" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D6" s="30">
-        <v>87</v>
-      </c>
-      <c r="E6" s="31">
-        <v>87192.7</v>
-      </c>
-      <c r="F6" s="30">
-        <v>22.9</v>
-      </c>
-      <c r="G6" s="31">
-        <v>22849.279999999999</v>
-      </c>
-      <c r="H6" s="32">
-        <f t="shared" si="0"/>
-        <v>-64343.42</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B7" s="28">
-        <v>45862</v>
-      </c>
-      <c r="C7" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D7" s="30">
-        <v>87</v>
-      </c>
-      <c r="E7" s="31">
-        <v>87192.7</v>
-      </c>
-      <c r="F7" s="30">
-        <v>22.4</v>
-      </c>
-      <c r="G7" s="31">
-        <v>22350.38</v>
-      </c>
-      <c r="H7" s="32">
-        <f t="shared" si="0"/>
-        <v>-64842.319999999992</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="28">
-        <v>45856</v>
-      </c>
-      <c r="C8" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D8" s="30">
-        <v>87</v>
-      </c>
-      <c r="E8" s="31">
-        <v>87192.7</v>
-      </c>
-      <c r="F8" s="30">
-        <v>22.2</v>
-      </c>
-      <c r="G8" s="31">
-        <v>22150.83</v>
-      </c>
-      <c r="H8" s="32">
-        <f t="shared" si="0"/>
-        <v>-65041.869999999995</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9" s="28">
-        <v>45854</v>
-      </c>
-      <c r="C9" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D9" s="30">
-        <v>87</v>
-      </c>
-      <c r="E9" s="31">
-        <v>87192.7</v>
-      </c>
-      <c r="F9" s="30">
-        <v>21.7</v>
-      </c>
-      <c r="G9" s="31">
-        <v>21651.94</v>
-      </c>
-      <c r="H9" s="32">
-        <f t="shared" si="0"/>
-        <v>-65540.759999999995</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="28">
-        <v>45841</v>
-      </c>
-      <c r="C10" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D10" s="30">
-        <v>81</v>
-      </c>
-      <c r="E10" s="31">
-        <v>81179.41</v>
-      </c>
-      <c r="F10" s="30">
-        <v>21</v>
-      </c>
-      <c r="G10" s="31">
-        <v>20953.490000000002</v>
-      </c>
-      <c r="H10" s="32">
-        <f t="shared" si="0"/>
-        <v>-60225.919999999998</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="27" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="28">
-        <v>45841</v>
-      </c>
-      <c r="C11" s="29">
-        <v>2500</v>
-      </c>
-      <c r="D11" s="30">
-        <v>9</v>
-      </c>
-      <c r="E11" s="31">
-        <v>22549.84</v>
-      </c>
-      <c r="F11" s="30">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="G11" s="31">
-        <v>25443.51</v>
-      </c>
-      <c r="H11" s="32">
-        <f t="shared" si="0"/>
-        <v>2893.6699999999983</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B12" s="28">
-        <v>45840</v>
-      </c>
-      <c r="C12" s="29">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="30">
-        <v>81</v>
-      </c>
-      <c r="E12" s="31">
-        <v>81179.41</v>
-      </c>
-      <c r="F12" s="30">
-        <v>19.600000000000001</v>
-      </c>
-      <c r="G12" s="31">
-        <v>19556.59</v>
-      </c>
-      <c r="H12" s="32">
-        <f t="shared" si="0"/>
-        <v>-61622.820000000007</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32">
-        <f>SUM(E4:E12)</f>
-        <v>616863.30000000005</v>
-      </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="32">
-        <f t="shared" ref="G13:H13" si="1">SUM(G4:G12)</f>
-        <v>250962.9</v>
-      </c>
-      <c r="H13" s="32">
-        <f t="shared" si="1"/>
-        <v>-365900.39999999997</v>
-      </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="26"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H14" s="34">
-        <f>H3+H13</f>
-        <v>-365900.39999999997</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J14" s="7">
-        <v>-101058.68999999999</v>
-      </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H15" s="32">
-        <v>-187350.93</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J15" s="7">
-        <v>-86292.24</v>
-      </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-    </row>
-    <row r="16" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H16" s="34">
-        <f>H14+H15</f>
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J16" s="7">
-        <v>-187350.93</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H17" s="35">
-        <v>377810</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J17" s="7">
-        <v>336660</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-    </row>
-    <row r="18" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="32" t="s">
-        <v>48</v>
-      </c>
-      <c r="H18" s="35">
-        <v>8610</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="J18" s="7">
-        <v>41150</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="26"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H19" s="41">
-        <f>H17+H18</f>
-        <v>386420</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J19" s="7">
-        <v>377810</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="5"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H20" s="46">
-        <f>H16-H19</f>
-        <v>-939671.33</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J20" s="7">
-        <v>-565160.92999999993</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A21" s="5"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="8"/>
-      <c r="D21" s="9"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="38">
-        <v>57000</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J21" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A22" s="6"/>
-      <c r="B22" s="12"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="39">
-        <f>H20+H21</f>
-        <v>-882671.33</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="7">
-        <v>-508160.92999999993</v>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K23" s="7"/>
-      <c r="M23" s="7"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M24" s="7"/>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M25" s="7"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C26" s="12"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="9"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="10"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="11"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:H12">
-    <sortCondition descending="1" ref="B4:B12"/>
-    <sortCondition ref="A4:A12"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68993354-A7E2-4931-8BC9-D8891EC066BA}">
   <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -5116,7 +5355,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DFDC5F2-0211-490B-8DD7-A2B28B5D4706}">
   <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -5565,7 +5804,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6E9199-1687-4EE7-A0F3-54DE6332B9D4}">
   <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -6251,7 +6490,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815483-6499-49C9-BB8D-67572F4517B8}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -6679,7 +6918,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DA818F-D2F1-4405-A36C-2376E8E1DAA2}">
   <dimension ref="A1:N14"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -7016,7 +7255,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDBED0F-338F-4C61-AC0B-5077E6985A08}">
   <dimension ref="A1:N25"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -7707,7 +7946,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F537F07A-D0A7-416B-8994-ABDD1C22435D}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -8112,477 +8351,4 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801544F9-630F-4E32-B67B-5CF42760770C}">
-  <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45576</v>
-      </c>
-      <c r="C2" s="29">
-        <v>6800</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="52">
-        <v>0</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="53">
-        <f>G2*0.9</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="34">
-        <f>SUM(H2:H2)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45931</v>
-      </c>
-      <c r="C4" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="30">
-        <v>2.62</v>
-      </c>
-      <c r="E4" s="31">
-        <v>26258.03</v>
-      </c>
-      <c r="F4" s="30">
-        <v>2.72</v>
-      </c>
-      <c r="G4" s="31">
-        <v>27139.759999999998</v>
-      </c>
-      <c r="H4" s="40">
-        <f>G4-E4</f>
-        <v>881.72999999999956</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45937</v>
-      </c>
-      <c r="C5" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D5" s="30">
-        <v>26</v>
-      </c>
-      <c r="E5" s="31">
-        <v>78172.759999999995</v>
-      </c>
-      <c r="F5" s="30">
-        <v>26.5</v>
-      </c>
-      <c r="G5" s="31">
-        <v>79323.91</v>
-      </c>
-      <c r="H5" s="40">
-        <f>G5-E5</f>
-        <v>1151.1500000000087</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45954</v>
-      </c>
-      <c r="C6" s="29">
-        <v>2500</v>
-      </c>
-      <c r="D6" s="30">
-        <v>31</v>
-      </c>
-      <c r="E6" s="31">
-        <v>77671.66</v>
-      </c>
-      <c r="F6" s="30">
-        <v>31.25</v>
-      </c>
-      <c r="G6" s="31">
-        <v>77951.960000000006</v>
-      </c>
-      <c r="H6" s="40">
-        <f>G6-E6</f>
-        <v>280.30000000000291</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32">
-        <f>SUM(E4:E6)</f>
-        <v>182102.45</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32">
-        <f t="shared" ref="G7:H7" si="0">SUM(G4:G6)</f>
-        <v>184415.63</v>
-      </c>
-      <c r="H7" s="32">
-        <f t="shared" si="0"/>
-        <v>2313.1800000000112</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="34">
-        <f>H3+H7</f>
-        <v>2313.1800000000112</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="7">
-        <v>30614.600000000002</v>
-      </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="32">
-        <v>-522636.73</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="41">
-        <f>H8+H9</f>
-        <v>-520323.55</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="7">
-        <v>-522636.73</v>
-      </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="35">
-        <v>396550</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-    </row>
-    <row r="12" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="35">
-        <v>19270</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="J12" s="7">
-        <v>10130</v>
-      </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="26"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="41">
-        <f>H11+H12</f>
-        <v>415820</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="7">
-        <v>396550</v>
-      </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="5"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="45">
-        <f>H10-H13</f>
-        <v>-936143.55</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="7">
-        <v>-919186.73</v>
-      </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="38">
-        <v>57000</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J15" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="6"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="42">
-        <f>H14+H15</f>
-        <v>-879143.55</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="7">
-        <v>-862186.73</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="K17" s="7"/>
-      <c r="M17" s="7"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="M18" s="7"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="M19" s="7"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C20" s="12"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="10"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>
--- a/Excel/03-PNL.xlsx
+++ b/Excel/03-PNL.xlsx
@@ -8,23 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c8862359375ebd62/A4/Excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7157" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{81AB62B3-7E47-4B15-88AC-EB2493449B96}"/>
+  <xr:revisionPtr revIDLastSave="7170" documentId="8_{B00F7D7D-2236-4C8B-840E-2CD3F92C0379}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C1F467A6-CB03-4820-8AE3-86F8ED682B53}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="1476" windowWidth="11784" windowHeight="10764" tabRatio="445" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="JUL26" sheetId="99" r:id="rId1"/>
-    <sheet name="JUN26" sheetId="98" r:id="rId2"/>
-    <sheet name="MAY26" sheetId="97" r:id="rId3"/>
-    <sheet name="APR26" sheetId="96" r:id="rId4"/>
-    <sheet name="MAR26" sheetId="95" r:id="rId5"/>
-    <sheet name="FEB26" sheetId="94" r:id="rId6"/>
-    <sheet name="JAN26" sheetId="93" r:id="rId7"/>
-    <sheet name="DEC25" sheetId="92" r:id="rId8"/>
-    <sheet name="NOV25" sheetId="91" r:id="rId9"/>
-    <sheet name="OCT25" sheetId="90" r:id="rId10"/>
-    <sheet name="SEP25" sheetId="89" r:id="rId11"/>
-    <sheet name="AUG25" sheetId="88" r:id="rId12"/>
+    <sheet name="AUG26" sheetId="100" r:id="rId1"/>
+    <sheet name="AUG25" sheetId="88" r:id="rId2"/>
+    <sheet name="JUL26" sheetId="99" r:id="rId3"/>
+    <sheet name="JUN26" sheetId="98" r:id="rId4"/>
+    <sheet name="MAY26" sheetId="97" r:id="rId5"/>
+    <sheet name="APR26" sheetId="96" r:id="rId6"/>
+    <sheet name="MAR26" sheetId="95" r:id="rId7"/>
+    <sheet name="FEB26" sheetId="94" r:id="rId8"/>
+    <sheet name="JAN26" sheetId="93" r:id="rId9"/>
+    <sheet name="DEC25" sheetId="92" r:id="rId10"/>
+    <sheet name="NOV25" sheetId="91" r:id="rId11"/>
+    <sheet name="OCT25" sheetId="90" r:id="rId12"/>
+    <sheet name="SEP25" sheetId="89" r:id="rId13"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="69">
   <si>
     <t>Name</t>
   </si>
@@ -251,6 +252,9 @@
   </si>
   <si>
     <t>Dummy</t>
+  </si>
+  <si>
+    <t>PROSPECT</t>
   </si>
 </sst>
 </file>
@@ -611,6 +615,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -958,6 +966,4172 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DAE960E6-C7E8-4477-A0CF-2D011FBFDCB7}">
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="28">
+        <v>46254</v>
+      </c>
+      <c r="C2" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="37">
+        <v>7.0499999999999993E-2</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2*0.9</f>
+        <v>1268.9999999999998</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2</f>
+        <v>1268.9999999999998</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="41">
+        <f>SUM(H2:H2)</f>
+        <v>1268.9999999999998</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="75">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="76">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="77">
+        <v>1.88</v>
+      </c>
+      <c r="E4" s="77">
+        <v>18841.64</v>
+      </c>
+      <c r="F4" s="77">
+        <v>1.9</v>
+      </c>
+      <c r="G4" s="77">
+        <v>18957.919999999998</v>
+      </c>
+      <c r="H4" s="77">
+        <v>116.28</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="75">
+        <v>45875</v>
+      </c>
+      <c r="C5" s="76">
+        <v>2800</v>
+      </c>
+      <c r="D5" s="77">
+        <v>10.5</v>
+      </c>
+      <c r="E5" s="77">
+        <v>29465.119999999999</v>
+      </c>
+      <c r="F5" s="77">
+        <v>11.6</v>
+      </c>
+      <c r="G5" s="77">
+        <v>32408.06</v>
+      </c>
+      <c r="H5" s="77">
+        <v>2942.94</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="75">
+        <v>45875</v>
+      </c>
+      <c r="C6" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D6" s="77">
+        <v>3.9</v>
+      </c>
+      <c r="E6" s="77">
+        <v>19543.2</v>
+      </c>
+      <c r="F6" s="77">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="G6" s="77">
+        <v>22549.95</v>
+      </c>
+      <c r="H6" s="77">
+        <v>3006.75</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="75">
+        <v>45876</v>
+      </c>
+      <c r="C7" s="76">
+        <v>3200</v>
+      </c>
+      <c r="D7" s="77">
+        <v>9.25</v>
+      </c>
+      <c r="E7" s="77">
+        <v>29665.56</v>
+      </c>
+      <c r="F7" s="77">
+        <v>9.4</v>
+      </c>
+      <c r="G7" s="77">
+        <v>30013.37</v>
+      </c>
+      <c r="H7" s="77">
+        <v>347.81</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="75">
+        <v>45876</v>
+      </c>
+      <c r="C8" s="76">
+        <v>10000</v>
+      </c>
+      <c r="D8" s="77">
+        <v>1.85</v>
+      </c>
+      <c r="E8" s="77">
+        <v>18540.98</v>
+      </c>
+      <c r="F8" s="77">
+        <v>2.06</v>
+      </c>
+      <c r="G8" s="77">
+        <v>20554.38</v>
+      </c>
+      <c r="H8" s="77">
+        <v>2013.4</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="75">
+        <v>45877</v>
+      </c>
+      <c r="C9" s="76">
+        <v>6000</v>
+      </c>
+      <c r="D9" s="77">
+        <v>6.1</v>
+      </c>
+      <c r="E9" s="77">
+        <v>36681.06</v>
+      </c>
+      <c r="F9" s="77">
+        <v>6.7</v>
+      </c>
+      <c r="G9" s="77">
+        <v>40110.97</v>
+      </c>
+      <c r="H9" s="77">
+        <v>3429.91</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="75">
+        <v>45877</v>
+      </c>
+      <c r="C10" s="76">
+        <v>3000</v>
+      </c>
+      <c r="D10" s="77">
+        <v>27.75</v>
+      </c>
+      <c r="E10" s="77">
+        <v>83434.39</v>
+      </c>
+      <c r="F10" s="77">
+        <v>31</v>
+      </c>
+      <c r="G10" s="77">
+        <v>92794.01</v>
+      </c>
+      <c r="H10" s="77">
+        <v>9359.6200000000008</v>
+      </c>
+      <c r="I10" s="73"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="75">
+        <v>45889</v>
+      </c>
+      <c r="C11" s="76">
+        <v>4000</v>
+      </c>
+      <c r="D11" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E11" s="77">
+        <v>96613.52</v>
+      </c>
+      <c r="F11" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G11" s="77">
+        <v>96984.72</v>
+      </c>
+      <c r="H11" s="77">
+        <v>371.2</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="75">
+        <v>45890</v>
+      </c>
+      <c r="C12" s="76">
+        <v>4000</v>
+      </c>
+      <c r="D12" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E12" s="77">
+        <v>96613.52</v>
+      </c>
+      <c r="F12" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G12" s="77">
+        <v>96984.72</v>
+      </c>
+      <c r="H12" s="77">
+        <v>371.2</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="75">
+        <v>45891</v>
+      </c>
+      <c r="C13" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D13" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E13" s="77">
+        <v>120766.9</v>
+      </c>
+      <c r="F13" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G13" s="77">
+        <v>121230.88</v>
+      </c>
+      <c r="H13" s="77">
+        <v>463.98</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="75">
+        <v>45896</v>
+      </c>
+      <c r="C14" s="76">
+        <v>6000</v>
+      </c>
+      <c r="D14" s="77">
+        <v>7.3</v>
+      </c>
+      <c r="E14" s="77">
+        <v>43897.02</v>
+      </c>
+      <c r="F14" s="77">
+        <v>8.4</v>
+      </c>
+      <c r="G14" s="77">
+        <v>50288.37</v>
+      </c>
+      <c r="H14" s="77">
+        <v>6391.35</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="75">
+        <v>45897</v>
+      </c>
+      <c r="C15" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D15" s="77">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E15" s="77">
+        <v>11024.36</v>
+      </c>
+      <c r="F15" s="77">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G15" s="77">
+        <v>11474.52</v>
+      </c>
+      <c r="H15" s="77">
+        <v>450.16</v>
+      </c>
+      <c r="I15" s="78"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32">
+        <f>SUM(E4:E15)</f>
+        <v>605087.27</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32">
+        <f>SUM(G4:G15)</f>
+        <v>634351.87</v>
+      </c>
+      <c r="H16" s="32">
+        <f>SUM(H4:H15)</f>
+        <v>29264.600000000002</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="41">
+        <f>H3+H16</f>
+        <v>30533.600000000002</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="7">
+        <v>-365900.39999999997</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="32">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="7">
+        <v>-187350.93</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+    </row>
+    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="26"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="41">
+        <f>H17+H18</f>
+        <v>-522717.73</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+    </row>
+    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="26"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="7">
+        <v>386420</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="7">
+        <v>377810</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+    </row>
+    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="26"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="35">
+        <v>10130</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" s="7">
+        <v>8610</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="26"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="41">
+        <f>H20+H21</f>
+        <v>396550</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="5"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="47">
+        <f>H19-H22</f>
+        <v>-919267.73</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="7">
+        <v>-939671.33</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="5"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="6"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="42">
+        <f>H23+H24</f>
+        <v>-862267.73</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="7">
+        <v>-882671.33</v>
+      </c>
+      <c r="K25" s="7"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K26" s="7"/>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D29" s="8"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="10"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDBED0F-338F-4C61-AC0B-5077E6985A08}">
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45995</v>
+      </c>
+      <c r="C2" s="29">
+        <v>45000</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="37">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="G2" s="31">
+        <f t="shared" ref="G2:G13" si="0">C2*F2</f>
+        <v>9999</v>
+      </c>
+      <c r="H2" s="40">
+        <f t="shared" ref="H2:H11" si="1">G2*0.9</f>
+        <v>8999.1</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="28">
+        <v>45995</v>
+      </c>
+      <c r="C3" s="29">
+        <v>27000</v>
+      </c>
+      <c r="D3" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="31"/>
+      <c r="F3" s="37">
+        <v>0.5</v>
+      </c>
+      <c r="G3" s="31">
+        <f t="shared" si="0"/>
+        <v>13500</v>
+      </c>
+      <c r="H3" s="40">
+        <v>12825</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="28">
+        <v>46002</v>
+      </c>
+      <c r="C4" s="29">
+        <v>7200</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="31"/>
+      <c r="F4" s="37">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G4" s="31">
+        <f t="shared" si="0"/>
+        <v>1260</v>
+      </c>
+      <c r="H4" s="40">
+        <f t="shared" si="1"/>
+        <v>1134</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="28">
+        <v>46002</v>
+      </c>
+      <c r="C5" s="29">
+        <v>55000</v>
+      </c>
+      <c r="D5" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="31"/>
+      <c r="F5" s="51">
+        <v>6.9099999999999995E-2</v>
+      </c>
+      <c r="G5" s="31">
+        <f t="shared" si="0"/>
+        <v>3800.4999999999995</v>
+      </c>
+      <c r="H5" s="40">
+        <f t="shared" si="1"/>
+        <v>3420.45</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="85" t="s">
+        <v>36</v>
+      </c>
+      <c r="B6" s="28">
+        <v>46002</v>
+      </c>
+      <c r="C6" s="29">
+        <v>6800</v>
+      </c>
+      <c r="D6" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" s="31"/>
+      <c r="F6" s="37">
+        <v>0.13</v>
+      </c>
+      <c r="G6" s="31">
+        <f t="shared" ref="G6" si="2">C6*F6</f>
+        <v>884</v>
+      </c>
+      <c r="H6" s="40">
+        <f t="shared" ref="H6" si="3">G6*0.9</f>
+        <v>795.6</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" s="28">
+        <v>45995</v>
+      </c>
+      <c r="C7" s="84">
+        <v>17500</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="31"/>
+      <c r="F7" s="51">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G7" s="31">
+        <f t="shared" si="0"/>
+        <v>3587.5</v>
+      </c>
+      <c r="H7" s="40">
+        <f t="shared" si="1"/>
+        <v>3228.75</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="28">
+        <v>46006</v>
+      </c>
+      <c r="C8" s="29">
+        <v>50000</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8" s="31"/>
+      <c r="F8" s="37">
+        <v>2.1000000000000001E-2</v>
+      </c>
+      <c r="G8" s="31">
+        <f t="shared" si="0"/>
+        <v>1050</v>
+      </c>
+      <c r="H8" s="40">
+        <f t="shared" si="1"/>
+        <v>945</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="28">
+        <v>46002</v>
+      </c>
+      <c r="C9" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="31"/>
+      <c r="F9" s="37">
+        <v>0.193</v>
+      </c>
+      <c r="G9" s="31">
+        <f t="shared" si="0"/>
+        <v>3860</v>
+      </c>
+      <c r="H9" s="40">
+        <f t="shared" si="1"/>
+        <v>3474</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="28">
+        <v>46013</v>
+      </c>
+      <c r="C10" s="29">
+        <v>50000</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="31"/>
+      <c r="F10" s="51">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="G10" s="31">
+        <f t="shared" si="0"/>
+        <v>6625</v>
+      </c>
+      <c r="H10" s="40">
+        <f t="shared" si="1"/>
+        <v>5962.5</v>
+      </c>
+      <c r="I10" s="11"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="28">
+        <v>46015</v>
+      </c>
+      <c r="C11" s="84">
+        <v>69000</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="31"/>
+      <c r="F11" s="51">
+        <v>0.1825</v>
+      </c>
+      <c r="G11" s="31">
+        <f t="shared" si="0"/>
+        <v>12592.5</v>
+      </c>
+      <c r="H11" s="40">
+        <f t="shared" si="1"/>
+        <v>11333.25</v>
+      </c>
+      <c r="I11" s="11"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B12" s="28">
+        <v>46016</v>
+      </c>
+      <c r="C12" s="29">
+        <v>20000</v>
+      </c>
+      <c r="D12" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="31"/>
+      <c r="F12" s="51">
+        <v>0.114</v>
+      </c>
+      <c r="G12" s="31">
+        <f t="shared" ref="G12" si="4">C12*F12</f>
+        <v>2280</v>
+      </c>
+      <c r="H12" s="40">
+        <f>G12</f>
+        <v>2280</v>
+      </c>
+      <c r="I12" s="11"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="85" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13" s="28">
+        <v>46013</v>
+      </c>
+      <c r="C13" s="29">
+        <v>120000</v>
+      </c>
+      <c r="D13" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="31"/>
+      <c r="F13" s="37">
+        <v>0.13722400000000001</v>
+      </c>
+      <c r="G13" s="31">
+        <f t="shared" si="0"/>
+        <v>16466.88</v>
+      </c>
+      <c r="H13" s="40">
+        <f>G13*0.9</f>
+        <v>14820.192000000001</v>
+      </c>
+      <c r="I13" s="11"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="27"/>
+      <c r="B14" s="28"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="30"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="34">
+        <f>SUM(H2:H13)</f>
+        <v>69217.84199999999</v>
+      </c>
+      <c r="I14" s="11"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="28">
+        <v>37617</v>
+      </c>
+      <c r="C15" s="29">
+        <v>0</v>
+      </c>
+      <c r="D15" s="30">
+        <v>21.3</v>
+      </c>
+      <c r="E15" s="31">
+        <v>0</v>
+      </c>
+      <c r="F15" s="30">
+        <v>21.3</v>
+      </c>
+      <c r="G15" s="31">
+        <v>0</v>
+      </c>
+      <c r="H15" s="32">
+        <f t="shared" ref="H15" si="5">G15-E15</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="11"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32">
+        <f>SUM(E15:E15)</f>
+        <v>0</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32">
+        <f>SUM(G15:G15)</f>
+        <v>0</v>
+      </c>
+      <c r="H16" s="40">
+        <f>SUM(H15:H15)</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="43">
+        <f>H14+H16</f>
+        <v>69217.84199999999</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="7">
+        <v>30614.600000000002</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A18" s="5"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="32">
+        <v>-522636.73</v>
+      </c>
+      <c r="I18" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A19" s="6"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="41">
+        <f>H17+H18</f>
+        <v>-453418.88799999998</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="7">
+        <v>-522636.73</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G20" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="35">
+        <v>396550</v>
+      </c>
+      <c r="I20" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="M20" s="7"/>
+    </row>
+    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G21" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="35">
+        <v>12050</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J21" s="7">
+        <v>10130</v>
+      </c>
+      <c r="M21" s="7"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G22" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="41">
+        <f>H20+H21</f>
+        <v>408600</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="7">
+        <v>396550</v>
+      </c>
+      <c r="M22" s="7"/>
+    </row>
+    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="C23" s="12"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="45">
+        <f>H19-H22</f>
+        <v>-862018.88800000004</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="7">
+        <v>-919186.73</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="6"/>
+      <c r="M23" s="7"/>
+    </row>
+    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G24" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="7">
+        <v>57000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="G25" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="42">
+        <f>H23+H24</f>
+        <v>-805018.88800000004</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="7">
+        <v>-862186.73</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F537F07A-D0A7-416B-8994-ABDD1C22435D}">
+  <dimension ref="A1:N18"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.375" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" s="28">
+        <v>44846</v>
+      </c>
+      <c r="C2" s="29">
+        <v>0</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="37">
+        <v>1.3</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2*0.9</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="34">
+        <f>SUM(H2:H2)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45590</v>
+      </c>
+      <c r="C4" s="29">
+        <v>1500</v>
+      </c>
+      <c r="D4" s="30">
+        <v>12</v>
+      </c>
+      <c r="E4" s="31">
+        <v>19756.14</v>
+      </c>
+      <c r="F4" s="30">
+        <v>0</v>
+      </c>
+      <c r="G4" s="31">
+        <v>19756.14</v>
+      </c>
+      <c r="H4" s="40">
+        <f>G4-E4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="26"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="32">
+        <f>SUM(E4:E4)</f>
+        <v>19756.14</v>
+      </c>
+      <c r="F5" s="30"/>
+      <c r="G5" s="32">
+        <f>SUM(G4:G4)</f>
+        <v>19756.14</v>
+      </c>
+      <c r="H5" s="32">
+        <f>SUM(H4:H4)</f>
+        <v>0</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="26"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H6" s="43">
+        <f>H3+H5</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J6" s="7">
+        <v>30614.600000000002</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="32">
+        <v>-522636.73</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="41">
+        <f>H6+H7</f>
+        <v>-522636.73</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J8" s="7">
+        <v>-522636.73</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9" s="35">
+        <v>396550</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="35">
+        <v>24420</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10" s="7">
+        <v>10130</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="41">
+        <f>H9+H10</f>
+        <v>420970</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="7">
+        <v>396550</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="5"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="9"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="45">
+        <f>H8-H11</f>
+        <v>-943606.73</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="7">
+        <v>-919186.73</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="5"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H13" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J13" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="6"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H14" s="42">
+        <f>H12+H13</f>
+        <v>-886606.73</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J14" s="7">
+        <v>-862186.73</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K15" s="7"/>
+      <c r="M15" s="7"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M16" s="7"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C18" s="12"/>
+      <c r="D18" s="8"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="10"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="11"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="6"/>
+      <c r="M18" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801544F9-630F-4E32-B67B-5CF42760770C}">
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.25" style="11" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45576</v>
+      </c>
+      <c r="C2" s="29">
+        <v>6800</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="52">
+        <v>0</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>0</v>
+      </c>
+      <c r="H2" s="53">
+        <f>G2*0.9</f>
+        <v>0</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="34">
+        <f>SUM(H2:H2)</f>
+        <v>0</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="27" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="28">
+        <v>45931</v>
+      </c>
+      <c r="C4" s="29">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="30">
+        <v>2.62</v>
+      </c>
+      <c r="E4" s="31">
+        <v>26258.03</v>
+      </c>
+      <c r="F4" s="30">
+        <v>2.72</v>
+      </c>
+      <c r="G4" s="31">
+        <v>27139.759999999998</v>
+      </c>
+      <c r="H4" s="40">
+        <f>G4-E4</f>
+        <v>881.72999999999956</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="27" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="28">
+        <v>45937</v>
+      </c>
+      <c r="C5" s="29">
+        <v>3000</v>
+      </c>
+      <c r="D5" s="30">
+        <v>26</v>
+      </c>
+      <c r="E5" s="31">
+        <v>78172.759999999995</v>
+      </c>
+      <c r="F5" s="30">
+        <v>26.5</v>
+      </c>
+      <c r="G5" s="31">
+        <v>79323.91</v>
+      </c>
+      <c r="H5" s="40">
+        <f>G5-E5</f>
+        <v>1151.1500000000087</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="28">
+        <v>45954</v>
+      </c>
+      <c r="C6" s="29">
+        <v>2500</v>
+      </c>
+      <c r="D6" s="30">
+        <v>31</v>
+      </c>
+      <c r="E6" s="31">
+        <v>77671.66</v>
+      </c>
+      <c r="F6" s="30">
+        <v>31.25</v>
+      </c>
+      <c r="G6" s="31">
+        <v>77951.960000000006</v>
+      </c>
+      <c r="H6" s="40">
+        <f>G6-E6</f>
+        <v>280.30000000000291</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="26"/>
+      <c r="B7" s="28"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="33"/>
+      <c r="E7" s="32">
+        <f>SUM(E4:E6)</f>
+        <v>182102.45</v>
+      </c>
+      <c r="F7" s="30"/>
+      <c r="G7" s="32">
+        <f t="shared" ref="G7:H7" si="0">SUM(G4:G6)</f>
+        <v>184415.63</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" si="0"/>
+        <v>2313.1800000000112</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="26"/>
+      <c r="B8" s="28"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="30"/>
+      <c r="G8" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="34">
+        <f>H3+H7</f>
+        <v>2313.1800000000112</v>
+      </c>
+      <c r="I8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="7">
+        <v>30614.600000000002</v>
+      </c>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="26"/>
+      <c r="B9" s="28"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="30"/>
+      <c r="G9" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H9" s="32">
+        <v>-522636.73</v>
+      </c>
+      <c r="I9" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J9" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+    </row>
+    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="26"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="30"/>
+      <c r="G10" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H10" s="41">
+        <f>H8+H9</f>
+        <v>-520323.55</v>
+      </c>
+      <c r="I10" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="7">
+        <v>-522636.73</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+    </row>
+    <row r="11" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="26"/>
+      <c r="B11" s="28"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H11" s="35">
+        <v>396550</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+    </row>
+    <row r="12" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="26"/>
+      <c r="B12" s="28"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="30"/>
+      <c r="G12" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="H12" s="35">
+        <v>19270</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12" s="7">
+        <v>10130</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="26"/>
+      <c r="B13" s="28"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="30"/>
+      <c r="G13" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="41">
+        <f>H11+H12</f>
+        <v>415820</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="7">
+        <v>396550</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="5"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="45">
+        <f>H10-H13</f>
+        <v>-936143.55</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J14" s="7">
+        <v>-919186.73</v>
+      </c>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="5"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="38">
+        <v>57000</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A16" s="6"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H16" s="42">
+        <f>H14+H15</f>
+        <v>-879143.55</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J16" s="7">
+        <v>-862186.73</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="K17" s="7"/>
+      <c r="M17" s="7"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M18" s="7"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="M19" s="7"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
+      <c r="C20" s="12"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="10"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="6"/>
+      <c r="M20" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805BC19F-42DC-4CD3-B954-E9F19E56BFF7}">
+  <dimension ref="A1:N40"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="55"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="74" t="s">
+        <v>51</v>
+      </c>
+      <c r="B2" s="75">
+        <v>45903</v>
+      </c>
+      <c r="C2" s="76">
+        <v>120000</v>
+      </c>
+      <c r="D2" s="74"/>
+      <c r="E2" s="74"/>
+      <c r="F2" s="74">
+        <v>0.15454999999999999</v>
+      </c>
+      <c r="G2" s="79">
+        <v>18546</v>
+      </c>
+      <c r="H2" s="79">
+        <v>16691.400000000001</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A3" s="74" t="s">
+        <v>42</v>
+      </c>
+      <c r="B3" s="75">
+        <v>45910</v>
+      </c>
+      <c r="C3" s="76">
+        <v>1200</v>
+      </c>
+      <c r="D3" s="74"/>
+      <c r="E3" s="74"/>
+      <c r="F3" s="80">
+        <v>0.31</v>
+      </c>
+      <c r="G3" s="79">
+        <v>372</v>
+      </c>
+      <c r="H3" s="79">
+        <v>339.6</v>
+      </c>
+      <c r="I3" s="10"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A4" s="74" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C4" s="81">
+        <v>17500</v>
+      </c>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="80">
+        <v>0.20499999999999999</v>
+      </c>
+      <c r="G4" s="79">
+        <v>3587.5</v>
+      </c>
+      <c r="H4" s="79">
+        <v>3228.75</v>
+      </c>
+      <c r="I4" s="10"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A5" s="74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C5" s="76">
+        <v>4000</v>
+      </c>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="80">
+        <v>0.15</v>
+      </c>
+      <c r="G5" s="79">
+        <v>600</v>
+      </c>
+      <c r="H5" s="79">
+        <v>540</v>
+      </c>
+      <c r="I5" s="10"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A6" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C6" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74">
+        <v>1</v>
+      </c>
+      <c r="G6" s="79">
+        <v>5000</v>
+      </c>
+      <c r="H6" s="79">
+        <v>4500</v>
+      </c>
+      <c r="I6" s="10"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A7" s="74" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C7" s="82">
+        <v>55000</v>
+      </c>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="80">
+        <v>0.2261</v>
+      </c>
+      <c r="G7" s="79">
+        <v>12435.5</v>
+      </c>
+      <c r="H7" s="79">
+        <v>11191.95</v>
+      </c>
+      <c r="I7" s="10"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A8" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="75">
+        <v>45909</v>
+      </c>
+      <c r="C8" s="81">
+        <v>50000</v>
+      </c>
+      <c r="D8" s="74"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74">
+        <v>0.22220000000000001</v>
+      </c>
+      <c r="G8" s="79">
+        <v>11110</v>
+      </c>
+      <c r="H8" s="79">
+        <v>9999</v>
+      </c>
+      <c r="I8" s="10"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A9" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C9" s="81">
+        <v>69000</v>
+      </c>
+      <c r="D9" s="74"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="80">
+        <v>0.19650000000000001</v>
+      </c>
+      <c r="G9" s="79">
+        <v>13558.5</v>
+      </c>
+      <c r="H9" s="79">
+        <v>12202.65</v>
+      </c>
+      <c r="I9" s="10"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A10" s="74" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C10" s="82">
+        <v>7200</v>
+      </c>
+      <c r="D10" s="74"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="G10" s="79">
+        <v>1260</v>
+      </c>
+      <c r="H10" s="79">
+        <v>1134</v>
+      </c>
+      <c r="I10" s="10"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A11" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C11" s="82">
+        <v>4200</v>
+      </c>
+      <c r="D11" s="74"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="83">
+        <v>0.24</v>
+      </c>
+      <c r="G11" s="79">
+        <v>1008</v>
+      </c>
+      <c r="H11" s="79">
+        <v>907.2</v>
+      </c>
+      <c r="I11" s="10"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A12" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="B12" s="75">
+        <v>45910</v>
+      </c>
+      <c r="C12" s="81">
+        <v>81000</v>
+      </c>
+      <c r="D12" s="74"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="80">
+        <v>0.25</v>
+      </c>
+      <c r="G12" s="79">
+        <v>20250</v>
+      </c>
+      <c r="H12" s="79">
+        <v>19926</v>
+      </c>
+      <c r="I12" s="10"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A13" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C13" s="76">
+        <v>27000</v>
+      </c>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="79">
+        <v>1350</v>
+      </c>
+      <c r="H13" s="79">
+        <v>1350</v>
+      </c>
+      <c r="I13" s="10"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A14" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C14" s="76">
+        <v>27000</v>
+      </c>
+      <c r="D14" s="74"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="79">
+        <v>13500</v>
+      </c>
+      <c r="H14" s="79">
+        <v>12825</v>
+      </c>
+      <c r="I14" s="10"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A15" s="74" t="s">
+        <v>34</v>
+      </c>
+      <c r="B15" s="75">
+        <v>45910</v>
+      </c>
+      <c r="C15" s="81">
+        <v>17500</v>
+      </c>
+      <c r="D15" s="74"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="79">
+        <v>1750</v>
+      </c>
+      <c r="H15" s="79">
+        <v>1575</v>
+      </c>
+      <c r="I15" s="10"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A16" s="74" t="s">
+        <v>8</v>
+      </c>
+      <c r="B16" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C16" s="76">
+        <v>20000</v>
+      </c>
+      <c r="D16" s="74"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="80">
+        <v>0.1128</v>
+      </c>
+      <c r="G16" s="79">
+        <v>2256</v>
+      </c>
+      <c r="H16" s="79">
+        <v>2256</v>
+      </c>
+      <c r="I16" s="10"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+      <c r="N16" s="6"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A17" s="74" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" s="75">
+        <v>45912</v>
+      </c>
+      <c r="C17" s="76">
+        <v>1000</v>
+      </c>
+      <c r="D17" s="74"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="80">
+        <v>0.36</v>
+      </c>
+      <c r="G17" s="79">
+        <v>360</v>
+      </c>
+      <c r="H17" s="79">
+        <v>324</v>
+      </c>
+      <c r="I17" s="10"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A18" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B18" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C18" s="76">
+        <v>8000</v>
+      </c>
+      <c r="D18" s="74"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74">
+        <v>0.8</v>
+      </c>
+      <c r="G18" s="79">
+        <v>6400</v>
+      </c>
+      <c r="H18" s="79">
+        <v>5760</v>
+      </c>
+      <c r="I18" s="10"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+      <c r="N18" s="6"/>
+    </row>
+    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A19" s="74" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C19" s="76">
+        <v>50000</v>
+      </c>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="83">
+        <v>0.13250000000000001</v>
+      </c>
+      <c r="G19" s="79">
+        <v>6625</v>
+      </c>
+      <c r="H19" s="79">
+        <v>5962.5</v>
+      </c>
+      <c r="I19" s="10"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+      <c r="N19" s="6"/>
+    </row>
+    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A20" s="74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B20" s="75">
+        <v>45905</v>
+      </c>
+      <c r="C20" s="82">
+        <v>25000</v>
+      </c>
+      <c r="D20" s="74"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="83">
+        <v>0.17169999999999999</v>
+      </c>
+      <c r="G20" s="79">
+        <v>4292.5</v>
+      </c>
+      <c r="H20" s="79">
+        <v>3863.25</v>
+      </c>
+      <c r="I20" s="10"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+      <c r="N20" s="6"/>
+    </row>
+    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A21" s="27"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="31"/>
+      <c r="H21" s="34">
+        <f>SUM(H2:H20)</f>
+        <v>114576.29999999999</v>
+      </c>
+      <c r="I21" s="10"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="6"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="74" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" s="75">
+        <v>45903</v>
+      </c>
+      <c r="C22" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D22" s="74">
+        <v>7.5</v>
+      </c>
+      <c r="E22" s="79">
+        <v>37583.06</v>
+      </c>
+      <c r="F22" s="74">
+        <v>8.3000000000000007</v>
+      </c>
+      <c r="G22" s="79">
+        <v>41408.080000000002</v>
+      </c>
+      <c r="H22" s="79">
+        <v>3825.02</v>
+      </c>
+      <c r="I22" s="56"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="75">
+        <v>45908</v>
+      </c>
+      <c r="C23" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D23" s="74">
+        <v>24.1</v>
+      </c>
+      <c r="E23" s="79">
+        <v>120766.9</v>
+      </c>
+      <c r="F23" s="74">
+        <v>23.4</v>
+      </c>
+      <c r="G23" s="79">
+        <v>116740.86</v>
+      </c>
+      <c r="H23" s="79">
+        <v>-4026.04</v>
+      </c>
+      <c r="I23" s="56"/>
+      <c r="J23" s="7"/>
+      <c r="K23" s="7"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="75">
+        <v>45911</v>
+      </c>
+      <c r="C24" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D24" s="74">
+        <v>23.2</v>
+      </c>
+      <c r="E24" s="79">
+        <v>116256.93</v>
+      </c>
+      <c r="F24" s="74">
+        <v>23.4</v>
+      </c>
+      <c r="G24" s="79">
+        <v>116740.86</v>
+      </c>
+      <c r="H24" s="74">
+        <v>483.93</v>
+      </c>
+      <c r="I24" s="56"/>
+      <c r="J24" s="7"/>
+      <c r="K24" s="7"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="74" t="s">
+        <v>61</v>
+      </c>
+      <c r="B25" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C25" s="74">
+        <v>4000</v>
+      </c>
+      <c r="D25" s="74">
+        <v>23.1</v>
+      </c>
+      <c r="E25" s="79">
+        <v>92604.66</v>
+      </c>
+      <c r="F25" s="74">
+        <v>25.75</v>
+      </c>
+      <c r="G25" s="79">
+        <v>102771.87</v>
+      </c>
+      <c r="H25" s="79">
+        <v>10167.209999999999</v>
+      </c>
+      <c r="I25" s="56"/>
+      <c r="J25" s="7"/>
+      <c r="K25" s="7"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A26" s="74" t="s">
+        <v>21</v>
+      </c>
+      <c r="B26" s="75">
+        <v>45915</v>
+      </c>
+      <c r="C26" s="74">
+        <v>5000</v>
+      </c>
+      <c r="D26" s="74">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="E26" s="79">
+        <v>44097.46</v>
+      </c>
+      <c r="F26" s="74">
+        <v>9.6999999999999993</v>
+      </c>
+      <c r="G26" s="79">
+        <v>48392.57</v>
+      </c>
+      <c r="H26" s="79">
+        <v>4295.1099999999997</v>
+      </c>
+      <c r="I26" s="56"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+      <c r="N26" s="6"/>
+    </row>
+    <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="26"/>
+      <c r="B27" s="28"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="33"/>
+      <c r="E27" s="32">
+        <f>SUM(E22:E26)</f>
+        <v>411309.01000000007</v>
+      </c>
+      <c r="F27" s="30"/>
+      <c r="G27" s="32">
+        <f>SUM(G22:G26)</f>
+        <v>426054.24</v>
+      </c>
+      <c r="H27" s="32">
+        <f>SUM(H22:H26)</f>
+        <v>14745.23</v>
+      </c>
+      <c r="I27" s="32"/>
+      <c r="K27" s="7"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+    </row>
+    <row r="28" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A28" s="26"/>
+      <c r="B28" s="28"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H28" s="34">
+        <f>H21+H27</f>
+        <v>129321.52999999998</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="J28" s="7">
+        <v>30614.600000000002</v>
+      </c>
+      <c r="K28" s="7"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+      <c r="N28" s="6"/>
+    </row>
+    <row r="29" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="26"/>
+      <c r="B29" s="28"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="33"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="32">
+        <v>-522636.73</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="J29" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K29" s="7"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+    </row>
+    <row r="30" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="26"/>
+      <c r="B30" s="28"/>
+      <c r="C30" s="29"/>
+      <c r="D30" s="33"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="30"/>
+      <c r="G30" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H30" s="41">
+        <f>H28+H29</f>
+        <v>-393315.2</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="J30" s="7">
+        <v>-522636.73</v>
+      </c>
+      <c r="K30" s="7"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+    </row>
+    <row r="31" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="26"/>
+      <c r="B31" s="28"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="33"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31" s="35">
+        <v>396550</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="J31" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K31" s="7"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+    </row>
+    <row r="32" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="26"/>
+      <c r="B32" s="28"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="33"/>
+      <c r="E32" s="32"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="H32" s="35">
+        <v>62010</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J32" s="7">
+        <v>10130</v>
+      </c>
+      <c r="K32" s="7"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+    </row>
+    <row r="33" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A33" s="26"/>
+      <c r="B33" s="28"/>
+      <c r="C33" s="29"/>
+      <c r="D33" s="33"/>
+      <c r="E33" s="32"/>
+      <c r="F33" s="30"/>
+      <c r="G33" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H33" s="41">
+        <f>H31+H32</f>
+        <v>458560</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="J33" s="7">
+        <v>396550</v>
+      </c>
+      <c r="K33" s="7"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+      <c r="N33" s="6"/>
+    </row>
+    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A34" s="5"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="8"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="10"/>
+      <c r="G34" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H34" s="45">
+        <f>H30-H33</f>
+        <v>-851875.2</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="J34" s="7">
+        <v>-919186.73</v>
+      </c>
+      <c r="K34" s="7"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+      <c r="N34" s="6"/>
+    </row>
+    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A35" s="5"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="10"/>
+      <c r="G35" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H35" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="J35" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K35" s="7"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+      <c r="N35" s="6"/>
+    </row>
+    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A36" s="6"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="8"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="10"/>
+      <c r="G36" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H36" s="42">
+        <f>H34+H35</f>
+        <v>-794875.2</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="7">
+        <v>-862186.73</v>
+      </c>
+      <c r="K36" s="7"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="6"/>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K37" s="7"/>
+      <c r="M37" s="7"/>
+    </row>
+    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="54" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" s="28">
+        <v>45546</v>
+      </c>
+      <c r="C38" s="29">
+        <v>24000</v>
+      </c>
+      <c r="D38" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="31"/>
+      <c r="F38" s="51">
+        <v>3.9899999999999998E-2</v>
+      </c>
+      <c r="G38" s="31">
+        <f>C38*F38</f>
+        <v>957.59999999999991</v>
+      </c>
+      <c r="H38" s="53">
+        <f>G38*0.9</f>
+        <v>861.83999999999992</v>
+      </c>
+      <c r="K38" s="7"/>
+      <c r="L38" s="15"/>
+      <c r="M38" s="15"/>
+    </row>
+    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="54" t="s">
+        <v>51</v>
+      </c>
+      <c r="B39" s="28">
+        <v>45530</v>
+      </c>
+      <c r="C39" s="29">
+        <v>30000</v>
+      </c>
+      <c r="D39" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E39" s="31"/>
+      <c r="F39" s="37">
+        <v>0.19</v>
+      </c>
+      <c r="G39" s="31">
+        <f>C39*F39</f>
+        <v>5700</v>
+      </c>
+      <c r="H39" s="32">
+        <f>G39</f>
+        <v>5700</v>
+      </c>
+      <c r="K39" s="7"/>
+      <c r="L39" s="15"/>
+      <c r="M39" s="15"/>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="C40" s="12"/>
+      <c r="D40" s="8"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="10"/>
+      <c r="J40" s="11"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="6"/>
+      <c r="M40" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N20">
+    <sortCondition ref="A2:A20"/>
+  </sortState>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961B3AB4-C9A4-46F9-AED6-DC61A66CC09A}">
+  <dimension ref="A1:N29"/>
+  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.625" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
+    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14" style="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="6" customWidth="1"/>
+    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
+    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
+    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="8.625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
+      <c r="M1" s="6"/>
+      <c r="N1" s="6"/>
+    </row>
+    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
+      <c r="A2" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="28">
+        <v>45897</v>
+      </c>
+      <c r="C2" s="29">
+        <v>600</v>
+      </c>
+      <c r="D2" s="30" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="31"/>
+      <c r="F2" s="72">
+        <v>2.5</v>
+      </c>
+      <c r="G2" s="31">
+        <f>C2*F2</f>
+        <v>1500</v>
+      </c>
+      <c r="H2" s="32">
+        <f>G2*0.9</f>
+        <v>1350</v>
+      </c>
+      <c r="I2" s="11"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="6"/>
+    </row>
+    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A3" s="27"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="29"/>
+      <c r="D3" s="30"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="30"/>
+      <c r="G3" s="31"/>
+      <c r="H3" s="41">
+        <f>SUM(H2:H2)</f>
+        <v>1350</v>
+      </c>
+      <c r="I3" s="11"/>
+      <c r="J3" s="7"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="6"/>
+    </row>
+    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A4" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="75">
+        <v>45874</v>
+      </c>
+      <c r="C4" s="76">
+        <v>10000</v>
+      </c>
+      <c r="D4" s="77">
+        <v>1.88</v>
+      </c>
+      <c r="E4" s="77">
+        <v>18841.64</v>
+      </c>
+      <c r="F4" s="77">
+        <v>1.9</v>
+      </c>
+      <c r="G4" s="77">
+        <v>18957.919999999998</v>
+      </c>
+      <c r="H4" s="77">
+        <v>116.28</v>
+      </c>
+      <c r="I4" s="11"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="15"/>
+      <c r="M4" s="15"/>
+      <c r="N4" s="6"/>
+    </row>
+    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A5" s="74" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" s="75">
+        <v>45875</v>
+      </c>
+      <c r="C5" s="76">
+        <v>2800</v>
+      </c>
+      <c r="D5" s="77">
+        <v>10.5</v>
+      </c>
+      <c r="E5" s="77">
+        <v>29465.119999999999</v>
+      </c>
+      <c r="F5" s="77">
+        <v>11.6</v>
+      </c>
+      <c r="G5" s="77">
+        <v>32408.06</v>
+      </c>
+      <c r="H5" s="77">
+        <v>2942.94</v>
+      </c>
+      <c r="I5" s="11"/>
+      <c r="J5" s="7"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="6"/>
+    </row>
+    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A6" s="74" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="75">
+        <v>45875</v>
+      </c>
+      <c r="C6" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D6" s="77">
+        <v>3.9</v>
+      </c>
+      <c r="E6" s="77">
+        <v>19543.2</v>
+      </c>
+      <c r="F6" s="77">
+        <v>4.5199999999999996</v>
+      </c>
+      <c r="G6" s="77">
+        <v>22549.95</v>
+      </c>
+      <c r="H6" s="77">
+        <v>3006.75</v>
+      </c>
+      <c r="I6" s="11"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="15"/>
+      <c r="M6" s="15"/>
+      <c r="N6" s="6"/>
+    </row>
+    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A7" s="74" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="75">
+        <v>45876</v>
+      </c>
+      <c r="C7" s="76">
+        <v>3200</v>
+      </c>
+      <c r="D7" s="77">
+        <v>9.25</v>
+      </c>
+      <c r="E7" s="77">
+        <v>29665.56</v>
+      </c>
+      <c r="F7" s="77">
+        <v>9.4</v>
+      </c>
+      <c r="G7" s="77">
+        <v>30013.37</v>
+      </c>
+      <c r="H7" s="77">
+        <v>347.81</v>
+      </c>
+      <c r="I7" s="11"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="15"/>
+      <c r="M7" s="15"/>
+      <c r="N7" s="6"/>
+    </row>
+    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A8" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="75">
+        <v>45876</v>
+      </c>
+      <c r="C8" s="76">
+        <v>10000</v>
+      </c>
+      <c r="D8" s="77">
+        <v>1.85</v>
+      </c>
+      <c r="E8" s="77">
+        <v>18540.98</v>
+      </c>
+      <c r="F8" s="77">
+        <v>2.06</v>
+      </c>
+      <c r="G8" s="77">
+        <v>20554.38</v>
+      </c>
+      <c r="H8" s="77">
+        <v>2013.4</v>
+      </c>
+      <c r="I8" s="11"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="15"/>
+      <c r="M8" s="15"/>
+      <c r="N8" s="6"/>
+    </row>
+    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A9" s="74" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="75">
+        <v>45877</v>
+      </c>
+      <c r="C9" s="76">
+        <v>6000</v>
+      </c>
+      <c r="D9" s="77">
+        <v>6.1</v>
+      </c>
+      <c r="E9" s="77">
+        <v>36681.06</v>
+      </c>
+      <c r="F9" s="77">
+        <v>6.7</v>
+      </c>
+      <c r="G9" s="77">
+        <v>40110.97</v>
+      </c>
+      <c r="H9" s="77">
+        <v>3429.91</v>
+      </c>
+      <c r="I9" s="11"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="15"/>
+      <c r="M9" s="15"/>
+      <c r="N9" s="6"/>
+    </row>
+    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A10" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="75">
+        <v>45877</v>
+      </c>
+      <c r="C10" s="76">
+        <v>3000</v>
+      </c>
+      <c r="D10" s="77">
+        <v>27.75</v>
+      </c>
+      <c r="E10" s="77">
+        <v>83434.39</v>
+      </c>
+      <c r="F10" s="77">
+        <v>31</v>
+      </c>
+      <c r="G10" s="77">
+        <v>92794.01</v>
+      </c>
+      <c r="H10" s="77">
+        <v>9359.6200000000008</v>
+      </c>
+      <c r="I10" s="73"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="15"/>
+      <c r="M10" s="15"/>
+      <c r="N10" s="6"/>
+    </row>
+    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A11" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="75">
+        <v>45889</v>
+      </c>
+      <c r="C11" s="76">
+        <v>4000</v>
+      </c>
+      <c r="D11" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E11" s="77">
+        <v>96613.52</v>
+      </c>
+      <c r="F11" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G11" s="77">
+        <v>96984.72</v>
+      </c>
+      <c r="H11" s="77">
+        <v>371.2</v>
+      </c>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="15"/>
+      <c r="M11" s="15"/>
+      <c r="N11" s="6"/>
+    </row>
+    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A12" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B12" s="75">
+        <v>45890</v>
+      </c>
+      <c r="C12" s="76">
+        <v>4000</v>
+      </c>
+      <c r="D12" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E12" s="77">
+        <v>96613.52</v>
+      </c>
+      <c r="F12" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G12" s="77">
+        <v>96984.72</v>
+      </c>
+      <c r="H12" s="77">
+        <v>371.2</v>
+      </c>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="15"/>
+      <c r="M12" s="15"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A13" s="74" t="s">
+        <v>62</v>
+      </c>
+      <c r="B13" s="75">
+        <v>45891</v>
+      </c>
+      <c r="C13" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D13" s="77">
+        <v>24.1</v>
+      </c>
+      <c r="E13" s="77">
+        <v>120766.9</v>
+      </c>
+      <c r="F13" s="77">
+        <v>24.3</v>
+      </c>
+      <c r="G13" s="77">
+        <v>121230.88</v>
+      </c>
+      <c r="H13" s="77">
+        <v>463.98</v>
+      </c>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="15"/>
+      <c r="N13" s="6"/>
+    </row>
+    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A14" s="74" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="75">
+        <v>45896</v>
+      </c>
+      <c r="C14" s="76">
+        <v>6000</v>
+      </c>
+      <c r="D14" s="77">
+        <v>7.3</v>
+      </c>
+      <c r="E14" s="77">
+        <v>43897.02</v>
+      </c>
+      <c r="F14" s="77">
+        <v>8.4</v>
+      </c>
+      <c r="G14" s="77">
+        <v>50288.37</v>
+      </c>
+      <c r="H14" s="77">
+        <v>6391.35</v>
+      </c>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="15"/>
+      <c r="N14" s="6"/>
+    </row>
+    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A15" s="74" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="75">
+        <v>45897</v>
+      </c>
+      <c r="C15" s="76">
+        <v>5000</v>
+      </c>
+      <c r="D15" s="77">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="E15" s="77">
+        <v>11024.36</v>
+      </c>
+      <c r="F15" s="77">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="G15" s="77">
+        <v>11474.52</v>
+      </c>
+      <c r="H15" s="77">
+        <v>450.16</v>
+      </c>
+      <c r="I15" s="78"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="6"/>
+    </row>
+    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="28"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="32">
+        <f>SUM(E4:E15)</f>
+        <v>605087.27</v>
+      </c>
+      <c r="F16" s="30"/>
+      <c r="G16" s="32">
+        <f>SUM(G4:G15)</f>
+        <v>634351.87</v>
+      </c>
+      <c r="H16" s="32">
+        <f>SUM(H4:H15)</f>
+        <v>29264.600000000002</v>
+      </c>
+      <c r="K16" s="7"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="15"/>
+    </row>
+    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A17" s="26"/>
+      <c r="B17" s="28"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="H17" s="41">
+        <f>H3+H16</f>
+        <v>30614.600000000002</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="J17" s="7">
+        <v>-365900.39999999997</v>
+      </c>
+      <c r="K17" s="7"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="6"/>
+    </row>
+    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="30"/>
+      <c r="G18" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="32">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="I18" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J18" s="7">
+        <v>-187350.93</v>
+      </c>
+      <c r="K18" s="7"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="15"/>
+    </row>
+    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="26"/>
+      <c r="B19" s="28"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="33"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="30"/>
+      <c r="G19" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="H19" s="41">
+        <f>H17+H18</f>
+        <v>-522636.73</v>
+      </c>
+      <c r="I19" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="J19" s="7">
+        <v>-553251.32999999996</v>
+      </c>
+      <c r="K19" s="7"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="15"/>
+    </row>
+    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="26"/>
+      <c r="B20" s="28"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="33"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20" s="7">
+        <v>386420</v>
+      </c>
+      <c r="I20" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="J20" s="7">
+        <v>377810</v>
+      </c>
+      <c r="K20" s="7"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+    </row>
+    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="26"/>
+      <c r="B21" s="28"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="30"/>
+      <c r="G21" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="H21" s="35">
+        <v>10130</v>
+      </c>
+      <c r="I21" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="J21" s="7">
+        <v>8610</v>
+      </c>
+      <c r="K21" s="7"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+    </row>
+    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A22" s="26"/>
+      <c r="B22" s="28"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="33"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="30"/>
+      <c r="G22" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="H22" s="41">
+        <f>H20+H21</f>
+        <v>396550</v>
+      </c>
+      <c r="I22" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="J22" s="7">
+        <v>386420</v>
+      </c>
+      <c r="K22" s="7"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+      <c r="N22" s="6"/>
+    </row>
+    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A23" s="5"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="7"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="47">
+        <f>H19-H22</f>
+        <v>-919186.73</v>
+      </c>
+      <c r="I23" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="J23" s="7">
+        <v>-939671.33</v>
+      </c>
+      <c r="K23" s="7"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+      <c r="N23" s="6"/>
+    </row>
+    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A24" s="5"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="38" t="s">
+        <v>30</v>
+      </c>
+      <c r="H24" s="7">
+        <v>57000</v>
+      </c>
+      <c r="I24" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J24" s="7">
+        <v>57000</v>
+      </c>
+      <c r="K24" s="7"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+      <c r="N24" s="6"/>
+    </row>
+    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="A25" s="6"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="38" t="s">
+        <v>31</v>
+      </c>
+      <c r="H25" s="42">
+        <f>H23+H24</f>
+        <v>-862186.73</v>
+      </c>
+      <c r="I25" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="J25" s="7">
+        <v>-882671.33</v>
+      </c>
+      <c r="K25" s="7"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+      <c r="N25" s="6"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="K26" s="7"/>
+      <c r="M26" s="7"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M27" s="7"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="M28" s="7"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="D29" s="8"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="10"/>
+      <c r="I29" s="7"/>
+      <c r="J29" s="11"/>
+      <c r="K29" s="7"/>
+      <c r="L29" s="6"/>
+      <c r="M29" s="7"/>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
+  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <headerFooter alignWithMargins="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28B9F8AE-F947-4FC1-BF85-790919A908D8}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -1013,27 +5187,28 @@
     </row>
     <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
       <c r="A2" s="27" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="B2" s="28">
-        <v>44736</v>
+        <v>46218</v>
       </c>
       <c r="C2" s="29">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="D2" s="30" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="31"/>
       <c r="F2" s="37">
-        <v>0.15559999999999999</v>
+        <v>7.0999999999999994E-2</v>
       </c>
       <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>6223.9999999999991</v>
+        <f>C2*F2*0.9</f>
+        <v>1277.9999999999998</v>
       </c>
       <c r="H2" s="32">
-        <v>0</v>
+        <f>G2</f>
+        <v>1277.9999999999998</v>
       </c>
       <c r="I2" s="11"/>
       <c r="J2" s="7"/>
@@ -1052,7 +5227,7 @@
       <c r="G3" s="31"/>
       <c r="H3" s="34">
         <f>SUM(H2:H2)</f>
-        <v>0</v>
+        <v>1277.9999999999998</v>
       </c>
       <c r="I3" s="11"/>
       <c r="J3" s="7"/>
@@ -1127,7 +5302,7 @@
       </c>
       <c r="H6" s="34">
         <f>H3+H5</f>
-        <v>0</v>
+        <v>1277.9999999999998</v>
       </c>
       <c r="I6" s="11" t="s">
         <v>12</v>
@@ -1175,7 +5350,7 @@
       </c>
       <c r="H8" s="34">
         <f>H6+H7</f>
-        <v>-57483.65400000001</v>
+        <v>-56205.65400000001</v>
       </c>
       <c r="I8" s="11" t="s">
         <v>28</v>
@@ -1270,7 +5445,7 @@
       </c>
       <c r="H12" s="46">
         <f>H8-H11</f>
-        <v>-276023.65399999998</v>
+        <v>-274745.65399999998</v>
       </c>
       <c r="I12" s="11" t="s">
         <v>15</v>
@@ -1320,7 +5495,7 @@
       </c>
       <c r="H14" s="39">
         <f>H12+H13</f>
-        <v>-216023.65399999998</v>
+        <v>-214745.65399999998</v>
       </c>
       <c r="I14" s="11" t="s">
         <v>31</v>
@@ -1355,7 +5530,7 @@
       </c>
       <c r="H16" s="32">
         <f>H15+H3</f>
-        <v>270100.40599999996</v>
+        <v>271378.40599999996</v>
       </c>
       <c r="I16" s="11" t="s">
         <v>64</v>
@@ -1371,7 +5546,7 @@
       </c>
       <c r="H17" s="32">
         <f>H16-H11</f>
-        <v>51560.405999999959</v>
+        <v>52838.405999999959</v>
       </c>
       <c r="I17" s="11" t="s">
         <v>65</v>
@@ -1401,2322 +5576,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{801544F9-630F-4E32-B67B-5CF42760770C}">
-  <dimension ref="A1:N20"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.25" style="11" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45576</v>
-      </c>
-      <c r="C2" s="29">
-        <v>6800</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="52">
-        <v>0</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="53">
-        <f>G2*0.9</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="34">
-        <f>SUM(H2:H2)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45931</v>
-      </c>
-      <c r="C4" s="29">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="30">
-        <v>2.62</v>
-      </c>
-      <c r="E4" s="31">
-        <v>26258.03</v>
-      </c>
-      <c r="F4" s="30">
-        <v>2.72</v>
-      </c>
-      <c r="G4" s="31">
-        <v>27139.759999999998</v>
-      </c>
-      <c r="H4" s="40">
-        <f>G4-E4</f>
-        <v>881.72999999999956</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="28">
-        <v>45937</v>
-      </c>
-      <c r="C5" s="29">
-        <v>3000</v>
-      </c>
-      <c r="D5" s="30">
-        <v>26</v>
-      </c>
-      <c r="E5" s="31">
-        <v>78172.759999999995</v>
-      </c>
-      <c r="F5" s="30">
-        <v>26.5</v>
-      </c>
-      <c r="G5" s="31">
-        <v>79323.91</v>
-      </c>
-      <c r="H5" s="40">
-        <f>G5-E5</f>
-        <v>1151.1500000000087</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="28">
-        <v>45954</v>
-      </c>
-      <c r="C6" s="29">
-        <v>2500</v>
-      </c>
-      <c r="D6" s="30">
-        <v>31</v>
-      </c>
-      <c r="E6" s="31">
-        <v>77671.66</v>
-      </c>
-      <c r="F6" s="30">
-        <v>31.25</v>
-      </c>
-      <c r="G6" s="31">
-        <v>77951.960000000006</v>
-      </c>
-      <c r="H6" s="40">
-        <f>G6-E6</f>
-        <v>280.30000000000291</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32">
-        <f>SUM(E4:E6)</f>
-        <v>182102.45</v>
-      </c>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32">
-        <f t="shared" ref="G7:H7" si="0">SUM(G4:G6)</f>
-        <v>184415.63</v>
-      </c>
-      <c r="H7" s="32">
-        <f t="shared" si="0"/>
-        <v>2313.1800000000112</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H8" s="34">
-        <f>H3+H7</f>
-        <v>2313.1800000000112</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="7">
-        <v>30614.600000000002</v>
-      </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H9" s="32">
-        <v>-522636.73</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H10" s="41">
-        <f>H8+H9</f>
-        <v>-520323.55</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J10" s="7">
-        <v>-522636.73</v>
-      </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H11" s="35">
-        <v>396550</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J11" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-    </row>
-    <row r="12" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="29"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="30"/>
-      <c r="G12" s="32" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="35">
-        <v>19270</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="J12" s="7">
-        <v>10130</v>
-      </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="26"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="30"/>
-      <c r="G13" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="41">
-        <f>H11+H12</f>
-        <v>415820</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="7">
-        <v>396550</v>
-      </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="5"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="9"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="45">
-        <f>H10-H13</f>
-        <v>-936143.55</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="7">
-        <v>-919186.73</v>
-      </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="5"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H15" s="38">
-        <v>57000</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J15" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A16" s="6"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="8"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H16" s="42">
-        <f>H14+H15</f>
-        <v>-879143.55</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J16" s="7">
-        <v>-862186.73</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="K17" s="7"/>
-      <c r="M17" s="7"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="M18" s="7"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="M19" s="7"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C20" s="12"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="9"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="10"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="11"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="6"/>
-      <c r="M20" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{805BC19F-42DC-4CD3-B954-E9F19E56BFF7}">
-  <dimension ref="A1:N40"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.125" style="10" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="55"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="74" t="s">
-        <v>51</v>
-      </c>
-      <c r="B2" s="75">
-        <v>45903</v>
-      </c>
-      <c r="C2" s="76">
-        <v>120000</v>
-      </c>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74">
-        <v>0.15454999999999999</v>
-      </c>
-      <c r="G2" s="79">
-        <v>18546</v>
-      </c>
-      <c r="H2" s="79">
-        <v>16691.400000000001</v>
-      </c>
-      <c r="I2" s="10"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="74" t="s">
-        <v>42</v>
-      </c>
-      <c r="B3" s="75">
-        <v>45910</v>
-      </c>
-      <c r="C3" s="76">
-        <v>1200</v>
-      </c>
-      <c r="D3" s="74"/>
-      <c r="E3" s="74"/>
-      <c r="F3" s="80">
-        <v>0.31</v>
-      </c>
-      <c r="G3" s="79">
-        <v>372</v>
-      </c>
-      <c r="H3" s="79">
-        <v>339.6</v>
-      </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="74" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C4" s="81">
-        <v>17500</v>
-      </c>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="80">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G4" s="79">
-        <v>3587.5</v>
-      </c>
-      <c r="H4" s="79">
-        <v>3228.75</v>
-      </c>
-      <c r="I4" s="10"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="74" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C5" s="76">
-        <v>4000</v>
-      </c>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-      <c r="F5" s="80">
-        <v>0.15</v>
-      </c>
-      <c r="G5" s="79">
-        <v>600</v>
-      </c>
-      <c r="H5" s="79">
-        <v>540</v>
-      </c>
-      <c r="I5" s="10"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B6" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C6" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-      <c r="F6" s="74">
-        <v>1</v>
-      </c>
-      <c r="G6" s="79">
-        <v>5000</v>
-      </c>
-      <c r="H6" s="79">
-        <v>4500</v>
-      </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="74" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C7" s="82">
-        <v>55000</v>
-      </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-      <c r="F7" s="80">
-        <v>0.2261</v>
-      </c>
-      <c r="G7" s="79">
-        <v>12435.5</v>
-      </c>
-      <c r="H7" s="79">
-        <v>11191.95</v>
-      </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="75">
-        <v>45909</v>
-      </c>
-      <c r="C8" s="81">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="74"/>
-      <c r="E8" s="74"/>
-      <c r="F8" s="74">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="G8" s="79">
-        <v>11110</v>
-      </c>
-      <c r="H8" s="79">
-        <v>9999</v>
-      </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="74" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C9" s="81">
-        <v>69000</v>
-      </c>
-      <c r="D9" s="74"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="80">
-        <v>0.19650000000000001</v>
-      </c>
-      <c r="G9" s="79">
-        <v>13558.5</v>
-      </c>
-      <c r="H9" s="79">
-        <v>12202.65</v>
-      </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="74" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C10" s="82">
-        <v>7200</v>
-      </c>
-      <c r="D10" s="74"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="74">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G10" s="79">
-        <v>1260</v>
-      </c>
-      <c r="H10" s="79">
-        <v>1134</v>
-      </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="74" t="s">
-        <v>33</v>
-      </c>
-      <c r="B11" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C11" s="82">
-        <v>4200</v>
-      </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="83">
-        <v>0.24</v>
-      </c>
-      <c r="G11" s="79">
-        <v>1008</v>
-      </c>
-      <c r="H11" s="79">
-        <v>907.2</v>
-      </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="B12" s="75">
-        <v>45910</v>
-      </c>
-      <c r="C12" s="81">
-        <v>81000</v>
-      </c>
-      <c r="D12" s="74"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="80">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="79">
-        <v>20250</v>
-      </c>
-      <c r="H12" s="79">
-        <v>19926</v>
-      </c>
-      <c r="I12" s="10"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C13" s="76">
-        <v>27000</v>
-      </c>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74">
-        <v>0.05</v>
-      </c>
-      <c r="G13" s="79">
-        <v>1350</v>
-      </c>
-      <c r="H13" s="79">
-        <v>1350</v>
-      </c>
-      <c r="I13" s="10"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A14" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="B14" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C14" s="76">
-        <v>27000</v>
-      </c>
-      <c r="D14" s="74"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74">
-        <v>0.5</v>
-      </c>
-      <c r="G14" s="79">
-        <v>13500</v>
-      </c>
-      <c r="H14" s="79">
-        <v>12825</v>
-      </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A15" s="74" t="s">
-        <v>34</v>
-      </c>
-      <c r="B15" s="75">
-        <v>45910</v>
-      </c>
-      <c r="C15" s="81">
-        <v>17500</v>
-      </c>
-      <c r="D15" s="74"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74">
-        <v>0.1</v>
-      </c>
-      <c r="G15" s="79">
-        <v>1750</v>
-      </c>
-      <c r="H15" s="79">
-        <v>1575</v>
-      </c>
-      <c r="I15" s="10"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A16" s="74" t="s">
-        <v>8</v>
-      </c>
-      <c r="B16" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C16" s="76">
-        <v>20000</v>
-      </c>
-      <c r="D16" s="74"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="80">
-        <v>0.1128</v>
-      </c>
-      <c r="G16" s="79">
-        <v>2256</v>
-      </c>
-      <c r="H16" s="79">
-        <v>2256</v>
-      </c>
-      <c r="I16" s="10"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="6"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A17" s="74" t="s">
-        <v>45</v>
-      </c>
-      <c r="B17" s="75">
-        <v>45912</v>
-      </c>
-      <c r="C17" s="76">
-        <v>1000</v>
-      </c>
-      <c r="D17" s="74"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="80">
-        <v>0.36</v>
-      </c>
-      <c r="G17" s="79">
-        <v>360</v>
-      </c>
-      <c r="H17" s="79">
-        <v>324</v>
-      </c>
-      <c r="I17" s="10"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A18" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="B18" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C18" s="76">
-        <v>8000</v>
-      </c>
-      <c r="D18" s="74"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74">
-        <v>0.8</v>
-      </c>
-      <c r="G18" s="79">
-        <v>6400</v>
-      </c>
-      <c r="H18" s="79">
-        <v>5760</v>
-      </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A19" s="74" t="s">
-        <v>23</v>
-      </c>
-      <c r="B19" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C19" s="76">
-        <v>50000</v>
-      </c>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="83">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="G19" s="79">
-        <v>6625</v>
-      </c>
-      <c r="H19" s="79">
-        <v>5962.5</v>
-      </c>
-      <c r="I19" s="10"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A20" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="75">
-        <v>45905</v>
-      </c>
-      <c r="C20" s="82">
-        <v>25000</v>
-      </c>
-      <c r="D20" s="74"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="83">
-        <v>0.17169999999999999</v>
-      </c>
-      <c r="G20" s="79">
-        <v>4292.5</v>
-      </c>
-      <c r="H20" s="79">
-        <v>3863.25</v>
-      </c>
-      <c r="I20" s="10"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="6"/>
-    </row>
-    <row r="21" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A21" s="27"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="34">
-        <f>SUM(H2:H20)</f>
-        <v>114576.29999999999</v>
-      </c>
-      <c r="I21" s="10"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-      <c r="N21" s="6"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="74" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="75">
-        <v>45903</v>
-      </c>
-      <c r="C22" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D22" s="74">
-        <v>7.5</v>
-      </c>
-      <c r="E22" s="79">
-        <v>37583.06</v>
-      </c>
-      <c r="F22" s="74">
-        <v>8.3000000000000007</v>
-      </c>
-      <c r="G22" s="79">
-        <v>41408.080000000002</v>
-      </c>
-      <c r="H22" s="79">
-        <v>3825.02</v>
-      </c>
-      <c r="I22" s="56"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="75">
-        <v>45908</v>
-      </c>
-      <c r="C23" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D23" s="74">
-        <v>24.1</v>
-      </c>
-      <c r="E23" s="79">
-        <v>120766.9</v>
-      </c>
-      <c r="F23" s="74">
-        <v>23.4</v>
-      </c>
-      <c r="G23" s="79">
-        <v>116740.86</v>
-      </c>
-      <c r="H23" s="79">
-        <v>-4026.04</v>
-      </c>
-      <c r="I23" s="56"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B24" s="75">
-        <v>45911</v>
-      </c>
-      <c r="C24" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D24" s="74">
-        <v>23.2</v>
-      </c>
-      <c r="E24" s="79">
-        <v>116256.93</v>
-      </c>
-      <c r="F24" s="74">
-        <v>23.4</v>
-      </c>
-      <c r="G24" s="79">
-        <v>116740.86</v>
-      </c>
-      <c r="H24" s="74">
-        <v>483.93</v>
-      </c>
-      <c r="I24" s="56"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="74" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C25" s="74">
-        <v>4000</v>
-      </c>
-      <c r="D25" s="74">
-        <v>23.1</v>
-      </c>
-      <c r="E25" s="79">
-        <v>92604.66</v>
-      </c>
-      <c r="F25" s="74">
-        <v>25.75</v>
-      </c>
-      <c r="G25" s="79">
-        <v>102771.87</v>
-      </c>
-      <c r="H25" s="79">
-        <v>10167.209999999999</v>
-      </c>
-      <c r="I25" s="56"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A26" s="74" t="s">
-        <v>21</v>
-      </c>
-      <c r="B26" s="75">
-        <v>45915</v>
-      </c>
-      <c r="C26" s="74">
-        <v>5000</v>
-      </c>
-      <c r="D26" s="74">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="E26" s="79">
-        <v>44097.46</v>
-      </c>
-      <c r="F26" s="74">
-        <v>9.6999999999999993</v>
-      </c>
-      <c r="G26" s="79">
-        <v>48392.57</v>
-      </c>
-      <c r="H26" s="79">
-        <v>4295.1099999999997</v>
-      </c>
-      <c r="I26" s="56"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="15"/>
-      <c r="M26" s="15"/>
-      <c r="N26" s="6"/>
-    </row>
-    <row r="27" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="26"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="29"/>
-      <c r="D27" s="33"/>
-      <c r="E27" s="32">
-        <f>SUM(E22:E26)</f>
-        <v>411309.01000000007</v>
-      </c>
-      <c r="F27" s="30"/>
-      <c r="G27" s="32">
-        <f>SUM(G22:G26)</f>
-        <v>426054.24</v>
-      </c>
-      <c r="H27" s="32">
-        <f>SUM(H22:H26)</f>
-        <v>14745.23</v>
-      </c>
-      <c r="I27" s="32"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="15"/>
-      <c r="M27" s="15"/>
-    </row>
-    <row r="28" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A28" s="26"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H28" s="34">
-        <f>H21+H27</f>
-        <v>129321.52999999998</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="J28" s="7">
-        <v>30614.600000000002</v>
-      </c>
-      <c r="K28" s="7"/>
-      <c r="L28" s="15"/>
-      <c r="M28" s="15"/>
-      <c r="N28" s="6"/>
-    </row>
-    <row r="29" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="26"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="33"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H29" s="32">
-        <v>-522636.73</v>
-      </c>
-      <c r="I29" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K29" s="7"/>
-      <c r="L29" s="15"/>
-      <c r="M29" s="15"/>
-    </row>
-    <row r="30" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="26"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="33"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="30"/>
-      <c r="G30" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H30" s="41">
-        <f>H28+H29</f>
-        <v>-393315.2</v>
-      </c>
-      <c r="I30" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="J30" s="7">
-        <v>-522636.73</v>
-      </c>
-      <c r="K30" s="7"/>
-      <c r="L30" s="15"/>
-      <c r="M30" s="15"/>
-    </row>
-    <row r="31" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="26"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="33"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="30"/>
-      <c r="G31" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H31" s="35">
-        <v>396550</v>
-      </c>
-      <c r="I31" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J31" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K31" s="7"/>
-      <c r="L31" s="15"/>
-      <c r="M31" s="15"/>
-    </row>
-    <row r="32" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="26"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="33"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="32" t="s">
-        <v>52</v>
-      </c>
-      <c r="H32" s="35">
-        <v>62010</v>
-      </c>
-      <c r="I32" s="10" t="s">
-        <v>50</v>
-      </c>
-      <c r="J32" s="7">
-        <v>10130</v>
-      </c>
-      <c r="K32" s="7"/>
-      <c r="L32" s="15"/>
-      <c r="M32" s="15"/>
-    </row>
-    <row r="33" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A33" s="26"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="33"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="30"/>
-      <c r="G33" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" s="41">
-        <f>H31+H32</f>
-        <v>458560</v>
-      </c>
-      <c r="I33" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J33" s="7">
-        <v>396550</v>
-      </c>
-      <c r="K33" s="7"/>
-      <c r="L33" s="15"/>
-      <c r="M33" s="15"/>
-      <c r="N33" s="6"/>
-    </row>
-    <row r="34" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A34" s="5"/>
-      <c r="B34" s="12"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="9"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="10"/>
-      <c r="G34" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H34" s="45">
-        <f>H30-H33</f>
-        <v>-851875.2</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="J34" s="7">
-        <v>-919186.73</v>
-      </c>
-      <c r="K34" s="7"/>
-      <c r="L34" s="15"/>
-      <c r="M34" s="15"/>
-      <c r="N34" s="6"/>
-    </row>
-    <row r="35" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A35" s="5"/>
-      <c r="B35" s="12"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="9"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="10"/>
-      <c r="G35" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H35" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I35" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="J35" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K35" s="7"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="6"/>
-    </row>
-    <row r="36" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A36" s="6"/>
-      <c r="B36" s="12"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H36" s="42">
-        <f>H34+H35</f>
-        <v>-794875.2</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="J36" s="7">
-        <v>-862186.73</v>
-      </c>
-      <c r="K36" s="7"/>
-      <c r="L36" s="15"/>
-      <c r="M36" s="15"/>
-      <c r="N36" s="6"/>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K37" s="7"/>
-      <c r="M37" s="7"/>
-    </row>
-    <row r="38" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="54" t="s">
-        <v>20</v>
-      </c>
-      <c r="B38" s="28">
-        <v>45546</v>
-      </c>
-      <c r="C38" s="29">
-        <v>24000</v>
-      </c>
-      <c r="D38" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E38" s="31"/>
-      <c r="F38" s="51">
-        <v>3.9899999999999998E-2</v>
-      </c>
-      <c r="G38" s="31">
-        <f>C38*F38</f>
-        <v>957.59999999999991</v>
-      </c>
-      <c r="H38" s="53">
-        <f>G38*0.9</f>
-        <v>861.83999999999992</v>
-      </c>
-      <c r="K38" s="7"/>
-      <c r="L38" s="15"/>
-      <c r="M38" s="15"/>
-    </row>
-    <row r="39" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="54" t="s">
-        <v>51</v>
-      </c>
-      <c r="B39" s="28">
-        <v>45530</v>
-      </c>
-      <c r="C39" s="29">
-        <v>30000</v>
-      </c>
-      <c r="D39" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E39" s="31"/>
-      <c r="F39" s="37">
-        <v>0.19</v>
-      </c>
-      <c r="G39" s="31">
-        <f>C39*F39</f>
-        <v>5700</v>
-      </c>
-      <c r="H39" s="32">
-        <f>G39</f>
-        <v>5700</v>
-      </c>
-      <c r="K39" s="7"/>
-      <c r="L39" s="15"/>
-      <c r="M39" s="15"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="C40" s="12"/>
-      <c r="D40" s="8"/>
-      <c r="E40" s="9"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="10"/>
-      <c r="J40" s="11"/>
-      <c r="K40" s="7"/>
-      <c r="L40" s="6"/>
-      <c r="M40" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N20">
-    <sortCondition ref="A2:A20"/>
-  </sortState>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{961B3AB4-C9A4-46F9-AED6-DC61A66CC09A}">
-  <dimension ref="A1:N29"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.625" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45897</v>
-      </c>
-      <c r="C2" s="29">
-        <v>600</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="72">
-        <v>2.5</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>1500</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2*0.9</f>
-        <v>1350</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="41">
-        <f>SUM(H2:H2)</f>
-        <v>1350</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="75">
-        <v>45874</v>
-      </c>
-      <c r="C4" s="76">
-        <v>10000</v>
-      </c>
-      <c r="D4" s="77">
-        <v>1.88</v>
-      </c>
-      <c r="E4" s="77">
-        <v>18841.64</v>
-      </c>
-      <c r="F4" s="77">
-        <v>1.9</v>
-      </c>
-      <c r="G4" s="77">
-        <v>18957.919999999998</v>
-      </c>
-      <c r="H4" s="77">
-        <v>116.28</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A5" s="74" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="75">
-        <v>45875</v>
-      </c>
-      <c r="C5" s="76">
-        <v>2800</v>
-      </c>
-      <c r="D5" s="77">
-        <v>10.5</v>
-      </c>
-      <c r="E5" s="77">
-        <v>29465.119999999999</v>
-      </c>
-      <c r="F5" s="77">
-        <v>11.6</v>
-      </c>
-      <c r="G5" s="77">
-        <v>32408.06</v>
-      </c>
-      <c r="H5" s="77">
-        <v>2942.94</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="74" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="75">
-        <v>45875</v>
-      </c>
-      <c r="C6" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D6" s="77">
-        <v>3.9</v>
-      </c>
-      <c r="E6" s="77">
-        <v>19543.2</v>
-      </c>
-      <c r="F6" s="77">
-        <v>4.5199999999999996</v>
-      </c>
-      <c r="G6" s="77">
-        <v>22549.95</v>
-      </c>
-      <c r="H6" s="77">
-        <v>3006.75</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A7" s="74" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="75">
-        <v>45876</v>
-      </c>
-      <c r="C7" s="76">
-        <v>3200</v>
-      </c>
-      <c r="D7" s="77">
-        <v>9.25</v>
-      </c>
-      <c r="E7" s="77">
-        <v>29665.56</v>
-      </c>
-      <c r="F7" s="77">
-        <v>9.4</v>
-      </c>
-      <c r="G7" s="77">
-        <v>30013.37</v>
-      </c>
-      <c r="H7" s="77">
-        <v>347.81</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A8" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="75">
-        <v>45876</v>
-      </c>
-      <c r="C8" s="76">
-        <v>10000</v>
-      </c>
-      <c r="D8" s="77">
-        <v>1.85</v>
-      </c>
-      <c r="E8" s="77">
-        <v>18540.98</v>
-      </c>
-      <c r="F8" s="77">
-        <v>2.06</v>
-      </c>
-      <c r="G8" s="77">
-        <v>20554.38</v>
-      </c>
-      <c r="H8" s="77">
-        <v>2013.4</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A9" s="74" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="75">
-        <v>45877</v>
-      </c>
-      <c r="C9" s="76">
-        <v>6000</v>
-      </c>
-      <c r="D9" s="77">
-        <v>6.1</v>
-      </c>
-      <c r="E9" s="77">
-        <v>36681.06</v>
-      </c>
-      <c r="F9" s="77">
-        <v>6.7</v>
-      </c>
-      <c r="G9" s="77">
-        <v>40110.97</v>
-      </c>
-      <c r="H9" s="77">
-        <v>3429.91</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A10" s="74" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="75">
-        <v>45877</v>
-      </c>
-      <c r="C10" s="76">
-        <v>3000</v>
-      </c>
-      <c r="D10" s="77">
-        <v>27.75</v>
-      </c>
-      <c r="E10" s="77">
-        <v>83434.39</v>
-      </c>
-      <c r="F10" s="77">
-        <v>31</v>
-      </c>
-      <c r="G10" s="77">
-        <v>92794.01</v>
-      </c>
-      <c r="H10" s="77">
-        <v>9359.6200000000008</v>
-      </c>
-      <c r="I10" s="73"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11" s="75">
-        <v>45889</v>
-      </c>
-      <c r="C11" s="76">
-        <v>4000</v>
-      </c>
-      <c r="D11" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E11" s="77">
-        <v>96613.52</v>
-      </c>
-      <c r="F11" s="77">
-        <v>24.3</v>
-      </c>
-      <c r="G11" s="77">
-        <v>96984.72</v>
-      </c>
-      <c r="H11" s="77">
-        <v>371.2</v>
-      </c>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B12" s="75">
-        <v>45890</v>
-      </c>
-      <c r="C12" s="76">
-        <v>4000</v>
-      </c>
-      <c r="D12" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E12" s="77">
-        <v>96613.52</v>
-      </c>
-      <c r="F12" s="77">
-        <v>24.3</v>
-      </c>
-      <c r="G12" s="77">
-        <v>96984.72</v>
-      </c>
-      <c r="H12" s="77">
-        <v>371.2</v>
-      </c>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="74" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13" s="75">
-        <v>45891</v>
-      </c>
-      <c r="C13" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D13" s="77">
-        <v>24.1</v>
-      </c>
-      <c r="E13" s="77">
-        <v>120766.9</v>
-      </c>
-      <c r="F13" s="77">
-        <v>24.3</v>
-      </c>
-      <c r="G13" s="77">
-        <v>121230.88</v>
-      </c>
-      <c r="H13" s="77">
-        <v>463.98</v>
-      </c>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.6" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="74" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="75">
-        <v>45896</v>
-      </c>
-      <c r="C14" s="76">
-        <v>6000</v>
-      </c>
-      <c r="D14" s="77">
-        <v>7.3</v>
-      </c>
-      <c r="E14" s="77">
-        <v>43897.02</v>
-      </c>
-      <c r="F14" s="77">
-        <v>8.4</v>
-      </c>
-      <c r="G14" s="77">
-        <v>50288.37</v>
-      </c>
-      <c r="H14" s="77">
-        <v>6391.35</v>
-      </c>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="74" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="75">
-        <v>45897</v>
-      </c>
-      <c r="C15" s="76">
-        <v>5000</v>
-      </c>
-      <c r="D15" s="77">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="E15" s="77">
-        <v>11024.36</v>
-      </c>
-      <c r="F15" s="77">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="G15" s="77">
-        <v>11474.52</v>
-      </c>
-      <c r="H15" s="77">
-        <v>450.16</v>
-      </c>
-      <c r="I15" s="78"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32">
-        <f>SUM(E4:E15)</f>
-        <v>605087.27</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32">
-        <f>SUM(G4:G15)</f>
-        <v>634351.87</v>
-      </c>
-      <c r="H16" s="32">
-        <f>SUM(H4:H15)</f>
-        <v>29264.600000000002</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="41">
-        <f>H3+H16</f>
-        <v>30614.600000000002</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="7">
-        <v>-365900.39999999997</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="29"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="32">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="7">
-        <v>-187350.93</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-    </row>
-    <row r="19" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="33"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="41">
-        <f>H17+H18</f>
-        <v>-522636.73</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-    </row>
-    <row r="20" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="33"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="7">
-        <v>386420</v>
-      </c>
-      <c r="I20" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="7">
-        <v>377810</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-    </row>
-    <row r="21" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="29"/>
-      <c r="D21" s="33"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="H21" s="35">
-        <v>10130</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J21" s="7">
-        <v>8610</v>
-      </c>
-      <c r="K21" s="7"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="15"/>
-    </row>
-    <row r="22" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A22" s="26"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="29"/>
-      <c r="D22" s="33"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="30"/>
-      <c r="G22" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="41">
-        <f>H20+H21</f>
-        <v>396550</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K22" s="7"/>
-      <c r="L22" s="15"/>
-      <c r="M22" s="15"/>
-      <c r="N22" s="6"/>
-    </row>
-    <row r="23" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A23" s="5"/>
-      <c r="B23" s="12"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="9"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="47">
-        <f>H19-H22</f>
-        <v>-919186.73</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="7">
-        <v>-939671.33</v>
-      </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="15"/>
-      <c r="N23" s="6"/>
-    </row>
-    <row r="24" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A24" s="5"/>
-      <c r="B24" s="12"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J24" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K24" s="7"/>
-      <c r="L24" s="15"/>
-      <c r="M24" s="15"/>
-      <c r="N24" s="6"/>
-    </row>
-    <row r="25" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A25" s="6"/>
-      <c r="B25" s="12"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="42">
-        <f>H23+H24</f>
-        <v>-862186.73</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="7">
-        <v>-882671.33</v>
-      </c>
-      <c r="K25" s="7"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="6"/>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K26" s="7"/>
-      <c r="M26" s="7"/>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M27" s="7"/>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M28" s="7"/>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="D29" s="8"/>
-      <c r="E29" s="9"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="10"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="11"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="6"/>
-      <c r="M29" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24B6D7D9-1BF8-42AF-8BE9-2337E6298F4C}">
   <dimension ref="A1:N27"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -4393,7 +6253,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68993354-A7E2-4931-8BC9-D8891EC066BA}">
   <dimension ref="A1:N35"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
@@ -5355,7 +7215,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9DFDC5F2-0211-490B-8DD7-A2B28B5D4706}">
   <dimension ref="A1:L21"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -5804,7 +7664,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CA6E9199-1687-4EE7-A0F3-54DE6332B9D4}">
   <dimension ref="A1:N26"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -6490,7 +8350,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5815483-6499-49C9-BB8D-67572F4517B8}">
   <dimension ref="A1:N18"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -6918,7 +8778,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DA818F-D2F1-4405-A36C-2376E8E1DAA2}">
   <dimension ref="A1:N14"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
@@ -7253,1102 +9113,4 @@
   <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4EDBED0F-338F-4C61-AC0B-5077E6985A08}">
-  <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.25" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="28">
-        <v>45995</v>
-      </c>
-      <c r="C2" s="29">
-        <v>45000</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="37">
-        <v>0.22220000000000001</v>
-      </c>
-      <c r="G2" s="31">
-        <f t="shared" ref="G2:G13" si="0">C2*F2</f>
-        <v>9999</v>
-      </c>
-      <c r="H2" s="40">
-        <f t="shared" ref="H2:H11" si="1">G2*0.9</f>
-        <v>8999.1</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A3" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="28">
-        <v>45995</v>
-      </c>
-      <c r="C3" s="29">
-        <v>27000</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="31"/>
-      <c r="F3" s="37">
-        <v>0.5</v>
-      </c>
-      <c r="G3" s="31">
-        <f t="shared" si="0"/>
-        <v>13500</v>
-      </c>
-      <c r="H3" s="40">
-        <v>12825</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="28">
-        <v>46002</v>
-      </c>
-      <c r="C4" s="29">
-        <v>7200</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="31"/>
-      <c r="F4" s="37">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="G4" s="31">
-        <f t="shared" si="0"/>
-        <v>1260</v>
-      </c>
-      <c r="H4" s="40">
-        <f t="shared" si="1"/>
-        <v>1134</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A5" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="B5" s="28">
-        <v>46002</v>
-      </c>
-      <c r="C5" s="29">
-        <v>55000</v>
-      </c>
-      <c r="D5" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="51">
-        <v>6.9099999999999995E-2</v>
-      </c>
-      <c r="G5" s="31">
-        <f t="shared" si="0"/>
-        <v>3800.4999999999995</v>
-      </c>
-      <c r="H5" s="40">
-        <f t="shared" si="1"/>
-        <v>3420.45</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-      <c r="N5" s="6"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A6" s="85" t="s">
-        <v>36</v>
-      </c>
-      <c r="B6" s="28">
-        <v>46002</v>
-      </c>
-      <c r="C6" s="29">
-        <v>6800</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" s="31"/>
-      <c r="F6" s="37">
-        <v>0.13</v>
-      </c>
-      <c r="G6" s="31">
-        <f t="shared" ref="G6" si="2">C6*F6</f>
-        <v>884</v>
-      </c>
-      <c r="H6" s="40">
-        <f t="shared" ref="H6" si="3">G6*0.9</f>
-        <v>795.6</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A7" s="27" t="s">
-        <v>22</v>
-      </c>
-      <c r="B7" s="28">
-        <v>45995</v>
-      </c>
-      <c r="C7" s="84">
-        <v>17500</v>
-      </c>
-      <c r="D7" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="31"/>
-      <c r="F7" s="51">
-        <v>0.20499999999999999</v>
-      </c>
-      <c r="G7" s="31">
-        <f t="shared" si="0"/>
-        <v>3587.5</v>
-      </c>
-      <c r="H7" s="40">
-        <f t="shared" si="1"/>
-        <v>3228.75</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-      <c r="N7" s="6"/>
-    </row>
-    <row r="8" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A8" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B8" s="28">
-        <v>46006</v>
-      </c>
-      <c r="C8" s="29">
-        <v>50000</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E8" s="31"/>
-      <c r="F8" s="37">
-        <v>2.1000000000000001E-2</v>
-      </c>
-      <c r="G8" s="31">
-        <f t="shared" si="0"/>
-        <v>1050</v>
-      </c>
-      <c r="H8" s="40">
-        <f t="shared" si="1"/>
-        <v>945</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-      <c r="N8" s="6"/>
-    </row>
-    <row r="9" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A9" s="27" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="28">
-        <v>46002</v>
-      </c>
-      <c r="C9" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D9" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E9" s="31"/>
-      <c r="F9" s="37">
-        <v>0.193</v>
-      </c>
-      <c r="G9" s="31">
-        <f t="shared" si="0"/>
-        <v>3860</v>
-      </c>
-      <c r="H9" s="40">
-        <f t="shared" si="1"/>
-        <v>3474</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-      <c r="N9" s="6"/>
-    </row>
-    <row r="10" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A10" s="27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="28">
-        <v>46013</v>
-      </c>
-      <c r="C10" s="29">
-        <v>50000</v>
-      </c>
-      <c r="D10" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="51">
-        <v>0.13250000000000001</v>
-      </c>
-      <c r="G10" s="31">
-        <f t="shared" si="0"/>
-        <v>6625</v>
-      </c>
-      <c r="H10" s="40">
-        <f t="shared" si="1"/>
-        <v>5962.5</v>
-      </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-      <c r="N10" s="6"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A11" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="28">
-        <v>46015</v>
-      </c>
-      <c r="C11" s="84">
-        <v>69000</v>
-      </c>
-      <c r="D11" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="51">
-        <v>0.1825</v>
-      </c>
-      <c r="G11" s="31">
-        <f t="shared" si="0"/>
-        <v>12592.5</v>
-      </c>
-      <c r="H11" s="40">
-        <f t="shared" si="1"/>
-        <v>11333.25</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A12" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B12" s="28">
-        <v>46016</v>
-      </c>
-      <c r="C12" s="29">
-        <v>20000</v>
-      </c>
-      <c r="D12" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="51">
-        <v>0.114</v>
-      </c>
-      <c r="G12" s="31">
-        <f t="shared" ref="G12" si="4">C12*F12</f>
-        <v>2280</v>
-      </c>
-      <c r="H12" s="40">
-        <f>G12</f>
-        <v>2280</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A13" s="85" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="28">
-        <v>46013</v>
-      </c>
-      <c r="C13" s="29">
-        <v>120000</v>
-      </c>
-      <c r="D13" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="31"/>
-      <c r="F13" s="37">
-        <v>0.13722400000000001</v>
-      </c>
-      <c r="G13" s="31">
-        <f t="shared" si="0"/>
-        <v>16466.88</v>
-      </c>
-      <c r="H13" s="40">
-        <f>G13*0.9</f>
-        <v>14820.192000000001</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="27"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="29"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="31"/>
-      <c r="H14" s="34">
-        <f>SUM(H2:H13)</f>
-        <v>69217.84199999999</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A15" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="B15" s="28">
-        <v>37617</v>
-      </c>
-      <c r="C15" s="29">
-        <v>0</v>
-      </c>
-      <c r="D15" s="30">
-        <v>21.3</v>
-      </c>
-      <c r="E15" s="31">
-        <v>0</v>
-      </c>
-      <c r="F15" s="30">
-        <v>21.3</v>
-      </c>
-      <c r="G15" s="31">
-        <v>0</v>
-      </c>
-      <c r="H15" s="32">
-        <f t="shared" ref="H15" si="5">G15-E15</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="11"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="6"/>
-    </row>
-    <row r="16" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="32">
-        <f>SUM(E15:E15)</f>
-        <v>0</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="32">
-        <f>SUM(G15:G15)</f>
-        <v>0</v>
-      </c>
-      <c r="H16" s="40">
-        <f>SUM(H15:H15)</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="7"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-    </row>
-    <row r="17" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A17" s="26"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H17" s="43">
-        <f>H14+H16</f>
-        <v>69217.84199999999</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J17" s="7">
-        <v>30614.600000000002</v>
-      </c>
-      <c r="K17" s="7"/>
-      <c r="L17" s="15"/>
-      <c r="M17" s="15"/>
-      <c r="N17" s="6"/>
-    </row>
-    <row r="18" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A18" s="5"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="32">
-        <v>-522636.73</v>
-      </c>
-      <c r="I18" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K18" s="7"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="6"/>
-    </row>
-    <row r="19" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A19" s="6"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H19" s="41">
-        <f>H17+H18</f>
-        <v>-453418.88799999998</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J19" s="7">
-        <v>-522636.73</v>
-      </c>
-      <c r="K19" s="7"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="15"/>
-      <c r="N19" s="6"/>
-    </row>
-    <row r="20" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G20" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H20" s="35">
-        <v>396550</v>
-      </c>
-      <c r="I20" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="J20" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K20" s="7"/>
-      <c r="M20" s="7"/>
-    </row>
-    <row r="21" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G21" s="32" t="s">
-        <v>55</v>
-      </c>
-      <c r="H21" s="35">
-        <v>12050</v>
-      </c>
-      <c r="I21" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="J21" s="7">
-        <v>10130</v>
-      </c>
-      <c r="M21" s="7"/>
-    </row>
-    <row r="22" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G22" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H22" s="41">
-        <f>H20+H21</f>
-        <v>408600</v>
-      </c>
-      <c r="I22" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J22" s="7">
-        <v>396550</v>
-      </c>
-      <c r="M22" s="7"/>
-    </row>
-    <row r="23" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C23" s="12"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H23" s="45">
-        <f>H19-H22</f>
-        <v>-862018.88800000004</v>
-      </c>
-      <c r="I23" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J23" s="7">
-        <v>-919186.73</v>
-      </c>
-      <c r="K23" s="7"/>
-      <c r="L23" s="6"/>
-      <c r="M23" s="7"/>
-    </row>
-    <row r="24" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G24" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I24" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J24" s="7">
-        <v>57000</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="G25" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H25" s="42">
-        <f>H23+H24</f>
-        <v>-805018.88800000004</v>
-      </c>
-      <c r="I25" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J25" s="7">
-        <v>-862186.73</v>
-      </c>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F537F07A-D0A7-416B-8994-ABDD1C22435D}">
-  <dimension ref="A1:N18"/>
-  <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="12.375" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12.625" style="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="8" customWidth="1"/>
-    <col min="4" max="4" width="13" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.75" style="7" customWidth="1"/>
-    <col min="6" max="6" width="13" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.75" style="7" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.375" style="11" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.875" style="7" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="6" customWidth="1"/>
-    <col min="12" max="12" width="12.375" style="7" customWidth="1"/>
-    <col min="13" max="13" width="12.875" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8.75" style="6" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-    </row>
-    <row r="2" spans="1:14" s="1" customFormat="1" ht="21" x14ac:dyDescent="0.6">
-      <c r="A2" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="28">
-        <v>44846</v>
-      </c>
-      <c r="C2" s="29">
-        <v>0</v>
-      </c>
-      <c r="D2" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="31"/>
-      <c r="F2" s="37">
-        <v>1.3</v>
-      </c>
-      <c r="G2" s="31">
-        <f>C2*F2</f>
-        <v>0</v>
-      </c>
-      <c r="H2" s="32">
-        <f>G2*0.9</f>
-        <v>0</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
-      <c r="N2" s="6"/>
-    </row>
-    <row r="3" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A3" s="27"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="30"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="31"/>
-      <c r="H3" s="34">
-        <f>SUM(H2:H2)</f>
-        <v>0</v>
-      </c>
-      <c r="I3" s="11"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="15"/>
-      <c r="M3" s="15"/>
-      <c r="N3" s="6"/>
-    </row>
-    <row r="4" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A4" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="28">
-        <v>45590</v>
-      </c>
-      <c r="C4" s="29">
-        <v>1500</v>
-      </c>
-      <c r="D4" s="30">
-        <v>12</v>
-      </c>
-      <c r="E4" s="31">
-        <v>19756.14</v>
-      </c>
-      <c r="F4" s="30">
-        <v>0</v>
-      </c>
-      <c r="G4" s="31">
-        <v>19756.14</v>
-      </c>
-      <c r="H4" s="40">
-        <f>G4-E4</f>
-        <v>0</v>
-      </c>
-      <c r="I4" s="11"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="15"/>
-      <c r="M4" s="15"/>
-      <c r="N4" s="6"/>
-    </row>
-    <row r="5" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="26"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="32">
-        <f>SUM(E4:E4)</f>
-        <v>19756.14</v>
-      </c>
-      <c r="F5" s="30"/>
-      <c r="G5" s="32">
-        <f>SUM(G4:G4)</f>
-        <v>19756.14</v>
-      </c>
-      <c r="H5" s="32">
-        <f>SUM(H4:H4)</f>
-        <v>0</v>
-      </c>
-      <c r="K5" s="7"/>
-      <c r="L5" s="15"/>
-      <c r="M5" s="15"/>
-    </row>
-    <row r="6" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A6" s="26"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="32"/>
-      <c r="F6" s="30"/>
-      <c r="G6" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="H6" s="43">
-        <f>H3+H5</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="J6" s="7">
-        <v>30614.600000000002</v>
-      </c>
-      <c r="K6" s="7"/>
-      <c r="L6" s="15"/>
-      <c r="M6" s="15"/>
-      <c r="N6" s="6"/>
-    </row>
-    <row r="7" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="26"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="32"/>
-      <c r="F7" s="30"/>
-      <c r="G7" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="H7" s="32">
-        <v>-522636.73</v>
-      </c>
-      <c r="I7" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="7">
-        <v>-553251.32999999996</v>
-      </c>
-      <c r="K7" s="7"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="15"/>
-    </row>
-    <row r="8" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="26"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="30"/>
-      <c r="G8" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="41">
-        <f>H6+H7</f>
-        <v>-522636.73</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="J8" s="7">
-        <v>-522636.73</v>
-      </c>
-      <c r="K8" s="7"/>
-      <c r="L8" s="15"/>
-      <c r="M8" s="15"/>
-    </row>
-    <row r="9" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="33"/>
-      <c r="E9" s="32"/>
-      <c r="F9" s="30"/>
-      <c r="G9" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="H9" s="35">
-        <v>396550</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="J9" s="7">
-        <v>386420</v>
-      </c>
-      <c r="K9" s="7"/>
-      <c r="L9" s="15"/>
-      <c r="M9" s="15"/>
-    </row>
-    <row r="10" spans="1:14" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="26"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="30"/>
-      <c r="G10" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="H10" s="35">
-        <v>24420</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="J10" s="7">
-        <v>10130</v>
-      </c>
-      <c r="K10" s="7"/>
-      <c r="L10" s="15"/>
-      <c r="M10" s="15"/>
-    </row>
-    <row r="11" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A11" s="26"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="41">
-        <f>H9+H10</f>
-        <v>420970</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="7">
-        <v>396550</v>
-      </c>
-      <c r="K11" s="7"/>
-      <c r="L11" s="15"/>
-      <c r="M11" s="15"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="12" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A12" s="5"/>
-      <c r="B12" s="12"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="9"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="45">
-        <f>H8-H11</f>
-        <v>-943606.73</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="J12" s="7">
-        <v>-919186.73</v>
-      </c>
-      <c r="K12" s="7"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="6"/>
-    </row>
-    <row r="13" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A13" s="5"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="38" t="s">
-        <v>30</v>
-      </c>
-      <c r="H13" s="7">
-        <v>57000</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J13" s="7">
-        <v>57000</v>
-      </c>
-      <c r="K13" s="7"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="15"/>
-      <c r="N13" s="6"/>
-    </row>
-    <row r="14" spans="1:14" s="1" customFormat="1" ht="21.75" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="A14" s="6"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="8"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="38" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="42">
-        <f>H12+H13</f>
-        <v>-886606.73</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="J14" s="7">
-        <v>-862186.73</v>
-      </c>
-      <c r="K14" s="7"/>
-      <c r="L14" s="15"/>
-      <c r="M14" s="15"/>
-      <c r="N14" s="6"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="K15" s="7"/>
-      <c r="M15" s="7"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="M16" s="7"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="M17" s="7"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.3">
-      <c r="C18" s="12"/>
-      <c r="D18" s="8"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="10"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="6"/>
-      <c r="M18" s="7"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555551" footer="0.51180555555555551"/>
-  <pageSetup paperSize="9" firstPageNumber="0" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter alignWithMargins="0"/>
-</worksheet>
 </file>